--- a/modeleKV/Simulations.xlsx
+++ b/modeleKV/Simulations.xlsx
@@ -536,11 +536,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[0.0, 5.942398898115364e-07, 1.1884797796230727e-06, 7.130878677738436e-06, 1.30732775758538e-05, 3.086116629746793e-05, 4.8649055019082065e-05, 6.64369437406962e-05, 0.0001104084314030158, 0.0001543799190653354, 0.000198351406727655, 0.00041359161972225517, 0.0006288318327168554, 0.0008440720457114556, 0.0016945630968747479, 0.00254505414803804, 0.003395545199201332, 0.004429735890258312, 0.005463926581315292, 0.006498117272372272, 0.0075323079634292515, 0.009551494891329488, 0.011570681819229725, 0.013589868747129962, 0.015609055675030199, 0.017628242602930437, 0.023132208131512455, 0.028636173660094473, 0.03414013918867649, 0.03964410471725851, 0.04514807024584053, 0.05318726614513808, 0.06122646204443563, 0.06926565794373318, 0.07730485384303074, 0.08534404974232829, 0.09338324564162584, 0.10136814410897318, 0.10935304257632053, 0.11733794104366788, 0.12374425315853846, 0.13015056527340904, 0.13655687738827962, 0.1429631895031502, 0.1493695016180208, 0.15598472064441063, 0.16259993967080047, 0.1692151586971903, 0.17583037772358015, 0.18244559674997, 0.18906081577635983, 0.1950778992872281, 0.20109498279809637, 0.20711206630896464, 0.2131291498198329, 0.21914623333070118, 0.225204470531308, 0.2312627077319148, 0.2373209449325216, 0.2433791821331284, 0.2494374193337352, 0.25549565653434203, 0.26134679034775843, 0.2671979241611748, 0.2730490579745912, 0.2789001917880076, 0.284751325601424, 0.2906024594148404, 0.29640380926051835, 0.3022051591061963, 0.3080065089518742, 0.31380785879755213, 0.31960920864323006, 0.325410558488908, 0.3343234593124836, 0.3432363601360592, 0.3521492609596348, 0.3610621617832104, 0.369975062606786, 0.3797599486122817, 0.3895448346177774, 0.3993297206232731, 0.4091146066287688, 0.4188994926342645, 0.4286843786397602, 0.44053022533717645, 0.4523760720345927, 0.4642219187320089, 0.47606776542942514, 0.48791361212684137, 0.4997594588242576, 0.5161377980398125, 0.5325161372553675, 0.5488944764709225, 0.5652728156864775, 0.5816511549020325, 0.605525089946702, 0.6293990249913715, 0.653272960036041, 0.6771468950807105, 0.70102083012538, 0.7356128001360817, 0.7702047701467833, 0.804796740157485, 0.8393887101681867, 0.8739806801788884, 0.9109644386055772, 0.947948197032266, 0.9849319554589547, 1.0219157138856434, 1.0588994723123322, 1.119373938218426, 1.1798484041245199, 1.2403228700306137, 1.3007973359367075, 1.3612718018428014, 1.4217462677488952, 1.4885083577761762, 1.5552704478034571, 1.622032537830738, 1.688794627858019, 1.7555567178853, 1.8565894205444984, 1.9576221232036968, 2.058654825862895, 2.1596875285220936, 2.260720231181292, 2.3617529338404903, 2.4904804680800705, 2.6192080023196507, 2.747935536559231, 2.876663070798811, 3.005390605038391, 3.1341181392779713, 3.28178437946316, 3.4294506196483487, 3.5771168598335374, 3.724783100018726, 3.872449340203915, 4.0201155803891035, 4.255248153640831, 4.490380726892558, 4.725513300144285, 4.960645873396012, 5.195778446647739, 5.430911019899466, 5.714016645812256, 5.997122271725046, 6.280227897637836, 6.563333523550626, 6.846439149463416, 7.129544775376206, 7.516444016041985, 7.903343256707765, 8.290242497373544, 8.677141738039325, 9.064040978705105, 9.450940219370885, 9.986702326513964, 10.0]</t>
+          <t>[0.0, 1.3287611344771806e-05, 2.6575222689543613e-05, 0.00015945133613726165, 0.0002923274495849797, 0.0008315390887316277, 0.0013707507278782757, 0.0019099623670249238, 0.003935557773157721, 0.0059611531792905185, 0.007986748585423316, 0.013972141396218028, 0.01995753420701274, 0.02594292701780745, 0.03192831982860216, 0.041706055349261605, 0.051483790869921046, 0.06126152639058049, 0.07103926191123994, 0.08081699743189938, 0.09157929894378179, 0.1023416004556642, 0.11310390196754662, 0.12386620347942903, 0.1316110277741525, 0.139355852068876, 0.14710067636359947, 0.14712487893952048, 0.14714908151544148, 0.1471732840913625, 0.1471974866672835, 0.1472216892432045, 0.1472458918191255, 0.14748791757833557, 0.14772994333754563, 0.1479719690967557, 0.14821399485596576, 0.14845602061517582, 0.15031476722780426, 0.15068651655032994, 0.15105826587285562, 0.1514300151953813, 0.15150436505988643, 0.15157871492439157, 0.1516530647888967, 0.15172741465340184, 0.1517571545992039, 0.15178689454500593, 0.15179284253416633, 0.1517940321319984, 0.15179522172983048, 0.1517954596493969, 0.1517956975689633, 0.1517959354885297, 0.15179603065635627, 0.15179612582418284, 0.1517962209920094, 0.15179625905914002, 0.15179629712627063, 0.15179630010574588, 0.1517963010646622, 0.15179630177336056, 0.15179630248205894, 0.15179630319075732, 0.1517963042839193, 0.15179630537708128, 0.15179631630870105, 0.15179632724032083, 0.1517964365565186, 0.15179654587271635, 0.15179763903469395, 0.15179873219667156, 0.15180556363655337, 0.15181239507643518, 0.151819226516317, 0.15186124884078522, 0.15190327116525346, 0.1519452934897217, 0.15236551673440402, 0.15278573997908634, 0.15320596322376867, 0.15434786121510066, 0.15548975920643265, 0.15663165719776465, 0.15777355518909664, 0.1610142128769683, 0.16425487056483995, 0.1674955282527116, 0.17073618594058326, 0.17397684362845492, 0.17953995503587045, 0.18510306644328597, 0.1906661778507015, 0.19622928925811703, 0.20179240066553256, 0.20713997871244352, 0.2124875567593545, 0.21783513480626546, 0.22318271285317642, 0.2285302909000874, 0.23387786894699836, 0.2391880319802178, 0.24449819501343723, 0.24980835804665666, 0.2551185210798761, 0.2604286841130955, 0.26640820737150833, 0.27238773062992117, 0.278367253888334, 0.28434677714674683, 0.29032630040515967, 0.2963058236635725, 0.3023902397422966, 0.30847465582102074, 0.31455907189974486, 0.320643487978469, 0.3267279040571931, 0.3328123201359172, 0.3406188802591303, 0.34842544038234335, 0.3562320005055564, 0.3640385606287695, 0.37184512075198256, 0.3795986614814883, 0.38735220221099403, 0.39510574294049977, 0.4028592836700055, 0.41061282439951124, 0.418366365129017, 0.42933205750549114, 0.4402977498819653, 0.45126344225843945, 0.4622291346349136, 0.47319482701138776, 0.4841605193878619, 0.499870084015929, 0.5155796486439961, 0.5312892132720632, 0.5469987779001304, 0.5627083425281976, 0.5784179071562647, 0.6019432034195282, 0.6254684996827917, 0.6489937959460552, 0.6725190922093187, 0.6960443884725822, 0.7242331518766266, 0.752421915280671, 0.7806106786847155, 0.8087994420887599, 0.8369882054928043, 0.8802558486239246, 0.9235234917550449, 0.9667911348861652, 1.0100587780172856, 1.0533264211484061, 1.1082989515604464, 1.1632714819724868, 1.218244012384527, 1.2732165427965674, 1.3281890732086077, 1.383161603620648, 1.442742613097028, 1.502323622573408, 1.561904632049788, 1.621485641526168, 1.681066651002548, 1.769498663430441, 1.857930675858334, 1.946362688286227, 2.0347947007141203, 2.1232267131420137, 2.211658725569907, 2.3335255338051293, 2.4553923420403514, 2.5772591502755735, 2.6991259585107956, 2.8209927667460177, 2.94285957498124, 3.0944613896042124, 3.246063204227185, 3.3976650188501574, 3.54926683347313, 3.7008686480961024, 3.852470462719075, 4.079691225339637, 4.306911987960199, 4.534132750580762, 4.761353513201324, 4.988574275821886, 5.215795038442448, 5.5126438885620015, 5.809492738681555, 6.106341588801108, 6.403190438920661, 6.700039289040214, 6.9968881391597675, 7.1719473241387, 7.347006509117633, 7.35770752378833, 7.360481532039981, 7.363255540291632, 7.364764292099966, 7.366273043908299, 7.367781795716632, 7.369290547524965, 7.3707992993332985, 7.372308051141632, 7.374304029638014, 7.376300008134397, 7.378295986630779, 7.380291965127162, 7.3822879436235445, 7.384283922119927, 7.388092014673398, 7.391900107226869, 7.39570819978034, 7.399516292333811, 7.403324384887282, 7.413807637814332, 7.424290890741383, 7.434774143668434, 7.445257396595484, 7.489637834302403, 7.534018272009322, 7.578398709716241, 7.757276322946964, 7.846715129562326, 7.936153936177687, 8.025592742793048, 8.3056167714281, 8.585640800063153, 8.865664828698206, 9.145688857333258, 9.6349062779419, 10.0]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.6284314395283689</v>
+        <v>0.6284318939460821</v>
       </c>
       <c r="D2" t="n">
         <v>9.81</v>
@@ -567,13 +567,13 @@
         <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>6.284314395283689</v>
+        <v>6.284318939460821</v>
       </c>
       <c r="M2" t="n">
-        <v>0.005064238931586606</v>
+        <v>0.005064231607709304</v>
       </c>
       <c r="N2" t="n">
-        <v>0.02532119465793303</v>
+        <v>0.02532115803854652</v>
       </c>
       <c r="O2" t="n">
         <v>19.6199</v>
@@ -603,11 +603,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[0.0, 5.942402908483678e-07, 1.1884805816967355e-06, 7.130883490180414e-06, 1.307328639866409e-05, 3.086118715137464e-05, 4.864908790408519e-05, 6.643698865679574e-05, 0.00011040850702206408, 0.00015438002538733242, 0.00019835154375260077, 0.0004135924747165978, 0.0006288334056805949, 0.000844074336644592, 0.0016944487960028499, 0.002544823255361108, 0.003395197714719366, 0.004429356880527615, 0.005463516046335864, 0.006497675212144113, 0.0075318343779523615, 0.009551119768839161, 0.01157040515972596, 0.01358969055061276, 0.01560897594149956, 0.01762826133238636, 0.023132200576280102, 0.028636139820173843, 0.03414007906406759, 0.03964401830796133, 0.04514795755185508, 0.053187421718595, 0.061226885885334925, 0.06926635005207485, 0.07730581421881477, 0.0853452783855547, 0.09338474255229462, 0.10136899319471987, 0.10935324383714512, 0.11733749447957037, 0.12374366816704216, 0.13014984185451395, 0.13655601554198574, 0.14296218922945753, 0.14936836291692931, 0.15598267293222168, 0.16259698294751404, 0.1692112929628064, 0.17582560297809877, 0.18243991299339113, 0.1890542230086835, 0.19507326769589334, 0.20109231238310318, 0.20711135707031303, 0.21313040175752287, 0.21914944644473272, 0.22521091012391095, 0.23127237380308918, 0.2373338374822674, 0.24339530116144564, 0.24945676484062387, 0.2555182285198021, 0.2613706438835017, 0.26722305924720124, 0.2730754746109008, 0.2789278899746004, 0.28478030533829995, 0.2906327207019995, 0.29643381515585115, 0.3022349096097028, 0.3080360040635544, 0.31383709851740604, 0.3196381929712577, 0.3254392874251093, 0.33433789027380706, 0.3432364931225048, 0.35213509597120257, 0.36103369881990033, 0.3699323016685981, 0.3797149580339743, 0.38949761439935054, 0.3992802707647268, 0.409062927130103, 0.41884558349547923, 0.42862823986085546, 0.4404682674011607, 0.4523082949414659, 0.4641483224817711, 0.47598835002207635, 0.48782837756238157, 0.4996684051026868, 0.5160414344943797, 0.5324144638860726, 0.5487874932777655, 0.5651605226694585, 0.5815335520611514, 0.6054019913841876, 0.6292704307072238, 0.6531388700302599, 0.6770073093532961, 0.7008757486763323, 0.7354598857274778, 0.7700440227786233, 0.8046281598297688, 0.8392122968809143, 0.8737964339320597, 0.9107715871737254, 0.9477467404153911, 0.9847218936570568, 1.0216970468987223, 1.0586722001403879, 1.1191373601074568, 1.1796025200745257, 1.2400676800415946, 1.3005328400086635, 1.3609979999757325, 1.4214631599428014, 1.4882101247467525, 1.5549570895507037, 1.6217040543546548, 1.688451019158606, 1.755197983962557, 1.8562070918419498, 1.9572161997213424, 2.0582253076007353, 2.159234415480128, 2.260243523359521, 2.361252631238914, 2.4899513072576966, 2.6186499832764794, 2.747348659295262, 2.8760473353140448, 3.0047460113328275, 3.13344468735161, 3.2810779766043034, 3.4287112658569967, 3.57634455510969, 3.723977844362383, 3.8716111336150765, 4.01924442286777, 4.2543242325061135, 4.489404042144457, 4.724483851782801, 4.959563661421145, 5.194643471059488, 5.429723280697832, 5.71276419718481, 5.995805113671787, 6.278846030158765, 6.561886946645743, 6.84492786313272, 7.127968779619698, 7.5147790390802625, 7.901589298540827, 8.288399558001391, 8.675209817461955, 9.062020076922519, 9.448830336383082, 9.984465874599545, 10.0]</t>
+          <t>[0.0, 1.3287620313463664e-05, 2.6575240626927328e-05, 0.00015945144376156397, 0.0002923276468962006, 0.0008315082921949771, 0.0013706889374937535, 0.00190986958279253, 0.003935275446857644, 0.005960681310922758, 0.00798608717498787, 0.01397116217496477, 0.01995623717494167, 0.02594131217491857, 0.031926387174895474, 0.041703722144691494, 0.05148105711448751, 0.06125839208428353, 0.07103572705407955, 0.08081306202387557, 0.09157524831624049, 0.10233743460860541, 0.11309962090097032, 0.12386180719333524, 0.13160626061094383, 0.13935071402855242, 0.14709516744616102, 0.14711936886309104, 0.14714357028002106, 0.14716777169695108, 0.1471919731138811, 0.14721617453081112, 0.14724037594774114, 0.14748239011704134, 0.14772440428634154, 0.14796641845564174, 0.14820843262494193, 0.14845044679424213, 0.15028290588197138, 0.15064939769951724, 0.1510158895170631, 0.15138238133460896, 0.15174887315215482, 0.1517720568275502, 0.1517766935626293, 0.15178133029770838, 0.15178596703278746, 0.15179060376786654, 0.15179097470667288, 0.15179134564547922, 0.1517914198332405, 0.15179149402100175, 0.15179156820876302, 0.15179159788386754, 0.15179162755897205, 0.15179163455434502, 0.15179163722093408, 0.15179163988752314, 0.15179164057335007, 0.151791641259177, 0.1517916419450039, 0.15179164302043607, 0.15179164409586823, 0.15179165485018983, 0.15179166560451143, 0.15179177314772743, 0.15179188069094343, 0.15179295612310342, 0.15179403155526341, 0.1518008153603875, 0.1518075991655116, 0.15181438297063568, 0.15185632691517362, 0.15189827085971155, 0.1519402148042495, 0.15235965424962886, 0.15277909369500822, 0.1531985331403876, 0.15433939827789853, 0.15548026341540946, 0.1566211285529204, 0.15776199369043134, 0.16100174952172838, 0.16424150535302542, 0.16748126118432247, 0.1707210170156195, 0.17396077284691655, 0.1795241285603125, 0.18508748427370844, 0.1906508399871044, 0.19621419570050033, 0.20177755141389628, 0.20712470560066273, 0.2124718597874292, 0.21781901397419565, 0.2231661681609621, 0.22851332234772856, 0.23386047653449502, 0.23916942996009635, 0.2444783833856977, 0.24978733681129903, 0.2550962902369004, 0.26040524366250173, 0.2663828039061935, 0.2723603641498853, 0.2783379243935771, 0.28431548463726886, 0.29029304488096064, 0.2962706051246524, 0.30235485644467774, 0.30843910776470307, 0.3145233590847284, 0.3206076104047537, 0.32669186172477904, 0.33277611304480437, 0.34058585802795066, 0.34839560301109695, 0.35620534799424325, 0.36401509297738954, 0.37182483796053584, 0.3795791443264533, 0.38733345069237074, 0.3950877570582882, 0.40284206342420564, 0.4105963697901231, 0.41835067615604055, 0.4293178568602777, 0.4402850375645148, 0.45125221826875195, 0.4622193989729891, 0.4731865796772262, 0.48415376038146335, 0.49986299832836784, 0.5155722362752724, 0.531281474222177, 0.5469907121690816, 0.5626999501159862, 0.5784091880628908, 0.601935019327019, 0.6254608505911472, 0.6489866818552754, 0.6725125131194036, 0.6960383443835318, 0.7242274152960159, 0.7524164862084999, 0.7806055571209839, 0.8087946280334679, 0.8369836989459519, 0.8802515072121533, 0.9235193154783546, 0.966787123744556, 1.0100549320107572, 1.0533227402769585, 1.108295845885058, 1.1632689514931576, 1.218242057101257, 1.2732151627093566, 1.3281882683174562, 1.3831613739255557, 1.4427424486086524, 1.5023235232917491, 1.5619045979748458, 1.6214856726579425, 1.6810667473410392, 1.7694992722529994, 1.8579317971649596, 1.9463643220769198, 2.03479684698888, 2.12322937190084, 2.2116618968128003, 2.333529109855683, 2.455396322898566, 2.577263535941449, 2.6991307489843317, 2.8209979620272145, 2.9428651750700974, 3.09446748134705, 3.246069787624003, 3.3976720939009555, 3.549274400177908, 3.700876706454861, 3.8524790127318136, 4.079700464120542, 4.30692191550927, 4.5341433668979985, 4.761364818286727, 4.988586269675455, 5.215807721064183, 5.512657770633274, 5.809507820202364, 6.106357869771454, 6.403207919340544, 6.5116977671744385, 6.565942691091386, 6.5922497730197085, 6.60540331398387, 6.611980084465951, 6.615306895050908, 6.617379484633389, 6.618837852881893, 6.620296221130397, 6.621754589378901, 6.6232129576274055, 6.62467132587591, 6.626129694124414, 6.628245511978564, 6.630361329832715, 6.632477147686865, 6.634592965541016, 6.636708783395166, 6.638824601249317, 6.641994536891196, 6.645164472533075, 6.6483344081749545, 6.651504343816834, 6.654674279458713, 6.6630112893448326, 6.671348299230952, 6.679685309117072, 6.688022319003191, 6.733917109923331, 6.7798119008434705, 6.82570669176361, 6.993658917997976, 7.077635031115159, 7.161611144232342, 7.245587257349525, 7.500249907003384, 7.754912556657242, 8.009575206311101, 8.26423785596496, 8.702744418714275, 9.141250981463589, 9.579757544212903, 10.0]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.6284033769873318</v>
+        <v>0.6284040749983208</v>
       </c>
       <c r="D3" t="n">
         <v>9.81</v>
@@ -634,13 +634,13 @@
         <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>6.284033769873318</v>
+        <v>6.284040749983208</v>
       </c>
       <c r="M3" t="n">
-        <v>0.005064691248016657</v>
+        <v>0.005064679996631363</v>
       </c>
       <c r="N3" t="n">
-        <v>0.02532345624008328</v>
+        <v>0.02532339998315682</v>
       </c>
       <c r="O3" t="n">
         <v>19.61987351447831</v>
@@ -670,11 +670,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[0.0, 5.942407981030446e-07, 1.1884815962060891e-06, 7.130889577236535e-06, 1.3073297558266982e-05, 3.0861213528606995e-05, 4.864912949894701e-05, 6.643704546928703e-05, 0.00011040860266942747, 0.0001543801598695679, 0.00019835171706970834, 0.00041359355617251914, 0.0006288353952753299, 0.0008440772343781407, 0.0016943043142248365, 0.0025445313940715324, 0.0033947584739182283, 0.004428877796895411, 0.0054629971198725934, 0.006497116442849776, 0.007531235765826958, 0.009550645734219518, 0.011570055702612079, 0.01358946567100464, 0.0156088756393972, 0.01762828560778976, 0.02313219177205894, 0.028636097936328122, 0.0341400041005973, 0.03964391026486648, 0.04514781642913566, 0.053187614193155805, 0.06122741195717595, 0.0692672097211961, 0.07730700748521624, 0.08534680524923638, 0.09338660301325652, 0.10137003727722849, 0.10935347154120045, 0.11733690580517242, 0.12374270567882788, 0.13014850555248333, 0.13655430542613878, 0.14296010529979422, 0.14936590517344966, 0.15598111765859754, 0.16259633014374542, 0.1692115426288933, 0.17582675511404117, 0.18244196759918904, 0.18905718008433692, 0.19507360549516423, 0.20109003090599153, 0.20710645631681884, 0.21312288172764615, 0.21913930713847346, 0.2251960191932164, 0.23125273124795936, 0.23730944330270232, 0.24336615535744527, 0.24942286741218822, 0.2554795794669312, 0.26133110998717934, 0.2671826405074275, 0.2730341710276757, 0.27888570154792386, 0.28473723206817203, 0.2905887625884202, 0.296389911240585, 0.3021910598927498, 0.3079922085449146, 0.3137933571970794, 0.3195945058492442, 0.325395654501409, 0.3343077475832697, 0.3432198406651304, 0.3521319337469911, 0.3610440268288518, 0.3699561199107125, 0.37974078860663923, 0.389525457302566, 0.39931012599849275, 0.4090947946944195, 0.41887946339034626, 0.428664132086273, 0.4405094969687854, 0.45235486185129775, 0.4642002267338101, 0.4760455916163225, 0.48789095649883485, 0.4997363213813472, 0.5161142372559808, 0.5324921531306144, 0.5488700690052479, 0.5652479848798815, 0.581625900754515, 0.6054989826372299, 0.6293720645199448, 0.6532451464026596, 0.6771182282853745, 0.7009913101680894, 0.7355819360825078, 0.7701725619969262, 0.8047631879113446, 0.839353813825763, 0.8739444397401814, 0.9109267097570395, 0.9479089797738975, 0.9848912497907556, 1.0218735198076137, 1.0588557898244717, 1.1193279055358787, 1.1798000212472857, 1.2402721369586927, 1.3007442526700996, 1.3612163683815066, 1.4216884840929136, 1.4884478799884635, 1.5552072758840134, 1.6219666717795633, 1.6887260676751132, 1.7554854635706632, 1.8565141473316564, 1.9575428310926497, 2.058571514853643, 2.159600198614636, 2.260628882375629, 2.361657566136622, 2.4903799653024934, 2.6191023644683646, 2.747824763634236, 2.876547162800107, 3.0052695619659784, 3.1339919611318496, 3.2816523697541817, 3.429312778376514, 3.576973186998846, 3.724633595621178, 3.87229400424351, 4.019954412865842, 4.255077678568674, 4.490200944271506, 4.725324209974338, 4.96044747567717, 5.195570741380002, 5.430694007082834, 5.713788582927359, 5.996883158771884, 6.279977734616409, 6.563072310460934, 6.846166886305459, 7.129261462149985, 7.51614564212528, 7.903029822100575, 8.289914002075871, 8.676798182051169, 9.063682362026466, 9.450566542001763, 9.986306879437356, 10.0]</t>
+          <t>[0.0, 1.3287631657586359e-05, 2.6575263315172718e-05, 0.0001594515798910363, 0.0002923278964668999, 0.0008314693551241285, 0.0013706108137813572, 0.0019097522724385858, 0.003934918465719691, 0.005960084659000796, 0.0079852508522819, 0.01396992510943784, 0.01995459936659378, 0.025939273623749717, 0.031923947880905655, 0.04170076405464975, 0.05147758022839385, 0.061254396402137944, 0.07103121257588205, 0.08080802874962614, 0.09156999469277913, 0.10233196063593211, 0.1130939265790851, 0.12385589252223808, 0.13160038693155915, 0.13934488134088022, 0.14708937575020128, 0.1471135772952304, 0.1471377788402595, 0.1471619803852886, 0.1471861819303177, 0.14721038347534682, 0.14723458502037592, 0.147476600470667, 0.14771861592095806, 0.14796063137124912, 0.1482026468215402, 0.14844466227183126, 0.1503033868106545, 0.15067513171841915, 0.1510468766261838, 0.15141862153394844, 0.15149297051550137, 0.1515673194970543, 0.15164166847860722, 0.15171601746016014, 0.15174575705278132, 0.1517754966454025, 0.15178144456392673, 0.15178263414763157, 0.15178382373133642, 0.15178501331504127, 0.15178548914852322, 0.1517855843152196, 0.15178567948191599, 0.15178569851525525, 0.15178571754859452, 0.15178573658193378, 0.15178573810460091, 0.15178573962726805, 0.1517857426726023, 0.15178574341280326, 0.15178574377764675, 0.15178574403378164, 0.15178574428991654, 0.1517857445522791, 0.1517857448146417, 0.15178574507700426, 0.15178574669129405, 0.15178574830558383, 0.1517857611378514, 0.15178577397011894, 0.15178590229279448, 0.15178603061547002, 0.15178731384222544, 0.15178859706898085, 0.1517956242725825, 0.15180265147618416, 0.15180967867978581, 0.1518507870800191, 0.15189189548025236, 0.15193300388048564, 0.1523440878828184, 0.15275517188515114, 0.1531662558874839, 0.15429678441147598, 0.15542731293546808, 0.15655784145946017, 0.15768836998345226, 0.16092197356507182, 0.16415557714669138, 0.16738918072831094, 0.1706227843099305, 0.17385638789155006, 0.17942328652568837, 0.18499018515982668, 0.190557083793965, 0.1961239824281033, 0.20169088106224162, 0.20703443562303292, 0.21237799018382422, 0.21772154474461552, 0.22306509930540683, 0.22840865386619813, 0.23375220842698943, 0.23905061658710025, 0.24434902474721107, 0.2496474329073219, 0.2549458410674327, 0.26024424922754347, 0.2662047768739075, 0.2721653045202715, 0.2781258321666355, 0.2840863598129995, 0.2900468874593635, 0.29600741510572753, 0.3020904890063927, 0.30817356290705783, 0.314256636807723, 0.3203397107083881, 0.3264227846090533, 0.3325058585097184, 0.34034504083091144, 0.34818422315210446, 0.35602340547329747, 0.3638625877944905, 0.3717017701156835, 0.37946349706384075, 0.387225224011998, 0.39498695096015524, 0.4027486779083125, 0.4105104048564697, 0.41827213180462697, 0.4292536992632347, 0.44023526672184243, 0.45121683418045017, 0.4621984016390579, 0.47317996909766563, 0.48416153655627336, 0.49986877565926924, 0.5155760147622651, 0.531283253865261, 0.5469904929682569, 0.5626977320712527, 0.5784049711742486, 0.6019377983318318, 0.625470625489415, 0.6490034526469982, 0.6725362798045814, 0.6960691069621646, 0.7242639122661949, 0.7524587175702252, 0.7806535228742555, 0.8088483281782858, 0.8370431334823161, 0.8803173513475385, 0.923591569212761, 0.9668657870779834, 1.0101400049432059, 1.0534142228084282, 1.1083985007462707, 1.163382778684113, 1.2183670566219555, 1.273351334559798, 1.3283356124976404, 1.3833198904354829, 1.4429082314009416, 1.5024965723664003, 1.562084913331859, 1.6216732542973178, 1.6812615952627765, 1.7697088714080196, 1.8581561475532626, 1.9466034236985057, 2.0350506998437488, 2.123497975988992, 2.211945252134235, 2.3338300122729057, 2.4557147724115764, 2.577599532550247, 2.699484292688918, 2.8213690528275888, 2.9432538129662595, 3.09487797234731, 3.2465021317283607, 3.3981262911094112, 3.549750450490462, 3.7013746098715123, 3.852998769252563, 4.080253254476174, 4.307507739699785, 4.534762224923396, 4.762016710147007, 4.989271195370618, 5.216525680594229, 5.513418491804461, 5.661864897409577, 5.810311303014694, 5.870048114775167, 5.92978492653564, 5.944686455166236, 5.946510796260491, 5.9477982605091135, 5.949085724757736, 5.950373189006358, 5.95166065325498, 5.9529481175036025, 5.954235581752225, 5.956112578281541, 5.957051076546199, 5.957989574810856, 5.958928073075514, 5.9598665713401715, 5.960805069604829, 5.961743567869487, 5.963457905889266, 5.965172243909045, 5.966886581928824, 5.968600919948603, 5.970315257968382, 5.980131220339634, 5.989947182710885, 5.999763145082137, 6.009579107453389, 6.032972519096297, 6.056365930739204, 6.079759342382112, 6.187133068173162, 6.294506793964213, 6.401880519755263, 6.509254245546313, 6.739697582553104, 6.970140919559895, 7.200584256566685, 7.431027593573476, 7.732036024370417, 8.033044455167357, 8.334052885964297, 8.635061316761238, 8.936069747558179, 9.469439959541875, 10.0]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6283678912018534</v>
+        <v>0.6283683057448869</v>
       </c>
       <c r="D4" t="n">
         <v>9.81</v>
@@ -701,13 +701,13 @@
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>6.283678912018534</v>
+        <v>6.283683057448869</v>
       </c>
       <c r="M4" t="n">
-        <v>0.005065263300231435</v>
+        <v>0.005065256616988814</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02532631650115717</v>
+        <v>0.02532628308494407</v>
       </c>
       <c r="O4" t="n">
         <v>19.61984001412804</v>
@@ -737,11 +737,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[0.0, 5.942414397086066e-07, 1.1884828794172133e-06, 7.13089727650328e-06, 1.3073311673589347e-05, 3.086124689208264e-05, 4.864918211057593e-05, 6.643711732906922e-05, 0.00011040872364984249, 0.00015438032997061574, 0.000198351936291389, 0.00041359492407584876, 0.0006288379118603085, 0.0008440808996447683, 0.001694121713095992, 0.0025441625265472155, 0.0033942033399984393, 0.004428272319203938, 0.005462341298409437, 0.006496410277614936, 0.007530479256820434, 0.009550046856469808, 0.011569614456119181, 0.013589182055768555, 0.015608749655417928, 0.0176283172550673, 0.023132182208890895, 0.02863604716271449, 0.03413991211653808, 0.039643777070361666, 0.04514764202418525, 0.053187868259874434, 0.061228094495563615, 0.0692683207312528, 0.07730854696694199, 0.08534877320263118, 0.09338899943832037, 0.1013713984239307, 0.10935379740954103, 0.11733619639515136, 0.12374172208136586, 0.13014724776758035, 0.13655277345379485, 0.14295829914000935, 0.14936382482622385, 0.15597812602899122, 0.1625924272317586, 0.16920672843452597, 0.17582102963729335, 0.18243533084006072, 0.1890496320428281, 0.1950678518234736, 0.20108607160411912, 0.20710429138476463, 0.21312251116541014, 0.21914073094605566, 0.22520027455635958, 0.2312598181666635, 0.2373193617769674, 0.24337890538727133, 0.24943844899757525, 0.2554979926078792, 0.2613509175345455, 0.26720384246121176, 0.27305676738787804, 0.2789096923145443, 0.2847626172412106, 0.2906155421678769, 0.2964163827557066, 0.3022172233435363, 0.308018063931366, 0.3138189045191957, 0.3196197451070254, 0.3254205856948551, 0.33431812318411586, 0.3432156606733766, 0.35211319816263736, 0.3610107356518981, 0.36990827314115887, 0.37969064075840747, 0.38947300837565607, 0.39925537599290467, 0.40903774361015327, 0.41882011122740187, 0.42860247884465047, 0.4404418845002776, 0.45228129015590474, 0.46412069581153187, 0.475960101467159, 0.48779950712278614, 0.49963891277841327, 0.5160113871176936, 0.5323838614569738, 0.548756335796254, 0.5651288101355343, 0.5815012844748145, 0.6053686240918275, 0.6292359637088404, 0.6531033033258533, 0.6769706429428662, 0.7008379825598792, 0.7354203943702238, 0.7700028061805684, 0.804585217990913, 0.8391676298012576, 0.8737500416116022, 0.9107232865805254, 0.9476965315494486, 0.9846697765183717, 1.021643021487295, 1.0586162664562182, 1.1190784216065648, 1.1795405767569114, 1.240002731907258, 1.3004648870576045, 1.3609270422079511, 1.4213891973582977, 1.4881327073995854, 1.554876217440873, 1.6216197274821607, 1.6883632375234483, 1.755106747564736, 1.856110698684157, 1.9571146498035779, 2.058118600922999, 2.1591225520424198, 2.2601265031618407, 2.3611304542812617, 2.489822548450549, 2.6185146426198367, 2.747206736789124, 2.8758988309584117, 3.004590925127699, 3.1332830192969867, 3.2809088339495487, 3.4285346486021107, 3.5761604632546726, 3.7237862779072346, 3.8714120925597966, 4.0190379072123585, 4.254105784169638, 4.489173661126917, 4.724241538084196, 4.959309415041475, 5.194377291998754, 5.4294451689560335, 5.712471957962157, 5.99549874696828, 6.278525535974403, 6.561552324980526, 6.844579113986649, 7.127605902992772, 7.514396846368352, 7.901187789743932, 8.287978733119512, 8.674769676495092, 9.061560619870672, 9.448351563246252, 9.983959218548776, 10.0]</t>
+          <t>[0.0, 1.328764600630075e-05, 2.65752920126015e-05, 0.000159451752075609, 0.00029232821213861647, 0.0008314201149104348, 0.0013705120176822532, 0.0019096039204540716, 0.00393446704715361, 0.005959330173853148, 0.007984193300552686, 0.013968359802595958, 0.01995252630463923, 0.0259366928066825, 0.03192085930872577, 0.0416970317255064, 0.05147320414228703, 0.06124937655906766, 0.07102554897584828, 0.08080172139262891, 0.09156348340077691, 0.10232524540892492, 0.11308700741707292, 0.12384876942522093, 0.13159280564049428, 0.1393368418557676, 0.14708087807104095, 0.1471050781842137, 0.14712927829738645, 0.1471534784105592, 0.14717767852373195, 0.1472018786369047, 0.14722607875007745, 0.14746807988180496, 0.14771008101353247, 0.14795208214525998, 0.1481940832769875, 0.148436084408715, 0.15026851649789177, 0.15063500291572712, 0.15100148933356247, 0.15136797575139782, 0.15173446216923317, 0.1517576456750698, 0.15176228237623712, 0.15176691907740444, 0.15177155577857177, 0.15177619247973909, 0.15177804716020601, 0.1517781213474247, 0.15177819553464336, 0.15177826972186204, 0.15177827671796362, 0.1517782837140652, 0.1517782863811312, 0.15177828904819718, 0.1517782899612599, 0.15177829064728166, 0.15177829133330342, 0.1517782920193252, 0.15177829309508672, 0.15177829417084826, 0.15177830492846361, 0.15177831568607897, 0.1517784232622325, 0.15177853083838605, 0.15177960659992146, 0.15178068236145686, 0.15178746762037687, 0.15179425287929688, 0.15180103813821688, 0.15184298786018272, 0.15188493758214855, 0.15192688730411438, 0.15234638452377272, 0.15276588174343106, 0.1531853789630894, 0.15432626342266736, 0.15546714788224533, 0.1566080323418233, 0.15774891680140127, 0.16098832722752965, 0.16422773765365803, 0.1674671480797864, 0.1707065585059148, 0.17394596893204317, 0.17950896037970787, 0.18507195182737257, 0.19063494327503727, 0.19619793472270197, 0.20176092617036667, 0.2071080180140712, 0.21245510985777571, 0.21780220170148024, 0.22314929354518476, 0.22849638538888928, 0.2338434772325938, 0.23915241433810006, 0.2444613514436063, 0.24977028854911257, 0.2550792256546188, 0.2603881627601251, 0.2663657261202946, 0.27234328948046405, 0.2783208528406335, 0.284298416200803, 0.29027597956097245, 0.2962535429211419, 0.30233770107341607, 0.3084218592256902, 0.31450601737796435, 0.3205901755302385, 0.32667433368251264, 0.3327584918347868, 0.3405678576031022, 0.34837722337141763, 0.35618658913973306, 0.3639959549080485, 0.3718053206763639, 0.37955940758032564, 0.38731349448428737, 0.3950675813882491, 0.40282166829221083, 0.41057575519617256, 0.4183298421001343, 0.4292967717189698, 0.4402637013378053, 0.4512306309566408, 0.4621975605754763, 0.4731644901943118, 0.4841314198131473, 0.4998406506408457, 0.5155498814685442, 0.5312591122962427, 0.5469683431239412, 0.5626775739516396, 0.5783868047793381, 0.601912216346977, 0.6254376279146159, 0.6489630394822548, 0.6724884510498936, 0.6960138626175325, 0.7242022447854808, 0.7523906269534291, 0.7805790091213773, 0.8087673912893256, 0.8369557734572739, 0.8802222968825846, 0.9234888203078953, 0.9667553437332059, 1.0100218671585166, 1.0532883905838273, 1.10826020243054, 1.1632320142772525, 1.2182038261239652, 1.2731756379706778, 1.3281474498173904, 1.383119261664103, 1.4426986648218663, 1.5022780679796295, 1.5618574711373927, 1.621436874295156, 1.6810162774529191, 1.7694464630557132, 1.8578766486585072, 1.9463068342613012, 2.034737019864095, 2.123167205466889, 2.2115973910696827, 2.333461292544583, 2.4553251940194833, 2.5771890954943837, 2.699052996969284, 2.8209168984441844, 2.9427807999190847, 3.09437893577208, 3.2459770716250755, 3.397575207478071, 3.5491733433310664, 3.700771479184062, 3.852369615037057, 4.079584565059391, 4.306799515081725, 4.534014465104058, 4.761229415126392, 4.988444365148726, 5.2156593151710595, 5.320527854320377, 5.341846162624207, 5.3451088310402, 5.347020953102194, 5.348072955906311, 5.349124958710427, 5.350176961514544, 5.35122896431866, 5.352280967122777, 5.3533329699268934, 5.354735099615983, 5.356137229305072, 5.357539358994162, 5.358941488683251, 5.36034361837234, 5.36174574806143, 5.3643879071985126, 5.367030066335595, 5.369672225472678, 5.372314384609761, 5.374956543746844, 5.382263731206585, 5.389570918666326, 5.396878106126067, 5.404185293585808, 5.435401585103903, 5.4666178766219975, 5.497834168140092, 5.623816143469272, 5.749798118798451, 5.875780094127631, 6.230117353637026, 6.584454613146422, 6.938791872655817, 7.2931291321652125, 7.638396074661462, 7.983663017157712, 8.328929959653962, 8.674196902150213, 9.019463844646463, 9.577074261328617, 10.0]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6283230206563284</v>
+        <v>0.6283227980630928</v>
       </c>
       <c r="D5" t="n">
         <v>9.81</v>
@@ -768,13 +768,13 @@
         <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>6.283230206563283</v>
+        <v>6.283227980630928</v>
       </c>
       <c r="M5" t="n">
-        <v>0.005065986779192006</v>
+        <v>0.005065990368603664</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02532993389596003</v>
+        <v>0.02532995184301832</v>
       </c>
       <c r="O5" t="n">
         <v>19.61979764103523</v>
@@ -804,11 +804,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[0.0, 5.942422512496885e-07, 1.188484502499377e-06, 7.130907014996262e-06, 1.3073329527493148e-05, 3.086128909220172e-05, 4.864924865691029e-05, 6.643720822161886e-05, 0.00011040887667311251, 0.00015438054512460618, 0.00019835221357609984, 0.0004135966543057189, 0.0006288410950353379, 0.0008440855357649569, 0.0016938909845901707, 0.0025436964334153845, 0.0033935018822405984, 0.004427507265925544, 0.00546151264961049, 0.006495518033295436, 0.007529523416980382, 0.009549290490165075, 0.011569057563349769, 0.013588824636534462, 0.015608591709719155, 0.01762835878290385, 0.023132172254101017, 0.028635985725298185, 0.03413979919649535, 0.03964361266769252, 0.04514742613888969, 0.053188189071997, 0.061228952005104316, 0.06926971493821163, 0.07731047787131895, 0.08535124080442627, 0.09339200373753359, 0.10137309647928391, 0.10935418922103424, 0.11733528196278456, 0.12374026252124617, 0.1301452430797078, 0.1365502236381694, 0.14295520419663102, 0.14936018475509263, 0.1559753874117719, 0.16259059006845114, 0.1692057927251304, 0.17582099538180965, 0.1824361980384889, 0.18905140069516815, 0.19506676829711803, 0.2010821358990679, 0.20709750350101777, 0.21311287110296764, 0.21912823870491752, 0.22518250572042572, 0.23123677273593393, 0.23729103975144214, 0.24334530676695035, 0.24939957378245856, 0.25545384079796674, 0.26130600486382716, 0.2671581689296876, 0.273010332995548, 0.2788624970614084, 0.28471466112726884, 0.29056682519312926, 0.2963676519267012, 0.3021684786602732, 0.30796930539384515, 0.3137701321274171, 0.3195709588609891, 0.32537178559456104, 0.33428260111696084, 0.34319341663936065, 0.35210423216176046, 0.36101504768416026, 0.36992586320656007, 0.3797101883855316, 0.38949451356450315, 0.3992788387434747, 0.40906316392244624, 0.4188474891014178, 0.4286318142803893, 0.4404764140592879, 0.45232101383818646, 0.464165613617085, 0.4760102133959836, 0.48785481317488216, 0.49969941295378073, 0.5160766584118801, 0.5324539038699795, 0.5488311493280789, 0.5652083947861782, 0.5815856402442776, 0.6054573646492596, 0.6293290890542416, 0.6532008134592235, 0.6770725378642055, 0.7009442622691875, 0.7355327478134575, 0.7701212333577274, 0.8047097189019974, 0.8392982044462673, 0.8738866899905373, 0.9108665896304758, 0.9478464892704144, 0.9848263889103529, 1.0218062885502914, 1.05878618819023, 1.119254556308346, 1.179722924426462, 1.240191292544578, 1.300659660662694, 1.3611280287808099, 1.4215963968989258, 1.4883515015314053, 1.5551066061638847, 1.6218617107963642, 1.6886168154288437, 1.7553719200613231, 1.8563942137657414, 1.9574165074701597, 2.058438801174578, 2.1594610948789965, 2.260483388583415, 2.3615056822878335, 2.4902199089802117, 2.61893413567259, 2.747648362364968, 2.8763625890573463, 3.0050768157497245, 3.1337910424421027, 3.281442181986878, 3.4290933215316537, 3.576744461076429, 3.7243956006212047, 3.87204674016598, 4.019697879710756, 4.254806341594869, 4.489914803478983, 4.725023265363096, 4.96013172724721, 5.195240189131323, 5.430348651015437, 5.713425662583056, 5.996502674150675, 6.279579685718295, 6.562656697285914, 6.845733708853533, 7.128810720421153, 7.515670944995857, 7.902531169570561, 8.289391394145266, 8.67625161871997, 9.063111843294674, 9.449972067869378, 9.985677775883676, 10.0]</t>
+          <t>[0.0, 1.3287664155413583e-05, 2.6575328310827166e-05, 0.000159451969864963, 0.00029232861141909885, 0.0008313578646172021, 0.0013703871178153053, 0.0019094163710134085, 0.003933896327434792, 0.005958376283856176, 0.00798285624027756, 0.013966381966563524, 0.01994990769284949, 0.025933433419135454, 0.03191695914542142, 0.04169230532014502, 0.05146765149486862, 0.06124299766959222, 0.07101834384431582, 0.08079369001903942, 0.09155511951364893, 0.10231654900825844, 0.11307797850286795, 0.12383940799747746, 0.13158337484973345, 0.13932734170198946, 0.14707130855424547, 0.14709550845065877, 0.14711970834707208, 0.1471439082434854, 0.1471681081398987, 0.147192308036312, 0.1472165079327253, 0.14745850689685838, 0.14770050586099145, 0.14794250482512453, 0.1481845037892576, 0.14842650275339067, 0.1502851919764922, 0.1506569298211125, 0.1510286676657328, 0.1514004055103531, 0.15147475307927716, 0.1515491006482012, 0.15162344821712526, 0.1516977957860493, 0.15172753481361892, 0.15175727384118853, 0.15176322164670245, 0.15176441120780523, 0.15176560076890802, 0.1517667903300108, 0.15176726615445194, 0.15176774197889306, 0.1517682178033342, 0.15176840813311063, 0.15176859846288707, 0.1517687887926635, 0.15176880401904563, 0.15176881924542776, 0.1517688344718099, 0.15176884056236273, 0.15176884665291557, 0.15176885883402125, 0.1517688612702424, 0.15176886370646353, 0.15176886412518042, 0.15176886434737616, 0.1517688645695719, 0.1517688650755733, 0.1517688655815747, 0.1517688704732558, 0.15176887536493688, 0.15176892428174776, 0.15176897319855864, 0.15176946236666744, 0.15176995153477624, 0.1517748432158642, 0.15177973489695218, 0.15178462657804015, 0.15182413271289993, 0.15186363884775972, 0.1519031449826195, 0.15229820633121735, 0.1526932676798152, 0.15308832902841304, 0.15419676243464175, 0.15530519584087046, 0.15641362924709917, 0.15752206265332788, 0.16073498947484025, 0.1639479162963526, 0.16716084311786497, 0.17037376993937733, 0.1735866967608897, 0.1791612242349952, 0.1847357517091007, 0.1903102791832062, 0.1958848066573117, 0.2014593341314172, 0.206793819149453, 0.2121283041674888, 0.21746278918552459, 0.22279727420356038, 0.22813175922159618, 0.23346624423963197, 0.23876265482881157, 0.24405906541799116, 0.24935547600717076, 0.25465188659635035, 0.2599482971855299, 0.2652447077747095, 0.27359637914715745, 0.2819480505196054, 0.2873505316928931, 0.2927530128661808, 0.29815549403946845, 0.3035579752127561, 0.3089604563860438, 0.3143629375593315, 0.3249281579612542, 0.3354933783631769, 0.3460585987650996, 0.35390467596287895, 0.3617507531606583, 0.36959683035843766, 0.377442907556217, 0.38528898475399637, 0.39547554134643775, 0.40566209793887914, 0.4158486545313205, 0.4260352111237619, 0.4362217677162033, 0.4464083243086447, 0.45992593982856705, 0.4734435553484894, 0.4869611708684118, 0.5004787863883342, 0.5139964019082566, 0.5275140174281789, 0.544359387644288, 0.5612047578603971, 0.5780501280765062, 0.5948954982926153, 0.6117408685087244, 0.6375661086164274, 0.6633913487241303, 0.6892165888318332, 0.7150418289395362, 0.7408670690472391, 0.7778472723077337, 0.8148274755682282, 0.8518076788287228, 0.8887878820892173, 0.9257680853497119, 0.965256179578412, 1.0047442738071122, 1.0442323680358123, 1.0837204622645125, 1.1232085564932126, 1.1869881596347371, 1.2507677627762617, 1.3145473659177862, 1.3783269690593107, 1.4421065722008353, 1.5058861753423598, 1.5770864434606433, 1.6482867115789268, 1.7194869796972103, 1.7906872478154938, 1.8618875159337773, 1.9695890644365055, 2.0772906129392337, 2.184992161441962, 2.29269370994469, 2.400395258447418, 2.5080968069501464, 2.6453939500909796, 2.7826910932318127, 2.919988236372646, 3.057285379513479, 3.1945825226543123, 3.3318796657951455, 3.4892472917544195, 3.6466149177136935, 3.8039825436729675, 3.9613501696322415, 4.1187177955915155, 4.276085421550789, 4.526791969160076, 4.652145242964719, 4.777498516769363, 4.800845028159787, 4.804065053055187, 4.805544611060106, 4.806586953641684, 4.807629296223262, 4.8086716388048405, 4.809713981386419, 4.810756323967997, 4.811798666549575, 4.813313937133597, 4.81482920771762, 4.816344478301642, 4.817859748885664, 4.819375019469686, 4.8208902900537085, 4.82315627021163, 4.825422250369551, 4.827688230527473, 4.829954210685394, 4.832220190843316, 4.838183473444998, 4.84414675604668, 4.850110038648362, 4.856073321250044, 4.888877702262311, 4.921682083274579, 4.9544864642868465, 5.073577486706578, 5.19266850912631, 5.311759531546042, 5.680731324618295, 5.827805412067497, 5.9748794995167, 6.121953586965902, 6.269027674415105, 6.559378296855826, 6.849728919296547, 7.140079541737268, 7.43043016417799, 7.783831971112431, 8.137233778046872, 8.490635584981312, 8.844037391915753, 9.197439198850194, 9.689088069742622, 10.0]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6282662890152124</v>
+        <v>0.6282668793077367</v>
       </c>
       <c r="D6" t="n">
         <v>9.81</v>
@@ -835,13 +835,13 @@
         <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>6.282662890152124</v>
+        <v>6.282668793077367</v>
       </c>
       <c r="M6" t="n">
-        <v>0.005066901724733047</v>
+        <v>0.005066892203451874</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02533450862366523</v>
+        <v>0.02533446101725937</v>
       </c>
       <c r="O6" t="n">
         <v>19.61974404520773</v>
@@ -871,11 +871,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[0.0, 5.942432777363632e-07, 1.1884865554727263e-06, 7.130919332836359e-06, 1.307335211019999e-05, 3.086134246948727e-05, 4.864933282877455e-05, 6.643732318806183e-05, 0.00011040907022628473, 0.0001543808172645076, 0.0001983525643027305, 0.00041359884284429614, 0.0006288451213858618, 0.0008440913999274275, 0.0016935995224422668, 0.002543107644957106, 0.0033926157674719452, 0.004426540843516299, 0.005460465919560653, 0.0064943909956050065, 0.00752831607164936, 0.009548335599899024, 0.011568355128148688, 0.013588374656398353, 0.015608394184648017, 0.01762841371289768, 0.02313216346091664, 0.028635913208935597, 0.03413966295695456, 0.03964341270497352, 0.04514716245299248, 0.05318861152484993, 0.06123006059670738, 0.06927150966856482, 0.07731295874042227, 0.08535440781227971, 0.09339585688413715, 0.10137529507868724, 0.10935473327323733, 0.11733417146778742, 0.12373866076179606, 0.13014315005580468, 0.1365476393498133, 0.1429521286438219, 0.1493566179378305, 0.15597090605952574, 0.16258519418122097, 0.1691994823029162, 0.17581377042461144, 0.18242805854630667, 0.1890423466680019, 0.19505923883072881, 0.20107613099345573, 0.20709302315618264, 0.21310991531890955, 0.21912680748163646, 0.2251832711660634, 0.23123973485049035, 0.2372961985349173, 0.24335266221934423, 0.24940912590377118, 0.2554655895881981, 0.26131932796949536, 0.26717306635079263, 0.2730268047320899, 0.27888054311338717, 0.28473428149468444, 0.2905880198759817, 0.2963884542585285, 0.3021888886410753, 0.3079893230236221, 0.3137897574061689, 0.31959019178871567, 0.32539062617126246, 0.3342864826371019, 0.3431823391029414, 0.35207819556878084, 0.3609740520346203, 0.36986990850045975, 0.3796518207781606, 0.3894337330558615, 0.39921564533356235, 0.4089975576112632, 0.4187794698889641, 0.42856138216666495, 0.44039980197613177, 0.4522382217855986, 0.4640766415950654, 0.4759150614045322, 0.48775348121399903, 0.49959190102346585, 0.5159634982870246, 0.5323350955505833, 0.5487066928141421, 0.5650782900777008, 0.5814498873412596, 0.6053154794927107, 0.6291810716441618, 0.6530466637956129, 0.6769122559470641, 0.7007778480985152, 0.7353575156581483, 0.7699371832177815, 0.8045168507774146, 0.8390965183370478, 0.873676185896681, 0.9106463948349163, 0.9476166037731516, 0.9845868127113869, 1.0215570216496221, 1.0585272305878575, 1.1189845992374159, 1.1794419678869743, 1.2398993365365327, 1.3003567051860911, 1.3608140738356496, 1.421271442485208, 1.4880094556218617, 1.5547474687585154, 1.6214854818951692, 1.688223495031823, 1.7549615081684766, 1.8559572585191118, 1.9569530088697469, 2.0579487592203822, 2.1589445095710174, 2.2599402599216525, 2.3609360102722876, 2.4896176289633836, 2.6182992476544795, 2.7469808663455755, 2.8756624850366714, 3.0043441037277674, 3.1330257224188633, 3.2806396448134088, 3.428253567207954, 3.5758674896024996, 3.723481411997045, 3.8710953343915904, 4.018709256786136, 4.253758147239042, 4.488807037691948, 4.723855928144854, 4.95890481859776, 5.193953709050666, 5.429002599503572, 5.712006856053182, 5.995011112602792, 6.278015369152402, 6.561019625702012, 6.844023882251622, 7.127028138801232, 7.513788343964114, 7.900548549126996, 8.287308754289878, 8.674068959452761, 9.060829164615644, 9.447589369778527, 9.983152612781113, 10.0]</t>
+          <t>[0.0, 1.3287687111520152e-05, 2.6575374223040304e-05, 0.00015945224533824183, 0.0002923291164534434, 0.00083127916111111, 0.0013702292057687767, 0.0019091792504264435, 0.003933174782286804, 0.005957170314147164, 0.007981165846007525, 0.013963880563883802, 0.019946595281760078, 0.025929309999636354, 0.03191202471751263, 0.04168633853462841, 0.051460652351744185, 0.06123496616885996, 0.07100927998597574, 0.08078359380309152, 0.09154467767844209, 0.10230576155379265, 0.1130668454291432, 0.12382792930449377, 0.1315712983955171, 0.13931466748654042, 0.14705803657756375, 0.1470822346059732, 0.14710643263438264, 0.14713063066279208, 0.14715482869120153, 0.14717902671961097, 0.14720322474802042, 0.14744520503211486, 0.1476871853162093, 0.14792916560030375, 0.1481711458843982, 0.14841312616849264, 0.15024551522742002, 0.1506119930392055, 0.15097847085099098, 0.15134494866277645, 0.15171142647456193, 0.15173460971158628, 0.15173924635899116, 0.15174388300639605, 0.15174851965380093, 0.1517531563012058, 0.15175501096016777, 0.15175686561912974, 0.1517569398054882, 0.15175694421039318, 0.15175694861529815, 0.15175694924163027, 0.1517569498679624, 0.15175695049429452, 0.1517569515224427, 0.15175695255059088, 0.15175696283207266, 0.15175697311355443, 0.1517570759283722, 0.15175717874318997, 0.15175820689136768, 0.1517592350395454, 0.1517658914555999, 0.15177254787165442, 0.15177920428770894, 0.1518209466073659, 0.15186268892702284, 0.1519044312466798, 0.1523218544432493, 0.15273927763981882, 0.15315670083638833, 0.1542948095621682, 0.15543291828794809, 0.15657102701372796, 0.15770913573950784, 0.16094587368838206, 0.16418261163725628, 0.1674193495861305, 0.17065608753500472, 0.17389282548387894, 0.17945623853957562, 0.1850196515952723, 0.190583064650969, 0.19614647770666568, 0.20170989076236237, 0.20705579822810855, 0.21240170569385472, 0.2177476131596009, 0.22309352062534707, 0.22843942809109324, 0.23378533555683942, 0.23909100012206158, 0.24439666468728374, 0.2497023292525059, 0.2550079938177281, 0.2603136583829503, 0.26628594000529104, 0.2722582216276318, 0.27823050324997256, 0.2842027848723133, 0.2901750664946541, 0.29614734811699484, 0.3022310044058401, 0.3083146606946854, 0.31439831698353066, 0.32048197327237593, 0.3265656295612212, 0.3326492858500665, 0.3404670569480564, 0.3482848280460463, 0.35610259914403625, 0.36392037024202617, 0.3717381413400161, 0.37949416504452493, 0.3872501887490338, 0.3950062124535426, 0.40276223615805146, 0.4105182598625603, 0.41827428356706914, 0.4292451411249375, 0.44021599868280586, 0.45118685624067423, 0.4621577137985426, 0.47312857135641095, 0.4840994289142793, 0.4998078647217193, 0.5155163005291592, 0.5312247363365992, 0.5469331721440391, 0.5626416079514791, 0.5783500437589191, 0.6018767530238968, 0.6254034622888744, 0.6489301715538521, 0.6724568808188298, 0.6959835900838075, 0.7241724834974675, 0.7523613769111276, 0.7805502703247876, 0.8087391637384477, 0.8369280571521077, 0.880194355091261, 0.9234606530304142, 0.9667269509695675, 1.0099932489087209, 1.0532595468478743, 1.1082323564155416, 1.163205165983209, 1.2181779755508764, 1.2731507851185437, 1.328123594686211, 1.3830964042538785, 1.4426751367442594, 1.5022538692346403, 1.5618326017250213, 1.6214113342154022, 1.680990066705783, 1.769420548067441, 1.8578510294290989, 1.9462815107907567, 2.0347119921524146, 2.1231424735140725, 2.2115729548757304, 2.3334363477817206, 2.455299740687711, 2.577163133593701, 2.6990265264996913, 2.8208899194056816, 2.942753312311672, 3.0943507480052834, 3.245948183698895, 3.3975456193925067, 3.5491430550861183, 3.70074049077973, 3.8523379264733415, 4.079551542346082, 4.193158350282452, 4.306765158218822, 4.31789969996886, 4.319545320242923, 4.320873742061718, 4.321809243914868, 4.322744745768018, 4.323680247621168, 4.324615749474319, 4.325551251327469, 4.326486753180619, 4.327845824565603, 4.329204895950587, 4.330563967335571, 4.331923038720555, 4.333282110105539, 4.3346411814905235, 4.3366748039181005, 4.338708426345677, 4.340742048773254, 4.342775671200831, 4.344809293628408, 4.3501600156261215, 4.355510737623835, 4.360861459621548, 4.366212181619261, 4.395652779611184, 4.4250933776031065, 4.454533975595029, 4.5609988986380925, 4.667463821681156, 4.773928744724219, 5.094196480154581, 5.414464215584943, 5.648731341819579, 5.882998468054214, 6.117265594288849, 6.351532720523484, 6.659398934897952, 6.9672651492724205, 7.275131363646889, 7.582997578021357, 7.890863792395825, 8.368684858753548, 8.846505925111272, 9.324326991468995, 9.802148057826718, 10.0]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6281945676476332</v>
+        <v>0.6281945501781742</v>
       </c>
       <c r="D7" t="n">
         <v>9.81</v>
@@ -902,13 +902,13 @@
         <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>6.281945676476331</v>
+        <v>6.281945501781741</v>
       </c>
       <c r="M7" t="n">
-        <v>0.005068058773472081</v>
+        <v>0.005068059055347325</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0253402938673604</v>
+        <v>0.02534029527673662</v>
       </c>
       <c r="O7" t="n">
         <v>19.61967625424572</v>
@@ -938,11 +938,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[0.0, 5.942445761009135e-07, 1.188489152201827e-06, 7.130934913210962e-06, 1.3073380674220097e-05, 3.08614099844169e-05, 4.864943929461371e-05, 6.643746860481051e-05, 0.00011040931504445142, 0.0001543811614840923, 0.0001983530079237332, 0.00041360161110568064, 0.000628850214287628, 0.0008440988174695755, 0.0016932314650892418, 0.0025423641127089083, 0.0033914967603285748, 0.004425320468321392, 0.005459144176314209, 0.006492967884307026, 0.0075267915922998425, 0.00954713067850141, 0.011567469764702978, 0.013587808850904546, 0.015608147937106114, 0.01762848702330768, 0.02313215808853593, 0.028635829153764177, 0.034139500218992425, 0.03964317128422067, 0.04514684234944892, 0.05318915790848166, 0.0612314734675144, 0.06927378902654713, 0.07731610458557986, 0.08535842014461259, 0.09340073570364532, 0.10137808363621975, 0.10935543156879418, 0.11733277950136861, 0.12373653694234917, 0.13014029438332972, 0.1365440518243103, 0.14294780926529085, 0.14935156670627142, 0.1559658463431947, 0.16258012598011795, 0.16919440561704122, 0.17580868525396448, 0.18242296489088775, 0.189037244527811, 0.19505319302335797, 0.20106914151890493, 0.20708509001445188, 0.21310103850999884, 0.2191169870055458, 0.22517126922462236, 0.2312255514436989, 0.23727983366277547, 0.24333411588185203, 0.24938839810092858, 0.25544268032000517, 0.2612969919847635, 0.2671513036495219, 0.27300561531428025, 0.2788599269790386, 0.28471423864379697, 0.29056855030855533, 0.29636869771710556, 0.3021688451256558, 0.307968992534206, 0.31376913994275624, 0.31956928735130646, 0.3253694347598567, 0.33426412082699913, 0.3431588068941416, 0.352053492961284, 0.36094817902842646, 0.3698428650955689, 0.37962446056334426, 0.3894060560311196, 0.39918765149889496, 0.4089692469666703, 0.41875084243444566, 0.428532437902221, 0.44037016792953715, 0.4522078979568533, 0.46404562798416943, 0.47588335801148557, 0.4877210880388017, 0.49955881806611785, 0.5159298037223513, 0.5323007893785847, 0.5486717750348181, 0.5650427606910515, 0.5814137463472849, 0.605278112752132, 0.629142479156979, 0.653006845561826, 0.676871211966673, 0.70073557837152, 0.7353133188349535, 0.7698910592983871, 0.8044687997618206, 0.8390465402252542, 0.8736242806886877, 0.9105923569803318, 0.9475604332719759, 0.98452850956362, 1.0214965858552643, 1.0584646621469085, 1.1189186622423266, 1.1793726623377447, 1.2398266624331629, 1.300280662528581, 1.3607346626239991, 1.4211886627194172, 1.487922814263889, 1.5546569658083607, 1.6213911173528324, 1.688125268897304, 1.7548594204417758, 1.8558494069035554, 1.956839393365335, 2.0578293798271146, 2.158819366288894, 2.2598093527506737, 2.3607993392124533, 2.489473598753463, 2.618147858294473, 2.7468221178354826, 2.8754963773764923, 3.004170636917502, 3.132844896458512, 3.2804504638721306, 3.4280560312857493, 3.575661598699368, 3.723267166112987, 3.8708727335266055, 4.018478300940224, 4.2535138545388875, 4.488549408137551, 4.723584961736215, 4.958620515334879, 5.193656068933542, 5.428691622532206, 5.711680032021765, 5.994668441511324, 6.277656851000883, 6.560645260490443, 6.843633669980002, 7.126622079469561, 7.513360696994241, 7.90009931451892, 8.2868379320436, 8.67357654956828, 9.06031516709296, 9.447053784617639, 9.982585815666416, 10.0]</t>
+          <t>[0.0, 1.3287716147841724e-05, 2.6575432295683448e-05, 0.0001594525937741007, 0.00029232975525251794, 0.0008311796804739697, 0.0013700296056954216, 0.0019088795309168734, 0.003932262732157523, 0.005955645933398172, 0.007979029134638821, 0.01396071958275126, 0.0199424100308637, 0.025924100478976142, 0.03190579092708858, 0.04167879283677773, 0.051451794746466877, 0.06122479665615602, 0.07099779856584518, 0.08077080047553434, 0.09153140581890994, 0.10229201116228553, 0.11305261650566113, 0.12381322184903673, 0.13155611994574762, 0.1392990180424585, 0.1470419161391694, 0.14706611269572162, 0.14709030925227384, 0.14711450580882607, 0.1471387023653783, 0.14716289892193052, 0.14718709547848274, 0.147429061044005, 0.14767102660952725, 0.1479129921750495, 0.14815495774057175, 0.148396923306094, 0.15022928201433128, 0.15059575375597872, 0.15096222549762617, 0.1513286972392736, 0.15169516898092106, 0.15171835202854084, 0.15174153507616062, 0.15174172054054158, 0.15174176553379048, 0.1517418105270394, 0.1517418555202883, 0.1517418710088731, 0.15174187796356645, 0.1517418849182598, 0.15174188626323545, 0.1517418873294, 0.15174188839556454, 0.1517418894617291, 0.15174189052789364, 0.15174189315405304, 0.15174189578021244, 0.15174189840637184, 0.15174192466796585, 0.15174195092955986, 0.15174214650371917, 0.15174234207787848, 0.1517442978194716, 0.15174625356106472, 0.151755486985222, 0.1517647204093793, 0.1517739538335366, 0.15182127053343433, 0.15186858723333208, 0.15191590393322982, 0.15238907093220724, 0.15286223793118467, 0.1533354049301621, 0.15454258546918814, 0.1557497660082142, 0.15695694654724024, 0.1581641270862663, 0.16144667030022986, 0.16472921351419342, 0.168011756728157, 0.17129429994212056, 0.17457684315608413, 0.18011584137931758, 0.18565483960255103, 0.19119383782578447, 0.19673283604901792, 0.20227183427225137, 0.20765017849195502, 0.21302852271165867, 0.21840686693136233, 0.22378521115106598, 0.22916355537076963, 0.23454189959047328, 0.23993094260452658, 0.24531998561857987, 0.25070902863263317, 0.25609807164668646, 0.26148711466073976, 0.26760267929343107, 0.2737182439261224, 0.2798338085588137, 0.285949373191505, 0.2920649378241963, 0.2981805024568876, 0.304275205738715, 0.31036990902054246, 0.3164646123023699, 0.3225593155841973, 0.32865401886602474, 0.3347487221478522, 0.3424756934955933, 0.35020266484333445, 0.3579296361910756, 0.36565660753881674, 0.3733835788865579, 0.381110550234299, 0.3901151220158971, 0.3991196937974952, 0.40812426557909326, 0.41712883736069134, 0.4261334091422894, 0.4351379809238875, 0.4450355318266738, 0.45493308272946015, 0.46483063363224647, 0.4747281845350328, 0.4846257354378191, 0.49452328634060544, 0.5099374627502846, 0.5253516391599637, 0.5407658155696429, 0.556179991979322, 0.5715941683890011, 0.5975830970285642, 0.6235720256681272, 0.6495609543076902, 0.6755498829472533, 0.7015388115868163, 0.7326612151779158, 0.7637836187690153, 0.7949060223601149, 0.8260284259512144, 0.8571508295423139, 0.9012915843285163, 0.9454323391147187, 0.9895730939009211, 1.0337138486871233, 1.0778546034733256, 1.121995358259528, 1.1707766470939909, 1.2195579359284539, 1.2683392247629168, 1.3171205135973798, 1.3659018024318428, 1.4146830912663058, 1.4970261007312338, 1.5793691101961618, 1.6617121196610898, 1.7440551291260178, 1.8263981385909458, 1.9087411480558738, 2.0011565345415687, 2.0935719210272636, 2.1859873075129586, 2.2784026939986535, 2.3708180804843484, 2.4632334669700433, 2.604546584273999, 2.7458597015779547, 2.8871728188819104, 3.028485936185866, 3.1697990534898217, 3.3111121707937774, 3.4825305761869854, 3.6539489815801933, 3.8253673869734013, 3.8524804411098184, 3.8795934952462354, 3.882681230838948, 3.88399705815028, 3.8847293120958635, 3.885461566041447, 3.8861938199870303, 3.8869260739326137, 3.887658327878197, 3.8883905818237805, 3.889373927960522, 3.890357274097264, 3.8913406202340055, 3.892323966370747, 3.893307312507489, 3.8942906586442305, 3.896121657421102, 3.8979526561979734, 3.899783654974845, 3.9016146537517162, 3.9034456525285877, 3.9085320177054497, 3.9136183828823117, 3.9187047480591737, 3.9237911132360357, 3.9456963839285533, 3.967601654621071, 3.9895069253135884, 4.07793517881409, 4.166363432314592, 4.254791685815094, 4.495260019904374, 4.735728353993655, 4.976196688082935, 5.216665022172216, 5.48109512083597, 5.745525219499725, 6.009955318163479, 6.274385416827234, 6.538815515490988, 6.852845437671844, 7.1668753598527, 7.4809052820335555, 7.794935204214411, 8.108965126395267, 8.571165923432318, 9.033366720469369, 9.49556751750642, 9.95776831454347, 10.0]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.6281039087644976</v>
+        <v>0.6281041312312601</v>
       </c>
       <c r="D8" t="n">
         <v>9.81</v>
@@ -969,13 +969,13 @@
         <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>6.281039087644976</v>
+        <v>6.281041312312601</v>
       </c>
       <c r="M8" t="n">
-        <v>0.00506952189987717</v>
+        <v>0.005069518308753124</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02534760949938585</v>
+        <v>0.02534759154376562</v>
       </c>
       <c r="O8" t="n">
         <v>19.61959050849376</v>
@@ -1005,11 +1005,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[0.0, 5.942462183561271e-07, 1.1884924367122541e-06, 7.130954620273526e-06, 1.3073416803834797e-05, 3.086149538165419e-05, 4.8649573959473585e-05, 6.643765253729297e-05, 0.00011040962470627208, 0.0001543815968752512, 0.00019835356904423032, 0.0004136051126777584, 0.0006288566563112865, 0.0008441081999448145, 0.0016927668827192537, 0.0025414255654936926, 0.0033900842482681316, 0.004423780074558494, 0.005457475900848857, 0.00649117172713922, 0.007524867553429583, 0.009545611216546701, 0.01156635487966382, 0.013587098542780939, 0.015607842205898058, 0.017628585869015174, 0.023132160534993583, 0.02863573520097199, 0.0341393098669504, 0.03964288453292881, 0.04514645919890722, 0.05318987124880683, 0.06123328329870644, 0.06927669534860606, 0.07732010739850567, 0.08536351944840528, 0.0934069314983049, 0.10138163825260178, 0.10935634500689867, 0.11733105176119556, 0.12373379686869124, 0.1301365419761869, 0.13653928708368257, 0.14294203219117824, 0.1493447772986739, 0.15595995711798946, 0.16257513693730502, 0.16919031675662058, 0.17580549657593614, 0.1824206763952517, 0.18903585621456725, 0.19504830497473263, 0.201060753734898, 0.2070732024950634, 0.21308565125522877, 0.21909810001539415, 0.22514566178568657, 0.231193223555979, 0.2372407853262714, 0.24328834709656383, 0.24933590886685625, 0.25538347063714867, 0.2612373570975627, 0.2670912435579767, 0.2729451300183907, 0.27879901647880473, 0.28465290293921874, 0.29050678939963276, 0.2963067371027996, 0.3021066848059664, 0.30790663250913325, 0.3137065802123001, 0.3195065279154669, 0.32530647561863374, 0.33421389324099304, 0.34312131086335235, 0.35202872848571165, 0.36093614610807095, 0.36984356373043026, 0.3796269765397787, 0.3894103893491272, 0.39919380215847566, 0.40897721496782413, 0.4187606277771726, 0.42854404058652107, 0.4403865866405074, 0.4522291326944937, 0.46407167874848004, 0.47591422480246637, 0.4877567708564527, 0.499599316910439, 0.5159747741851581, 0.5323502314598773, 0.5487256887345964, 0.5651011460093155, 0.5814766032840346, 0.6053446675966764, 0.6292127319093181, 0.6530807962219599, 0.6769488605346017, 0.7008169248472434, 0.7353996282063476, 0.7699823315654518, 0.804565034924556, 0.8391477382836602, 0.8737304416427644, 0.9107039345907404, 0.9476774275387164, 0.9846509204866924, 1.0216244134346684, 1.0585979063826443, 1.119056127149816, 1.1795143479169878, 1.2399725686841596, 1.3004307894513314, 1.3608890102185032, 1.421347230985675, 1.4880907370530727, 1.5548342431204705, 1.6215777491878682, 1.688321255255266, 1.7550647613226638, 1.8560697552846244, 1.957074749246585, 2.0580797432085456, 2.159084737170506, 2.2600897311324664, 2.3610947250944267, 2.489786849644444, 2.6184789741944616, 2.747171098744479, 2.8758632232944965, 3.004555347844514, 3.1332474723945314, 3.2808735280995123, 3.428499583804493, 3.576125639509474, 3.723751695214455, 3.871377750919436, 4.019003806624417, 4.25407221892094, 4.489140631217463, 4.724209043513986, 4.9592774558105095, 5.194345868107033, 5.429414280403556, 5.712443824986355, 5.995473369569154, 6.278502914151954, 6.561532458734753, 6.844562003317552, 7.1275915479003515, 7.514386998294119, 7.901182448687887, 8.287977899081655, 8.674773349475423, 9.06156879986919, 9.448364250262959, 9.983976371374482, 10.0]</t>
+          <t>[0.0, 1.3287752874857196e-05, 2.657550574971439e-05, 0.00015945303449828635, 0.0002923305632468583, 0.0008310539576501814, 0.0013697773520535044, 0.0019085007464568274, 0.003931110070634761, 0.005953719394812694, 0.007976328718990629, 0.01395672542290775, 0.01993712212682487, 0.025917518830741993, 0.031897915534659115, 0.041669254991470416, 0.051440594448281717, 0.06121193390509302, 0.07098327336190433, 0.08075461281871563, 0.0915145848331236, 0.10227455684753156, 0.11303452886193953, 0.1237945008763475, 0.1315369865030325, 0.1392794721297175, 0.1470219577564025, 0.14704615302398588, 0.14707034829156926, 0.14709454355915264, 0.147118738826736, 0.1471429340943194, 0.14716712936190277, 0.14740908203773653, 0.1476510347135703, 0.14789298738940407, 0.14813494006523784, 0.1483768927410716, 0.15023027343723916, 0.15060094957647266, 0.15097162571570616, 0.15134230185493966, 0.15171297799417316, 0.15171768457722815, 0.15172239116028313, 0.15172257942360534, 0.15172276768692755, 0.15172281319741343, 0.15172282882140892, 0.1517228444454044, 0.1517228461838787, 0.15172284753212034, 0.15172284860035135, 0.15172284966858235, 0.15172285073681335, 0.15172285180504436, 0.15172285443551647, 0.1517228570659886, 0.1517228596964607, 0.1517228860011819, 0.15172291230590307, 0.15172310815061707, 0.15172330399533107, 0.1517252624424711, 0.1517272208896111, 0.15173646072081462, 0.15174570055201814, 0.15175494038322165, 0.15180227066063934, 0.15184960093805702, 0.1518969312154747, 0.15237023398965155, 0.1528435367638284, 0.15331683953800523, 0.15452410218586074, 0.15573136483371625, 0.15693862748157175, 0.15814589012942726, 0.16142798280033682, 0.1647100754712464, 0.16799216814215595, 0.17127426081306552, 0.17455635348397508, 0.18009482374118463, 0.18563329399839418, 0.19117176425560373, 0.19671023451281328, 0.20224870477002282, 0.2076269952820816, 0.21300528579414035, 0.21838357630619912, 0.22376186681825788, 0.22914015733031665, 0.2345184478423754, 0.23990756928391965, 0.2452966907254639, 0.25068581216700814, 0.2560749336085524, 0.2614640550500966, 0.2675798204954028, 0.273695585940709, 0.27981135138601515, 0.2859271168313213, 0.2920428822766275, 0.2981586477219337, 0.3042532401935256, 0.31034783266511756, 0.3164424251367095, 0.32253701760830145, 0.3286316100798934, 0.33472620255148533, 0.342453486877448, 0.3501807712034106, 0.35790805552937327, 0.3656353398553359, 0.37336262418129856, 0.3810899085072612, 0.3900942158171107, 0.39909852312696015, 0.4081028304368096, 0.4171071377466591, 0.42611144505650855, 0.435115752366358, 0.44501350773696946, 0.4549112631075809, 0.46480901847819234, 0.4747067738488038, 0.4846045292194152, 0.49450228459002665, 0.5099173648319909, 0.5253324450739552, 0.5407475253159194, 0.5561626055578837, 0.5715776857998479, 0.5975667986959792, 0.6235559115921104, 0.6495450244882417, 0.675534137384373, 0.7015232502805042, 0.732645383109487, 0.7637675159384698, 0.7948896487674526, 0.8260117815964354, 0.8571339144254182, 0.9012758095926728, 0.9454177047599275, 0.9895595999271821, 1.0337014950944368, 1.0778433902616915, 1.1219852854289463, 1.170765797016819, 1.2195463086046918, 1.2683268201925646, 1.3171073317804374, 1.3658878433683102, 1.414668354956183, 1.4970131766872312, 1.5793579984182795, 1.6617028201493278, 1.744047641880376, 1.8263924636114244, 1.9087372853424727, 2.00115291037688, 2.093568535411287, 2.1859841604456944, 2.2783997854801017, 2.370815410514509, 2.463231035548916, 2.6045449771414377, 2.7458589187339593, 2.887172860326481, 3.0284868019190023, 3.169800743511524, 3.3111146851040454, 3.3968242960169004, 3.4825339069297554, 3.4911505346161364, 3.492202934033472, 3.4929454799974105, 3.4936880259613488, 3.494430571925287, 3.4951731178892254, 3.4959156638531637, 3.496658209817102, 3.4977404127541405, 3.498822615691179, 3.4999048186282176, 3.500987021565256, 3.5020692245022946, 3.503151427439333, 3.504765986813054, 3.5063805461867745, 3.507995105560495, 3.509609664934216, 3.5112242243079366, 3.5154764916293577, 3.519728758950779, 3.5239810262722, 3.528233293593621, 3.551603529996886, 3.574973766400151, 3.5983440028034157, 3.6828746249733273, 3.767405247143239, 3.8519358693131505, 4.085608058331363, 4.319280247349576, 4.552952436367789, 4.786624625386002, 5.005416677034003, 5.2242087286820045, 5.443000780330006, 5.661792831978007, 5.880584883626008, 6.236809049569158, 6.593033215512308, 6.949257381455458, 7.305481547398608, 7.661705713341758, 8.017929879284907, 8.484259102922804, 8.950588326560702, 9.4169175501986, 9.883246773836497, 10.0]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.6279893313195548</v>
+        <v>0.6279889980891631</v>
       </c>
       <c r="D9" t="n">
         <v>9.81</v>
@@ -1036,13 +1036,13 @@
         <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>6.279893313195548</v>
+        <v>6.279889980891631</v>
       </c>
       <c r="M9" t="n">
-        <v>0.005071371949953078</v>
+        <v>0.005071377332008225</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02535685974976539</v>
+        <v>0.02535688666004112</v>
       </c>
       <c r="O9" t="n">
         <v>19.61948205253208</v>
@@ -1072,11 +1072,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[0.0, 5.942482955904618e-07, 1.1884965911809236e-06, 7.1309795470855415e-06, 1.3073462502990159e-05, 3.0861603397797434e-05, 4.864974429260471e-05, 6.643788518741198e-05, 0.0001104100163872948, 0.00015438214758717761, 0.00019835427878706042, 0.0004136095418573381, 0.0006288648049276157, 0.0008441200679978933, 0.0016921807781542795, 0.0025402414883106657, 0.003388302198467052, 0.004421836805876193, 0.005455371413285334, 0.006488906020694476, 0.007522440628103617, 0.009543696635413945, 0.011564952642724273, 0.013586208650034601, 0.01560746465734493, 0.01762872066465526, 0.02313217861258009, 0.028635636560504923, 0.03413909450842975, 0.03964255245635458, 0.0451460104042794, 0.053190820541146995, 0.06123563067801459, 0.06928044081488219, 0.07732525095174979, 0.08537006108861739, 0.09341487122548499, 0.1013862367089923, 0.10935760219249961, 0.11732896767600692, 0.12373062967945868, 0.13013229168291043, 0.13653395368636217, 0.14293561568981392, 0.14933727769326566, 0.15595153648932863, 0.1625657952853916, 0.1691800540814546, 0.17579431287751757, 0.18240857167358054, 0.18902283046964352, 0.1950360487072489, 0.20104926694485425, 0.20706248518245962, 0.213075703420065, 0.21908892165767035, 0.22513692884266928, 0.2311849360276682, 0.23723294321266714, 0.24328095039766606, 0.249328957582665, 0.2553769647676639, 0.26123291254355496, 0.267088860319446, 0.27294480809533705, 0.2788007558712281, 0.28465670364711915, 0.2905126514230102, 0.29631197659665665, 0.3021113017703031, 0.30791062694394955, 0.313709952117596, 0.31950927729124246, 0.3253086024648889, 0.33420001159929713, 0.34309142073370535, 0.3519828298681136, 0.3608742390025218, 0.36976564813693, 0.3795463576618128, 0.38932706718669563, 0.39910777671157843, 0.40888848623646123, 0.41866919576134404, 0.42844990528622684, 0.44028568872695, 0.4521214721676732, 0.46395725560839635, 0.4757930390491195, 0.4876288224898427, 0.49946460593056585, 0.5158338750716965, 0.5322031442128272, 0.5485724133539579, 0.5649416824950886, 0.5813109516362193, 0.6051718454895616, 0.6290327393429039, 0.6528936331962463, 0.6767545270495886, 0.7006154209029309, 0.7351876927622334, 0.7697599646215358, 0.8043322364808383, 0.8389045083401407, 0.8734767801994432, 0.9104388023363853, 0.9474008244733274, 0.9843628466102695, 1.0213248687472116, 1.0582868908841538, 1.118731316606788, 1.1791757423294222, 1.2396201680520564, 1.3000645937746906, 1.3605090194973248, 1.420953445219959, 1.4876766345365764, 1.5543998238531938, 1.6211230131698111, 1.6878462024864285, 1.7545693918030458, 1.8555430295250037, 1.9565166672469616, 2.0574903049689195, 2.1584639426908776, 2.2594375804128357, 2.360411218134794, 2.4890645869231802, 2.6177179557115666, 2.746371324499953, 2.8750246932883394, 3.003678062076726, 3.1323314308651122, 3.2799132939676405, 3.427495157070169, 3.575077020172697, 3.7226588832752254, 3.8702407463777537, 4.017822609480282, 4.252820311195249, 4.487818012910216, 4.722815714625183, 4.95781341634015, 5.192811118055117, 5.427808819770084, 5.710752357544079, 5.993695895318075, 6.27663943309207, 6.559582970866066, 6.842526508640061, 7.125470046414057, 7.512147416171787, 7.898824785929518, 8.285502155687249, 8.67217952544498, 9.05885689520271, 9.445534264960441, 9.980977841230501, 10.0]</t>
+          <t>[0.0, 1.3287799329650526e-05, 2.6575598659301052e-05, 0.0001594535919558063, 0.00029233158525231157, 0.0008308950945762241, 0.0013694586039001368, 0.0019080221132240494, 0.003929653564157047, 0.005951285015090045, 0.007972916466023043, 0.013951678381846449, 0.019930440297669855, 0.02590920221349326, 0.031887964129316666, 0.041657212275830524, 0.05142646042234438, 0.06119570856885824, 0.07096495671537209, 0.08073420486188594, 0.09149344159231995, 0.10225267832275396, 0.11301191505318797, 0.12377115178362198, 0.13151270176848187, 0.13925425175334177, 0.14699580173820168, 0.14701999408190436, 0.14704418642560704, 0.14706837876930973, 0.1470925711130124, 0.1471167634567151, 0.14714095580041778, 0.14738287923744461, 0.14762480267447145, 0.1478667261114983, 0.14810864954852512, 0.14835057298555196, 0.15018284507538487, 0.15054929949335147, 0.15091575391131806, 0.15128220832928466, 0.15164866274725125, 0.15167184525664149, 0.15169502776603172, 0.15169595506640732, 0.15169688236678291, 0.1516978096671585, 0.1516987369675341, 0.15169875180434012, 0.15169876664114612, 0.15169878147795213, 0.15169878741267454, 0.15169878859961902, 0.15169878906213946, 0.1516987893508414, 0.15169878957892893, 0.15169878980701645, 0.1516987903201254, 0.15169879083323434, 0.1516987957634129, 0.15169880069359148, 0.1516988499953772, 0.1516988992971629, 0.15169939231502, 0.1516998853328771, 0.15170481551144804, 0.151709745690019, 0.15171467586858994, 0.15175436627907407, 0.1517940566895582, 0.15183374710004233, 0.1522306512048836, 0.15262755530972488, 0.15302445941456616, 0.1541350327879752, 0.15524560616138422, 0.15635617953479325, 0.15746675290820228, 0.1606794155789356, 0.16389207824966895, 0.16710474092040228, 0.17031740359113562, 0.17353006626186895, 0.17910191393627445, 0.18467376161067994, 0.19024560928508544, 0.19581745695949093, 0.20138930463389643, 0.20672419137713866, 0.21205907812038088, 0.2173939648636231, 0.22272885160686534, 0.22806373835010757, 0.2333986250933498, 0.23869337932631338, 0.24398813355927695, 0.24928288779224053, 0.2545776420252041, 0.2598723962581677, 0.2651671504911313, 0.2735283605488074, 0.2818895706064835, 0.28729071062058437, 0.2926918506346852, 0.2980929906487861, 0.30349413066288694, 0.3088952706769878, 0.31429641069108866, 0.3248631897606449, 0.3354299688302011, 0.3459967478997573, 0.35384112816815394, 0.36168550843655056, 0.3695298887049472, 0.3773742689733438, 0.38521864924174043, 0.3953926494683468, 0.40556664969495315, 0.4157406499215595, 0.4259146501481659, 0.43608865037477224, 0.4462626506013786, 0.45977980558437453, 0.4732969605673705, 0.4868141155503664, 0.5003312705333623, 0.5138484255163582, 0.5273655804993541, 0.5442057547437775, 0.5610459289882009, 0.5778861032326243, 0.5947262774770478, 0.6115664517214712, 0.637383141045592, 0.6631998303697129, 0.6890165196938337, 0.7148332090179546, 0.7406498983420754, 0.7776192248046483, 0.8145885512672212, 0.8515578777297941, 0.888527204192367, 0.9254965306549399, 0.964973567627001, 1.0044506045990622, 1.0439276415711234, 1.0834046785431846, 1.1228817155152457, 1.186643546595834, 1.2504053776764223, 1.3141672087570107, 1.377929039837599, 1.4416908709181873, 1.5054527019987756, 1.5766323610724715, 1.6478120201461675, 1.7189916792198634, 1.7901713382935593, 1.8613509973672553, 1.969022259445074, 2.0766935215228925, 2.184364783600711, 2.2920360456785294, 2.3997073077563478, 2.507378569834166, 2.6446366875965177, 2.7818948053588692, 2.9191529231212208, 3.0564110408835723, 3.1066086148361434, 3.128301412514216, 3.1390833579416384, 3.1401371836002507, 3.140723685483584, 3.1413101873669174, 3.1418966892502507, 3.142483191133584, 3.1430696930169173, 3.1436561949002506, 3.1444438561240107, 3.1452315173477707, 3.146019178571531, 3.146806839795291, 3.147594501019051, 3.148382162242811, 3.149848670981445, 3.151315179720079, 3.152781688458713, 3.1542481971973473, 3.1557147059359814, 3.15978870396106, 3.1638627019861385, 3.167936700011217, 3.1720106980362957, 3.189557166597604, 3.207103635158912, 3.2246501037202204, 3.2955543024824125, 3.3664585012446047, 3.437362700006797, 3.6126397260860883, 3.78791675216538, 3.9631937782446713, 4.138470804323963, 4.345868230039416, 4.55326565575487, 4.760663081470323, 4.968060507185776, 5.17545793290123, 5.478478998257681, 5.781500063614132, 6.084521128970583, 6.387542194327034, 6.690563259683485, 6.9935843250399365, 7.395253080590258, 7.79692183614058, 8.198590591690902, 8.600259347241224, 9.001928102791545, 9.403596858341867, 9.882893299388343, 10.0]</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.627844555184058</v>
+        <v>0.6278448242260618</v>
       </c>
       <c r="D10" t="n">
         <v>9.81</v>
@@ -1103,13 +1103,13 @@
         <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>6.27844555184058</v>
+        <v>6.278448242260618</v>
       </c>
       <c r="M10" t="n">
-        <v>0.005073711058506403</v>
+        <v>0.005073706710167309</v>
       </c>
       <c r="N10" t="n">
-        <v>0.02536855529253201</v>
+        <v>0.02536853355083654</v>
       </c>
       <c r="O10" t="n">
         <v>19.61934487144314</v>
@@ -1139,11 +1139,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[0.0, 5.942509230219617e-07, 1.1885018460439234e-06, 7.131011076263541e-06, 1.3073520306483159e-05, 3.08617400241829e-05, 4.8649959741882634e-05, 6.643817945958237e-05, 0.0001104105118129267, 0.000154382844166271, 0.00019835517651961532, 0.00041361514444324544, 0.0006288751123668756, 0.0008441350802905057, 0.0016914418679977903, 0.002538748655705075, 0.0033860554434123596, 0.004419386980488469, 0.0054527185175645785, 0.006486050054640688, 0.007519381591716797, 0.00954128662034704, 0.011563191648977284, 0.013585096677607527, 0.01560700170623777, 0.017628906734868013, 0.02313222505040221, 0.028635543365936406, 0.0341388616814706, 0.0396421799970048, 0.045145498312538994, 0.0531920815994982, 0.06123866488645741, 0.06928524817341662, 0.07733183146037584, 0.08537841474733505, 0.09342499803429427, 0.10139214264149127, 0.10935928724868826, 0.11732643185588526, 0.1237266146861277, 0.13012679751637013, 0.13652698034661256, 0.142927163176855, 0.14932734600709743, 0.15594159318168896, 0.16255584035628048, 0.169170087530872, 0.17578433470546354, 0.18239858188005506, 0.1890128290546466, 0.19502409455617095, 0.20103536005769532, 0.20704662555921968, 0.21305789106074405, 0.2190691565622684, 0.2251127091941974, 0.2311562618261264, 0.23719981445805538, 0.24324336708998437, 0.24928691972191336, 0.2553304723538423, 0.2611875702389803, 0.2670446681241183, 0.2729017660092563, 0.2787588638943943, 0.2846159617795323, 0.2904730596646703, 0.29627180393602887, 0.30207054820738743, 0.307869292478746, 0.3136680367501046, 0.31946678102146314, 0.3252655252928217, 0.33415468530283055, 0.3430438453128394, 0.3519330053228482, 0.36082216533285705, 0.3697113253428659, 0.3794914278438147, 0.3892715303447635, 0.39905163284571227, 0.40883173534666106, 0.41861183784760986, 0.42839194034855865, 0.4402263741384946, 0.4520608079284305, 0.46389524171836644, 0.47572967550830236, 0.4875641092982383, 0.4993985430881742, 0.5157666303448002, 0.5321347176014262, 0.5485028048580521, 0.5648708921146781, 0.5812389793713041, 0.6050974535997763, 0.6289559278282485, 0.6528144020567207, 0.6766728762851929, 0.7005313505136651, 0.7350998036060068, 0.7696682566983485, 0.8042367097906902, 0.8388051628830319, 0.8733736159753736, 0.9103314086732172, 0.9472892013710608, 0.9842469940689044, 1.021204786766748, 1.0581625794645917, 1.1186002984899155, 1.1790380175152393, 1.239475736540563, 1.2999134555658869, 1.3603511745912107, 1.4207888936165345, 1.4875044238149169, 1.5542199540132993, 1.6209354842116817, 1.687651014410064, 1.7543665446084464, 1.8553287749184164, 1.9562910052283864, 2.057253235538356, 2.158215465848326, 2.2591776961582957, 2.3601399264682654, 2.4887787032246957, 2.617417479981126, 2.7460562567375564, 2.8746950334939867, 3.003333810250417, 3.1319725870068473, 3.2795378923345293, 3.4271031976622113, 3.5746685029898932, 3.722233808317575, 3.869799113645257, 4.017364418972939, 4.252335683658167, 4.487306948343395, 4.722278213028623, 4.957249477713852, 5.19222074239908, 5.427192007084308, 5.710104214005361, 5.9930164209264145, 6.275928627847468, 6.558840834768521, 6.841753041689574, 7.124665248610627, 7.511299866400934, 7.897934484191241, 8.284569101981548, 8.671203719771855, 9.057838337562162, 9.444472955352468, 9.979854738547234, 10.0]</t>
+          <t>[0.0, 1.3287858088936105e-05, 2.657571617787221e-05, 0.00015945429706723323, 0.00029233287795659427, 0.0008306944220172147, 0.001369055966077835, 0.0019074175101384554, 0.003927813694084442, 0.005948209878030429, 0.007968606061976417, 0.013945304396098611, 0.019922002730220805, 0.025898701064343, 0.03187539939846519, 0.04164199993544252, 0.05140860047241985, 0.06117520100939718, 0.07094180154637451, 0.08070840208335184, 0.09146667404794788, 0.10222494601254392, 0.11298321797713996, 0.123741489941736, 0.13148208866740757, 0.13922268739307914, 0.1469632861187507, 0.14698747548976843, 0.14701166486078615, 0.14703585423180388, 0.1470600436028216, 0.14708423297383932, 0.14710842234485705, 0.1473503160550343, 0.14759220976521154, 0.14783410347538878, 0.14807599718556602, 0.14831789089574327, 0.15015010206472207, 0.15051654429851782, 0.15088298653231358, 0.15124942876610933, 0.1516158709999051, 0.1516390531325019, 0.1516622352650987, 0.15166687169161805, 0.15166779897692192, 0.1516679844339827, 0.15166816989104345, 0.15166835534810422, 0.15166837084845666, 0.1516683863488091, 0.15166839331060875, 0.1516683957441341, 0.15166839709120875, 0.15166839815910368, 0.15166839922699862, 0.15166840029489356, 0.1516684013627885, 0.15166840399330908, 0.15166840662382966, 0.15166840925435024, 0.15166843555955603, 0.15166846186476182, 0.15166865776971591, 0.15166885367467, 0.15167081272421093, 0.15167277177375185, 0.15168201577708562, 0.1516912597804194, 0.15170050378375316, 0.15174785434281027, 0.15179520490186738, 0.15184255546092448, 0.15231606105149556, 0.15278956664206664, 0.15326307223263771, 0.15447034302392273, 0.15567761381520775, 0.15688488460649277, 0.1580921553977778, 0.16137280676707566, 0.16465345813637353, 0.1679341095056714, 0.17121476087496926, 0.17449541224426712, 0.1800324489570037, 0.1855694856697403, 0.19110652238247688, 0.19664355909521347, 0.20218059580795006, 0.20755863677801728, 0.2129366777480845, 0.21831471871815172, 0.22369275968821895, 0.22907080065828617, 0.2344488416283534, 0.23983789725269206, 0.24522695287703072, 0.2506160085013694, 0.25600506412570806, 0.2613941197500467, 0.2675099455021096, 0.2736257712541725, 0.27974159700623535, 0.28585742275829823, 0.2919732485103611, 0.298089074262424, 0.30418330590154063, 0.3102775375406573, 0.31637176917977394, 0.3224660008188906, 0.32856023245800725, 0.3346544640971239, 0.3423820605335513, 0.3501096569699787, 0.3578372534064061, 0.3655648498428335, 0.3732924462792609, 0.3810200427156883, 0.3900236331236165, 0.3990272235315447, 0.4080308139394729, 0.4170344043474011, 0.4260379947553293, 0.43504158516325747, 0.44493950430494905, 0.45483742344664063, 0.4647353425883322, 0.4746332617300238, 0.4845311808717154, 0.49442910001340695, 0.5098455106828461, 0.5252619213522853, 0.5406783320217246, 0.5560947426911638, 0.571511153360603, 0.5974993290333455, 0.6234875047060879, 0.6494756803788304, 0.6754638560515729, 0.7014520317243154, 0.7325719976912725, 0.7636919636582296, 0.7948119296251867, 0.8259318955921437, 0.8570518615591008, 0.9011938149891321, 0.9453357684191633, 0.9894777218491946, 1.0336196752792257, 1.0777616287092568, 1.121903582139288, 1.1706799782228965, 1.219456374306505, 1.2682327703901135, 1.317009166473722, 1.3657855625573305, 1.414561958640939, 1.4969060864109134, 1.5792502141808877, 1.661594341950862, 1.7439384697208364, 1.8262825974908108, 1.9086267252607851, 2.0010380099963534, 2.0934492947319217, 2.18586057946749, 2.278271864203058, 2.3706831489386264, 2.4630944336741947, 2.60440229568035, 2.745710157686505, 2.796225473151833, 2.8176405181519617, 2.821149240100436, 2.8227909181107016, 2.823759746708579, 2.8242950308707795, 2.82483031503298, 2.8253655991951807, 2.8259008833573813, 2.826436167519582, 2.8269714516817825, 2.8276868701881406, 2.8284022886944986, 2.8291177072008566, 2.8298331257072147, 2.8305485442135727, 2.8312639627199307, 2.8326060887773785, 2.8339482148348263, 2.835290340892274, 2.836632466949722, 2.8379745930071696, 2.8416925754110065, 2.8454105578148434, 2.8491285402186803, 2.8528465226225173, 2.8687786808055056, 2.884710838988494, 2.900642997171482, 2.9645334431151555, 3.028423889058829, 3.092314335002502, 3.2474340134841815, 3.4025536919658608, 3.55767337044754, 3.7127930489292194, 3.8968916092868238, 4.080990169644428, 4.265088730002033, 4.449187290359637, 4.633285850717241, 4.903971110910666, 5.17465637110409, 5.445341631297515, 5.716026891490939, 5.9867121516843635, 6.257397411877788, 6.615179026761501, 6.972960641645214, 7.330742256528927, 7.68852387141264, 8.046305486296353, 8.404087101180066, 8.829814553339508, 9.25554200549895, 9.681269457658393, 10.0]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.6276616710166519</v>
+        <v>0.6276618204844946</v>
       </c>
       <c r="D11" t="n">
         <v>9.81</v>
@@ -1170,13 +1170,13 @@
         <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>6.276616710166519</v>
+        <v>6.276618204844945</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0050766681822198</v>
+        <v>0.005076665764361884</v>
       </c>
       <c r="N11" t="n">
-        <v>0.025383340911099</v>
+        <v>0.02538332882180942</v>
       </c>
       <c r="O11" t="n">
         <v>19.61917135722715</v>
@@ -1206,11 +1206,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[0.0, 5.942542463917016e-07, 1.1885084927834032e-06, 7.13105095670042e-06, 1.3073593420617436e-05, 3.086191283934457e-05, 4.86502322580717e-05, 6.643855167679882e-05, 0.00011041113846397605, 0.00015438372525115328, 0.00019835631203833051, 0.00041362223140662053, 0.0006288881507749105, 0.0008441540701432006, 0.0016905111122795112, 0.002536868154415822, 0.0033832251965521328, 0.00441630122798287, 0.005449377259413607, 0.006482453290844344, 0.007515529322275082, 0.009538256838342528, 0.011560984354409973, 0.01358371187047742, 0.015606439386544865, 0.017629166902612313, 0.0231323213774089, 0.028635475852205487, 0.034138630327002074, 0.03964178480179866, 0.04514493927659525, 0.0531937756836251, 0.06124261209065495, 0.0692914484976848, 0.07734028490471465, 0.08538912131174449, 0.09343795771877433, 0.1013997708628615, 0.10936158400694868, 0.11732339715103585, 0.12372162445103722, 0.1301198517510386, 0.13651807905103996, 0.14291630635104133, 0.1493145336510427, 0.15592968517690114, 0.1625448367027596, 0.16915998822861805, 0.1757751397544765, 0.18239029128033496, 0.1890054428061934, 0.19501184529142077, 0.20101824777664812, 0.20702465026187547, 0.21303105274710282, 0.21903745523233017, 0.22507132309518857, 0.23110519095804696, 0.23713905882090536, 0.24317292668376375, 0.24920679454662215, 0.2552406624094805, 0.26109800124945953, 0.26695534008943855, 0.2728126789294176, 0.2786700177693966, 0.2845273566093756, 0.29038469544935464, 0.29618286380622344, 0.30198103216309224, 0.30777920051996105, 0.31357736887682985, 0.31937553723369866, 0.32517370559056746, 0.33407462717123987, 0.3429755487519123, 0.3518764703325847, 0.3607773919132571, 0.3696783134939295, 0.379459988516545, 0.3892416635391605, 0.399023338561776, 0.40880501358439153, 0.41858668860700704, 0.42836836362962255, 0.44020690160759196, 0.45204543958556137, 0.4638839775635308, 0.4757225155415002, 0.4875610535194696, 0.499399591497439, 0.5157716083363638, 0.5321436251752887, 0.5485156420142135, 0.5648876588531384, 0.5812596756920633, 0.6051205278150351, 0.628981379938007, 0.6528422320609788, 0.6767030841839506, 0.7005639363069225, 0.7351351976863375, 0.7697064590657525, 0.8042777204451675, 0.8388489818245826, 0.8734202432039976, 0.9103810462405703, 0.9473418492771429, 0.9843026523137156, 1.0212634553502884, 1.0582242583868613, 1.1186622804406305, 1.1791003024943998, 1.239538324548169, 1.2999763466019383, 1.3604143686557075, 1.4208523907094768, 1.4875729187086268, 1.554293446707777, 1.621013974706927, 1.687734502706077, 1.7544550307052271, 1.8554257987406166, 1.9563965667760062, 2.0573673348113957, 2.158338102846785, 2.2593088708821742, 2.3602796389175635, 2.4889279882154294, 2.617576337513295, 2.746224686811161, 2.874873036109027, 3.0035213854068927, 3.1321697347047586, 3.279746111783442, 3.427322488862125, 3.5748988659408085, 3.722475243019492, 3.870051620098175, 4.0176279971768585, 4.252617100258853, 4.487606203340847, 4.722595306422841, 4.957584409504835, 5.192573512586829, 5.4275626156688235, 5.710498229672117, 5.993433843675411, 6.276369457678705, 6.559305071681998, 6.842240685685292, 7.125176299688586, 7.511843601760332, 7.898510903832078, 8.285178205903826, 8.671845507975572, 9.058512810047318, 9.445180112119065, 9.980606978721621, 10.0]</t>
+          <t>[0.0, 1.3287932412041555e-05, 2.657586482408311e-05, 0.00015945518894449863, 0.00029233451306491417, 0.0008304410222462024, 0.0013685475314274907, 0.001906654040608779, 0.003925490331723099, 0.005944326622837419, 0.007963162913951738, 0.013937257614136337, 0.019911352314320938, 0.025885447014505538, 0.03185954171469014, 0.04162279272180265, 0.051386043728915164, 0.061149294736027676, 0.07091254574314018, 0.08067579675025269, 0.09143281761704301, 0.10218983848383334, 0.11294685935062367, 0.12370388021741399, 0.1314435023958294, 0.13918312457424478, 0.14692274675266018, 0.1469469330719677, 0.14697111939127525, 0.14699530571058278, 0.14701949202989031, 0.14704367834919785, 0.14706786466850538, 0.14730972786158072, 0.14755159105465607, 0.1477934542477314, 0.14803531744080675, 0.1482771806338821, 0.15013558134758975, 0.15050726149033128, 0.1508789416330728, 0.15125062177581433, 0.15162230191855586, 0.15162702567834344, 0.15162797043030096, 0.1516289151822585, 0.15162985993421602, 0.15162990559564266, 0.1516299512570693, 0.15162999691849594, 0.15163000393966528, 0.1516300077835035, 0.15163001022969633, 0.15163001158126999, 0.151630012652092, 0.15163001372291401, 0.15163001479373603, 0.15163001586455804, 0.15163001850133742, 0.1516300211381168, 0.15163002377489618, 0.15163005014268996, 0.15163007651048374, 0.15163027281949729, 0.15163046912851083, 0.15163243221864628, 0.15163439530878173, 0.15164364942728883, 0.15165290354579594, 0.15166215766430305, 0.1517095319481832, 0.15175690623206337, 0.15180428051594352, 0.1522780233547451, 0.1527517661935467, 0.15322550903234827, 0.15443290055937306, 0.15564029208639785, 0.15684768361342263, 0.15805507514044742, 0.1613347896137119, 0.16461450408697637, 0.16789421856024084, 0.1711739330335053, 0.17445364750676978, 0.17998963487842784, 0.1855256222500859, 0.19106160962174396, 0.196597596993402, 0.20213358436506007, 0.20751149948644282, 0.21288941460782557, 0.21826732972920831, 0.22364524485059106, 0.2290231599719738, 0.23440107509335656, 0.2397902344190082, 0.24517939374465986, 0.2505685530703115, 0.25595771239596316, 0.2613468717216148, 0.2674630060995845, 0.2735791404775542, 0.2796952748555239, 0.28581140923349363, 0.29192754361146334, 0.29804367798943304, 0.3041376787028626, 0.3102316794162922, 0.3163256801297218, 0.32241968084315137, 0.32851368155658095, 0.33460768227001053, 0.3423358010634947, 0.3500639198569789, 0.35779203865046305, 0.3655201574439472, 0.3732482762374314, 0.38097639503091557, 0.3899794614582539, 0.39898252788559224, 0.4079855943129306, 0.4169886607402689, 0.42599172716760725, 0.4349947935949456, 0.44489304717185213, 0.4547913007487587, 0.4646895543256652, 0.47458780790257177, 0.4844860614794783, 0.49438431505638486, 0.5098023143856657, 0.5252203137149465, 0.5406383130442273, 0.556056312373508, 0.5714743117027888, 0.5974625828217441, 0.6234508539406994, 0.6494391250596547, 0.67542739617861, 0.7014156672975653, 0.732534827550596, 0.7636539878036266, 0.7947731480566572, 0.8258923083096879, 0.8570114685627185, 0.9011551207776469, 0.9452987729925754, 0.9894424252075038, 1.0335860774224321, 1.0777297296373605, 1.1218733818522888, 1.1706478605541544, 1.21942233925602, 1.2681968179578855, 1.316971296659751, 1.3657457753616167, 1.4145202540634823, 1.4968669282007638, 1.5792136023380454, 1.661560276475327, 1.7439069506126086, 1.8262536247498902, 1.9086002988871718, 2.0010111177531202, 2.0934219366190687, 2.185832755485017, 2.2782435743509657, 2.370654393216914, 2.4630652120828627, 2.512663995895421, 2.5333674375574033, 2.53881377906041, 2.53969962567208, 2.5401861890305826, 2.540672752389085, 2.5411593157475876, 2.54164587910609, 2.5421324424645926, 2.542619005823095, 2.5432668056786523, 2.5439146055342094, 2.5445624053897666, 2.545210205245324, 2.545858005100881, 2.546505804956438, 2.547728673278379, 2.54895154160032, 2.5501744099222607, 2.5513972782442016, 2.5526201465661424, 2.5559999620575575, 2.5593797775489726, 2.5627595930403877, 2.566139408531803, 2.580559208135905, 2.5949790077400072, 2.6093988073441094, 2.6668009128482106, 2.724203018352312, 2.781605123856413, 2.925891188280965, 3.070177252705517, 3.214463317130069, 3.358749381554621, 3.5424938530483234, 3.7262383245420256, 3.909982796035728, 4.09372726752943, 4.277471739023133, 4.47554842688494, 4.673625114746747, 4.871701802608554, 5.069778490470361, 5.267855178332168, 5.562701235422851, 5.857547292513534, 6.152393349604217, 6.4472394066949, 6.742085463785583, 7.036931520876266, 7.426169385811285, 7.815407250746304, 8.204645115681323, 8.593882980616343, 8.983120845551362, 9.372358710486381, 9.89689087715361, 10.0]</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.6274307264766951</v>
+        <v>0.6274310479795931</v>
       </c>
       <c r="D12" t="n">
         <v>9.81</v>
@@ -1237,13 +1237,13 @@
         <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>6.27430726476695</v>
+        <v>6.274310479795931</v>
       </c>
       <c r="M12" t="n">
-        <v>0.005080406107450482</v>
+        <v>0.005080400900934565</v>
       </c>
       <c r="N12" t="n">
-        <v>0.02540203053725241</v>
+        <v>0.02540200450467283</v>
       </c>
       <c r="O12" t="n">
         <v>19.61895188686585</v>
@@ -1273,11 +1273,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[0.0, 5.942584500521307e-07, 1.1885169001042613e-06, 7.131101400625569e-06, 1.3073685901146876e-05, 3.0862131429607124e-05, 4.865057695806737e-05, 6.643902248652762e-05, 0.00011041193110178897, 0.00015438483971705032, 0.00019835774833231167, 0.0004136311961961234, 0.0006289046440599352, 0.0008441780919237469, 0.0016893399649361525, 0.002534501837948558, 0.0033796637109609635, 0.004412418706631742, 0.005445173702302521, 0.0064779286979733, 0.007510683693644079, 0.009534454051360827, 0.011558224409077575, 0.013581994766794322, 0.01560576512451107, 0.01762953548222782, 0.023132503167290253, 0.028635470852352688, 0.03413843853741512, 0.039641406222477554, 0.04514437390753999, 0.0531960844750011, 0.06124779504246221, 0.06929950560992332, 0.07735121617738443, 0.08540292674484554, 0.09345463731230665, 0.10140971522498142, 0.1093647931376562, 0.11731987105033097, 0.12371573602468237, 0.1301116009990338, 0.1365074659733852, 0.1429033309477366, 0.149299195922088, 0.15591434222501913, 0.16252948852795024, 0.16914463483088135, 0.17575978113381246, 0.18237492743674358, 0.1889900737396747, 0.19499570091993967, 0.20100132810020466, 0.20700695528046964, 0.21301258246073462, 0.2190182096409996, 0.225046991303107, 0.23107577296521442, 0.23710455462732183, 0.24313333628942924, 0.24916211795153664, 0.25519089961364405, 0.2610522411338983, 0.26691358265415255, 0.2727749241744068, 0.27863626569466104, 0.2844976072149153, 0.29035894873516954, 0.2961561068891586, 0.3019532650431477, 0.30775042319713675, 0.3135475813511258, 0.3193447395051149, 0.32514189765910395, 0.3340253613742367, 0.3429088250893695, 0.35179228880450225, 0.360675752519635, 0.3695592162347678, 0.3793364766874348, 0.38911373714010183, 0.39889099759276886, 0.4086682580454359, 0.4184455184981029, 0.42822277895076993, 0.44005393805299925, 0.45188509715522857, 0.4637162562574579, 0.4755474153596872, 0.4873785744619165, 0.49920973356414583, 0.5155736498150107, 0.5319375660658756, 0.5483014823167405, 0.5646653985676053, 0.5810293148184702, 0.6048799020531079, 0.6287304892877457, 0.6525810765223834, 0.6764316637570211, 0.7002822509916589, 0.7348390193295004, 0.7693957876673418, 0.8039525560051833, 0.8385093243430248, 0.8730660926808663, 0.9100112574427247, 0.9469564222045831, 0.9839015869664415, 1.0208467517282998, 1.057791916490158, 1.1182089003772144, 1.178625884264271, 1.2390428681513275, 1.299459852038384, 1.3598768359254405, 1.420293819812497, 1.4869862016035653, 1.5536785833946336, 1.620370965185702, 1.6870633469767702, 1.7537557287678385, 1.854683567348713, 1.9556114059295875, 2.056539244510462, 2.1574670830913365, 2.258394921672211, 2.3593227602530855, 2.487917340524319, 2.6165119207955523, 2.7451065010667857, 2.873701081338019, 3.0022956616092524, 3.130890241880486, 3.278405445644533, 3.4259206494085803, 3.5734358531726276, 3.720951056936675, 3.868466260700722, 4.015981464464769, 4.2508727051924, 4.485763945920031, 4.720655186647662, 4.9555464273752925, 5.190437668102923, 5.425328908830554, 5.708146038727102, 5.990963168623649, 6.2737802985201965, 6.556597428416744, 6.839414558313291, 7.122231688209839, 7.5087365395283, 7.895241390846762, 8.281746242165223, 8.668251093483684, 9.054755944802146, 9.441260796120607, 9.976455220977437, 10.0]</t>
+          <t>[0.0, 1.3288026421795586e-05, 2.657605284359117e-05, 0.00015945631706154703, 0.00029233658127950286, 0.0008301211732592412, 0.0013679057652389796, 0.001905690357218718, 0.003922557648079541, 0.005939424938940363, 0.007956292229801185, 0.013927102695040761, 0.019897913160280337, 0.025868723625519913, 0.031839534090759486, 0.041598562798167, 0.05135759150557452, 0.06111662021298204, 0.07087564892038956, 0.08063467762779708, 0.09139016171443286, 0.10214564580106864, 0.11290112988770441, 0.12365661397434019, 0.13139471780947123, 0.13913282164460228, 0.14687092547973332, 0.1468951070542181, 0.14691928862870288, 0.14694347020318765, 0.14696765177767243, 0.1469918333521572, 0.14701601492664199, 0.14725783067148976, 0.14749964641633753, 0.1477414621611853, 0.14798327790603308, 0.14822509365088085, 0.1500833943910016, 0.15045505453902575, 0.1508267146870499, 0.15119837483507403, 0.15157003498309818, 0.15157475861547753, 0.1515794822478569, 0.15158042697433277, 0.15158137170080865, 0.15158141737463204, 0.15158146304845543, 0.15158150872227882, 0.15158152440194356, 0.1515815400816083, 0.15158154710750843, 0.15158155095443598, 0.1515815523074008, 0.1515815533793691, 0.1515815544513374, 0.15158155552330568, 0.15158155659527398, 0.15158155923494146, 0.15158156187460894, 0.15158156451427643, 0.15158159091095127, 0.15158161730762612, 0.1515818138356348, 0.15158201036364347, 0.1515839756437302, 0.15158594092381691, 0.15159520203915156, 0.1516044631544862, 0.15161372426982084, 0.1516611209368054, 0.15170851760378995, 0.1517559142707745, 0.15222988094062007, 0.15270384761046563, 0.1531778142803112, 0.15438526575387485, 0.1555927172274385, 0.15680016870100216, 0.15800762017456582, 0.1612860904935898, 0.16456456081261378, 0.16784303113163776, 0.17112150145066174, 0.17439997176968572, 0.17993466562140306, 0.1854693594731204, 0.19100405332483775, 0.1965387471765551, 0.20207344102827243, 0.20745115872498196, 0.2128288764216915, 0.21820659411840101, 0.22358431181511054, 0.22896202951182007, 0.2343397472085296, 0.23972892029580892, 0.24511809338308824, 0.2505072664703676, 0.25589643955764696, 0.26128561264492633, 0.2674019290280509, 0.2735182454111754, 0.27963456179429996, 0.2857508781774245, 0.29186719456054905, 0.2979835109436736, 0.3040772026818443, 0.310170894420015, 0.3162645861581857, 0.3223582778963564, 0.3284519696345271, 0.3345456613726978, 0.34227420433778716, 0.3500027473028765, 0.35773129026796585, 0.3654598332330552, 0.37318837619814454, 0.3809169191632339, 0.38991934066214906, 0.39892176216106423, 0.4079241836599794, 0.41692660515889457, 0.42592902665780974, 0.4349314481567249, 0.4448299544078192, 0.4547284606589135, 0.46462696691000777, 0.47452547316110205, 0.48442397941219634, 0.4943224856632906, 0.5097419843488742, 0.5251614830344578, 0.5405809817200413, 0.5560004804056249, 0.5714199790912085, 0.5974077788619611, 0.6233955786327137, 0.6493833784034663, 0.6753711781742189, 0.7013589779449715, 0.7324765594203246, 0.7635941408956778, 0.7947117223710309, 0.8258293038463841, 0.8569468853217372, 0.9010913893240015, 0.9452358933262657, 0.9893803973285299, 1.033524901330794, 1.0776694053330584, 1.1218139093353228, 1.1705852030006636, 1.2193564966660044, 1.2681277903313453, 1.316899083996686, 1.365670377662027, 1.4144416713273678, 1.496789186908459, 1.5791367024895504, 1.6614842180706417, 1.743831733651733, 1.8261792492328244, 1.9085267648139157, 2.000934974867846, 2.0933431849217765, 2.185751394975707, 2.2781596050296375, 2.282355295116473, 2.284091555517471, 2.2848375485012853, 2.285253945651026, 2.2856703428007665, 2.286086739950507, 2.2865031371002478, 2.2869195342499884, 2.287335931399729, 2.2878962402108756, 2.288456549022022, 2.2890168578331687, 2.289577166644315, 2.2901374754554618, 2.2906977842666083, 2.291737866776737, 2.2927779492868656, 2.2938180317969943, 2.294858114307123, 2.2958981968172516, 2.298790791245703, 2.3016833856741545, 2.304575980102606, 2.3074685745310575, 2.3199509817235957, 2.332433388916134, 2.344915796108672, 2.395389012476214, 2.445862228843756, 2.496335445211298, 2.610251541941503, 2.7241676386717084, 2.8380837354019137, 2.951999832132119, 3.0971386133834673, 3.2422773946348156, 3.387416175886164, 3.532554957137512, 3.6776937383888604, 3.8913241102700145, 4.104954482151168, 4.318584854032322, 4.532215225913475, 4.745845597794629, 4.959475969675783, 5.2024296403199655, 5.445383310964148, 5.688336981608331, 5.931290652252514, 6.174244322896697, 6.41719799354088, 6.777210979902043, 7.137223966263207, 7.4972369526243705, 7.857249938985534, 8.217262925346699, 8.577275911707863, 9.03613991883783, 9.495003925967795, 9.953867933097762, 10.0]</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.6271392160900274</v>
+        <v>0.6271394035823543</v>
       </c>
       <c r="D13" t="n">
         <v>9.81</v>
@@ -1304,13 +1304,13 @@
         <v>2</v>
       </c>
       <c r="L13" t="n">
-        <v>6.271392160900274</v>
+        <v>6.271394035823543</v>
       </c>
       <c r="M13" t="n">
-        <v>0.005085130211165047</v>
+        <v>0.00508512717062016</v>
       </c>
       <c r="N13" t="n">
-        <v>0.02542565105582523</v>
+        <v>0.0254256358531008</v>
       </c>
       <c r="O13" t="n">
         <v>19.61867428863441</v>
@@ -1340,11 +1340,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[0.0, 5.942637672001492e-07, 1.1885275344002983e-06, 7.13116520640179e-06, 1.3073802878403282e-05, 3.0862407921206894e-05, 4.8651012964010506e-05, 6.643961800681412e-05, 0.00011041293369780844, 0.00015438624938880275, 0.00019835956507979706, 0.0004136425366476901, 0.0006289255082155831, 0.0008442084797834761, 0.0016878683318436263, 0.0025315281839037767, 0.003375188035963927, 0.004407540361768098, 0.005439892687572268, 0.006472245013376439, 0.007504597339180609, 0.009529690768076185, 0.01155478419697176, 0.013579877625867336, 0.015604971054762912, 0.01763006448365849, 0.023132828214330013, 0.028635591945001537, 0.03413835567567306, 0.039641119406344585, 0.04514388313701611, 0.053199265215676264, 0.06125464729433642, 0.06931002937299657, 0.07736541145165673, 0.0854207935303169, 0.09347617560897706, 0.10142274936026323, 0.1093693231115494, 0.11731589686283557, 0.12370886163024221, 0.13010182639764883, 0.13649479116505547, 0.1428877559324621, 0.14928072069986875, 0.15589494811598378, 0.16250917553209882, 0.16912340294821385, 0.17573763036432888, 0.1823518577804439, 0.18896608519655894, 0.1949675157651727, 0.20096894633378648, 0.20697037690240025, 0.21297180747101402, 0.2189732380396278, 0.22499478456551097, 0.23101633109139416, 0.23703787761727735, 0.24305942414316054, 0.24908097066904372, 0.25510251719492694, 0.2609651675705683, 0.2668278179462097, 0.27269046832185106, 0.27855311869749244, 0.2844157690731338, 0.2902784194487752, 0.29607432413021534, 0.3018702288116555, 0.30766613349309563, 0.3134620381745358, 0.3192579428559759, 0.32505384753741606, 0.3339327320761989, 0.3428116166149817, 0.35169050115376455, 0.3605693856925474, 0.3694482702313302, 0.3792256136652968, 0.38900295709926336, 0.39878030053322994, 0.4085576439671965, 0.4183349874011631, 0.4281123308351297, 0.43994044554357453, 0.4517685602520194, 0.46359667496046425, 0.4754247896689091, 0.48725290437735397, 0.4990810190857988, 0.5154436668739836, 0.5318063146621683, 0.5481689624503531, 0.5645316102385378, 0.5808942580267226, 0.60474127514624, 0.6285882922657574, 0.6524353093852748, 0.6762823265047923, 0.7001293436243097, 0.7346796233948168, 0.769229903165324, 0.8037801829358312, 0.8383304627063384, 0.8728807424768456, 0.9098183832391178, 0.94675602400139, 0.9836936647636623, 1.0206313055259346, 1.057568946288207, 1.1179745396382668, 1.1783801329883266, 1.2387857263383864, 1.2991913196884461, 1.359596913038506, 1.4200025063885657, 1.4866815382040937, 1.5533605700196216, 1.6200396018351495, 1.6867186336506774, 1.7533976654662053, 1.854305533822971, 1.9552134021797367, 2.0561212705365026, 2.1570291388932685, 2.2579370072500344, 2.3588448756068003, 2.4874141169728627, 2.615983358338925, 2.7445525997049875, 2.87312184107105, 3.0016910824371124, 3.1302603238031748, 3.2777467240404827, 3.4252331242777907, 3.5727195245150987, 3.7202059247524066, 3.8676923249897146, 4.015178725227022, 4.250024016113912, 4.484869307000801, 4.719714597887691, 4.954559888774581, 5.18940517966147, 5.42425047054836, 5.70701345324849, 5.98977643594862, 6.27253941864875, 6.5553024013488805, 6.838065384049011, 7.120828366749141, 7.50725945336041, 7.893690539971679, 8.280121626582948, 8.666552713194218, 9.052983799805487, 9.439414886416756, 9.974502396105677, 10.0]</t>
+          <t>[0.0, 1.328814533338145e-05, 2.65762906667629e-05, 0.0001594577440005774, 0.0002923391973343919, 0.0008297176732942658, 0.0013670961492541398, 0.0019044746252140138, 0.0039188578635002995, 0.005933241101786585, 0.00794762434007287, 0.013914295536403921, 0.019880966732734973, 0.025847637929066025, 0.03181430912539708, 0.04156801463574886, 0.05132172014610063, 0.06107542565645241, 0.07082913116680419, 0.08058283667715596, 0.0913364163006894, 0.10208999592422283, 0.11284357554775626, 0.12359715517128969, 0.13133311599273928, 0.13906907681418887, 0.14680503763563846, 0.1468292125132055, 0.14685338739077253, 0.14687756226833956, 0.1469017371459066, 0.14692591202347363, 0.14695008690104067, 0.147191835676711, 0.14743358445238136, 0.1476753332280517, 0.14791708200372206, 0.1481588307793924, 0.14999074743088325, 0.15035713076118143, 0.1507235140914796, 0.15108989742177778, 0.15145628075207596, 0.1514794610855333, 0.15150264141899067, 0.15150727748568213, 0.1515119135523736, 0.15151654961906505, 0.15151747683240335, 0.15151840404574166, 0.15151933125907996, 0.15152025847241826, 0.15152033264948533, 0.1515204068265524, 0.15152040762658653, 0.1515204082560828, 0.15152040888557905, 0.1515204095150753, 0.15152041054882287, 0.15152041158257043, 0.15152042192004603, 0.15152043225752163, 0.1515205356322776, 0.15152063900703358, 0.15152167275459336, 0.15152270650215313, 0.1515293882425961, 0.15153606998303906, 0.15154275172348203, 0.1515845960597807, 0.15162644039607936, 0.15166828473237803, 0.15208672809536472, 0.1525051714583514, 0.1529236148213381, 0.15406206532691566, 0.15520051583249322, 0.1563389663380708, 0.15747741684364835, 0.16070805576175262, 0.1639386946798569, 0.16716933359796116, 0.17039997251606542, 0.1736306114341697, 0.1791875627346952, 0.18474451403522069, 0.19030146533574618, 0.19585841663627168, 0.20141536793679718, 0.20676018174250083, 0.21210499554820447, 0.21744980935390812, 0.22279462315961177, 0.2281394369653154, 0.23348425077101906, 0.23878964371836203, 0.244095036665705, 0.24940042961304798, 0.254705822560391, 0.260011215507734, 0.26598357354421953, 0.2719559315807051, 0.2779282896171906, 0.2839006476536762, 0.2898730056901617, 0.29584536372664727, 0.3019273760728493, 0.30800938841905134, 0.3140914007652534, 0.3201734131114554, 0.32625542545765746, 0.3323374378038595, 0.34014842835944575, 0.347959418915032, 0.3557704094706183, 0.36358140002620454, 0.3713923905817908, 0.37914451613674016, 0.3868966416916895, 0.3946487672466389, 0.40240089280158825, 0.4101530183565376, 0.417905143911487, 0.4288715124624724, 0.43983788101345783, 0.45080424956444326, 0.4617706181154287, 0.4727369866664141, 0.48370335521739954, 0.499411653102791, 0.5151199509881825, 0.530828248873574, 0.5465365467589656, 0.5622448446443571, 0.5779531425297486, 0.601472366146831, 0.6249915897639133, 0.6485108133809957, 0.6720300369980781, 0.6955492606151604, 0.7237259095251382, 0.7519025584351159, 0.7800792073450936, 0.8082558562550713, 0.8364325051650491, 0.8796759684064877, 0.9229194316479262, 0.9661628948893648, 1.0094063581308035, 1.0526498213722422, 1.1075995860318177, 1.1625493506913933, 1.2174991153509689, 1.2724488800105445, 1.32739864467012, 1.3823484093296956, 1.441897437802962, 1.5014464662762286, 1.560995494749495, 1.6205445232227615, 1.680093551696028, 1.7684824293047303, 1.8568713069134326, 1.945260184522135, 2.033649062130837, 2.0476214161865496, 2.0545580000404664, 2.055233362055229, 2.0556090359623624, 2.0559847098694957, 2.056360383776629, 2.056736057683762, 2.0571117315908953, 2.0574874054980286, 2.057991753976069, 2.0584961024541095, 2.05900045093215, 2.0595047994101905, 2.060009147888231, 2.0605134963662715, 2.061453021752053, 2.062392547137834, 2.0633320725236155, 2.064271597909397, 2.065211123295178, 2.067820629506276, 2.070430135717374, 2.0730396419284722, 2.0756491481395702, 2.0868842256088103, 2.0981193030780503, 2.1093543805472903, 2.154648403793153, 2.1999424270390158, 2.2452364502848785, 2.3457497766351683, 2.446263102985458, 2.5467764293357478, 2.6472897556860375, 2.786756897771112, 2.9262240398561867, 3.0656911819412613, 3.205158324026336, 3.3446254661114105, 3.5289688760688054, 3.7133122860262002, 3.897655695983595, 4.08199910594099, 4.266342515898385, 4.464783547928106, 4.663224579957827, 4.861665611987548, 5.060106644017269, 5.25854767604699, 5.456988708076711, 5.785927255294967, 6.114865802513224, 6.44380434973148, 6.772742896949737, 7.101681444167993, 7.43061999138625, 7.823164740413569, 8.215709489440888, 8.608254238468207, 9.000798987495527, 9.393343736522846, 9.785888485550165, 10.0]</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6267714562091956</v>
+        <v>0.6267719816498798</v>
       </c>
       <c r="D14" t="n">
         <v>9.81</v>
@@ -1371,13 +1371,13 @@
         <v>2</v>
       </c>
       <c r="L14" t="n">
-        <v>6.267714562091956</v>
+        <v>6.267719816498798</v>
       </c>
       <c r="M14" t="n">
-        <v>0.005091099390224257</v>
+        <v>0.005091090854202534</v>
       </c>
       <c r="N14" t="n">
-        <v>0.02545549695112129</v>
+        <v>0.02545545427101267</v>
       </c>
       <c r="O14" t="n">
         <v>19.61832316706319</v>
@@ -1407,11 +1407,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[0.0, 5.942704928244625e-07, 1.188540985648925e-06, 7.13124591389355e-06, 1.3073950842138175e-05, 3.086275765355432e-05, 4.8651564464970464e-05, 6.644037127638661e-05, 0.00011041420187492108, 0.00015438803247345555, 0.00019836186307199002, 0.0004136568827420112, 0.0006289519024120324, 0.0008442469220820535, 0.0016860222493675007, 0.002527797576652948, 0.0033695729039383954, 0.004401421274911052, 0.005433269645883709, 0.006465118016856365, 0.007496966387829021, 0.009523739764058322, 0.011550513140287622, 0.013577286516516922, 0.015604059892746222, 0.01763083326897552, 0.023133389819421406, 0.028635946369867292, 0.034138502920313174, 0.039641059470759056, 0.04514361602120494, 0.05320368912892416, 0.061263762236643385, 0.06932383534436261, 0.07738390845208183, 0.08544398155980105, 0.09350405466752028, 0.10143990125220309, 0.1093757478368859, 0.11731159442156872, 0.12370070493308874, 0.13008981544460876, 0.1364789259561288, 0.1428680364676488, 0.14925714697916884, 0.15587231495463738, 0.16248748293010593, 0.16910265090557447, 0.17571781888104301, 0.18233298685651156, 0.1889481548319801, 0.19494429893557205, 0.200940443039164, 0.20693658714275595, 0.2129327312463479, 0.21892887534993985, 0.2249367777121689, 0.23094468007439797, 0.23695258243662704, 0.2429604847988561, 0.24896838716108516, 0.2549762895233142, 0.26084277524226673, 0.2667092609612193, 0.2725757466801718, 0.27844223239912436, 0.2843087181180769, 0.29017520383702944, 0.29596969203881757, 0.3017641802406057, 0.3075586684423938, 0.31335315664418195, 0.3191476448459701, 0.3249421330477582, 0.33381667753552124, 0.3426912220232843, 0.3515657665110473, 0.36044031099881035, 0.3693148554865734, 0.37908974477723045, 0.3888646340678875, 0.3986395233585446, 0.40841441264920164, 0.4181893019398587, 0.42796419123051577, 0.4397896889607187, 0.4516151866909216, 0.4634406844211245, 0.47526618215132743, 0.48709167988153035, 0.49891717761173326, 0.5152763295218917, 0.5316354814320502, 0.5479946333422087, 0.5643537852523671, 0.5807129371625256, 0.6045531507445571, 0.6283933643265885, 0.65223357790862, 0.6760737914906515, 0.699914005072683, 0.734454216974251, 0.7689944288758189, 0.8035346407773869, 0.8380748526789549, 0.8726150645805228, 0.9095418439591773, 0.9464686233378317, 0.9833954027164861, 1.0203221820951405, 1.0572489614737948, 1.1176364666980176, 1.1780239719222405, 1.2384114771464634, 1.2987989823706863, 1.3591864875949091, 1.419573992819132, 1.486233071709133, 1.552892150599134, 1.619551229489135, 1.686210308379136, 1.752869387269137, 1.8537476647795348, 1.9546259422899326, 2.0555042198003304, 2.1563824973107284, 2.2572607748211264, 2.3581390523315244, 2.4866701899173056, 2.6152013275030868, 2.743732465088868, 2.872263602674649, 3.0007947402604302, 3.1293258778462114, 3.276769099916204, 3.4242123219861966, 3.5716555440561892, 3.719098766126182, 3.8665419881961745, 4.013985210266167, 4.248761538967815, 4.4835378676694635, 4.718314196371112, 4.95309052507276, 5.187866853774408, 5.422643182476056, 5.705324358169977, 5.988005533863898, 6.270686709557819, 6.55336788525174, 6.836049060945661, 7.118730236639582, 7.505049654876734, 7.891369073113886, 8.277688491351038, 8.66400790958819, 9.050327327825341, 9.436646746062493, 9.97157295669432, 10.0]</t>
+          <t>[0.0, 1.3288295743893842e-05, 2.6576591487787685e-05, 0.0001594595489267261, 0.00029234250636566453, 0.0008292090069883019, 0.0013660755076109392, 0.0019029420082335765, 0.003914193586025098, 0.00592544516381662, 0.007936696741608141, 0.013898157641895975, 0.019859618542183807, 0.02582107944247164, 0.03178254034275947, 0.041529520835489594, 0.05127650132821972, 0.06102348182094984, 0.07077046231367996, 0.08051744280641009, 0.09126855218492799, 0.1020196615634459, 0.1127707709419638, 0.12352188032048171, 0.13125560396741395, 0.13898932761434618, 0.1467230512612784, 0.14674721914767508, 0.14677138703407175, 0.14679555492046842, 0.1468197228068651, 0.14684389069326176, 0.14686805857965843, 0.14710973744362513, 0.14735141630759183, 0.14759309517155852, 0.14783477403552522, 0.14807645289949192, 0.14992926148454278, 0.15029982320155294, 0.1506703849185631, 0.15104094663557327, 0.15141150835258343, 0.15143503765784455, 0.15143974351889677, 0.15144068469110722, 0.15144162586331766, 0.1514425670355281, 0.1514427552699702, 0.1514429435044123, 0.15144313173885438, 0.1514431773207461, 0.15144322290263784, 0.15144326848452958, 0.15144328415374134, 0.1514432998229531, 0.15144330227548222, 0.15144330363175032, 0.15144330470659573, 0.15144330578144113, 0.15144330685628654, 0.15144330793113195, 0.151443310578271, 0.15144331322541008, 0.15144331587254914, 0.15144334234393977, 0.1514433688153304, 0.1514435659239226, 0.1514437630325148, 0.1514457341184368, 0.15144770520435877, 0.15145698542000272, 0.15146626563564666, 0.1514755458512906, 0.15152300534610733, 0.15157046484092404, 0.15161792433574076, 0.1520925192839079, 0.15256711423207506, 0.1530417091802422, 0.15424931841679748, 0.15545692765335276, 0.15666453688990803, 0.1578721461264633, 0.1611470652972357, 0.16442198446800807, 0.16769690363878045, 0.17097182280955284, 0.17424674198032522, 0.17977774949552602, 0.18530875701072683, 0.19083976452592763, 0.19637077204112843, 0.20190177955632924, 0.20727893463792507, 0.2126560897195209, 0.21803324480111674, 0.22341039988271258, 0.22878755496430841, 0.23416471004590425, 0.2395539181896367, 0.24494312633336915, 0.25033233447710157, 0.255721542620834, 0.26111075076456647, 0.26722757912927375, 0.27334440749398103, 0.2794612358586883, 0.2855780642233956, 0.2916948925881029, 0.29781172095281017, 0.30390453370670334, 0.3099973464605965, 0.3160901592144897, 0.32218297196838286, 0.32827578472227603, 0.3343685974761692, 0.3420983446522231, 0.349828091828277, 0.3575578390043309, 0.3652875861803848, 0.3730173333564387, 0.3807470805324926, 0.38974767012628003, 0.39874825972006744, 0.40774884931385486, 0.41674943890764227, 0.4257500285014297, 0.4347506180952171, 0.44464984418796566, 0.45454907028071423, 0.4644482963734628, 0.47434752246621137, 0.48424674855895994, 0.4941459746517085, 0.5095697388416092, 0.5249935030315098, 0.5404172672214105, 0.5558410314113111, 0.5712647956012118, 0.5972512231660964, 0.6232376507309809, 0.6492240782958655, 0.67521050586075, 0.7011969334256346, 0.7323099969008335, 0.7634230603760325, 0.7945361238512314, 0.8256491873264303, 0.8567622508016293, 0.9009091415430397, 0.9450560322844501, 0.9892029230258605, 1.033349813767271, 1.0774967045086814, 1.1216435952500918, 1.1704057889136026, 1.2191679825771133, 1.267930176240624, 1.3166923699041349, 1.3654545635676456, 1.4142167572311564, 1.4965665692675827, 1.578916381304009, 1.6612661933404353, 1.7436160053768617, 1.825965817413288, 1.838812482775397, 1.8451578155079653, 1.8486834863318558, 1.849453675106718, 1.8500618623294582, 1.8503995034991791, 1.8507371446689, 1.851074785838621, 1.8514124270083419, 1.8517500681780628, 1.8520877093477837, 1.8525404051090992, 1.8529931008704148, 1.8534457966317304, 1.853898492393046, 1.8543511881543615, 1.854803883915677, 1.8556489072278068, 1.8564939305399366, 1.8573389538520664, 1.8581839771641961, 1.859029000476326, 1.8613742474144206, 1.8637194943525153, 1.86606474129061, 1.8684099882287046, 1.87849377763163, 1.8885775670345553, 1.8986613564374806, 1.9391833715283753, 1.97970538661927, 2.020227401710165, 2.1153999352988673, 2.2105724688875696, 2.305745002476272, 2.4009175360649744, 2.506145648390978, 2.6113737607169814, 2.716601873042985, 2.8218299853689883, 2.927058097694992, 3.1000933381002462, 3.2731285785055007, 3.446163818910755, 3.6191990593160095, 3.792234299721264, 3.9652695401265183, 4.188635954133672, 4.412002368140826, 4.635368782147979, 4.858735196155132, 5.082101610162286, 5.305468024169439, 5.611761001123764, 5.918053978078088, 6.224346955032413, 6.530639931986737, 6.836932908941062, 7.1432258858953865, 7.560147439503732, 7.977068993112077, 8.393990546720422, 8.810912100328768, 9.227833653937113, 9.644755207545458, 10.0]</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.6263078174142976</v>
+        <v>0.6263077739643857</v>
       </c>
       <c r="D15" t="n">
         <v>9.81</v>
@@ -1438,13 +1438,13 @@
         <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>6.263078174142976</v>
+        <v>6.263077739643857</v>
       </c>
       <c r="M15" t="n">
-        <v>0.005098639787460646</v>
+        <v>0.005098640494893849</v>
       </c>
       <c r="N15" t="n">
-        <v>0.02549319893730323</v>
+        <v>0.02549320247446924</v>
       </c>
       <c r="O15" t="n">
         <v>19.61787904911208</v>
@@ -1474,11 +1474,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[0.0, 5.942790000884973e-07, 1.1885580001769946e-06, 7.131348001061967e-06, 1.307413800194694e-05, 3.086320003114589e-05, 4.865226206034484e-05, 6.644132408954379e-05, 0.00011041580599665126, 0.00015439028790375874, 0.00019836476981086623, 0.00041367503177989985, 0.0006289852937489335, 0.0008442955557179671, 0.0016837113435611798, 0.0025231271314043926, 0.0033625429192476056, 0.004393762313354324, 0.005424981707461043, 0.006456201101567761, 0.00748742049567448, 0.009516329112996047, 0.011545237730317615, 0.013574146347639184, 0.015603054964960752, 0.01763196358228232, 0.023134338328118714, 0.028636713073955107, 0.0341390878197915, 0.03964146256562789, 0.04514383731146428, 0.053209932612646935, 0.06127602791382959, 0.06934212321501225, 0.07740821851619491, 0.08547431381737756, 0.09354040911856022, 0.10146272959019667, 0.10938505006183312, 0.11730737053346957, 0.12369172190223544, 0.13007607327100132, 0.1364604246397672, 0.1428447760085331, 0.149229127377299, 0.1558443435276413, 0.1624595596779836, 0.1690747758283259, 0.1756899919786682, 0.1823052081290105, 0.1889204242793528, 0.19490961160169748, 0.20089879892404217, 0.20688798624638685, 0.21287717356873154, 0.21886636089107622, 0.22485937449550158, 0.23085238809992695, 0.2368454017043523, 0.24283841530877767, 0.24883142891320303, 0.25482444251762837, 0.2606944951557817, 0.266564547793935, 0.27243460043208834, 0.27830465307024166, 0.284174705708395, 0.2900447583465483, 0.2958373629578382, 0.3016299675691281, 0.30742257218041796, 0.31321517679170785, 0.31900778140299774, 0.3248003860142876, 0.33366913499398293, 0.34253788397367824, 0.35140663295337354, 0.36027538193306885, 0.36914413091276416, 0.37891749601027613, 0.3886908611077881, 0.3984642262053001, 0.40823759130281206, 0.41801095640032404, 0.427784321497836, 0.4396060167171285, 0.451427711936421, 0.4632494071557135, 0.475071102375006, 0.4868927975942985, 0.498714492813591, 0.5150705192047365, 0.531426545595882, 0.5477825719870275, 0.564138598378173, 0.5804946247693186, 0.604327776637123, 0.6281609285049274, 0.6519940803727319, 0.6758272322405363, 0.6996603841083407, 0.7341892562710167, 0.7687181284336927, 0.8032470005963687, 0.8377758727590446, 0.8723047449217206, 0.9092189142955618, 0.946133083669403, 0.9830472530432441, 1.0199614224170852, 1.0568755917909263, 1.1172427525417674, 1.1776099132926086, 1.2379770740434497, 1.2983442347942908, 1.358711395545132, 1.4190785562959731, 1.485714790112642, 1.5523510239293108, 1.6189872577459796, 1.6856234915626485, 1.7522597253793173, 1.8531040467379862, 1.9539483680966552, 2.054792689455324, 2.155637010813993, 2.256481332172662, 2.3573256535313307, 2.4858132811264073, 2.614300908721484, 2.7427885363165605, 2.871276163911637, 2.9997637915067137, 3.1282514191017903, 3.275645274254631, 3.4230391294074716, 3.570432984560312, 3.717826839713153, 3.8652206948659935, 4.012614550018834, 4.247312080940791, 4.482009611862748, 4.7167071427847045, 4.951404673706661, 5.186102204628618, 5.420799735550575, 5.703387755289615, 5.985975775028655, 6.2685637947676955, 6.551151814506736, 6.833739834245776, 7.116327853984816, 7.502520264982358, 7.8887126759799004, 8.274905086977443, 8.661097497974986, 9.047289908972528, 9.433482319970071, 9.968224735933836, 10.0]</t>
+          <t>[0.0, 1.3288485998731162e-05, 2.6576971997462323e-05, 0.00015946183198477395, 0.00029234669197208556, 0.0008285683112541384, 0.0013647899305361912, 0.001901011549818244, 0.003908318392069244, 0.0059156252343202445, 0.007922932076571245, 0.013877841154692094, 0.019832750232812946, 0.025787659310933797, 0.03174256838905465, 0.041481077277769896, 0.05121958616648514, 0.06095809505520039, 0.07069660394391564, 0.08043511283263088, 0.09118314495468696, 0.10193117707674304, 0.11267920919879912, 0.1234272413208552, 0.1311579537711021, 0.138888666221349, 0.14661937867159588, 0.14664353714800293, 0.14666769562440998, 0.14669185410081703, 0.14671601257722408, 0.14674017105363113, 0.14676432953003818, 0.14700591429410867, 0.14724749905817916, 0.14748908382224965, 0.14773066858632014, 0.14797225335039063, 0.1498300738953304, 0.15020163800431835, 0.1505732021133063, 0.15094476622229425, 0.1513163303312822, 0.15133994549060992, 0.15134466852247547, 0.1513456131288486, 0.1513458020501232, 0.15134599097139784, 0.15134603670566213, 0.15134608243992642, 0.1513461281741907, 0.15134614389209974, 0.15134615094105397, 0.15134615230080328, 0.15134615337836227, 0.15134615445592126, 0.15134615553348024, 0.15134615661103923, 0.15134615926479408, 0.15134616191854894, 0.1513461645723038, 0.15134619110985234, 0.1513462176474009, 0.15134641524363904, 0.1513466128398772, 0.15134858880225868, 0.15135056476464018, 0.15135985999275464, 0.1513691552208691, 0.15137845044898357, 0.15142595626386984, 0.15147346207875612, 0.1515209678936424, 0.15199602604250512, 0.15247108419136784, 0.15294614234023057, 0.15415388828682536, 0.15536163423342014, 0.15656938018001493, 0.1577771261266097, 0.16104957417168408, 0.16432202221675846, 0.16759447026183283, 0.1708669183069072, 0.17413936635198157, 0.1796677745564884, 0.18519618276099525, 0.1907245909655021, 0.19625299917000893, 0.20178140737451578, 0.2071581837849798, 0.21253496019544382, 0.21791173660590785, 0.22328851301637187, 0.2286652894268359, 0.23404206583729992, 0.23943134361736737, 0.24482062139743482, 0.25020989917750225, 0.2555991769575697, 0.2609884547376371, 0.26710572306528413, 0.27322299139293116, 0.2793402597205782, 0.2854575280482252, 0.29157479637587225, 0.2976920647035193, 0.30378426952443127, 0.30987647434534327, 0.31596867916625526, 0.32206088398716726, 0.32815308880807925, 0.33424529362899125, 0.34197598008288166, 0.34970666653677207, 0.3574373529906625, 0.3651680394445529, 0.3728987258984433, 0.3806294123523337, 0.38962871570277435, 0.398628019053215, 0.4076273224036556, 0.41662662575409626, 0.4256259291045369, 0.43462523245497753, 0.44452503447250746, 0.4544248364900374, 0.46432463850756733, 0.47422444052509727, 0.4841242425426272, 0.49402404456015714, 0.5094510071435031, 0.5248779697268491, 0.540304932310195, 0.555731894893541, 0.571158857476887, 0.5971445420860523, 0.6231302266952176, 0.6491159113043828, 0.6751015959135481, 0.7010872805227134, 0.7321973915008266, 0.7633075024789399, 0.7944176134570531, 0.8255277244351663, 0.8566378354132795, 0.9007869044284953, 0.944935973443711, 0.9890850424589268, 1.0332341114741426, 1.0773831804893583, 1.121532249504574, 1.1702883554506762, 1.2190444613967784, 1.2678005673428805, 1.3165566732889826, 1.3653127792350848, 1.414068885181187, 1.4964212073246588, 1.5787735294681307, 1.6199496905398667, 1.6611258516116028, 1.6651804493904387, 1.6656662952518464, 1.6660085464681644, 1.6663507976844825, 1.6666930489008005, 1.6670353001171185, 1.6673775513334366, 1.6677198025497546, 1.6682172798438393, 1.668714757137924, 1.6692122344320086, 1.6697097117260933, 1.670207189020178, 1.6707046663142626, 1.6714486896047367, 1.6721927128952108, 1.6729367361856848, 1.673680759476159, 1.674424782766633, 1.67638272233638, 1.6783406619061272, 1.6802986014758743, 1.6822565410456214, 1.6930276911697146, 1.7037988412938079, 1.7145699914179011, 1.7531767193184025, 1.7917834472189038, 1.8303901751194052, 1.9132145557670879, 1.9960389364147706, 2.0788633170624533, 2.161687697710136, 2.27185764559683, 2.382027593483524, 2.492197541370218, 2.602367489256912, 2.712537437143606, 2.8371328146003165, 2.961728192057027, 3.0863235695137377, 3.210918946970448, 3.335514324427159, 3.4601097018838693, 3.6633786950869216, 3.866647688289974, 4.0699166814930265, 4.273185674696079, 4.476454667899132, 4.679723661102185, 4.921716132163381, 5.163708603224577, 5.405701074285773, 5.647693545346969, 5.889686016408165, 6.131678487469361, 6.4627609536430315, 6.793843419816702, 7.124925885990373, 7.4560083521640435, 7.787090818337714, 8.118173284511386, 8.574281702634819, 9.030390120758252, 9.486498538881685, 9.942606957005118, 10.0]</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.6257238035141243</v>
+        <v>0.6257239630099057</v>
       </c>
       <c r="D16" t="n">
         <v>9.81</v>
@@ -1505,13 +1505,13 @@
         <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>6.257238035141242</v>
+        <v>6.257239630099057</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0051081617717145</v>
+        <v>0.005108159167594478</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0255408088585725</v>
+        <v>0.02554079583797239</v>
       </c>
       <c r="O16" t="n">
         <v>19.61731730420472</v>
@@ -1541,11 +1541,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[0.0, 5.942897610626422e-07, 1.1885795221252844e-06, 7.131477132751707e-06, 1.307437474337813e-05, 3.086375960164175e-05, 4.865314445990537e-05, 6.644252931816899e-05, 0.00011041783507645372, 0.00015439314083473844, 0.00019836844659302318, 0.0004136979929749022, 0.0006290275393567812, 0.0008443570857386603, 0.0016808262056964437, 0.002517295325654227, 0.00335376444561201, 0.004384201543432314, 0.005414638641252618, 0.006445075739072922, 0.007475512836893227, 0.009507138838365046, 0.011538764839836865, 0.013570390841308684, 0.015602016842780503, 0.017633642844252322, 0.023135913411315677, 0.02863818397837903, 0.034140454545442386, 0.039642725112505744, 0.0451449956795691, 0.05321884731716068, 0.061292698954752256, 0.06936655059234384, 0.07744040222993542, 0.08551425386752701, 0.09358810550511859, 0.1014933887027156, 0.1093986719003126, 0.11730395509790961, 0.12368238286140135, 0.13006081062489308, 0.13643923838838481, 0.14281766615187655, 0.14919609391536828, 0.1558104708394862, 0.16242484776360414, 0.16903922468772206, 0.17565360161184, 0.18226797853595791, 0.18888235546007584, 0.19486239760366958, 0.20084243974726332, 0.20682248189085706, 0.2128025240344508, 0.21878256617804454, 0.22475873019264225, 0.23073489420723997, 0.2367110582218377, 0.2426872222364354, 0.24866338625103312, 0.25463955026563084, 0.26051305489897836, 0.2663865595323259, 0.2722600641656734, 0.2781335687990209, 0.2840070734323684, 0.28988057806571593, 0.295670750243918, 0.30146092242212, 0.30725109460032207, 0.3130412667785241, 0.31883143895672617, 0.3246216111349282, 0.3334827064947573, 0.3423438018545864, 0.3512048972144155, 0.3600659925742446, 0.3689270879340737, 0.37869973853009686, 0.38847238912612003, 0.3982450397221432, 0.40801769031816637, 0.41779034091418954, 0.4275629915102127, 0.43937948900266827, 0.4511959864951238, 0.4630124839875794, 0.47482898148003494, 0.4866454789724905, 0.49846197646494605, 0.514815042648103, 0.5311681088312599, 0.5475211750144168, 0.5638742411975737, 0.5802273073807306, 0.6040527180747886, 0.6278781287688465, 0.6517035394629045, 0.6755289501569625, 0.6993543608510204, 0.7338699732462007, 0.768385585641381, 0.8029011980365613, 0.8374168104317417, 0.871932422826922, 0.9088315217462293, 0.9457306206655366, 0.9826297195848439, 1.0195288185041513, 1.0564279174234588, 1.1167713166184596, 1.1771147158134605, 1.2374581150084614, 1.2978015142034622, 1.358144913398463, 1.418488312593464, 1.4850975114108327, 1.5517067102282014, 1.61831590904557, 1.6849251078629388, 1.7515343066803075, 1.85233835834095, 1.9531424100015926, 2.0539464616622354, 2.1547505133228784, 2.2555545649835214, 2.3563586166441643, 2.484794842238503, 2.6132310678328414, 2.74166729342718, 2.8701035190215185, 2.998539744615857, 3.1269759702101956, 3.2743114492597845, 3.4216469283093733, 3.568982407358962, 3.716317886408551, 3.86365336545814, 4.010988844507729, 4.245593236855971, 4.480197629204213, 4.714802021552455, 4.949406413900697, 5.1840108062489385, 5.41861519859718, 5.701093372679198, 5.983571546761215, 6.266049720843233, 6.54852789492525, 6.831006069007268, 7.113484243089285, 7.499527022211169, 7.8855698013330535, 8.271612580454939, 8.657655359576824, 9.043698138698709, 9.429740917820594, 9.964266511957172, 10.0]</t>
+          <t>[0.0, 1.3288726655260171e-05, 2.6577453310520343e-05, 0.00015946471986312205, 0.0002923519864157238, 0.0008277622026316791, 0.0013631724188476345, 0.0018985826350635898, 0.0039009260059951895, 0.005903269376926789, 0.00790561274785839, 0.013852295503117394, 0.0197989782583764, 0.0257456610136354, 0.031692343768894404, 0.04142019244831004, 0.05114804112772568, 0.06087588980714132, 0.07060373848655696, 0.0803315871659726, 0.09107579066391538, 0.10181999416185816, 0.11256419765980094, 0.12330840115774372, 0.13103503747334314, 0.13876167378894255, 0.14648831010454197, 0.14651245584302824, 0.14653660158151452, 0.1465607473200008, 0.14658489305848707, 0.14660903879697335, 0.14663318453545962, 0.14687464192032237, 0.14711609930518513, 0.14735755669004788, 0.14759901407491063, 0.1478404714597734, 0.14967180857861795, 0.15003807600238686, 0.15040434342615577, 0.15077061084992469, 0.1511368782736936, 0.15116005518052228, 0.15118323208735096, 0.15120640899417964, 0.1512110443755454, 0.15121567975691114, 0.15122031513827688, 0.15122124221455002, 0.15122216929082316, 0.1512230963670963, 0.15122328178235092, 0.15122346719760554, 0.15122365261286017, 0.1512238380281148, 0.15122385286133516, 0.15122385728472365, 0.15122386170811214, 0.15122386368154841, 0.1512238644862656, 0.15122386511975822, 0.15122386575325084, 0.15122386638674346, 0.15122386742756555, 0.15122386846838765, 0.1512238788766086, 0.15122388928482955, 0.15122399336703907, 0.15122409744924858, 0.15122513827134376, 0.15122617909343894, 0.1512328927994238, 0.15123960650540869, 0.15124632021139356, 0.15128829330642926, 0.15133026640146496, 0.15137223949650067, 0.1517919704468577, 0.1522117013972147, 0.15263143234757173, 0.1537703183012137, 0.1549092042548557, 0.15604809020849766, 0.15718697616213964, 0.16041002371121, 0.16363307126028034, 0.1668561188093507, 0.17007916635842105, 0.1733022139074914, 0.1788510580581333, 0.18439990220877522, 0.18994874635941714, 0.19549759051005905, 0.20104643466070096, 0.2063899166675448, 0.21173339867438865, 0.2170768806812325, 0.22242036268807633, 0.22776384469492017, 0.233107326701764, 0.23841245847007725, 0.24371759023839049, 0.24902272200670372, 0.254327853775017, 0.25963298554333025, 0.2656055681388122, 0.27157815073429414, 0.2775507333297761, 0.28352331592525803, 0.28949589852074, 0.2954684811162219, 0.30154846024337295, 0.307628439370524, 0.313708418497675, 0.319788397624826, 0.32586837675197705, 0.3319483558791281, 0.33975072562910125, 0.3475530953790744, 0.3553554651290476, 0.36315783487902076, 0.37096020462899393, 0.378707430558145, 0.38645465648729604, 0.3942018824164471, 0.40194910834559816, 0.4096963342747492, 0.4174435602039003, 0.4284042976094234, 0.4393650350149465, 0.4503257724204696, 0.46128650982599273, 0.47224724723151584, 0.48320798463703896, 0.4989162615966532, 0.5146245385562674, 0.5303328155158817, 0.546041092475496, 0.5617493694351103, 0.5774576463947246, 0.60096759362266, 0.6244775408505953, 0.6479874880785306, 0.6714974353064659, 0.6950073825344012, 0.7231688147136894, 0.7513302468929777, 0.7794916790722659, 0.8076531112515541, 0.8358145434308424, 0.8790295455110676, 0.9222445475912928, 0.965459549671518, 1.0086745517517433, 1.0518895538319684, 1.1068107217347338, 1.1617318896374993, 1.2166530575402648, 1.2715742254430302, 1.3264953933457957, 1.3814165612485612, 1.4409286134292192, 1.4706846395195483, 1.4821720598552741, 1.493659480191, 1.499031857291071, 1.4997272963401778, 1.5002253920268676, 1.5007234877135573, 1.5012215834002471, 1.501719679086937, 1.5022177747736267, 1.5030311765932356, 1.5038445784128445, 1.5046579802324533, 1.5054713820520622, 1.5079538664832213, 1.5104363509143803, 1.5129188353455394, 1.5228277702312296, 1.5327367051169198, 1.54264564000261, 1.5803019106672846, 1.6179581813319592, 1.6556144519966338, 1.730271768376266, 1.8049290847558983, 1.8795864011355305, 1.9542437175151628, 2.051998703126935, 2.1497536887387074, 2.2475086743504797, 2.345263659962252, 2.4430186455740244, 2.554827834015576, 2.666637022457128, 2.7784462108986796, 2.8902553993402313, 3.002064587781783, 3.113873776223335, 3.2950378308007373, 3.47620188537814, 3.6573659399555423, 3.8385299945329447, 4.019694049110347, 4.20085810368775, 4.4170790896978565, 4.633300075707963, 4.849521061718069, 5.065742047728175, 5.281963033738282, 5.498184019748388, 5.793645769996108, 6.089107520243829, 6.384569270491549, 6.6800310207392695, 6.97549277098699, 7.27095452123471, 7.67687916249669, 8.08280380375867, 8.488728445020651, 8.894653086282633, 9.300577727544614, 9.706502368806595, 10.0]</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.6249889514692164</v>
+        <v>0.624989229762176</v>
       </c>
       <c r="D17" t="n">
         <v>9.81</v>
@@ -1572,13 +1572,13 @@
         <v>2</v>
       </c>
       <c r="L17" t="n">
-        <v>6.249889514692164</v>
+        <v>6.249892297621759</v>
       </c>
       <c r="M17" t="n">
-        <v>0.005120181023928462</v>
+        <v>0.005120176464137843</v>
       </c>
       <c r="N17" t="n">
-        <v>0.02560090511964231</v>
+        <v>0.02560088232068921</v>
       </c>
       <c r="O17" t="n">
         <v>19.6166067782281</v>
@@ -1608,11 +1608,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[0.0, 5.943033729638898e-07, 1.1886067459277797e-06, 7.131640475566679e-06, 1.3074674205205577e-05, 3.0864467420329094e-05, 4.865426063545261e-05, 6.644405385057613e-05, 0.00011042040172553449, 0.00015439674960049285, 0.00019837309747545122, 0.0004137270440302829, 0.0006290809905851145, 0.0008444349371399462, 0.0016772359334238658, 0.0025100369297077854, 0.0033428379259917047, 0.004372306259310561, 0.005401774592629418, 0.006431242925948274, 0.00746071125926713, 0.00949580105364961, 0.011530890848032091, 0.013565980642414571, 0.015601070436797052, 0.017636160231179532, 0.02313849515644479, 0.028640830081710048, 0.034143165006975305, 0.03964549993224056, 0.04514783485750582, 0.053231711556639236, 0.06131558825577265, 0.06939946495490606, 0.07748334165403947, 0.08556721835317288, 0.09365109505230629, 0.10153495075319009, 0.1094188064540739, 0.1173026621549577, 0.12367351871623906, 0.13004437527752044, 0.13641523183880183, 0.14278608840008322, 0.1491569449613646, 0.15577150227758207, 0.16238605959379954, 0.169000616910017, 0.17561517422623446, 0.18222973154245192, 0.18884428885866938, 0.19481233052795274, 0.2007803721972361, 0.20674841386651946, 0.21271645553580282, 0.21868449720508618, 0.22463664602897887, 0.23058879485287156, 0.23654094367676426, 0.24249309250065695, 0.24844524132454965, 0.2543973901484423, 0.2602763565576615, 0.2661553229668807, 0.2720342893760999, 0.2779132557853191, 0.2837922221945383, 0.2896711886037575, 0.2954583765743828, 0.30124556454500806, 0.30703275251563333, 0.3128199404862586, 0.3186071284568839, 0.32439431642750916, 0.33324730174743783, 0.3421002870673665, 0.3509532723872952, 0.35980625770722385, 0.36865924302715253, 0.3784298034352914, 0.3882003638434303, 0.3979709242515692, 0.4077414846597081, 0.417512045067847, 0.4272826054759859, 0.4390934994539378, 0.45090439343188965, 0.4627152874098415, 0.4745261813877934, 0.4863370753657453, 0.49814796934369715, 0.5144966012837227, 0.5308452332237481, 0.5471938651637736, 0.563542497103799, 0.5798911290438244, 0.6037058823859182, 0.6275206357280119, 0.6513353890701056, 0.6751501424121993, 0.698964895754293, 0.7334632394873316, 0.7679615832203702, 0.8024599269534088, 0.8369582706864475, 0.8714566144194861, 0.9083364712379564, 0.9452163280564266, 0.9820961848748969, 1.0189760416933673, 1.0558558985118376, 1.1161679348525113, 1.176479971193185, 1.2367920075338588, 1.2971040438745325, 1.3574160802152062, 1.41772811655588, 1.4843024413747983, 1.5508767661937166, 1.617451091012635, 1.6840254158315533, 1.7505997406504716, 1.8513520241287775, 1.9521043076070834, 2.0528565910853893, 2.1536088745636954, 2.2543611580420015, 2.3551134415203077, 2.4834832503201905, 2.6118530591200733, 2.740222867919956, 2.868592676719839, 2.9969624855197217, 3.1253322943196045, 3.272592431175997, 3.4198525680323897, 3.5671127048887823, 3.714372841745175, 3.8616329786015675, 4.00889311545796, 4.243377262560738, 4.477861409663516, 4.712345556766294, 4.9468297038690725, 5.181313850971851, 5.415797998074629, 5.698134200499881, 5.980470402925134, 6.262806605350386, 6.545142807775639, 6.827479010200891, 7.109815212626144, 7.495664540739935, 7.881513868853727, 8.26736319696752, 8.653212525081312, 9.039061853195104, 9.424911181308897, 9.959156572618273, 10.0]</t>
+          <t>[0.0, 1.3289031069655228e-05, 2.6578062139310457e-05, 0.00015946837283586275, 0.00029235868353241507, 0.0008267493784346262, 0.0013611400733368373, 0.0018955307682390484, 0.0038916374352993416, 0.005887744102359635, 0.007883850769419928, 0.01382022636730559, 0.019756601965191252, 0.025692977563076914, 0.031629353160962576, 0.04134378793613666, 0.05105822271131075, 0.06077265748648483, 0.07048709226165892, 0.080201527036833, 0.09094088396102838, 0.10168024088522376, 0.11241959780941914, 0.12315895473361452, 0.13088074046406892, 0.13860252619452332, 0.14632431192497772, 0.14634844250538537, 0.14637257308579302, 0.14639670366620067, 0.14642083424660832, 0.14644496482701597, 0.14646909540742362, 0.1467104012115001, 0.1469517070155766, 0.1471930128196531, 0.1474343186237296, 0.1476756244278061, 0.14950666688474643, 0.1498728753761345, 0.15023908386752258, 0.15060529235891065, 0.15097150085029873, 0.15099467607795347, 0.15101785130560821, 0.15104102653326296, 0.1510642017609177, 0.15106605577913007, 0.15106790979734244, 0.15106976381555481, 0.1510699121370118, 0.15107006045846877, 0.15107009012276015, 0.15107011978705154, 0.1510701268221328, 0.1510701282412309, 0.1510701289376933, 0.15107012963415573, 0.15107013033061814, 0.15107013142403686, 0.15107013251745557, 0.15107014345164274, 0.1510701543858299, 0.15107026372770158, 0.15107037306957324, 0.15107146648828992, 0.1510725599070066, 0.15107942299589802, 0.15108628608478944, 0.15109314917368086, 0.1511354079457566, 0.15117766671783237, 0.15121992548990812, 0.15164251321066566, 0.1520651009314232, 0.15248768865218074, 0.15362961785877724, 0.15477154706537374, 0.15591347627197025, 0.15705540547856675, 0.16027666880552394, 0.16349793213248112, 0.1667191954594383, 0.1699404587863955, 0.17316172211335268, 0.17870537046987398, 0.18424901882639527, 0.18979266718291657, 0.19533631553943787, 0.20087996389595916, 0.20622387512528048, 0.2115677863546018, 0.21691169758392312, 0.22225560881324444, 0.22759952004256576, 0.23294343127188707, 0.23825175807023352, 0.24356008486857997, 0.24886841166692641, 0.2541767384652729, 0.25948506526361936, 0.265463209652321, 0.27144135404102265, 0.2774194984297243, 0.28339764281842594, 0.2893757872071276, 0.29535393159582923, 0.30143323742917055, 0.3075125432625119, 0.3135918490958532, 0.3196711549291945, 0.32575046076253583, 0.33182976659587715, 0.33961863590462515, 0.34740750521337316, 0.35519637452212116, 0.36298524383086916, 0.37077411313961717, 0.37851651974840006, 0.38625892635718295, 0.39400133296596584, 0.40174373957474874, 0.40948614618353163, 0.4172285527923145, 0.42818215790878017, 0.4391357630252458, 0.45008936814171147, 0.4610429732581771, 0.47199657837464276, 0.4829501834911084, 0.49865953390886963, 0.5143688843266309, 0.5300782347443921, 0.5457875851621533, 0.5614969355799145, 0.5772062859976758, 0.6007097930232009, 0.6242133000487261, 0.6477168070742513, 0.6712203140997764, 0.6947238211253016, 0.7228761107890718, 0.7510284004528419, 0.7791806901166121, 0.8073329797803822, 0.8354852694441524, 0.8786841608741541, 0.9218830523041559, 0.9650819437341577, 1.0082808351641595, 1.0514797265941613, 1.1063837965439942, 1.161287866493827, 1.21619193644366, 1.2710960063934928, 1.3260000763433257, 1.3461620389246052, 1.350515320314919, 1.351055966310319, 1.3514839718997231, 1.3517223878187021, 1.3519608037376811, 1.3521992196566601, 1.3524376355756391, 1.3526760514946181, 1.352914467413597, 1.3532348453146694, 1.3535552232157417, 1.353875601116814, 1.3541959790178864, 1.3545163569189587, 1.354836734820031, 1.3554326861936652, 1.3560286375672994, 1.3566245889409336, 1.3572205403145678, 1.357816491688202, 1.3594726196169378, 1.3611287475456735, 1.3627848754744092, 1.364441003403145, 1.3715780955761054, 1.378715187749066, 1.3858522799220265, 1.4147109295245919, 1.4435695791271572, 1.4724282287297226, 1.5364331418513089, 1.6004380549728952, 1.6644429680944814, 1.7284478812160677, 1.8003796103175354, 1.872311339419003, 1.9442430685204706, 2.016174797621938, 2.088106526723406, 2.2046566189291585, 2.321206711134911, 2.4377568033406636, 2.554306895546416, 2.6708569877521686, 2.787407079957921, 2.9414602070996407, 3.0955133342413603, 3.24956646138308, 3.4036195885247995, 3.557672715666519, 3.7117258428082387, 3.8878589650330686, 4.0639920872578985, 4.240125209482729, 4.416258331707559, 4.59239145393239, 4.76852457615722, 5.049763896116137, 5.331003216075055, 5.612242536033972, 5.893481855992889, 6.174721175951807, 6.455960495910724, 6.795517799404527, 7.1350751028983295, 7.474632406392132, 7.814189709885935, 8.153747013379737, 8.493304316873541, 8.958191349737072, 9.423078382600604, 9.887965415464135, 10.0]</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.624065547267972</v>
+        <v>0.6240656230404478</v>
       </c>
       <c r="D18" t="n">
         <v>9.81</v>
@@ -1639,13 +1639,13 @@
         <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>6.24065547267972</v>
+        <v>6.240656230404477</v>
       </c>
       <c r="M18" t="n">
-        <v>0.005135344477834043</v>
+        <v>0.005135343230792941</v>
       </c>
       <c r="N18" t="n">
-        <v>0.02567672238917022</v>
+        <v>0.0256767161539647</v>
       </c>
       <c r="O18" t="n">
         <v>19.61570806573987</v>
@@ -1675,11 +1675,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[0.0, 5.943205913713719e-07, 1.1886411827427437e-06, 7.131847096456462e-06, 1.307505301017018e-05, 3.086536277733265e-05, 4.8655672544495126e-05, 6.64459823116576e-05, 0.0001104236484160707, 0.0001544013145204838, 0.0001983789806248969, 0.00041376380296641156, 0.0006291486253079263, 0.0008445334476494409, 0.0016727862461141762, 0.0025010390445789118, 0.0033292918430436473, 0.004357567017007446, 0.005385842190971246, 0.006414117364935045, 0.007442392538898845, 0.009481906498921418, 0.011521420458943991, 0.013560934418966565, 0.015600448378989138, 0.01763996233901171, 0.02314268309575527, 0.02864540385249883, 0.03414812460924239, 0.03965084536598595, 0.045153566122729506, 0.05325046906998747, 0.06134737201724543, 0.0694442749645034, 0.07754117791176135, 0.0856380808590193, 0.09373498380627726, 0.10159193949611176, 0.10944889518594625, 0.11730585087578074, 0.12366709754832321, 0.13002834422086568, 0.13638959089340813, 0.14275083756595058, 0.14911208423849304, 0.15572793181870376, 0.16234377939891448, 0.1689596269791252, 0.17557547455933592, 0.18219132213954664, 0.18880716971975736, 0.19475924664895256, 0.20071132357814775, 0.20666340050734294, 0.21261547743653814, 0.21856755436573333, 0.22448701470639007, 0.2304064750470468, 0.23632593538770355, 0.2422453957283603, 0.24816485606901703, 0.25408431640967377, 0.25997092868778837, 0.26585754096590297, 0.27174415324401757, 0.2776307655221322, 0.2835173778002468, 0.2894039900783614, 0.29518746442138577, 0.30097093876441017, 0.30675441310743456, 0.31253788745045896, 0.31832136179348336, 0.32410483613650776, 0.33294951268190254, 0.3417941892272973, 0.3506388657726921, 0.3594835423180869, 0.36832821886348166, 0.3780954425411234, 0.3878626662187652, 0.39762988989640696, 0.40739711357404873, 0.4171643372516905, 0.42693156092933227, 0.43873637956290346, 0.45054119819647465, 0.46234601683004584, 0.474150835463617, 0.4859556540971882, 0.4977604727307594, 0.5141032945680182, 0.530446116405277, 0.5467889382425357, 0.5631317600797945, 0.5794745819170533, 0.6032755617153271, 0.627076541513601, 0.6508775213118749, 0.6746785011101488, 0.6984794809084227, 0.7329560937017023, 0.767432706494982, 0.8019093192882616, 0.8363859320815412, 0.8708625448748208, 0.9077184483740621, 0.9445743518733034, 0.9814302553725447, 1.018286158871786, 1.0551420623710273, 1.115414087363703, 1.1756861123563789, 1.2359581373490547, 1.2962301623417305, 1.3565021873344063, 1.4167742123270821, 1.4833048465884149, 1.5498354808497476, 1.6163661151110804, 1.6828967493724132, 1.749427383633746, 1.8501149979109093, 1.9508026121880726, 2.051490226465236, 2.1521778407423997, 2.2528654550195633, 2.353553069296727, 2.4818396002651917, 2.6101261312336566, 2.7384126622021214, 2.8666991931705863, 2.994985724139051, 3.123272255107516, 3.270437983574877, 3.417603712042238, 3.5647694405095987, 3.7119351689769595, 3.8591008974443204, 4.006266625911682, 4.2406000870881115, 4.474933548264541, 4.709267009440971, 4.943600470617401, 5.177933931793831, 5.412267392970261, 5.694425739755077, 5.9765840865398925, 6.258742433324708, 6.540900780109524, 6.82305912689434, 7.105217473679156, 7.490824396055646, 7.876431318432136, 8.262038240808625, 8.647645163185114, 9.033252085561603, 9.418859007938092, 9.95275332075595, 10.0]</t>
+          <t>[0.0, 1.3289416139757938e-05, 2.6578832279515876e-05, 0.00015947299367709524, 0.00029236715507467465, 0.0008254790235930557, 0.0013585908921114368, 0.001891702760629818, 0.003879986443583036, 0.005868270126536254, 0.00785655380948947, 0.013780046636175412, 0.019703539462861352, 0.025627032289547293, 0.031550525116233234, 0.04124810892697266, 0.05094569273771208, 0.0606432765484515, 0.07034086035919093, 0.08003844416993036, 0.09077169768353087, 0.10150495119713138, 0.11223820471073188, 0.12297145822433239, 0.13068736588656385, 0.1384032735487953, 0.14611918121102677, 0.14614329342247123, 0.1461674056339157, 0.14619151784536016, 0.14621563005680463, 0.1462397422682491, 0.14626385447969356, 0.14650497659413822, 0.14674609870858288, 0.14698722082302754, 0.1472283429374722, 0.14746946505191685, 0.14932635678251258, 0.14969773512863171, 0.15006911347475085, 0.15044049182087, 0.15081187016698913, 0.15083547981469508, 0.15085908946240104, 0.15086381139194222, 0.1508685333214834, 0.15087325525102457, 0.1508741996369328, 0.15087514402284102, 0.15087608840874925, 0.15087703279465747, 0.15087710834553014, 0.15087712345570467, 0.1508771385658792, 0.15087715367605373, 0.1508771548848677, 0.15087715609368166, 0.1508771585113096, 0.15087715917821395, 0.150877159431986, 0.15087715968575807, 0.1508771602325025, 0.15087716077924693, 0.1508771659203469, 0.15087717106144685, 0.15087722247244648, 0.1508772738834461, 0.15087778799344234, 0.15087830210343858, 0.150883443203401, 0.1508885843033634, 0.15089372540332582, 0.15093446859855056, 0.1509752117937753, 0.15101595498900003, 0.15142338694124738, 0.15183081889349473, 0.15223825084574208, 0.15335921649810852, 0.15448018215047496, 0.1556011478028414, 0.15672211345520784, 0.15992063872965806, 0.16311916400410828, 0.1663176892785585, 0.16951621455300872, 0.17271473982745894, 0.17826063137723855, 0.18380652292701816, 0.18935241447679776, 0.19489830602657737, 0.20044419757635698, 0.20577867296452707, 0.21111314835269715, 0.21644762374086723, 0.22178209912903732, 0.2271165745172074, 0.2324510499053775, 0.2377335170917965, 0.2430159842782155, 0.2482984514646345, 0.2535809186510535, 0.2588633858374725, 0.2648000109161611, 0.27073663599484976, 0.2766732610735384, 0.28260988615222704, 0.2885465112309157, 0.2944831363096043, 0.3005584303529565, 0.30663372439630865, 0.3127090184396608, 0.318784312483013, 0.32485960652636514, 0.3309349005697173, 0.3387910431630818, 0.34664718575644626, 0.35450332834981074, 0.3623594709431752, 0.3702156135365397, 0.37950675772085, 0.38879790190516034, 0.39808904608947066, 0.407380190273781, 0.4166713344580913, 0.4259624786424016, 0.43773292684729703, 0.44950337505219246, 0.4612738232570879, 0.4730442714619833, 0.4848147196668787, 0.49658516787177415, 0.5130410603593059, 0.5294969528468376, 0.5459528453343694, 0.5624087378219012, 0.5788646303094329, 0.5953205227969647, 0.6185774593827371, 0.6418343959685096, 0.665091332554282, 0.6883482691400544, 0.7116052057258269, 0.747037876449357, 0.7824705471728872, 0.8179032178964174, 0.8533358886199476, 0.8887685593434778, 0.9265519964767908, 0.9643354336101038, 1.0021188707434168, 1.0399023078767298, 1.0776857450100428, 1.1446569653527754, 1.211628185695508, 1.2162985054281503, 1.2178197823631116, 1.2182261435358812, 1.2184487968321713, 1.2186714501284615, 1.2188941034247516, 1.2191167567210417, 1.2193394100173318, 1.219562063313622, 1.219858027261813, 1.220153991210004, 1.2204499551581949, 1.2207459191063859, 1.2210418830545768, 1.2213378470027678, 1.2218980136375432, 1.2224581802723187, 1.223018346907094, 1.2235785135418695, 1.224138680176645, 1.2256853866733906, 1.2272320931701362, 1.2287787996668817, 1.2303255061636273, 1.2369119573094458, 1.2434984084552643, 1.2500848596010827, 1.2762748045588703, 1.302464749516658, 1.3286546944744455, 1.380851558322128, 1.4330484221698103, 1.4852452860174927, 1.5374421498651751, 1.6001725152082782, 1.6629028805513812, 1.7256332458944843, 1.7883636112375874, 1.8510939765806904, 1.9534881820733627, 2.055882387566035, 2.158276593058707, 2.260670798551379, 2.363065004044051, 2.465459209536723, 2.601137130417609, 2.7368150512984952, 2.8724929721793813, 3.0081708930602673, 3.1438488139411533, 3.2795267348220394, 3.4344292537317096, 3.58933177264138, 3.74423429155105, 3.8991368104607202, 4.05403932937039, 4.20894184828006, 4.456006947289116, 4.703072046298172, 4.950137145307228, 5.197202244316284, 5.444267343325341, 5.691332442334397, 5.988768335168776, 6.286204228003155, 6.583640120837534, 6.881076013671913, 7.178511906506292, 7.475947799340671, 7.882665440102505, 8.28938308086434, 8.696100721626175, 9.10281836238801, 9.509536003149845, 9.91625364391168, 10.0]</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.622907163309016</v>
+        <v>0.6229072854917556</v>
       </c>
       <c r="D19" t="n">
         <v>9.81</v>
@@ -1706,13 +1706,13 @@
         <v>2</v>
       </c>
       <c r="L19" t="n">
-        <v>6.229071633090159</v>
+        <v>6.229072854917555</v>
       </c>
       <c r="M19" t="n">
-        <v>0.005154462035770834</v>
+        <v>0.005154460013684255</v>
       </c>
       <c r="N19" t="n">
-        <v>0.02577231017885417</v>
+        <v>0.02577230006842127</v>
       </c>
       <c r="O19" t="n">
         <v>19.61457132456068</v>
@@ -1742,11 +1742,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[0.0, 5.943423722811132e-07, 1.1886847445622265e-06, 7.132108467373359e-06, 1.3075532190184492e-05, 3.086649538446723e-05, 4.865745857874997e-05, 6.644842177303272e-05, 0.00011042775541124608, 0.00015440708904945944, 0.0001983864226876728, 0.00041381031940627505, 0.0006292342161248773, 0.0008446581128434797, 0.001667298787345858, 0.0024899394618482363, 0.0033125801363506147, 0.004339395758452765, 0.005366211380554916, 0.006393027002657066, 0.007419842624759217, 0.009465021842616845, 0.011510201060474474, 0.013555380278332103, 0.015600559496189732, 0.01764573871404736, 0.023149417003231067, 0.028653095292414773, 0.03415677358159848, 0.03966045187078218, 0.045164130159965885, 0.053278075888028, 0.061392021616090114, 0.06950596734415224, 0.07761991307221436, 0.08573385880027648, 0.0938478045283386, 0.10167107046694498, 0.10949433640555137, 0.11731760234415775, 0.12514086828276413, 0.13136124524178824, 0.13758162220081235, 0.14380199915983646, 0.15002237611886057, 0.15624275307788468, 0.1629813251997675, 0.1697198973216503, 0.1764584694435331, 0.1831970415654159, 0.18993561368729872, 0.19667418580918153, 0.2020389604691196, 0.20740373512905766, 0.21276850978899572, 0.2181332844489338, 0.22349805910887185, 0.22886283376880992, 0.23411615535704372, 0.23936947694527752, 0.24462279853351132, 0.24987612012174512, 0.2551294417099789, 0.26038276329821275, 0.266730558117281, 0.2730783529363493, 0.2794261477554176, 0.28577394257448585, 0.2921217373935541, 0.2984695322126224, 0.30379863606192675, 0.3091277399112311, 0.31445684376053545, 0.3197859476098398, 0.32511505145914416, 0.3304441553084485, 0.33863981792315984, 0.34683548053787117, 0.3550311431525825, 0.3632268057672938, 0.37142246838200516, 0.3796181309967165, 0.38771978809467833, 0.3958214451926402, 0.403923102290602, 0.41202475938856387, 0.4201264164865257, 0.42822807358448756, 0.4377467616411536, 0.4472654496978197, 0.45678413775448573, 0.4663028258111518, 0.47582151386781785, 0.4853402019244839, 0.500149931814611, 0.5149596617047381, 0.5297693915948651, 0.5445791214849922, 0.5593888513751193, 0.5845205851024482, 0.6096523188297771, 0.634784052557106, 0.6599157862844349, 0.6850475200117638, 0.7154623693155998, 0.7458772186194358, 0.7762920679232718, 0.8067069172271077, 0.8371217665309437, 0.879748944489607, 0.9223761224482704, 0.9650033004069337, 1.0076304783655972, 1.0502576563242605, 1.0928848342829238, 1.1404806383342019, 1.18807644238548, 1.235672246436758, 1.283268050488036, 1.330863854539314, 1.3784596585905922, 1.4580375869283202, 1.5376155152660482, 1.6171934436037763, 1.6967713719415043, 1.7763493002792323, 1.8559272286169604, 1.9456666164153504, 2.0354060042137405, 2.1251453920121306, 2.2148847798105207, 2.3046241676089108, 2.394363555407301, 2.530145538446349, 2.665927521485397, 2.801709504524445, 2.937491487563493, 3.0732734706025413, 3.2090554536415894, 3.3887960341603542, 3.568536614679119, 3.748277195197884, 3.928017775716649, 4.107758356235413, 4.287498936754178, 4.497240812773783, 4.7069826887933885, 4.916724564812994, 5.1264664408325995, 5.336208316852205, 5.5459501928718105, 5.8530841854265585, 6.1602181779813066, 6.467352170536055, 6.774486163090803, 7.081620155645551, 7.388754148200299, 7.7961950667518565, 8.203635985303414, 8.611076903854972, 9.01851782240653, 9.425958740958087, 9.833399659509645, 10.0]</t>
+          <t>[0.0, 1.3289903245636307e-05, 2.6579806491272613e-05, 0.0001594788389476357, 0.0002923778714039988, 0.0008238890841958679, 0.001355400296987737, 0.0018869115097796061, 0.0038654038050385765, 0.005843896100297547, 0.007822388395556518, 0.013729827628966577, 0.019637266862376636, 0.025544706095786695, 0.031452145329196754, 0.041128618099513375, 0.05080509086983, 0.06048156364014662, 0.07015803641046324, 0.07983450918077986, 0.09056021647311374, 0.10128592376544762, 0.1120116310577815, 0.12273733835011538, 0.13044534606450636, 0.13815335377889734, 0.14586136149328832, 0.1458854490173958, 0.1459095365415033, 0.14593362406561078, 0.14595771158971826, 0.14598179911382575, 0.14600588663793324, 0.1462467618790081, 0.14648763712008295, 0.1467285123611578, 0.14696938760223266, 0.14721026284330752, 0.14904049383749318, 0.1494065400363303, 0.14977258623516743, 0.15013863243400455, 0.15050467863284167, 0.150620532854784, 0.1506251670236617, 0.15062980119253938, 0.15063443536141707, 0.1506353621951926, 0.15063540747207718, 0.1506354145351007, 0.15063542159812424, 0.15063542297516364, 0.15063542406776964, 0.15063542516037565, 0.15063542625298165, 0.15063542734558766, 0.1506354300384019, 0.15063543273121616, 0.1506354354240304, 0.1506354623521729, 0.1506354892803154, 0.150635689910935, 0.15063589054155463, 0.1506378968477508, 0.15063990315394699, 0.15064929799954205, 0.1506586928451371, 0.15066808769073217, 0.1507159211239355, 0.15076375455713883, 0.15081158799034217, 0.15128992232237548, 0.1517682566544088, 0.1522465909864421, 0.15345518535904432, 0.15466377973164652, 0.15587237410424873, 0.15708096847685094, 0.16033540235110905, 0.16358983622536716, 0.16684427009962527, 0.17009870397388338, 0.1733531378481415, 0.1788625771353983, 0.1843720164226551, 0.1898814557099119, 0.19539089499716872, 0.20090033428442552, 0.20627441675469477, 0.211648499224964, 0.21702258169523325, 0.2223966641655025, 0.22777074663577174, 0.23314482910604098, 0.23853471149048738, 0.2439245938749338, 0.2493144762593802, 0.25470435864382657, 0.26009424102827294, 0.2662149061483793, 0.2723355712684856, 0.27845623638859196, 0.2845769015086983, 0.29069756662880464, 0.296818231748911, 0.3029060756478485, 0.308993919546786, 0.31508176344572353, 0.32116960734466105, 0.32725745124359856, 0.3333452951425361, 0.34108310764109784, 0.3488209201396596, 0.35655873263822135, 0.3642965451367831, 0.37203435763534487, 0.37977217013390663, 0.38876222625608686, 0.3977522823782671, 0.40674233850044733, 0.41573239462262757, 0.4247224507448078, 0.43371250686698803, 0.4436167774706659, 0.4535210480743438, 0.46342531867802167, 0.47332958928169955, 0.4832338598853774, 0.4931381304890553, 0.5085890536373496, 0.524039976785644, 0.5394908999339383, 0.5549418230822326, 0.5703927462305269, 0.5963733355342244, 0.622353924837922, 0.6483345141416195, 0.674315103445317, 0.7002956927490145, 0.7313848149526433, 0.7624739371562721, 0.7935630593599009, 0.8246521815635297, 0.8557413037671585, 0.8999074586693151, 0.9440736135714717, 0.9882397684736283, 1.032405923375785, 1.0765720782779415, 1.0927600726569977, 1.0962450881801797, 1.0981922591420676, 1.0987636637416383, 1.0991052208581586, 1.0992954097947685, 1.0994855987313783, 1.0996757876679881, 1.099865976604598, 1.1000561655412078, 1.1002463544778176, 1.1005018617873503, 1.100757369096883, 1.1010128764064158, 1.1012683837159485, 1.1015238910254812, 1.101779398335014, 1.1022548647233796, 1.1027303311117453, 1.103205797500111, 1.1036812638884768, 1.1041567302768425, 1.1054778451726686, 1.1067989600684947, 1.1081200749643207, 1.1094411898601468, 1.115133110529134, 1.1208250311981212, 1.1265169518671083, 1.1495702776681165, 1.1726236034691246, 1.1956769292701328, 1.2454133455884668, 1.2951497619068009, 1.344886178225135, 1.394622594543469, 1.4509788679201052, 1.5073351412967415, 1.5636914146733778, 1.620047688050014, 1.6764039614266504, 1.7532192459626834, 1.8300345304987164, 1.9068498150347495, 1.9836650995707825, 2.0604803841068158, 2.1745523086159397, 2.2886242331250637, 2.4026961576341876, 2.5167680821433116, 2.6308400066524356, 2.7449119311615595, 2.885991862200526, 3.027071793239492, 3.1681517242784585, 3.309231655317425, 3.450311586356391, 3.5913915173953574, 3.8024530654031543, 4.013514613410951, 4.224576161418748, 4.435637709426544, 4.64669925743434, 4.857760805442137, 5.132598579458325, 5.4074363534745125, 5.6822741274907, 5.957111901506888, 6.231949675523076, 6.506787449539264, 6.831337819915757, 7.15588819029225, 7.480438560668744, 7.804988931045237, 8.12953930142173, 8.454089671798222, 8.933323482887793, 9.412557293977365, 9.891791105066936, 10.0]</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.6214570178944209</v>
+        <v>0.6214570844881709</v>
       </c>
       <c r="D20" t="n">
         <v>9.81</v>
@@ -1773,13 +1773,13 @@
         <v>2</v>
       </c>
       <c r="L20" t="n">
-        <v>6.214570178944208</v>
+        <v>6.214570844881709</v>
       </c>
       <c r="M20" t="n">
-        <v>0.005178545569311519</v>
+        <v>0.00517854445947221</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0258927278465576</v>
+        <v>0.02589272229736105</v>
       </c>
       <c r="O20" t="n">
         <v>19.61313351154996</v>
@@ -1809,11 +1809,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[0.0, 5.943699253663023e-07, 1.1887398507326046e-06, 7.132439104395627e-06, 1.307613835805865e-05, 3.086792814477967e-05, 4.865971793150069e-05, 6.645150771822172e-05, 0.00011043295080832854, 0.00015441439389843537, 0.0001983958369885422, 0.00041386919073265025, 0.0006293425444767584, 0.0008448158982208665, 0.0016605724604978867, 0.002476329022774907, 0.0032920855850519276, 0.004317130907827829, 0.005342176230603731, 0.006367221553379633, 0.007392266876155535, 0.009444724064889774, 0.011497181253624013, 0.013549638442358252, 0.01560209563109249, 0.01765455281982673, 0.023160160229403263, 0.028665767638979794, 0.03417137504855633, 0.039676982458132865, 0.0451825898677094, 0.05331898571073464, 0.061455381553759875, 0.06959177739678511, 0.07772817323981035, 0.08586456908283559, 0.09400096492586082, 0.10178218625602098, 0.10956340758618113, 0.11734462891634129, 0.12512585024650144, 0.1313343647426142, 0.13754287923872696, 0.14375139373483972, 0.14995990823095248, 0.15616842272706524, 0.16290740205860296, 0.16964638139014068, 0.1763853607216784, 0.18312434005321612, 0.18986331938475384, 0.19660229871629156, 0.20196506296400854, 0.20732782721172552, 0.2126905914594425, 0.21805335570715947, 0.22341611995487645, 0.22877888420259343, 0.23401705917136267, 0.23925523414013192, 0.24449340910890116, 0.2497315840776704, 0.25496975904643965, 0.2602079340152089, 0.26660083980367266, 0.2729937455921364, 0.27938665138060015, 0.2857795571690639, 0.29217246295752763, 0.2985653687459914, 0.3038995517433609, 0.30923373474073046, 0.3145679177381, 0.31990210073546954, 0.3252362837328391, 0.3305704667302086, 0.3388054188080464, 0.34704037088588413, 0.3552753229637219, 0.36351027504155964, 0.3717452271193974, 0.37998017919723515, 0.3896571682505123, 0.3993341573037894, 0.40901114635706654, 0.41868813541034366, 0.4283651244636208, 0.4380421135168979, 0.45001070403391524, 0.46197929455093256, 0.4739478850679499, 0.4859164755849672, 0.4978850661019845, 0.5098536566190018, 0.5283300461345777, 0.5468064356501535, 0.5652828251657294, 0.5837592146813052, 0.602235604196881, 0.6207119937124569, 0.6453123204894058, 0.6699126472663547, 0.6945129740433036, 0.7191133008202525, 0.7437136275972014, 0.7812622486217224, 0.8188108696462435, 0.8563594906707646, 0.8939081116952856, 0.9314567327198067, 0.9712047136155396, 1.0109526945112726, 1.0507006754070054, 1.0904486563027382, 1.130196637198471, 1.1942380221189546, 1.258279407039438, 1.3223207919599216, 1.386362176880405, 1.4504035618008886, 1.514444946721372, 1.5861374395877403, 1.6578299324541086, 1.7295224253204768, 1.801214918186845, 1.8729074110532133, 1.9813608111483194, 2.0898142112434255, 2.1982676113385313, 2.306721011433637, 2.415174411528743, 2.523627811623849, 2.6618948418258923, 2.8001618720279358, 2.938428902229979, 3.0766959324320227, 3.214962962634066, 3.3532299928361096, 3.5116989098756672, 3.670167826915225, 3.8286367439547826, 3.9871056609943403, 4.145574578033898, 4.304043495073456, 4.556528668108851, 4.809013841144246, 5.061499014179641, 5.313984187215036, 5.566469360250431, 5.818954533285826, 6.123483674496567, 6.428012815707309, 6.73254195691805, 7.037071098128791, 7.341600239339533, 7.646129380550274, 8.062570162294703, 8.479010944039132, 8.89545172578356, 9.31189250752799, 9.728333289272419, 10.0]</t>
+          <t>[0.0, 1.329051944077543e-05, 2.658103888155086e-05, 0.00015948623328930516, 0.00029239142769705944, 0.0008219045329840708, 0.001351417638271082, 0.0018809307435580932, 0.0038472015242545015, 0.00581347230495091, 0.007779743085647319, 0.013667257870159839, 0.01955477265467236, 0.02544228743918488, 0.0313298022236974, 0.040979861568176575, 0.05062992091265575, 0.06027998025713493, 0.0699300396016141, 0.07958009894609328, 0.09029633959032018, 0.1010125802345471, 0.111728820878774, 0.12244506152300091, 0.13014362331083618, 0.13784218509867144, 0.1455407468865067, 0.14556480489209367, 0.14558886289768064, 0.1456129209032676, 0.14563697890885458, 0.14566103691444154, 0.1456850949200285, 0.1459256749758982, 0.1461662550317679, 0.14640683508763758, 0.14664741514350726, 0.14688799519937695, 0.14873866306812134, 0.1491087966418702, 0.1494789302156191, 0.14984906378936796, 0.15021919736311684, 0.15024271454090604, 0.15026623171869524, 0.15028974889648444, 0.15031326607427364, 0.1503226729453893, 0.15033207981650498, 0.1503324560913496, 0.1503328323661942, 0.15033320864103883, 0.1503332387430264, 0.15033326884501397, 0.15033329894700154, 0.15033331098779656, 0.1503333148648009, 0.15033331874180522, 0.1503333205624612, 0.15033332166233118, 0.15033332229053978, 0.15033332291874837, 0.15033332354695697, 0.1503333245949068, 0.15033332564285665, 0.15033333612235503, 0.1503333466018534, 0.1503334513968372, 0.150333556191821, 0.15033460414165903, 0.15033565209149705, 0.15034242372760898, 0.1503491953637209, 0.15035596699983284, 0.15039826848987092, 0.150440569979909, 0.1504828714699471, 0.15090588637032798, 0.15132890127070886, 0.15175191617108974, 0.15289133424503343, 0.15403075231897712, 0.1551701703929208, 0.1563095884668645, 0.1595095715439055, 0.1627095546209465, 0.1659095376979875, 0.1691095207750285, 0.1723095038520695, 0.17783424833502698, 0.18335899281798446, 0.18888373730094193, 0.1944084817838994, 0.1999332262668569, 0.20527264946084217, 0.21061207265482745, 0.21595149584881274, 0.22129091904279802, 0.2266303422367833, 0.23196976543076858, 0.23727367797747548, 0.24257759052418237, 0.24788150307088927, 0.25318541561759617, 0.25848932816430303, 0.2644618690734828, 0.27043440998266255, 0.2764069508918423, 0.28237949180102206, 0.2883520327102018, 0.2943245736193816, 0.3003985263400504, 0.30647247906071917, 0.31254643178138797, 0.31862038450205676, 0.32469433722272556, 0.33076828994339436, 0.3385466106934903, 0.3463249314435862, 0.35410325219368216, 0.3618815729437781, 0.36965989369387403, 0.3773929926901005, 0.385126091686327, 0.3928591906825535, 0.40059228967877997, 0.40832538867500645, 0.41605848767123293, 0.4270035405401617, 0.4379485934090905, 0.44889364627801925, 0.459838699146948, 0.4707837520158768, 0.4817288048848056, 0.4974377574858365, 0.5131467100868674, 0.5288556626878983, 0.5445646152889292, 0.5602735678899601, 0.575982520490991, 0.5994658466023263, 0.6229491727136616, 0.6464324988249969, 0.6699158249363322, 0.6933991510476675, 0.7215161917445136, 0.7496332324413598, 0.777750273138206, 0.8058673138350522, 0.8339843545318983, 0.8771154389938075, 0.9202465234557167, 0.9633776079176258, 0.9775176554280102, 0.9916577029383945, 0.9921835071013297, 0.9925995341348417, 0.9929011229170467, 0.9932027116992517, 0.9935043004814567, 0.9938058892636616, 0.9941074780458666, 0.9946039483456731, 0.9951004186454796, 0.9955968889452861, 0.9960933592450926, 0.9976135283171359, 0.9991336973891792, 1.0006538664612226, 1.0067515288304079, 1.0128491911995932, 1.0189468535687785, 1.042997263522891, 1.0670476734770036, 1.0910980834311161, 1.1347368327461302, 1.1783755820611443, 1.2220143313761584, 1.2656530806911725, 1.3150756075557055, 1.3644981344202385, 1.4139206612847715, 1.4633431881493044, 1.5127657150138374, 1.595008640209489, 1.6772515654051405, 1.759494490600792, 1.8417374157964437, 1.9239803409920953, 2.030719199028662, 2.1374580570652286, 2.2441969151017953, 2.350935773138362, 2.4576746311749287, 2.5644134892114954, 2.6823282572341176, 2.80024302525674, 2.918157793279362, 3.0360725613019843, 3.1539873293246066, 3.271902097347229, 3.4413632017586693, 3.6108243061701097, 3.78028541058155, 3.9497465149929907, 4.119207619404431, 4.288668723815872, 4.520857367626423, 4.753046011436974, 4.985234655247526, 5.217423299058077, 5.4496119428686285, 5.68180058667918, 5.991749291632699, 6.301697996586218, 6.611646701539737, 6.921595406493256, 7.231544111446775, 7.541492816400294, 7.958801008284229, 8.376109200168163, 8.793417392052095, 9.210725583936028, 9.628033775819961, 10.0]</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.6196464980170189</v>
+        <v>0.619646693177721</v>
       </c>
       <c r="D21" t="n">
         <v>9.81</v>
@@ -1840,13 +1840,13 @@
         <v>2</v>
       </c>
       <c r="L21" t="n">
-        <v>6.196464980170188</v>
+        <v>6.19646693177721</v>
       </c>
       <c r="M21" t="n">
-        <v>0.005208851742882068</v>
+        <v>0.005208848461776837</v>
       </c>
       <c r="N21" t="n">
-        <v>0.02604425871441034</v>
+        <v>0.02604424230888418</v>
       </c>
       <c r="O21" t="n">
         <v>19.61131488626249</v>
@@ -1876,11 +1876,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[0.0, 5.944047814512516e-07, 1.1888095629025031e-06, 7.13285737741502e-06, 1.3076905191927536e-05, 3.086974066120871e-05, 4.8662576130489876e-05, 6.645541159977104e-05, 0.00011043952326207938, 0.00015442363492438772, 0.00019840774658669606, 0.00041394371013290073, 0.0006294796736791054, 0.00084501563722531, 0.0016523878551712855, 0.002459760073117261, 0.0032671322910632367, 0.004290053061574974, 0.005312973832086711, 0.006335894602598448, 0.0073588153731101846, 0.009420660752844477, 0.011482506132578769, 0.013544351512313061, 0.015606196892047354, 0.017668042271781648, 0.023177179287398382, 0.028686316303015116, 0.03419545331863185, 0.039704590334248585, 0.04521372734986532, 0.05337998264407202, 0.061546237938278715, 0.0697124932324854, 0.0778787485266921, 0.0860450038208988, 0.0942112591151055, 0.10194024302075337, 0.10966922692640124, 0.11739821083204911, 0.12512719473769698, 0.13132072669115877, 0.13751425864462055, 0.14370779059808234, 0.14990132255154412, 0.1560948545050059, 0.1628281488049083, 0.16956144310481072, 0.17629473740471313, 0.18302803170461554, 0.18976132600451795, 0.19649462030442036, 0.20185444259249488, 0.2072142648805694, 0.21257408716864393, 0.21793390945671845, 0.22329373174479297, 0.2286535540328675, 0.23387416320026322, 0.23909477236765894, 0.24431538153505467, 0.2495359907024504, 0.2547565998698461, 0.25997720903724186, 0.2664283837171494, 0.2728795583970569, 0.27933073307696443, 0.28578190775687196, 0.2922330824367795, 0.298684257116687, 0.3040330400457232, 0.30938182297475936, 0.31473060590379554, 0.3200793888328317, 0.3254281717618679, 0.33077695469090407, 0.33906714181540487, 0.3473573289399057, 0.3556475160644065, 0.3639377031889073, 0.3722278903134081, 0.3805180774379089, 0.3885766640335553, 0.3966352506292017, 0.4046938372248481, 0.4127524238204945, 0.4208110104161409, 0.4288695970117873, 0.43931964897986514, 0.449769700947943, 0.46021975291602085, 0.4706698048840987, 0.48111985685217656, 0.4915699088202544, 0.5087969414155172, 0.52602397401078, 0.5432510066060429, 0.5604780392013057, 0.5777050717965685, 0.5949321043918313, 0.6226347530278941, 0.6503374016639568, 0.6780400503000196, 0.7057426989360823, 0.7334453475721451, 0.7611479962082078, 0.7985098739251743, 0.8358717516421407, 0.8732336293591071, 0.9105955070760735, 0.9479573847930399, 0.9928328053148034, 1.037708225836567, 1.0825836463583307, 1.1274590668800943, 1.172334487401858, 1.2378614411234716, 1.3033883948450853, 1.368915348566699, 1.4344423022883126, 1.4999692560099263, 1.56549620973154, 1.6474235253646992, 1.7293508409978584, 1.8112781566310177, 1.893205472264177, 1.9751327878973362, 2.0693470753520353, 2.1635613628067345, 2.2577756502614337, 2.351989937716133, 2.446204225170832, 2.540418512625531, 2.685324634985187, 2.830230757344843, 2.975136879704499, 3.120043002064155, 3.264949124423811, 3.409855246783467, 3.5836095769314036, 3.7573639070793403, 3.931118237227277, 4.104872567375214, 4.27862689752315, 4.452381227671086, 4.689105985130383, 4.92583074258968, 5.162555500048977, 5.3992802575082735, 5.63600501496757, 5.872729772426867, 6.196575815323581, 6.5204218582202955, 6.84426790111701, 7.168113944013724, 7.491959986910438, 7.8158060298071526, 8.248578551884396, 8.68135107396164, 9.114123596038883, 9.546896118116127, 9.97966864019337, 10.0]</t>
+          <t>[0.0, 1.3291298961194234e-05, 2.6582597922388468e-05, 0.00015949558753433082, 0.0002924085771462731, 0.0008194356987631072, 0.0013464628203799414, 0.0018734899419967756, 0.0038245581673561377, 0.0057756263927155, 0.007726694618074861, 0.013589600591947028, 0.019452506565819195, 0.025315412539691363, 0.031178318513563532, 0.04079544719372112, 0.05041257587387871, 0.06002970455403629, 0.06964683323419388, 0.07926396191435146, 0.08996853467764626, 0.10067310744094106, 0.11137768020423586, 0.12208225296753066, 0.12976856568307943, 0.1374548783986282, 0.14514119111417695, 0.14516521084141304, 0.14518923056864913, 0.14521325029588522, 0.1452372700231213, 0.1452612897503574, 0.1452853094775935, 0.1455255067499544, 0.1457657040223153, 0.14600590129467622, 0.14624609856703713, 0.14648629583939804, 0.1483153284132946, 0.1486811349280739, 0.1490469414428532, 0.14941274795763249, 0.14977855447241178, 0.14989438020292353, 0.14991754534902588, 0.14994071049512822, 0.14994534352434868, 0.14994997655356915, 0.1499546095827896, 0.1499555361886337, 0.14995646279447777, 0.1499566481156466, 0.14995683343681543, 0.1499568788922417, 0.149956924347668, 0.14995692827690627, 0.14995692967410676, 0.14995693078334768, 0.1499569318925886, 0.14995693300182952, 0.14995693411107044, 0.14995693684583233, 0.14995693958059422, 0.1499569423153561, 0.149956969662975, 0.1499569970105939, 0.14995720082423536, 0.14995740463787682, 0.14995944277429146, 0.1499614809107061, 0.14997097707555088, 0.14998047324039565, 0.14998996940524043, 0.15003812737995714, 0.15008628535467386, 0.15013444332939058, 0.15061602307655775, 0.15109760282372492, 0.1515791825708921, 0.15278870482174728, 0.15399822707260247, 0.15520774932345766, 0.15641727157431284, 0.15965485681623826, 0.16289244205816367, 0.16613002730008908, 0.1693676125420145, 0.1726051977839399, 0.17809648739604633, 0.18358777700815276, 0.1890790666202592, 0.19457035623236563, 0.20006164584447206, 0.205433444796036, 0.21080524374759996, 0.2161770426991639, 0.22154884165072786, 0.2269206406022918, 0.23229243955385576, 0.23768354462588326, 0.24307464969791076, 0.24846575476993826, 0.25385685984196577, 0.25924796491399327, 0.26537304705479564, 0.271498129195598, 0.2776232113364004, 0.28374829347720276, 0.28987337561800514, 0.2959984577588075, 0.30208236154698315, 0.3081662653351588, 0.3142501691233344, 0.32033407291151006, 0.3264179766996857, 0.33250188048786133, 0.34024791744711774, 0.34799395440637415, 0.35573999136563056, 0.36348602832488697, 0.3712320652841434, 0.3789781022433998, 0.3879595588935522, 0.39694101554370465, 0.4059224721938571, 0.4149039288440095, 0.42388538549416194, 0.43286684214431437, 0.4427765175989853, 0.4526861930536562, 0.4625958685083271, 0.47250554396299804, 0.48241521941766896, 0.4923248948723399, 0.5078017730746288, 0.5232786512769178, 0.5387555294792067, 0.5542324076814956, 0.5697092858837846, 0.5956880318220669, 0.6216667777603492, 0.6476455236986315, 0.6736242696369138, 0.6996030155751961, 0.730675493841438, 0.76174797210768, 0.7928204503739219, 0.8238929286401638, 0.8549654069064058, 0.8705005864755857, 0.8860357660447656, 0.8925509513155607, 0.8957091024117029, 0.8963960202775438, 0.8966800920517733, 0.89683644145261, 0.8969927908534466, 0.8971491402542833, 0.8973054896551199, 0.8974618390559566, 0.8976181884567932, 0.8978266268652428, 0.8980350652736925, 0.8982435036821421, 0.8984519420905918, 0.8986603804990414, 0.898868818907491, 0.8992614375282437, 0.8996540561489964, 0.9000466747697491, 0.9004392933905018, 0.9008319120112545, 0.9019179232108028, 0.9030039344103511, 0.9040899456098994, 0.9051759568094477, 0.9098165679872066, 0.9144571791649654, 0.9190977903427242, 0.9377182006256702, 0.9563386109086163, 0.9749590211915623, 1.007929351821182, 1.0408996824508017, 1.0738700130804213, 1.106840343710041, 1.1581313989022437, 1.2094224540944465, 1.2607135092866493, 1.312004564478852, 1.3632956196710548, 1.4258815730102676, 1.4884675263494804, 1.5510534796886932, 1.613639433027906, 1.6762253863671188, 1.7388113397063316, 1.8330633065498896, 1.9273152733934475, 2.0215672402370055, 2.1158192070805635, 2.2100711739241214, 2.329732656424855, 2.449394138925588, 2.5690556214263216, 2.688717103927055, 2.8083785864277884, 2.9280400689285218, 3.094469605547445, 3.2608991421663687, 3.427328678785292, 3.5937582154042156, 3.760187752023139, 3.9266172886420625, 4.14802055993888, 4.369423831235697, 4.590827102532515, 4.812230373829332, 5.03363364512615, 5.255036916422967, 5.51458447410526, 5.774132031787553, 6.033679589469846, 6.293227147152138, 6.552774704834431, 6.812322262516724, 7.1938562755303845, 7.575390288544045, 7.956924301557706, 8.338458314571366, 8.719992327585025, 9.101526340598685, 9.60892191866277, 10.0]</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.6173931247993982</v>
+        <v>0.6173932379650005</v>
       </c>
       <c r="D22" t="n">
         <v>9.81</v>
@@ -1907,13 +1907,13 @@
         <v>2</v>
       </c>
       <c r="L22" t="n">
-        <v>6.173931247993982</v>
+        <v>6.173932379650005</v>
       </c>
       <c r="M22" t="n">
-        <v>0.005246943864066328</v>
+        <v>0.005246941940580709</v>
       </c>
       <c r="N22" t="n">
-        <v>0.02623471932033164</v>
+        <v>0.02623470970290354</v>
       </c>
       <c r="O22" t="n">
         <v>19.60901458858012</v>
@@ -1943,11 +1943,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[0.0, 5.944488780282292e-07, 1.1888977560564584e-06, 7.133386536338751e-06, 1.3077875316621043e-05, 3.087203368348269e-05, 4.866619205034434e-05, 6.646035041720599e-05, 0.00011044783811067776, 0.00015443532580414952, 0.00019842281349762128, 0.00041403805564296705, 0.0006296532977883129, 0.0008452685399336587, 0.0016425159212537816, 0.0024397633025739045, 0.0032370106838940276, 0.004257415261249784, 0.00527781983860554, 0.006298224415961296, 0.007318628993317052, 0.00939264829230413, 0.01146666759129121, 0.01354068689027829, 0.01561470618926537, 0.017688725488252448, 0.0232039652241127, 0.028719204959972953, 0.034234444695833206, 0.03974968443169346, 0.04526492416755371, 0.05347131729000547, 0.061677710412457225, 0.06988410353490898, 0.07809049665736073, 0.08629688977981248, 0.09450328290226423, 0.10218031029233846, 0.10985733768241268, 0.11753436507248691, 0.12521139246256113, 0.13288841985263536, 0.14056544724270958, 0.1471557981074257, 0.15374614897214184, 0.16033649983685797, 0.1669268507015741, 0.17351720156629022, 0.18010755243100635, 0.1860609114584641, 0.19201427048592185, 0.1979676295133796, 0.20392098854083734, 0.2098743475682951, 0.21595781269785097, 0.22204127782740685, 0.22812474295696272, 0.2342082080865186, 0.24029167321607448, 0.24637513834563035, 0.2522363983306096, 0.2580976583155889, 0.26395891830056817, 0.26982017828554744, 0.2756814382705267, 0.28105719943111324, 0.28643296059169976, 0.2918087217522863, 0.2971844829128728, 0.30256024407345933, 0.30793600523404585, 0.31587654760122275, 0.32381708996839964, 0.33175763233557654, 0.33969817470275343, 0.3476387170699303, 0.3555792594371072, 0.36574950412827895, 0.37591974881945067, 0.3860899935106224, 0.3962602382017941, 0.40643048289296585, 0.4166007275841376, 0.42757462824477294, 0.4385485289054083, 0.44952242956604366, 0.460496330226679, 0.4714702308873144, 0.48244413154794974, 0.49873194391693876, 0.5150197562859278, 0.5313075686549168, 0.5475953810239058, 0.5638831933928948, 0.5801710057618839, 0.6016949883924486, 0.6232189710230134, 0.6447429536535781, 0.6662669362841429, 0.6877909189147077, 0.7214200693555332, 0.7550492197963586, 0.7886783702371841, 0.8223075206780096, 0.8559366711188351, 0.892004563037527, 0.9280724549562188, 0.9641403468749107, 1.0002082387936024, 1.0362761307122943, 1.1009918878064133, 1.1657076449005324, 1.2304234019946514, 1.2951391590887704, 1.3598549161828895, 1.4245706732770085, 1.4907119341653312, 1.556853195053654, 1.6229944559419767, 1.6891357168302994, 1.7552769777186221, 1.8214182386069449, 1.9073671068179952, 1.9933159750290455, 2.0792648432400958, 2.165213711451146, 2.2511625796621964, 2.3371114478732467, 2.458178796713657, 2.5792461455540674, 2.7003134943944778, 2.821380843234888, 2.9424481920752985, 3.063515540915709, 3.225670033651935, 3.3878245263881612, 3.5499790191243874, 3.7121335118606136, 3.8742880045968398, 4.036442497333066, 4.253900534930774, 4.471358572528482, 4.68881661012619, 4.906274647723897, 5.123732685321605, 5.341190722919313, 5.631615181210967, 5.922039639502621, 6.2124640977942756, 6.50288855608593, 6.793313014377584, 7.083737472669238, 7.474434513872108, 7.865131555074978, 8.255828596277848, 8.646525637480718, 9.037222678683587, 9.427919719886457, 9.955595105529621, 10.0]</t>
+          <t>[0.0, 1.3292285138155904e-05, 2.6584570276311808e-05, 0.00015950742165787084, 0.00029243027303942987, 0.0008163771202589548, 0.0013403239674784797, 0.0018642708146980047, 0.0037965093405906846, 0.005728747866483364, 0.007660986392376045, 0.013493686850561326, 0.019326387308746605, 0.025159087766931883, 0.03099178822511716, 0.04056798904648493, 0.050144189867852705, 0.05972039068922048, 0.06929659151058826, 0.07887279233195604, 0.08956293991265914, 0.10025308749336223, 0.11094323507406532, 0.12163338265476842, 0.1293046157785846, 0.13697584890240078, 0.14464708202621696, 0.14467105462972887, 0.1446950272332408, 0.1447189998367527, 0.14474297244026463, 0.14476694504377655, 0.14479091764728846, 0.14503064368240765, 0.14527036971752683, 0.145510095752646, 0.1457498217877652, 0.14598954782288437, 0.14781780659937915, 0.1481834583546781, 0.14854911010997707, 0.14891476186527602, 0.14928041362057498, 0.14939622404420352, 0.14941938612892924, 0.14944254821365496, 0.14946571029838068, 0.1494888723831064, 0.14948924297646202, 0.14948961356981763, 0.14948968768848875, 0.14948970251222296, 0.14948970369947387, 0.14948970435701708, 0.1494897050145603, 0.1494897056721035, 0.14948970637980347, 0.14948970708750342, 0.14948970779520337, 0.14948971487220292, 0.14948972194920246, 0.14948977014777023, 0.149489818346338, 0.14949030033201577, 0.14949078231769353, 0.14949515426842971, 0.1494995262191659, 0.14951324352761924, 0.1495269608360726, 0.14954067814452593, 0.14959561406962285, 0.14965054999471977, 0.1497054859198167, 0.1502548451707859, 0.15080420442175513, 0.15135356367272434, 0.15263872548196344, 0.15392388729120254, 0.15520904910044164, 0.15649421090968074, 0.15976561443501372, 0.1630370179603467, 0.16630842148567967, 0.16957982501101265, 0.17285122853634563, 0.1783067477251473, 0.18376226691394895, 0.1892177861027506, 0.19467330529155227, 0.20012882448035393, 0.20553338689627895, 0.21093794931220397, 0.216342511728129, 0.221747074144054, 0.22715163655997903, 0.23255619897590404, 0.23804833822431595, 0.24354047747272786, 0.24903261672113977, 0.2545247559695517, 0.2600168952179637, 0.2663613196941656, 0.2727057441703675, 0.27905016864656945, 0.2853945931227714, 0.2917390175989733, 0.29808344207517523, 0.30417785402904707, 0.3102722659829189, 0.31636667793679074, 0.3224610898906626, 0.3285555018445344, 0.33464991379840625, 0.3434412196233603, 0.3522325254483144, 0.3610238312732685, 0.36981513709822256, 0.37860644292317663, 0.3873977487481307, 0.3956294581645236, 0.4038611675809165, 0.4120928769973094, 0.4203245864137023, 0.4285562958300952, 0.4367880052464881, 0.44781432835926405, 0.45884065147204, 0.46986697458481597, 0.4808932976975919, 0.4919196208103679, 0.5029459439231438, 0.5219762357281766, 0.5410065275332094, 0.5600368193382422, 0.579067111143275, 0.5980974029483078, 0.6171276947533406, 0.6461994279013857, 0.6752711610494309, 0.704342894197476, 0.7334146273455211, 0.7624863604935662, 0.7915580936416113, 0.8042883509257114, 0.8093789595297708, 0.8107380445306209, 0.8111700658373492, 0.811509750178886, 0.8117547619755386, 0.8119997737721912, 0.8122447855688438, 0.8124897973654964, 0.812734809162149, 0.8131367978410627, 0.8135387865199765, 0.8139407751988902, 0.8143427638778039, 0.815571952751848, 0.8168011416258921, 0.8180303304999362, 0.8229507587869234, 0.8278711870739105, 0.8327916153608976, 0.8520236633001359, 0.8712557112393742, 0.8904877591786124, 0.9247492120915478, 0.9590106650044832, 0.9932721179174185, 1.027533570830354, 1.0671392758766232, 1.1067449809228924, 1.1463506859691617, 1.185956391015431, 1.2255620960617002, 1.2796803565309691, 1.333798617000238, 1.387916877469507, 1.442035137938776, 1.4961533984080448, 1.5502716588773138, 1.634502793473353, 1.718733928069392, 1.8029650626654312, 1.8871961972614704, 1.9714273318575095, 2.055658466453549, 2.1586510412971225, 2.261643616140696, 2.3646361909842697, 2.4676287658278433, 2.570621340671417, 2.6736139155149905, 2.8271570756773268, 2.980700235839663, 3.1342433960019993, 3.2877865561643356, 3.441329716326672, 3.594872876489008, 3.796796764522175, 3.998720652555342, 4.200644540588509, 4.4025684286216755, 4.604492316654842, 4.806416204688009, 5.042840984615939, 5.279265764543869, 5.5156905444717985, 5.752115324399728, 5.988540104327658, 6.224964884255588, 6.571928484056238, 6.918892083856889, 7.26585568365754, 7.61281928345819, 7.959782883258841, 8.306746483059491, 8.767660799167016, 9.228575115274541, 9.689489431382066, 10.0]</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.6145995938683858</v>
+        <v>0.6145996269497056</v>
       </c>
       <c r="D23" t="n">
         <v>9.81</v>
@@ -1974,13 +1974,13 @@
         <v>2</v>
       </c>
       <c r="L23" t="n">
-        <v>6.145995938683858</v>
+        <v>6.145996269497056</v>
       </c>
       <c r="M23" t="n">
-        <v>0.005294749984958232</v>
+        <v>0.005294749414969884</v>
       </c>
       <c r="N23" t="n">
-        <v>0.02647374992479116</v>
+        <v>0.02647374707484942</v>
       </c>
       <c r="O23" t="n">
         <v>19.60610504505627</v>
@@ -2010,11 +2010,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[0.0, 5.945046676994561e-07, 1.1890093353989121e-06, 7.134056012393473e-06, 1.3079102689388034e-05, 3.087493474714006e-05, 4.8670766804892084e-05, 6.646659886264411e-05, 0.00011045835782497391, 0.00015445011678730372, 0.00019844187574963353, 0.0004141575321633959, 0.0006298731885771582, 0.0008455888449909205, 0.0016413683311895383, 0.002437147817388156, 0.003232927303586774, 0.0040287067897853916, 0.005628657681912624, 0.0072286085740398565, 0.008828559466167089, 0.010428510358294322, 0.012028461250421554, 0.017014693520785565, 0.022000925791149574, 0.026987158061513583, 0.03197339033187759, 0.0369596226022416, 0.04403336667449801, 0.05110711074675442, 0.05818085481901083, 0.06525459889126724, 0.07232834296352364, 0.07940208703578004, 0.08813937367631304, 0.09687666031684604, 0.10328030602942907, 0.1096839517420121, 0.11608759745459514, 0.12249124316717817, 0.1288948888797612, 0.1359802262474419, 0.14306556361512263, 0.15015090098280334, 0.15723623835048406, 0.16432157571816478, 0.1714069130858455, 0.1783247391576919, 0.1852425652295383, 0.1921603913013847, 0.19907821737323111, 0.20599604344507752, 0.21291386951692393, 0.2193308342510943, 0.22574779898526465, 0.232164763719435, 0.23858172845360537, 0.24499869318777573, 0.2514156579219461, 0.25628552513598685, 0.2611553923500276, 0.26602525956406836, 0.2708951267781091, 0.2757649939921499, 0.28063486120619063, 0.2870822155652922, 0.2935295699243937, 0.29997692428349526, 0.3064242786425968, 0.31287163300169835, 0.3193189873607999, 0.33097656873708575, 0.3397026475856276, 0.3484287264341695, 0.3571548052827114, 0.36588088413125325, 0.3746069629797951, 0.38447200241696333, 0.39433704185413154, 0.40420208129129975, 0.41406712072846796, 0.4239321601656362, 0.4337971996028044, 0.4468789137202124, 0.4599606278376204, 0.47304234195502837, 0.48612405607243636, 0.49920577018984436, 0.5122874843072523, 0.5281589193034397, 0.5440303542996271, 0.5599017892958145, 0.5757732242920018, 0.5916446592881892, 0.6160523308668864, 0.6404600024455835, 0.6648676740242807, 0.6892753456029779, 0.713683017181675, 0.7488215004260178, 0.7839599836703606, 0.8190984669147033, 0.8542369501590461, 0.8893754334033889, 0.9272048054446156, 0.9650341774858423, 1.002863549527069, 1.0406929215682958, 1.0785222936095227, 1.1393978778454164, 1.20027346208131, 1.2611490463172037, 1.3220246305530974, 1.382900214788991, 1.4437757990248847, 1.5118480942757162, 1.5799203895265477, 1.6479926847773791, 1.7160649800282106, 1.784137275279042, 1.8898132353754833, 1.9954891954719245, 2.1011651555683657, 2.206841115664807, 2.312517075761248, 2.4181930358576893, 2.5496873429402727, 2.681181650022856, 2.8126759571054394, 2.9441702641880227, 3.075664571270606, 3.2071588783531895, 3.3586472861313283, 3.5101356939094672, 3.661624101687606, 3.813112509465745, 3.964600917243884, 4.116089325022022, 4.357203061593634, 4.598316798165246, 4.8394305347368585, 5.0805442713084705, 5.321658007880083, 5.562771744451695, 5.853350136926949, 6.143928529402203, 6.434506921877457, 6.725085314352711, 7.015663706827965, 7.306242099303219, 7.703469219102929, 8.100696338902639, 8.497923458702349, 8.89515057850206, 9.29237769830177, 9.68960481810148, 10.0]</t>
+          <t>[0.0, 1.3293532823710937e-05, 2.6587065647421874e-05, 0.00015952239388453121, 0.00029245772212164057, 0.0008126071932632832, 0.0013327566644049259, 0.0018529061355465684, 0.0037619466738386567, 0.005670987212130745, 0.007580027750422833, 0.013375940187571673, 0.019171852624720515, 0.024967765061869356, 0.030763677499018198, 0.04028923871321959, 0.04981479992742099, 0.05934036114162238, 0.06886592235582378, 0.07839148357002518, 0.08906396151793704, 0.0997364394658489, 0.11040891741376076, 0.12108139536167262, 0.128733830798184, 0.1363862662346954, 0.1440387016712068, 0.1440626155319459, 0.14408652939268501, 0.14411044325342412, 0.14413435711416323, 0.14415827097490233, 0.14418218483564144, 0.1444213234430325, 0.14466046205042354, 0.1448996006578146, 0.14513873926520565, 0.1453778778725967, 0.14720524276377314, 0.14757071574200842, 0.1479361887202437, 0.14830166169847897, 0.14866713467671425, 0.14878293139871848, 0.14889872812072272, 0.14890335998960288, 0.14890799185848305, 0.14890891823225907, 0.1489098446060351, 0.14891077097981112, 0.14891169735358714, 0.14891206790309755, 0.14891214201299963, 0.1489122161229017, 0.14891229023280378, 0.14891231987676462, 0.14891234952072546, 0.1489123566789483, 0.1489123594519696, 0.14891236018156204, 0.14891236091115448, 0.14891236164074692, 0.14891236279029366, 0.1489123639398404, 0.14891237543530775, 0.1489123869307751, 0.14891250188544866, 0.14891261684012222, 0.1489137663868578, 0.14891491593359338, 0.1489220251409443, 0.14892913434829522, 0.14893624355564614, 0.1489794794259288, 0.14902271529621144, 0.1490659511664941, 0.14949830986932064, 0.14993066857214718, 0.15036302727497372, 0.15150842250453156, 0.1526538177340894, 0.15379921296364724, 0.15494460819320507, 0.15811263332605613, 0.16128065845890718, 0.16444868359175824, 0.1676167087246093, 0.17078473385746035, 0.1762692491286296, 0.18175376439979885, 0.1872382796709681, 0.19272279494213734, 0.1982073102133066, 0.2035431263405481, 0.20887894246778962, 0.21421475859503114, 0.21955057472227266, 0.22488639084951417, 0.2302222069767557, 0.23553191426408135, 0.240841621551407, 0.24615132883873267, 0.2514610361260583, 0.2567707434133839, 0.26275601313549135, 0.2687412828575988, 0.27472655257970624, 0.2807118223018137, 0.28669709202392113, 0.2926823617460286, 0.2987480403107079, 0.3048137188753872, 0.31087939744006654, 0.31694507600474586, 0.3230107545694252, 0.3290764331341045, 0.3367984439122384, 0.3445204546903723, 0.3522424654685062, 0.3599644762466401, 0.36768648702477397, 0.37539293818547004, 0.3830993893461661, 0.3908058405068622, 0.39851229166755825, 0.4062187428282543, 0.4139251939889504, 0.42483857445130524, 0.4357519549136601, 0.44666533537601494, 0.4575787158383698, 0.46849209630072464, 0.4794054767630795, 0.49512206045786666, 0.5108386441526538, 0.5265552278474409, 0.542271811542228, 0.5579883952370152, 0.5737049789318023, 0.5971470785831418, 0.6205891782344812, 0.6440312778858207, 0.6674733775371602, 0.6909154771884997, 0.7189642179227608, 0.7283319862849997, 0.7322230627074539, 0.7341497739111102, 0.7348501037219435, 0.7351411772928498, 0.735352835888385, 0.7355644944839201, 0.7357761530794553, 0.7359878116749905, 0.7361994702705257, 0.7365486140451779, 0.7368977578198301, 0.7372469015944824, 0.7375960453691346, 0.7386660112997565, 0.7397359772303784, 0.7408059431610003, 0.7451031740724017, 0.749400404983803, 0.7536976358952043, 0.7708949647307729, 0.7880922935663415, 0.80528962240191, 0.8355226239842095, 0.865755625566509, 0.8959886271488084, 0.9262216287311079, 0.961792791669328, 0.997363954607548, 1.032935117545768, 1.0685062804839878, 1.1040774434222076, 1.1574548230982413, 1.210832202774275, 1.2642095824503088, 1.3175869621263425, 1.3709643418023763, 1.42434172147841, 1.4927589357592166, 1.5611761500400232, 1.6295933643208298, 1.6980105786016364, 1.766427792882443, 1.8348450071632496, 1.934603327973838, 2.0343616487844263, 2.1341199695950146, 2.233878290405603, 2.3336366112161913, 2.4333949320267796, 2.5672098344131866, 2.7010247367995937, 2.8348396391860007, 2.9686545415724077, 3.1024694439588147, 3.2362843463452218, 3.3889331495132486, 3.5415819526812755, 3.6942307558493024, 3.8468795590173293, 3.999528362185356, 4.1521771653533825, 4.3955381115440515, 4.63889905773472, 4.882260003925389, 5.125620950116058, 5.368981896306727, 5.612342842497396, 5.905644895705513, 6.19894694891363, 6.4922490021217465, 6.785551055329863, 7.07885310853798, 7.372155161746097, 7.7731714089997785, 8.17418765625346, 8.575203903507141, 8.976220150760822, 9.377236398014503, 9.778252645268184, 10.0]</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.611153500492971</v>
+        <v>0.611153536860171</v>
       </c>
       <c r="D24" t="n">
         <v>9.81</v>
@@ -2041,13 +2041,13 @@
         <v>2</v>
       </c>
       <c r="L24" t="n">
-        <v>6.11153500492971</v>
+        <v>6.11153536860171</v>
       </c>
       <c r="M24" t="n">
-        <v>0.005354629033341843</v>
+        <v>0.005354628396078543</v>
       </c>
       <c r="N24" t="n">
-        <v>0.02677314516670921</v>
+        <v>0.02677314198039272</v>
       </c>
       <c r="O24" t="n">
         <v>19.60242489375145</v>
@@ -2077,11 +2077,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[0.0, 5.94575255782134e-07, 1.189150511564268e-06, 7.1349030693856085e-06, 1.3080655627206949e-05, 3.087860532904964e-05, 4.867655503089233e-05, 6.647450473273503e-05, 0.0001104716679576113, 0.00015446883118248756, 0.00019846599440736382, 0.0004143088822493571, 0.0006301517700913504, 0.0008459946579333437, 0.0016471818873487188, 0.0024483691167640938, 0.0032495563461794686, 0.004050743575594843, 0.005652384037579536, 0.007254024499564228, 0.00885566496154892, 0.010457305423533611, 0.012058945885518303, 0.017094714900042964, 0.022130483914567626, 0.027166252929092288, 0.032202021943616946, 0.0372377909581416, 0.04435875984730785, 0.051479728736474106, 0.05860069762564036, 0.06572166651480661, 0.07284263540397287, 0.07996360429313913, 0.0885722500892998, 0.09718089588546046, 0.10350923489936502, 0.10983757391326958, 0.11616591292717414, 0.1224942519410787, 0.12882259095498327, 0.13589088224719797, 0.14295917353941268, 0.15002746483162738, 0.15709575612384208, 0.16416404741605678, 0.17123233870827148, 0.178090432649844, 0.18494852659141653, 0.19180662053298905, 0.19866471447456158, 0.2055228084161341, 0.21238090235770662, 0.21890622435954268, 0.22543154636137874, 0.2319568683632148, 0.23848219036505086, 0.24500751236688692, 0.251532834368723, 0.2564386731464192, 0.26134451192411545, 0.2662503507018117, 0.2711561894795079, 0.27606202825720416, 0.2809678670349004, 0.28736716925491146, 0.2937664714749225, 0.3001657736949336, 0.30656507591494464, 0.3129643781349557, 0.31936368035496676, 0.3308549858581892, 0.3394872009418228, 0.3481194160254564, 0.35675163110909, 0.36538384619272357, 0.37401606127635717, 0.38499952872651305, 0.39598299617666893, 0.4069664636268248, 0.4179499310769807, 0.4289333985271366, 0.43991686597729246, 0.45286600667830074, 0.465815147379309, 0.4787642880803173, 0.49171342878132557, 0.5046625694823339, 0.5176117101833422, 0.5344062419065181, 0.551200773629694, 0.5679953053528699, 0.5847898370760458, 0.6015843687992217, 0.6270357956152892, 0.6524872224313567, 0.6779386492474242, 0.7033900760634917, 0.7288415028795592, 0.7652648528153895, 0.8016882027512198, 0.8381115526870501, 0.8745349026228804, 0.9109582525587107, 0.9497889972628736, 0.9886197419670365, 1.0274504866711993, 1.066281231375362, 1.1051119760795247, 1.16782420857826, 1.2305364410769952, 1.2932486735757305, 1.3559609060744657, 1.418673138573201, 1.4813853710719362, 1.551432945720271, 1.6214805203686056, 1.6915280950169402, 1.761575669665275, 1.8316232443136096, 1.9376392509890839, 2.0436552576645584, 2.149671264340033, 2.255687271015508, 2.3617032776909825, 2.4677192843664573, 2.602797378922311, 2.737875473478165, 2.872953568034019, 3.0080316625898726, 3.1431097571457265, 3.2781878517015803, 3.4330552335274476, 3.587922615353315, 3.742789997179182, 3.8976573790050493, 4.0525247608309165, 4.207392142656784, 4.4540983700118275, 4.700804597366871, 4.947510824721915, 5.194217052076959, 5.440923279432003, 5.687629506787046, 5.985125660106362, 6.282621813425677, 6.580117966744992, 6.877614120064307, 7.1751102733836225, 7.472606426702938, 7.879385302875142, 8.286164179047347, 8.692943055219551, 9.099721931391755, 9.50650080756396, 9.913279683736164, 10.0]</t>
+          <t>[0.0, 1.3295111468658855e-05, 2.659022293731771e-05, 0.00015954133762390623, 0.00029249245231049477, 0.0008079893426675322, 0.0013234862330245697, 0.0018389831233816072, 0.003719632495872968, 0.005600281868364329, 0.007480931240855689, 0.013232474451319528, 0.018984017661783367, 0.024735560872247205, 0.030487104082711044, 0.03995034375682099, 0.04941358343093093, 0.05887682310504087, 0.0683400627791508, 0.07780330245326075, 0.0884543194605939, 0.09910533646792705, 0.1097563534752602, 0.12040737048259334, 0.12803644776990217, 0.135665525057211, 0.14329460234451982, 0.14331844321104265, 0.14334228407756547, 0.1433661249440883, 0.14338996581061111, 0.14341380667713394, 0.14343764754365676, 0.143676056208885, 0.14391446487411322, 0.14415287353934145, 0.14439128220456968, 0.1446296908697979, 0.14645605909716344, 0.14682133274263656, 0.14718660638810968, 0.1475518800335828, 0.14791715367905592, 0.14803294207149867, 0.14814873046394142, 0.14817188814242996, 0.1481950458209185, 0.1481996773566162, 0.14820060366375576, 0.1482015299708953, 0.14820245627803486, 0.14820264153946278, 0.1482028268008907, 0.14820284288053553, 0.14820285896018037, 0.14820286155789036, 0.14820286300905863, 0.14820286416286, 0.14820286531666135, 0.1482028664704627, 0.14820286762426407, 0.14820287047143904, 0.148202873318614, 0.14820287616578898, 0.14820290463753866, 0.14820293310928834, 0.14820314545605187, 0.1482033578028154, 0.14820548127045075, 0.14820760473808609, 0.14821737145683325, 0.14822713817558042, 0.1482369048943276, 0.1482859303029742, 0.14833495571162084, 0.14838398112026746, 0.1488742352067337, 0.14936448929319995, 0.1498547433796662, 0.15106688740281293, 0.15227903142595967, 0.1534911754491064, 0.15470331947225313, 0.15789865376337642, 0.1610939880544997, 0.164289322345623, 0.16748465663674628, 0.17067999092786956, 0.176124311570664, 0.18156863221345843, 0.18701295285625286, 0.1924572734990473, 0.19790159414184172, 0.20326870710396835, 0.208635820066095, 0.21400293302822163, 0.21937004599034826, 0.2247371589524749, 0.23010427191460153, 0.235501179027558, 0.24089808614051444, 0.2462949932534709, 0.25169190036642736, 0.2570888074793838, 0.2632302513842154, 0.26937169528904703, 0.27551313919387865, 0.2816545830987103, 0.2877960270035419, 0.2939374709083735, 0.300012205491479, 0.3060869400745845, 0.31216167465768996, 0.31823640924079544, 0.3243111438239009, 0.3303858784070064, 0.338954942802313, 0.34752400719761956, 0.35609307159292614, 0.3646621359882327, 0.3732312003835393, 0.3818002647788459, 0.3899708626757682, 0.3981414605726905, 0.4063120584696128, 0.41448265636653514, 0.42265325426345746, 0.43082385216037977, 0.4416210765549423, 0.45241830094950486, 0.4632155253440674, 0.47401274973862995, 0.4848099741331925, 0.49560719852775503, 0.5136586911597071, 0.5317101837916591, 0.5497616764236112, 0.5678131690555632, 0.5858646616875153, 0.6039161543194673, 0.631882660492154, 0.6598491666648407, 0.6641422862274325, 0.6662497166720662, 0.6669603969715852, 0.6671581487051292, 0.6672676111273597, 0.6673770735495901, 0.6674865359718205, 0.6675959983940509, 0.6677054608162813, 0.6678149232385118, 0.6679614017222358, 0.6681078802059599, 0.668254358689684, 0.668400837173408, 0.6685473156571321, 0.6686937941408562, 0.6689680524442182, 0.6692423107475802, 0.6695165690509423, 0.6697908273543043, 0.6700650856576663, 0.6708253950578478, 0.6715857044580292, 0.6723460138582107, 0.6731063232583921, 0.676368713264064, 0.6796311032697359, 0.6828934932754077, 0.6960263760239878, 0.7091592587725678, 0.7222921415211478, 0.7455208173732863, 0.7687494932254249, 0.7919781690775634, 0.8152068449297019, 0.8539595390698536, 0.8927122332100053, 0.931464927350157, 0.9702176214903087, 1.0089703156304604, 1.0607521187903814, 1.1125339219503025, 1.1643157251102236, 1.2160975282701447, 1.2678793314300658, 1.319661134589987, 1.3822744304855572, 1.4448877263811275, 1.5075010222766978, 1.570114318172268, 1.6327276140678384, 1.7309621502142545, 1.8291966863606706, 1.9274312225070866, 2.0256657586535027, 2.1239002947999186, 2.2221348309463345, 2.34198559334025, 2.4618363557341656, 2.581687118128081, 2.7015378805219967, 2.8213886429159123, 2.941239405309828, 3.1077649434024095, 3.274290481494991, 3.4408160195875728, 3.6073415576801544, 3.773867095772736, 3.9403926338653177, 4.162654958681717, 4.384917283498116, 4.607179608314516, 4.829441933130915, 5.051704257947314, 5.273966582763713, 5.534461327588219, 5.794956072412725, 6.05545081723723, 6.315945562061736, 6.576440306886242, 6.836935051710747, 7.220044885078329, 7.603154718445912, 7.986264551813494, 8.369374385181075, 8.752484218548656, 9.135594051916236, 9.64519420659096, 10.0]</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.6069268253021186</v>
+        <v>0.6069267911613294</v>
       </c>
       <c r="D25" t="n">
         <v>9.81</v>
@@ -2108,13 +2108,13 @@
         <v>2</v>
       </c>
       <c r="L25" t="n">
-        <v>6.069268253021185</v>
+        <v>6.069267911613294</v>
       </c>
       <c r="M25" t="n">
-        <v>0.005429468645042354</v>
+        <v>0.005429469255878298</v>
       </c>
       <c r="N25" t="n">
-        <v>0.02714734322521177</v>
+        <v>0.02714734627939149</v>
       </c>
       <c r="O25" t="n">
         <v>19.59777003517474</v>
@@ -2144,11 +2144,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[0.0, 5.946645750668049e-07, 1.1893291501336098e-06, 7.135974900801659e-06, 1.3082620651469708e-05, 3.0883249934941384e-05, 4.868387921841306e-05, 6.648450850188473e-05, 0.00011048851009924339, 0.00015449251169660205, 0.0001984965132939607, 0.00041450068677916733, 0.0006305048602643739, 0.0008465090337495805, 0.0016547950760173635, 0.0024630811182851466, 0.0032713671605529297, 0.004079653202820712, 0.005683664397223858, 0.007287675591627003, 0.008891686786030148, 0.010495697980433294, 0.012099709174836439, 0.017202237272468904, 0.02230476537010137, 0.027407293467733837, 0.032509821565366304, 0.03761234966299877, 0.04479693101075478, 0.051981512358510784, 0.05916609370626679, 0.0663506750540228, 0.0735352564017788, 0.0807198377495348, 0.08914308958042756, 0.09756634141132033, 0.10598959324221309, 0.11195124776229236, 0.11791290228237163, 0.1238745568024509, 0.12983621132253015, 0.1357978658426094, 0.14282186817713954, 0.1498458705116697, 0.15686987284619985, 0.16389387518073, 0.17091787751526016, 0.17794187984979032, 0.18387387343678202, 0.18980586702377372, 0.19573786061076542, 0.20166985419775713, 0.20760184778474883, 0.21373641270509317, 0.2198709776254375, 0.22600554254578184, 0.23214010746612618, 0.23827467238647052, 0.24440923730681485, 0.25011063170527414, 0.25581202610373344, 0.26151342050219273, 0.267214814900652, 0.2729162092991113, 0.27827990730283925, 0.2836436053065672, 0.2890073033102951, 0.29437100131402305, 0.299734699317751, 0.3050983973214789, 0.312844921106111, 0.3205914448907431, 0.3283379686753752, 0.33608449246000727, 0.34383101624463935, 0.35157754002927144, 0.3609198466985441, 0.37026215336781676, 0.3796044600370894, 0.3889467667063621, 0.39828907337563474, 0.4076313800449074, 0.4184350991146627, 0.429238818184418, 0.4400425372541733, 0.4508462563239286, 0.4616499753936839, 0.4724536944634392, 0.487919601913995, 0.5033855093645508, 0.5188514168151066, 0.5343173242656624, 0.5497832317162181, 0.5652491391667739, 0.5880131119835803, 0.6107770848003867, 0.6335410576171931, 0.6563050304339996, 0.679069003250806, 0.7018329760676124, 0.7308413645816199, 0.7598497530956273, 0.7888581416096347, 0.8178665301236422, 0.8468749186376496, 0.8914122908990302, 0.9359496631604107, 0.9804870354217913, 1.0250244076831718, 1.0695617799445523, 1.1213400519356587, 1.173118323926765, 1.2248965959178715, 1.2766748679089779, 1.3284531399000843, 1.3802314118911907, 1.440505363108637, 1.5007793143260835, 1.5610532655435299, 1.6213272167609762, 1.6816011679784226, 1.7698304699875391, 1.8580597719966556, 1.9462890740057721, 2.034518376014889, 2.1227476780240053, 2.210976980033122, 2.3329934069148686, 2.4550098337966153, 2.577026260678362, 2.699042687560109, 2.8210591144418555, 2.9430755413236023, 3.094868663069726, 3.24666178481585, 3.398454906561974, 3.550248028308098, 3.702041150054222, 3.8538342718003458, 4.081307269933646, 4.308780268066946, 4.536253266200246, 4.763726264333546, 4.991199262466846, 5.2186722606001466, 5.514823073229999, 5.810973885859851, 6.107124698489703, 6.403275511119555, 6.699426323749408, 6.99557713637926, 7.345843532695868, 7.696109929012477, 8.046376325329085, 8.396642721645694, 8.746909117962304, 9.097175514278913, 9.615250878718088, 10.0]</t>
+          <t>[0.0, 1.3297109031756244e-05, 2.6594218063512488e-05, 0.00015956530838107493, 0.0002925363986986374, 0.0008023753957504657, 0.001312214392802294, 0.0018220533898541224, 0.003668237573147274, 0.005514421756440425, 0.007360605939733577, 0.013059289073650268, 0.01875797220756696, 0.024456655341483655, 0.030155338475400348, 0.03954237929810116, 0.04892942012080197, 0.058316460943502776, 0.06770350176620359, 0.0770905425889044, 0.08771577497518197, 0.09834100736145955, 0.10896623974773713, 0.1195914721340147, 0.12719163216959362, 0.1347917922051725, 0.1423919522407514, 0.1424157027408626, 0.1424394532409738, 0.14246320374108498, 0.14248695424119617, 0.14251070474130736, 0.14253445524141856, 0.14277196024253047, 0.1430094652436424, 0.1432469702447543, 0.14348447524586622, 0.14372198024697813, 0.14554729919671947, 0.14591236298666774, 0.146277426776616, 0.14664249056656428, 0.14700755435651255, 0.14712334653752324, 0.14723913871853392, 0.14726229715473604, 0.14728545559093817, 0.1473086140271403, 0.14733177246334242, 0.14733362513823858, 0.14733547781313475, 0.14733584834811397, 0.1473362188830932, 0.14733658941807243, 0.14733661906087075, 0.14733664870366908, 0.1473366783464674, 0.14733669020358675, 0.1473367020607061, 0.14733671391782543, 0.14733671866067316, 0.1473367234035209, 0.14733672530065997, 0.14733672591811808, 0.1473367265355762, 0.14733672678768364, 0.1473367270397911, 0.1473367276093928, 0.14733672817899449, 0.14733673366382147, 0.14733673914864845, 0.14733679399691826, 0.14733684884518808, 0.14733739732788623, 0.14733794581058438, 0.14734343063756586, 0.14734891546454734, 0.14735440029152883, 0.1473971189228144, 0.14743983755409998, 0.14748255618538555, 0.14790974249824132, 0.14833692881109709, 0.14876411512395285, 0.14989579760252245, 0.15102748008109204, 0.15215916255966164, 0.15329084503823123, 0.1564074708485371, 0.15952409665884296, 0.16264072246914882, 0.16575734827945468, 0.16887397408976054, 0.17432041959548353, 0.1797668651012065, 0.1852133106069295, 0.19065975611265248, 0.19610620161837547, 0.20143034488372427, 0.20675448814907307, 0.21207863141442188, 0.21740277467977068, 0.22272691794511948, 0.22805106121046828, 0.23334298919277763, 0.23863491717508697, 0.24392684515739632, 0.24921877313970567, 0.254510701122015, 0.26046982986007267, 0.2664289585981303, 0.27238808733618797, 0.2783472160742456, 0.28430634481230327, 0.2902654735503609, 0.2963196210484136, 0.30237376854646625, 0.3084279160445189, 0.3144820635425716, 0.32053621104062424, 0.3265903585386769, 0.33431471253512207, 0.34203906653156724, 0.3497634205280124, 0.35748777452445757, 0.36521212852090273, 0.3729058141067917, 0.38059949969268064, 0.3882931852785696, 0.39598687086445855, 0.4036805564503475, 0.41137424203623646, 0.42228210712371306, 0.43318997221118966, 0.44409783729866625, 0.45500570238614285, 0.46591356747361945, 0.47682143256109605, 0.4925375352081534, 0.5082536378552107, 0.5239697405022681, 0.5396858431493254, 0.5554019457963828, 0.5711180484434402, 0.5945235150075144, 0.6022744677434442, 0.6054718583310742, 0.6063647884606752, 0.606598758366714, 0.6067686161940479, 0.6069384740213818, 0.6071083318487157, 0.6072781896760496, 0.6074480475033835, 0.6077279351237407, 0.6080078227440978, 0.608287710364455, 0.6085675979848121, 0.609424942126983, 0.6102822862691538, 0.6111396304113247, 0.6145806299032797, 0.6180216293952346, 0.6214626288871896, 0.6351055632552597, 0.6487484976233298, 0.6623914319913998, 0.6844137375984051, 0.7064360432054103, 0.7284583488124156, 0.7504806544194208, 0.7858784387368654, 0.8212762230543099, 0.8566740073717545, 0.892071791689199, 0.9274695760066436, 0.9786579695893094, 1.0298463631719752, 1.081034756754641, 1.1322231503373068, 1.1834115439199726, 1.2345999375026384, 1.2918981547715729, 1.3491963720405074, 1.4064945893094418, 1.4637928065783763, 1.5210910238473108, 1.6102112630179197, 1.6993315021885287, 1.7884517413591376, 1.8775719805297466, 1.9666922197003556, 2.0558124588709648, 2.1674013834992256, 2.2789903081274865, 2.3905792327557474, 2.502168157384008, 2.613757082012269, 2.72534600664053, 2.8524114877661053, 2.9794769688916807, 3.106542450017256, 3.2336079311428314, 3.3606734122684068, 3.487738893393982, 3.669476152533014, 3.8512134116720462, 4.032950670811078, 4.21468792995011, 4.396425189089142, 4.578162448228174, 4.827230167134686, 5.076297886041197, 5.3253656049477085, 5.57443332385422, 5.823501042760731, 6.072568761667243, 6.404988866051669, 6.737408970436095, 7.069829074820522, 7.402249179204948, 7.7346692835893744, 8.067089387973802, 8.515232024436845, 8.963374660899888, 9.41151729736293, 9.859659933825974, 10.0]</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.6017789637713979</v>
+        <v>0.6017790371352268</v>
       </c>
       <c r="D26" t="n">
         <v>9.81</v>
@@ -2175,13 +2175,13 @@
         <v>2</v>
       </c>
       <c r="L26" t="n">
-        <v>6.017789637713979</v>
+        <v>6.017790371352268</v>
       </c>
       <c r="M26" t="n">
-        <v>0.005522757719390599</v>
+        <v>0.005522756372814521</v>
       </c>
       <c r="N26" t="n">
-        <v>0.02761378859695299</v>
+        <v>0.0276137818640726</v>
       </c>
       <c r="O26" t="n">
         <v>19.59188231302026</v>
@@ -2211,11 +2211,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[0.0, 5.947776079968284e-07, 1.1895552159936568e-06, 7.137331295961941e-06, 1.3085107375930226e-05, 3.0889127652894774e-05, 4.8693147929859324e-05, 6.649716820682387e-05, 0.00011050982377881893, 0.000154522479350814, 0.00019853513492280905, 0.00041474388402821166, 0.0006309526331336143, 0.0008471613822390168, 0.0016648743937297044, 0.002482587405220392, 0.0033003004167110796, 0.004118013428201768, 0.005725417244525171, 0.007332821060848574, 0.008940224877171978, 0.01054762869349538, 0.012155032509818784, 0.01734948528815081, 0.022543938066482836, 0.027738390844814862, 0.032932843623146885, 0.03812729640147891, 0.045399475432279277, 0.05267165446307964, 0.05994383349388001, 0.06721601252468037, 0.07448819155548074, 0.0817603705862811, 0.0899408020790275, 0.09812123357177388, 0.10630166506452027, 0.11277451103914929, 0.11924735701377831, 0.12572020298840733, 0.13219304896303635, 0.13866589493766537, 0.14583038955191555, 0.15299488416616572, 0.1601593787804159, 0.16732387339466606, 0.17448836800891623, 0.1816528626231664, 0.1877153826863763, 0.1937779027495862, 0.1998404228127961, 0.205902942876006, 0.2119654629392159, 0.21820372372381325, 0.2244419845084106, 0.23068024529300796, 0.2369185060776053, 0.24315676686220267, 0.24939502764680002, 0.2552783871635632, 0.26116174668032643, 0.26704510619708965, 0.2729284657138529, 0.2788118252306161, 0.2846951847473793, 0.29046423511539404, 0.29623328548340877, 0.3020023358514235, 0.3077713862194382, 0.31354043658745295, 0.3193094869554677, 0.32759349505284224, 0.3358775031502168, 0.34416151124759137, 0.35244551934496593, 0.3607295274423405, 0.3702590779087829, 0.37978862837522526, 0.38931817884166764, 0.39884772930811, 0.4083772797745524, 0.4179068302409948, 0.42953052950704196, 0.44115422877308913, 0.4527779280391363, 0.4644016273051835, 0.47602532657123064, 0.4876490258372778, 0.5037565295143963, 0.5198640331915148, 0.5359715368686332, 0.5520790405457516, 0.5681865442228701, 0.591547269961761, 0.6149079957006519, 0.6382687214395428, 0.6616294471784337, 0.6849901729173247, 0.7188264983706762, 0.7526628238240278, 0.7864991492773794, 0.820335474730731, 0.8541718001840826, 0.8903373243732055, 0.9265028485623283, 0.9626683727514512, 0.9988338969405741, 1.034999421129697, 1.09413092158135, 1.153262422033003, 1.212393922484656, 1.271525422936309, 1.3306569233879622, 1.3897884238396152, 1.455052740268698, 1.5203170566977806, 1.5855813731268633, 1.650845689555946, 1.7161100059850287, 1.8171699997560318, 1.9182299935270348, 2.0192899872980377, 2.1203499810690403, 2.221409974840043, 2.3224699686110455, 2.4485727938155097, 2.574675619019974, 2.7007784442244382, 2.8268812694289025, 2.9529840946333668, 3.079086919837831, 3.2243552938362425, 3.369623667834654, 3.5148920418330656, 3.660160415831477, 3.8054287898298886, 3.9506971638283, 4.181862887990856, 4.413028612153411, 4.644194336315967, 4.875360060478522, 5.106525784641078, 5.337691508803633, 5.616137580573091, 5.894583652342549, 6.1730297241120065, 6.451475795881464, 6.729921867650922, 7.0083679394203795, 7.388918994134857, 7.769470048849335, 8.150021103563812, 8.53057215827829, 8.911123212992766, 9.291674267707243, 9.818218147090521, 10.0]</t>
+          <t>[0.0, 1.3299636950013003e-05, 2.6599273900026006e-05, 0.00015959564340015605, 0.0002925920129002861, 0.0007956119753822271, 0.0012986319378641682, 0.0018016519003461093, 0.0036064105546189055, 0.005411169208891701, 0.007215927863164497, 0.012852599167970836, 0.018489270472777174, 0.02412594177758351, 0.029762613082389845, 0.039057219449592055, 0.048351825816794265, 0.057646432183996475, 0.06694103855119868, 0.07623564491840087, 0.08683028723798177, 0.09742492955756266, 0.10801957187714355, 0.11861421419672444, 0.1261789636273975, 0.13374371305807056, 0.14130846248874362, 0.14133210233071447, 0.14135574217268532, 0.14137938201465616, 0.141403021856627, 0.14142666169859786, 0.1414503015405687, 0.14168669996027716, 0.14192309837998562, 0.14215949679969409, 0.14239589521940255, 0.142632293639111, 0.14448254950854608, 0.1448526006824331, 0.14522265185632013, 0.14559270303020716, 0.14596275420409419, 0.14608073879143663, 0.14619872337877907, 0.14622232029624754, 0.14624591721371602, 0.1462695141311845, 0.1462742335146782, 0.1462789528981719, 0.14628367228166558, 0.14628461615836433, 0.14628556003506307, 0.14628650391176182, 0.14628744778846056, 0.14628752329859646, 0.14628759880873235, 0.14628761391075953, 0.14628762901278672, 0.1462876441148139, 0.14628765015562478, 0.14628765619643566, 0.14628766827805742, 0.14628767069438178, 0.1462876714005852, 0.14628767210678864, 0.14628767236920273, 0.14628767263161682, 0.14628767322052671, 0.1462876738094366, 0.14628767946113122, 0.14628768511282583, 0.14628774162977196, 0.14628779814671808, 0.1462883633161793, 0.14628892848564054, 0.14629458018025285, 0.14630023187486516, 0.14630588356947746, 0.14634948294876787, 0.14639308232805828, 0.1464366817073487, 0.1468726755002528, 0.1473086692931569, 0.147744663086061, 0.14888294015970904, 0.1500212172333571, 0.15115949430700515, 0.1522977713806532, 0.15539386373346406, 0.15848995608627492, 0.16158604843908578, 0.16468214079189664, 0.1677782331447075, 0.17319421825368958, 0.17861020336267167, 0.18402618847165375, 0.18944217358063584, 0.19485815868961792, 0.20018196504541394, 0.20550577140120996, 0.21082957775700598, 0.216153384112802, 0.221477190468598, 0.22680099682439403, 0.2321025204647989, 0.23740404410520377, 0.24270556774560864, 0.2480070913860135, 0.2533086150264184, 0.25928591330645323, 0.2652632115864881, 0.2712405098665229, 0.2772178081465578, 0.2831951064265926, 0.2891724047066275, 0.29522187215082696, 0.30127133959502644, 0.30732080703922593, 0.3133702744834254, 0.3194197419276249, 0.3254692093718244, 0.33314225273397197, 0.34081529609611955, 0.3484883394582671, 0.3561613828204147, 0.3638344261825623, 0.37150679923581925, 0.3791791722890762, 0.3868515453423332, 0.39452391839559015, 0.4021962914488471, 0.4098686645021041, 0.4208048618664343, 0.4317410592307645, 0.4426772565950947, 0.45361345395942493, 0.46454965132375514, 0.47548584868808536, 0.49134003904316303, 0.5071942293982408, 0.5230484197533185, 0.5389026101083962, 0.544926085187111, 0.5509495602658259, 0.5523261115724633, 0.5524736516364398, 0.5526211917004163, 0.5527043404489329, 0.5527874891974495, 0.552870637945966, 0.5529537866944826, 0.5530369354429991, 0.5531200841915157, 0.5532326979278546, 0.5533453116641934, 0.5534579254005323, 0.5535705391368712, 0.55368315287321, 0.5537957666095489, 0.5540027891647044, 0.5542098117198598, 0.5544168342750153, 0.5546238568301708, 0.5548308793853263, 0.5554087038640678, 0.5559865283428094, 0.5565643528215509, 0.5571421773002925, 0.5596505612459886, 0.5621589451916846, 0.5646673291373807, 0.5749152185618919, 0.585163107986403, 0.5954109974109142, 0.615469832472584, 0.6355286675342539, 0.6555875025959237, 0.6756463376575935, 0.7085930408318593, 0.741539744006125, 0.7744864471803907, 0.8074331503546565, 0.8403798535289222, 0.8827614645093533, 0.9251430754897845, 0.9675246864702156, 1.0099062974506468, 1.052287908431078, 1.094669519411509, 1.1494723199743246, 1.2042751205371403, 1.2590779210999559, 1.3138807216627715, 1.368683522225587, 1.4431851624033734, 1.5176868025811596, 1.5921884427589459, 1.6666900829367322, 1.7411917231145184, 1.8156933632923047, 1.8960244969810935, 1.9763556306698824, 2.0566867643586715, 2.1370178980474606, 2.2173490317362496, 2.2976801654250387, 2.4271805622731693, 2.5566809591213, 2.6861813559694303, 2.815681752817561, 2.9451821496656914, 3.074682546513822, 3.230641728189837, 3.3866009098658525, 3.542560091541868, 3.698519273217883, 3.8544784548938984, 4.010437636569914, 4.2521423210225695, 4.493847005475225, 4.735551689927881, 4.977256374380537, 5.218961058833193, 5.4606657432858485, 5.756588185091421, 6.052510626896994, 6.348433068702566, 6.644355510508139, 6.9402779523137115, 7.236200394119284, 7.682149569511448, 8.12809874490361, 8.574047920295772, 9.019997095687934, 9.465946271080096, 9.911895446472258, 10.0]</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.5955610137429067</v>
+        <v>0.595560904468618</v>
       </c>
       <c r="D27" t="n">
         <v>9.81</v>
@@ -2242,13 +2242,13 @@
         <v>2</v>
       </c>
       <c r="L27" t="n">
-        <v>5.955610137429066</v>
+        <v>5.955609044686179</v>
       </c>
       <c r="M27" t="n">
-        <v>0.005638680337490636</v>
+        <v>0.005638682406675619</v>
       </c>
       <c r="N27" t="n">
-        <v>0.02819340168745318</v>
+        <v>0.02819341203337809</v>
       </c>
       <c r="O27" t="n">
         <v>19.58443519693777</v>
@@ -2278,11 +2278,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[0.0, 5.949206695156695e-07, 1.189841339031339e-06, 7.139048034188033e-06, 1.3088254729344728e-05, 3.089656686164719e-05, 4.8704878993949655e-05, 6.651319112625212e-05, 0.00011053679980718213, 0.00015456040848811213, 0.00019858401716904214, 0.00041505244622941443, 0.0006315208752897867, 0.000847989304350159, 0.0016784213712643047, 0.0025088534381784502, 0.0033392855050925958, 0.004169717572006741, 0.005782090361472542, 0.007394463150938343, 0.009006835940404145, 0.010619208729869947, 0.01223158151933575, 0.01755662975138012, 0.022881677983424487, 0.028206726215468856, 0.03353177444751322, 0.03885682267955759, 0.046253624096727106, 0.05365042551389662, 0.06104722693106614, 0.06844402834823565, 0.07584082976540517, 0.08323763118257468, 0.09112604487375935, 0.09901445856494401, 0.10690287225612867, 0.11327546101976312, 0.11964804978339756, 0.126020638547032, 0.13239322731066644, 0.13876581607430089, 0.14527747927024626, 0.15178914246619163, 0.158300805662137, 0.16481246885808237, 0.17132413205402774, 0.17783579524997312, 0.18386675662248442, 0.18989771799499572, 0.19592867936750702, 0.20195964074001832, 0.20799060211252962, 0.21414280304746997, 0.2202950039824103, 0.22644720491735065, 0.232599405852291, 0.23875160678723134, 0.24490380772217168, 0.2505268594348396, 0.2561499111475075, 0.26177296286017543, 0.26739601457284334, 0.27301906628551126, 0.2786421179981792, 0.28443268029855795, 0.2902232425989367, 0.2960138048993155, 0.3018043671996943, 0.30759492950007306, 0.31338549180045183, 0.3235334120536877, 0.33368133230692354, 0.3415282745222533, 0.3493752167375831, 0.35722215895291287, 0.36506910116824265, 0.3729160433835724, 0.38445529397186584, 0.39599454456015926, 0.40753379514845267, 0.4190730457367461, 0.4306122963250395, 0.4421515469133329, 0.45569433202517945, 0.469237117137026, 0.4827799022488725, 0.49632268736071905, 0.5098654724725655, 0.523408257584412, 0.5412383897135585, 0.5590685218427051, 0.5768986539718516, 0.5947287861009981, 0.6125589182301446, 0.6370443646076405, 0.6615298109851363, 0.6860152573626321, 0.710500703740128, 0.7349861501176238, 0.7725142804678948, 0.8100424108181659, 0.8475705411684369, 0.8850986715187079, 0.9226268018689789, 0.9698089350709698, 1.0169910682729606, 1.0641732014749514, 1.1113553346769423, 1.158537467878933, 1.214944844665161, 1.2713522214513888, 1.3277595982376167, 1.3841669750238446, 1.4405743518100724, 1.4969817285963003, 1.5770800362242132, 1.6571783438521261, 1.737276651480039, 1.817374959107952, 1.897473266735865, 2.00132892344557, 2.1051845801552744, 2.209040236864979, 2.3128958935746837, 2.4167515502843884, 2.520607206994093, 2.661493232398292, 2.8023792578024906, 2.9432652832066895, 3.0841513086108883, 3.225037334015087, 3.365923359419286, 3.555220391136062, 3.744517422852838, 3.9338144545696143, 4.1231114862863905, 4.312408518003167, 4.501705549719944, 4.716579334298278, 4.931453118876613, 5.1463269034549475, 5.361200688033282, 5.576074472611617, 5.790948257189951, 6.111534900964932, 6.432121544739912, 6.752708188514893, 7.073294832289873, 7.393881476064854, 7.714468119839834, 8.141300835084728, 8.568133550329621, 8.994966265574515, 9.421798980819409, 9.848631696064302, 10.0]</t>
+          <t>[0.0, 1.330283646666803e-05, 2.660567293333606e-05, 0.00015963403760001636, 0.0002926624022666967, 0.0007875505226320016, 0.0012824386429973066, 0.0017773267633626115, 0.0035328855759307817, 0.0052884443884989515, 0.007044003201067121, 0.012609324123183798, 0.018174645045300475, 0.02373996596741715, 0.02930528688953383, 0.03848884508862688, 0.047672403287719926, 0.056855961486812975, 0.06603951968590602, 0.07522307788499906, 0.08578218122176078, 0.09634128455852249, 0.10690038789528421, 0.11745949123204592, 0.12498056632243282, 0.13250164141281973, 0.14002271650320663, 0.14004621986286409, 0.14006972322252154, 0.140093226582179, 0.14011672994183644, 0.1401402333014939, 0.14016373666115134, 0.14039877025772585, 0.14063380385430035, 0.14086883745087486, 0.14110387104744937, 0.14133890464402388, 0.14319349731608366, 0.14356441585049562, 0.14393533438490758, 0.14430625291931953, 0.1446771714537315, 0.1447956557187646, 0.1449141399837977, 0.14493783683680433, 0.14496153368981096, 0.1449852305428176, 0.14500892739582422, 0.14501840613702688, 0.14502788487822954, 0.14502826402787763, 0.14502864317752573, 0.14502871900745534, 0.14502873417344125, 0.14502874933942717, 0.14502876450541308, 0.14502877057180744, 0.1450287717850863, 0.14502877299836517, 0.14502877371753148, 0.1450287744366978, 0.14502877499033767, 0.1450287752608561, 0.14502877553137455, 0.14502877613900286, 0.14502877674663117, 0.1450287825805146, 0.14502878841439804, 0.14502884675323235, 0.14502890509206667, 0.14502948848040986, 0.14503007186875305, 0.14503590575218495, 0.14504173963561684, 0.14504757351904873, 0.14509215153207722, 0.1451367295451057, 0.1451813075581342, 0.14562708768841903, 0.14607286781870388, 0.14651864794898872, 0.1476636664586634, 0.1488086849683381, 0.1499537034780128, 0.15109872198768748, 0.1541699899594146, 0.15724125793114174, 0.16031252590286887, 0.163383793874596, 0.16645506184632314, 0.17183503383096932, 0.1772150058156155, 0.18259497780026168, 0.18797494978490786, 0.19335492176955404, 0.19867878413648513, 0.2040026465034162, 0.2093265088703473, 0.21465037123727837, 0.21997423360420945, 0.22529809597114053, 0.23061172327156443, 0.23592535057198832, 0.24123897787241222, 0.24655260517283611, 0.25186623247326, 0.2578667887975355, 0.263867345121811, 0.26986790144608647, 0.27586845777036195, 0.28186901409463744, 0.2878695704189129, 0.2939140810955619, 0.29995859177221085, 0.3060031024488598, 0.31204761312550877, 0.31809212380215773, 0.3241366344788067, 0.33176411011656737, 0.33939158575432804, 0.3470190613920887, 0.3546465370298494, 0.36227401266761006, 0.36990148830537073, 0.3788352272279599, 0.3877689661505491, 0.3967027050731383, 0.4056364439957275, 0.4145701829183167, 0.4235039218409059, 0.43332839410247265, 0.4431528663640394, 0.45297733862560613, 0.46280181088717287, 0.4726262831487396, 0.48245075541030635, 0.49773599486458664, 0.503006637498243, 0.5041411031123072, 0.5045652828259288, 0.5047459606838434, 0.5048780217985998, 0.5050100829133561, 0.5051421440281125, 0.5052742051428689, 0.5054062662576253, 0.505624855963603, 0.5058434456695806, 0.5060620353755583, 0.5062806250815359, 0.5069514546713767, 0.5076222842612175, 0.5082931138510582, 0.510992972010675, 0.5136928301702917, 0.5163926883299084, 0.5271116079510518, 0.5378305275721953, 0.5485494471933388, 0.5696695780496002, 0.5907897089058616, 0.611909839762123, 0.6330299706183844, 0.6571472432798979, 0.6812645159414115, 0.705381788602925, 0.7294990612644385, 0.7536163339259521, 0.8009628198834342, 0.8483093058409164, 0.8956557917983985, 0.9430022777558806, 0.9903487637133628, 1.037695249670845, 1.08562901625958, 1.1335627828483152, 1.1814965494370504, 1.2294303160257856, 1.2773640826145207, 1.3252978492032559, 1.4074263463833916, 1.4895548435635273, 1.571683340743663, 1.6538118379237987, 1.7359403351039344, 1.8180688322840701, 1.8985633780545046, 1.979057923824939, 2.0595524695953733, 2.1400470153658073, 2.2205415611362413, 2.3010361069066754, 2.4344398274917523, 2.567843548076829, 2.701247268661906, 2.834650989246983, 2.9680547098320598, 3.1014584304171366, 3.2612291500789086, 3.4209998697406805, 3.5807705894024524, 3.7405413090642243, 3.9003120287259962, 4.060082748387768, 4.30224549215575, 4.544408235923732, 4.786570979691714, 5.028733723459696, 5.2708964672276775, 5.513059210995659, 5.829544788754654, 6.146030366513648, 6.462515944272643, 6.7790015220316375, 7.095487099790632, 7.411972677549627, 7.843063605333963, 8.274154533118299, 8.705245460902635, 9.13633638868697, 9.567427316471306, 9.998518244255642, 10.0]</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.5881225521416606</v>
+        <v>0.5881222483494669</v>
       </c>
       <c r="D28" t="n">
         <v>9.81</v>
@@ -2309,13 +2309,13 @@
         <v>2</v>
       </c>
       <c r="L28" t="n">
-        <v>5.881225521416606</v>
+        <v>5.881222483494668</v>
       </c>
       <c r="M28" t="n">
-        <v>0.005782216242443789</v>
+        <v>0.005782222216006651</v>
       </c>
       <c r="N28" t="n">
-        <v>0.02891108121221894</v>
+        <v>0.02891111108003325</v>
       </c>
       <c r="O28" t="n">
         <v>19.57501567331031</v>
@@ -2345,11 +2345,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[0.0, 5.951017677552405e-07, 1.190203535510481e-06, 7.141221213062886e-06, 1.3092238890615292e-05, 3.09059839867918e-05, 4.8719729082968314e-05, 6.653347417914482e-05, 0.00011057094830448325, 0.00015460842242982168, 0.00019864589655516012, 0.0004154442680846075, 0.000632242639614055, 0.0008490410111435024, 0.001697023316121143, 0.0025450056210987834, 0.003392987926076424, 0.004240970231054065, 0.005860829396873031, 0.007480688562691996, 0.009100547728510962, 0.010720406894329928, 0.012340266060148894, 0.01785998472390468, 0.023379703387660468, 0.028899422051416254, 0.03441914071517204, 0.03993885937892783, 0.04752228812057948, 0.05510571686223113, 0.06268914560388278, 0.07027257434553442, 0.07785600308718607, 0.08543943182883772, 0.0929990297092784, 0.10055862758971908, 0.10811822547015976, 0.11567782335060044, 0.12323742123104112, 0.1303810115879818, 0.13752460194492247, 0.14466819230186315, 0.15181178265880382, 0.1589553730157445, 0.16609896337268518, 0.1729484470373888, 0.1797979307020924, 0.18664741436679602, 0.19349689803149964, 0.20034638169620325, 0.20719586536090687, 0.21385713858020333, 0.2205184117994998, 0.22717968501879626, 0.23384095823809273, 0.2405022314573892, 0.24716350467668566, 0.2521320249999463, 0.2571005453232069, 0.26206906564646754, 0.26703758596972815, 0.27200610629298877, 0.2769746266162494, 0.28328281484689705, 0.2895910030775447, 0.29589919130819237, 0.30220737953884, 0.3085155677694877, 0.31482375600013535, 0.32406679122098725, 0.33330982644183915, 0.34255286166269105, 0.35179589688354296, 0.36103893210439486, 0.3705345899618054, 0.3800302478192159, 0.3895259056766264, 0.39902156353403695, 0.40851722139144747, 0.418012879248858, 0.4302686364357399, 0.44252439362262186, 0.4547801508095038, 0.4670359079963857, 0.47929166518326766, 0.4915474223701496, 0.5081299240972547, 0.5247124258243597, 0.5412949275514648, 0.5578774292785699, 0.5744599310056749, 0.5982245559889052, 0.6219891809721355, 0.6457538059553658, 0.6695184309385961, 0.6932830559218264, 0.7278592772845788, 0.7624354986473312, 0.7970117200100836, 0.831587941372836, 0.8661641627355884, 0.9029840196458736, 0.9398038765561588, 0.976623733466444, 1.0134435903767294, 1.0502634472870147, 1.1103692138358865, 1.1704749803847583, 1.23058074693363, 1.2906865134825019, 1.3507922800313736, 1.4108980465802454, 1.4773463780343001, 1.5437947094883548, 1.6102430409424096, 1.6766913723964643, 1.743139703850519, 1.8461776906808296, 1.9492156775111402, 2.0522536643414506, 2.155291651171761, 2.2583296380020714, 2.361367624832382, 2.4898319671550877, 2.6182963094777936, 2.7467606518004994, 2.8752249941232053, 3.003689336445911, 3.132153678768617, 3.2801298649738353, 3.4281060511790535, 3.576082237384272, 3.72405842358949, 3.8720346097947083, 4.0200107959999265, 4.2555277128170035, 4.4910446296340805, 4.7265615464511574, 4.962078463268234, 5.197595380085311, 5.433112296902388, 5.717025924390912, 6.000939551879435, 6.284853179367959, 6.568766806856482, 6.852680434345006, 7.136594061833529, 7.524717694615871, 7.912841327398214, 8.300964960180556, 8.689088592962898, 9.07721222574524, 9.465335858527583, 10.0]</t>
+          <t>[0.0, 1.3306886701456804e-05, 2.661377340291361e-05, 0.00015968264041748165, 0.00029275150743204967, 0.0007780611615997345, 0.0012633708157674193, 0.0017486804699351041, 0.003446629343032838, 0.005144578216130572, 0.006842527089228306, 0.012327736135504759, 0.017812945181781212, 0.023298154228057665, 0.028783363274334117, 0.03783503788122089, 0.04688671248810766, 0.055938387094994435, 0.06499006170188121, 0.07404173630876798, 0.08456052859393882, 0.09507932087910967, 0.10559811316428051, 0.11611690544945136, 0.12358467052185705, 0.13105243559426275, 0.13852020066666842, 0.13854353743251968, 0.13856687419837094, 0.1385902109642222, 0.13861354773007345, 0.1386368844959247, 0.13866022126177596, 0.13889358892028852, 0.1391269565788011, 0.13936032423731365, 0.1395936918958262, 0.13982705955433877, 0.14168152406219414, 0.14205241696376522, 0.1424233098653363, 0.14279420276690738, 0.14316509566847846, 0.1432837288897583, 0.14340236211103813, 0.14352099533231796, 0.14352574066116916, 0.14353048599002036, 0.1435314350557906, 0.14353238412156086, 0.1435333331873311, 0.14353352300048516, 0.14353371281363922, 0.14353390262679327, 0.14353409243994733, 0.14353410762499966, 0.14353412281005198, 0.14353412760334164, 0.1435341323966313, 0.14353413314888974, 0.1435341339011482, 0.14353413465340664, 0.1435341359033651, 0.14353413715332358, 0.14353414965290828, 0.14353416215249298, 0.14353428714834, 0.143534412144187, 0.14353566210265706, 0.14353691206112712, 0.14354455381300799, 0.14355219556488885, 0.14355983731676972, 0.14360553750385832, 0.14365123769094693, 0.14369693787803553, 0.14415393974892157, 0.14461094161980761, 0.14506794349069366, 0.14622122180512986, 0.14737450011956607, 0.14852777843400228, 0.14968105674843848, 0.15272637901340938, 0.15577170127838028, 0.15881702354335117, 0.16186234580832207, 0.16490766807329296, 0.17024520691699693, 0.1755827457607009, 0.18092028460440487, 0.18625782344810884, 0.19159536229181282, 0.19692703381042198, 0.20225870532903115, 0.2075903768476403, 0.21292204836624948, 0.21825371988485864, 0.2235853914034678, 0.22892119422604265, 0.2342569970486175, 0.23959279987119234, 0.24492860269376718, 0.250264405516342, 0.25630914213700856, 0.26235387875767513, 0.2683986153783417, 0.27444335199900827, 0.28048808861967484, 0.2865328252403414, 0.2925736883456104, 0.29861455145087945, 0.3046554145561485, 0.3106962776614175, 0.3167371407666865, 0.32277800387195554, 0.3304657827104775, 0.33815356154899945, 0.3458413403875214, 0.35352911922604335, 0.3612168980645653, 0.36890467690308726, 0.3778200527712553, 0.38673542863942334, 0.3956508045075914, 0.4045661803757594, 0.41348155624392746, 0.4223969321120955, 0.43226752318285266, 0.4421381142536098, 0.452008705324367, 0.46187929639512415, 0.4622371073773667, 0.4623767811504144, 0.46248939630074387, 0.46256862245202657, 0.46264784860330926, 0.46272707475459196, 0.46280630090587466, 0.46288552705715735, 0.46296475320844005, 0.46307966001424405, 0.46319456682004806, 0.46330947362585206, 0.46342438043165607, 0.4635392872374601, 0.4636541940432641, 0.46382639756347077, 0.46399860108367746, 0.46417080460388416, 0.46434300812409085, 0.46451521164429754, 0.4649680672538423, 0.4654209228633871, 0.4658737784729319, 0.46632663408247665, 0.4688197937637639, 0.4713129534450512, 0.47380611312633847, 0.48253239366143236, 0.49125867419652625, 0.49998495473162013, 0.5189036638932506, 0.537822373054881, 0.5567410822165114, 0.5756597913781418, 0.5990443903795815, 0.6224289893810211, 0.6458135883824607, 0.6691981873839004, 0.69258278638534, 0.7300893127309853, 0.7675958390766306, 0.805102365422276, 0.8426088917679213, 0.8801154181135666, 0.917621944459212, 0.9675404704668167, 1.0174589964744214, 1.067377522482026, 1.1172960484896308, 1.1672145744972355, 1.2171331005048402, 1.2806722070777394, 1.3442113136506386, 1.4077504202235378, 1.471289526796437, 1.5348286333693362, 1.6082724483881252, 1.6817162634069143, 1.7551600784257033, 1.8286038934444924, 1.9020477084632814, 1.9754915234820705, 2.0838128608227895, 2.1921341981635085, 2.3004555355042275, 2.4087768728449466, 2.5170982101856656, 2.6254195475263846, 2.76001843467188, 2.894617321817375, 3.0292162089628705, 3.1638150961083658, 3.298413983253861, 3.4330128703993563, 3.634127780092559, 3.8352426897857614, 4.036357599478964, 4.237472509172166, 4.438587418865368, 4.63970232855857, 4.902481829954121, 5.165261331349672, 5.428040832745223, 5.690820334140774, 5.953599835536325, 6.216379336931876, 6.526029839657394, 6.835680342382911, 7.145330845108429, 7.454981347833947, 7.764631850559464, 8.074282353284982, 8.531248196205263, 8.988214039125545, 9.445179882045826, 9.902145724966108, 10.0]</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.5793214388330745</v>
+        <v>0.5793213694287901</v>
       </c>
       <c r="D29" t="n">
         <v>9.81</v>
@@ -2376,13 +2376,13 @@
         <v>2</v>
       </c>
       <c r="L29" t="n">
-        <v>5.793214388330745</v>
+        <v>5.793213694287901</v>
       </c>
       <c r="M29" t="n">
-        <v>0.005959238874777518</v>
+        <v>0.005959240302643835</v>
       </c>
       <c r="N29" t="n">
-        <v>0.02979619437388759</v>
+        <v>0.02979620151321917</v>
       </c>
       <c r="O29" t="n">
         <v>19.56310133970982</v>
@@ -2412,11 +2412,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[0.0, 5.95331064962098e-07, 1.190662129924196e-06, 7.143972779545177e-06, 1.3097283429166157e-05, 3.091790746959021e-05, 4.8738531510014264e-05, 6.655915555043832e-05, 0.00011061418563830342, 0.0001546692157261685, 0.00019872424581403357, 0.0004159423445660842, 0.0006331604433181348, 0.0008503785420701854, 0.0017233894257766681, 0.002596400309483151, 0.003469411193189634, 0.0043424220768961165, 0.005973979174262659, 0.007605536271629201, 0.009237093368995744, 0.010868650466362286, 0.012500207563728829, 0.018334586903023017, 0.024168966242317208, 0.0300033455816114, 0.03583772492090559, 0.04167210426019978, 0.04956103022807375, 0.05744995619594773, 0.0653388821638217, 0.07322780813169566, 0.08111673409956963, 0.08900566006744359, 0.09644722892954363, 0.10388879779164367, 0.11133036665374371, 0.11877193551584375, 0.1262135043779438, 0.13365507324004383, 0.14016357454693595, 0.14667207585382808, 0.1531805771607202, 0.15968907846761232, 0.16619757977450444, 0.17270608108139657, 0.17868540764868612, 0.18466473421597568, 0.19064406078326523, 0.1966233873505548, 0.20260271391784435, 0.20857283476739918, 0.21454295561695402, 0.22051307646650886, 0.2264831973160637, 0.23245331816561854, 0.23842343901517338, 0.24394553946122846, 0.24946763990728354, 0.25498974035333866, 0.26051184079939377, 0.2660339412454489, 0.271556041691504, 0.277359041336148, 0.28316204098079206, 0.2889650406254361, 0.29476804027008013, 0.30057103991472417, 0.3063740395593682, 0.31779741987893745, 0.3267474115640642, 0.335697403249191, 0.3446473949343178, 0.35359738661944456, 0.36254737830457134, 0.37255127210859645, 0.38255516591262156, 0.3925590597166467, 0.4025629535206718, 0.4125668473246969, 0.422570741128722, 0.43533071730705336, 0.4480906934853847, 0.4608506696637161, 0.47361064584204743, 0.4863706220203788, 0.49913059819871014, 0.5149849290971585, 0.5308392599956069, 0.5466935908940552, 0.5625479217925036, 0.5784022526909519, 0.6022976967112346, 0.6261931407315172, 0.6500885847517999, 0.6739840287720825, 0.6978794727923652, 0.7325525561984282, 0.7672256396044912, 0.8018987230105542, 0.8365718064166172, 0.8712448898226802, 0.9083937074855755, 0.9455425251484707, 0.9826913428113659, 1.0198401604742613, 1.0569889781371566, 1.1170203023782532, 1.1770516266193498, 1.2370829508604464, 1.297114275101543, 1.3571455993426396, 1.4171769235837361, 1.4840402953932252, 1.5509036672027143, 1.6177670390122034, 1.6846304108216925, 1.7514937826311816, 1.8552479370020338, 1.959002091372886, 2.0627562457437385, 2.166510400114591, 2.2702645544854434, 2.374018708856296, 2.503274743710057, 2.632530778563818, 2.761786813417579, 2.89104284827134, 3.020298883125101, 3.149554917978862, 3.298455799783234, 3.447356681587606, 3.596257563391978, 3.74515844519635, 3.894059327000722, 4.042960208805094, 4.279962995035639, 4.516965781266184, 4.753968567496729, 4.990971353727274, 5.227974139957819, 5.464976926188364, 5.750792751662, 6.0366085771356355, 6.322424402609271, 6.608240228082907, 6.894056053556542, 7.179871879030178, 7.570645652371523, 7.961419425712868, 8.352193199054213, 8.742966972395557, 9.133740745736901, 9.524514519078245, 10.0]</t>
+          <t>[0.0, 1.3312014964936698e-05, 2.6624029929873397e-05, 0.0001597441795792404, 0.00029286432922860737, 0.0007670495865000652, 0.001241234843771523, 0.001715420101042981, 0.00334701687688752, 0.004978613652732059, 0.006610210428576598, 0.012008182772634261, 0.017406155116691926, 0.02280412746074959, 0.028202099804807257, 0.03709929629927315, 0.04599649279373905, 0.05489368928820494, 0.06379088578267084, 0.07268808227713673, 0.0831627906608712, 0.09363749904460568, 0.10411220742834015, 0.11458691581207463, 0.1219898445501596, 0.12939277328824456, 0.1367957020263295, 0.13681883617863602, 0.13684197033094253, 0.13686510448324904, 0.13688823863555555, 0.13691137278786206, 0.13693450694016857, 0.13716584846323365, 0.13739718998629874, 0.13762853150936383, 0.13785987303242891, 0.138091214555494, 0.13991612868774886, 0.14174104282000372, 0.14175564213306174, 0.14177024144611977, 0.14177316130873138, 0.141776081171343, 0.1417790010339546, 0.14177958500647692, 0.14178016897899923, 0.14178075295152154, 0.141780869746026, 0.14178098654053045, 0.14178099314907913, 0.1417809970590025, 0.1417809986320662, 0.1417810002051299, 0.1417810017781936, 0.14178100335125732, 0.14178100523706044, 0.14178100712286357, 0.1417810090086667, 0.14178101089446982, 0.1417810172940104, 0.141781023693551, 0.1417810300930916, 0.1417810940884975, 0.14178115808390343, 0.14178179803796262, 0.1417824379920218, 0.1417874459739898, 0.14179245395595777, 0.14180785261122125, 0.14182325126648473, 0.14183864992174822, 0.14189852027622937, 0.14195839063071053, 0.14201826098519169, 0.14261696453000325, 0.1432156680748148, 0.14381437161962637, 0.14511656158754174, 0.1464187515554571, 0.14772094152337248, 0.14902313149128785, 0.1521254800492821, 0.15522782860727638, 0.15833017716527065, 0.1614325257232649, 0.16453487428125918, 0.1698283069781673, 0.17512173967507544, 0.18041517237198357, 0.1857086050688917, 0.19100203776579983, 0.19629547046270795, 0.20285820190933224, 0.20942093335595652, 0.2159836648025808, 0.22254639624920508, 0.22910912769582936, 0.23567185914245364, 0.2414787645661735, 0.24728566998989338, 0.25309257541361324, 0.2588994808373331, 0.264706386261053, 0.27038390848105087, 0.27606143070104877, 0.28173895292104667, 0.28741647514104457, 0.29309399736104247, 0.29877151958104037, 0.30568439051001484, 0.3125972614389893, 0.3195101323679638, 0.32642300329693824, 0.3333358742259127, 0.3402487451548872, 0.3519902397052192, 0.3637317342555512, 0.37547322880588324, 0.38721472335621526, 0.3989562179065473, 0.4106977124568793, 0.42157697336275907, 0.4234538775976449, 0.42533078183253076, 0.425435951922246, 0.4254953539609804, 0.4255547559997149, 0.4256141580384493, 0.42567356007718377, 0.4257329621159182, 0.42579236415465266, 0.42587293778011015, 0.42595351140556764, 0.42603408503102513, 0.4261146586564826, 0.4261952322819401, 0.4262758059073976, 0.42642360143706803, 0.42657139696673846, 0.4267191924964089, 0.4268669880260793, 0.42701478355574973, 0.4274276345962646, 0.42784048563677946, 0.4282533366772943, 0.4286661877178092, 0.4304606990855535, 0.43225521045329784, 0.4340497218210422, 0.4411017240629685, 0.4481537263048948, 0.4552057285468211, 0.46985223859344977, 0.4844987486400784, 0.49914525868670706, 0.5137917687333358, 0.5328235002038584, 0.551855231674381, 0.5708869631449036, 0.5899186946154262, 0.6089504260859488, 0.6380780166567721, 0.6672056072275954, 0.6963331977984186, 0.7254607883692419, 0.7545883789400651, 0.7889659573322758, 0.8233435357244865, 0.8577211141166972, 0.8920986925089078, 0.9264762709011185, 0.9727235147191097, 1.0189707585371008, 1.065218002355092, 1.111465246173083, 1.157712489991074, 1.203959733809065, 1.2605196018746647, 1.3170794699402644, 1.373639338005864, 1.4301992060714637, 1.4867590741370633, 1.5738289051008827, 1.660898736064702, 1.7479685670285214, 1.8350383979923408, 1.9221082289561602, 2.0091780599199796, 2.118153847385468, 2.2271296348509564, 2.336105422316445, 2.445081209781933, 2.5540569972474216, 2.66303278471291, 2.787212336041631, 2.9113918873703524, 3.0355714386990735, 3.1597509900277947, 3.283930541356516, 3.408110092685237, 3.5858435219519036, 3.76357695121857, 3.9413103804852367, 4.119043809751903, 4.29677723901857, 4.4745106682852365, 4.7177412064808895, 4.9609717446765424, 5.204202282872195, 5.447432821067848, 5.690663359263501, 5.933893897459154, 6.2609261737638615, 6.587958450068569, 6.914990726373276, 7.242023002677983, 7.56905527898269, 7.896087555287397, 8.334273429328675, 8.772459303369953, 9.21064517741123, 9.648831051452508, 10.0]</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.5690365453868939</v>
+        <v>0.5690365493690428</v>
       </c>
       <c r="D30" t="n">
         <v>9.81</v>
@@ -2443,13 +2443,13 @@
         <v>2</v>
       </c>
       <c r="L30" t="n">
-        <v>5.690365453868938</v>
+        <v>5.690365493690428</v>
       </c>
       <c r="M30" t="n">
-        <v>0.006176602849555329</v>
+        <v>0.006176602763106919</v>
       </c>
       <c r="N30" t="n">
-        <v>0.03088301424777664</v>
+        <v>0.0308830138155346</v>
       </c>
       <c r="O30" t="n">
         <v>19.54803143269989</v>
@@ -2479,11 +2479,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[0.0, 5.956214680830018e-07, 1.1912429361660037e-06, 7.147457616996022e-06, 1.310367229782604e-05, 3.093300847847101e-05, 4.876234465911598e-05, 6.659168083976094e-05, 0.00011066894582630225, 0.00015474621081284357, 0.00019882347579938488, 0.0004165763502250259, 0.0006343292246506669, 0.0008520820990763078, 0.001762670672470081, 0.0026732592458638543, 0.0035838478192576277, 0.004494436392651401, 0.006145238312321234, 0.007796040231991067, 0.0094468421516609, 0.011097644071330733, 0.012748445991000567, 0.019180384109018855, 0.025612322227037142, 0.032044260345055434, 0.03847619846307372, 0.04490813658109201, 0.05339715638482614, 0.061886176188560266, 0.07037519599229439, 0.07886421579602851, 0.08735323559976263, 0.09584225540349675, 0.10317633263097968, 0.11051040985846261, 0.11784448708594554, 0.12517856431342847, 0.1325126415409114, 0.13984671876839436, 0.14637651255062084, 0.15290630633284732, 0.1594361001150738, 0.1659658938973003, 0.17249568767952678, 0.17902548146175326, 0.1844721508339723, 0.18991882020619136, 0.1953654895784104, 0.20081215895062945, 0.2062588283228485, 0.21216049336359366, 0.21806215840433882, 0.22396382344508398, 0.22986548848582913, 0.2357671535265743, 0.24166881856731945, 0.24764112744535755, 0.2536134363233956, 0.2595857452014337, 0.26555805407947175, 0.2715303629575098, 0.2775026718355479, 0.28322113757390693, 0.288939603312266, 0.294658069050625, 0.3003765347889841, 0.3060950005273431, 0.31181346626570217, 0.31964399131198995, 0.32747451635827773, 0.3353050414045655, 0.3431355664508533, 0.3509660914971411, 0.36027819871294525, 0.3695903059287494, 0.3789024131445536, 0.38821452036035775, 0.3975266275761619, 0.4068387347919661, 0.41834957920724947, 0.42986042362253285, 0.44137126803781623, 0.4528821124530996, 0.464392956868383, 0.4759038012836664, 0.4919525485827266, 0.5080012958817868, 0.524050043180847, 0.5400987904799073, 0.5561475377789675, 0.5721962850780278, 0.594888363035098, 0.6175804409921681, 0.6402725189492383, 0.6629645969063085, 0.6856566748633787, 0.7198958387765193, 0.7541350026896599, 0.7883741666028006, 0.8226133305159412, 0.8568524944290818, 0.8934229760827734, 0.929993457736465, 0.9665639393901566, 1.0031344210438482, 1.0397049026975398, 1.0990600593648838, 1.1584152160322279, 1.217770372699572, 1.277125529366916, 1.33648068603426, 1.395835842701604, 1.4615764292981985, 1.527317015894793, 1.5930576024913876, 1.6587981890879822, 1.7245387756845767, 1.8279945059937002, 1.9314502363028236, 2.034905966611947, 2.138361696921071, 2.2418174272301945, 2.345273157539318, 2.451988913806541, 2.558704670073764, 2.665420426340987, 2.77213618260821, 2.878851938875433, 2.985567695142656, 3.1398977411202655, 3.294227787097875, 3.4485578330754847, 3.6028878790530943, 3.757217925030704, 3.9115479710083134, 4.122285717663795, 4.333023464319276, 4.543761210974758, 4.754498957630239, 4.96523670428572, 5.175974450941202, 5.490795418160398, 5.805616385379595, 6.120437352598791, 6.435258319817987, 6.750079287037184, 7.06490025425638, 7.437711017493068, 7.810521780729755, 8.183332543966443, 8.556143307203133, 8.928954070439822, 9.301764833676511, 9.814963631781977, 10.0]</t>
+          <t>[0.0, 1.3318509976273833e-05, 2.6637019952547667e-05, 0.00015982211971528603, 0.00029300721947802437, 0.0007544751216508781, 0.0012159430238237318, 0.0016774109259965855, 0.003234011472977132, 0.004790612019957678, 0.006347212566938225, 0.011653618535348331, 0.016960024503758435, 0.022266430472168537, 0.02757283644057864, 0.03629200343234231, 0.04501117042410598, 0.053730337415869654, 0.062449504407633326, 0.071168671399397, 0.0815975445099587, 0.09202641762052038, 0.10245529073108207, 0.11288416384164376, 0.12020969891581218, 0.1275352339899806, 0.134860769064149, 0.1348836613612558, 0.13490655365836257, 0.13492944595546935, 0.13495233825257613, 0.1349752305496829, 0.1349981228467897, 0.1352270458178575, 0.1354559687889253, 0.1356848917599931, 0.1359138147310609, 0.1361427377021287, 0.1379717968505148, 0.13833760868019201, 0.13870342050986922, 0.13906923233954643, 0.13943504416922364, 0.139551934009818, 0.13966882385041235, 0.13969220181853123, 0.1397155797866501, 0.139738957754769, 0.13974363334839277, 0.13974830894201654, 0.1397492440607413, 0.13975017917946606, 0.13975111429819081, 0.13975204941691557, 0.13975242346440547, 0.13975249827390346, 0.13975250317962343, 0.13975250551143925, 0.13975250653171356, 0.139752507350137, 0.13975250816856044, 0.13975250898698388, 0.13975251035715314, 0.1397525117273224, 0.13975252542901495, 0.1397525391307075, 0.1397526761476331, 0.13975281316455868, 0.1397541833338145, 0.13975555350307034, 0.13976372385416042, 0.1397718942052505, 0.13978006455634057, 0.13982790964993883, 0.13987575474353708, 0.13992359983713534, 0.14040205077311793, 0.14088050170910052, 0.1413589526450831, 0.1425216644094902, 0.14368437617389732, 0.14484708793830442, 0.14600979970271152, 0.14897930810525725, 0.15194881650780298, 0.1549183249103487, 0.15788783331289444, 0.16085734171544017, 0.16609801851836875, 0.17133869532129734, 0.17657937212422592, 0.1818200489271545, 0.1870607257300831, 0.19230140253301167, 0.19872038820539667, 0.20513937387778167, 0.21155835955016666, 0.21797734522255166, 0.22439633089493666, 0.23081531656732165, 0.23699437174114676, 0.24317342691497187, 0.24935248208879698, 0.2555315372626221, 0.26171059243644723, 0.26731369429341156, 0.2729167961503759, 0.2785198980073402, 0.28412299986430456, 0.2897261017212689, 0.2953292035782332, 0.3033935297613121, 0.311457855944391, 0.3195221821274699, 0.3275865083105488, 0.3356508344936277, 0.3437151606767066, 0.35270879272413574, 0.3617024247715649, 0.37069605681899404, 0.3796896888664232, 0.3886833209138523, 0.3921832386822722, 0.39300976370693497, 0.3934881017924023, 0.3936392724791049, 0.3937324914418844, 0.3937853905837112, 0.393838289725538, 0.39389118886736485, 0.3939440880091917, 0.3939969871510185, 0.3940498862928453, 0.39412187015935, 0.3941938540258547, 0.3942658378923594, 0.3943378217588641, 0.3944098056253688, 0.3944817894918735, 0.39461321910765107, 0.3947446487234286, 0.3948760783392062, 0.39500750795498374, 0.3951389375707613, 0.3955066986848948, 0.3958744597990283, 0.3962422209131618, 0.3966099820272953, 0.3982126801308106, 0.39981537823432595, 0.40141807633784127, 0.40740285291365563, 0.41338762948947, 0.41937240606528436, 0.4342200957679443, 0.4490677854706042, 0.46391547517326415, 0.4787631648759241, 0.49382279979673693, 0.5088824347175498, 0.5239420696383627, 0.5390017045591755, 0.5540613394799884, 0.579504187367128, 0.6049470352542677, 0.6303898831414074, 0.6558327310285471, 0.6812755789156868, 0.7067184268028265, 0.7479298123552878, 0.7891411979077491, 0.8303525834602103, 0.8715639690126716, 0.9127753545651329, 0.9539867401175942, 0.994136951468039, 1.034287162818484, 1.0744373741689288, 1.1145875855193736, 1.1547377968698185, 1.2221773663830364, 1.2896169358962544, 1.3570565054094723, 1.4244960749226903, 1.4919356444359082, 1.5593752139491261, 1.628892194488552, 1.6984091750279777, 1.7679261555674035, 1.8374431361068293, 1.906960116646255, 1.9764770971856809, 2.090581692791855, 2.2046862883980287, 2.3187908840042026, 2.4328954796103766, 2.5470000752165505, 2.6611046708227244, 2.797520994078492, 2.9339373173342596, 3.070353640590027, 3.2067699638457947, 3.3431862871015623, 3.47960261035733, 3.6848560536460204, 3.890109496934711, 4.095362940223401, 4.300616383512091, 4.505869826800781, 4.711123270089471, 4.978178431878992, 5.245233593668512, 5.512288755458033, 5.779343917247553, 6.046399079037074, 6.313454240826594, 6.619490035819585, 6.9255258308125764, 7.2315616258055675, 7.5375974207985585, 7.84363321579155, 8.14966901078454, 8.610406559285224, 9.071144107785907, 9.53188165628659, 9.992619204787273, 10.0]</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.5571797818247779</v>
+        <v>0.557179705011169</v>
       </c>
       <c r="D31" t="n">
         <v>9.81</v>
@@ -2510,13 +2510,13 @@
         <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>5.571797818247779</v>
+        <v>5.571797050111689</v>
       </c>
       <c r="M31" t="n">
-        <v>0.006442275567225818</v>
+        <v>0.006442277343509002</v>
       </c>
       <c r="N31" t="n">
-        <v>0.03221137783612909</v>
+        <v>0.03221138671754501</v>
       </c>
       <c r="O31" t="n">
         <v>19.52897018220085</v>
@@ -2546,11 +2546,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[0.0, 5.9598938799805e-07, 1.1919787759961e-06, 7.1518726559766e-06, 1.31117665359571e-05, 3.09521403908463e-05, 4.8792514245735496e-05, 6.663288810062469e-05, 0.00011073832376481984, 0.000154843759429015, 0.00019894919509321016, 0.00041738478689668174, 0.0006358203787001533, 0.0008542559705036249, 0.001826473222294287, 0.002798690474084949, 0.0037709077258756113, 0.004743124977666274, 0.006428341956958664, 0.008113558936251054, 0.009798775915543444, 0.011483992894835834, 0.013169209874128224, 0.0213991971834412, 0.02962918449275418, 0.03785917180206716, 0.04608915911138014, 0.05431914642069312, 0.06332592473275349, 0.07233270304481386, 0.08133948135687423, 0.0903462596689346, 0.09764134384505929, 0.10493642802118398, 0.11223151219730867, 0.11952659637343337, 0.12682168054955806, 0.13411676472568274, 0.1406055875325877, 0.14709441033949266, 0.15358323314639763, 0.1600720559533026, 0.16656087876020756, 0.17304970156711252, 0.17875128417768654, 0.18445286678826056, 0.19015444939883458, 0.1958560320094086, 0.20155761461998262, 0.2077368509957374, 0.2139160873714922, 0.220095323747247, 0.2262745601230018, 0.23245379649875658, 0.23863303287451137, 0.2445264973340429, 0.25041996179357445, 0.256313426253106, 0.26220689071263753, 0.26810035517216907, 0.2739938196317006, 0.2797161182144794, 0.2854384167972582, 0.29116071538003696, 0.29688301396281574, 0.30260531254559453, 0.3083276111283733, 0.3161909031947113, 0.32405419526104934, 0.33191748732738735, 0.33978077939372536, 0.3476440714600634, 0.35693989662782444, 0.3662357217955855, 0.37553154696334656, 0.3848273721311076, 0.3941231972988687, 0.40341902246662975, 0.41494522093798103, 0.4264714194093323, 0.4379976178806836, 0.44952381635203487, 0.46105001482338615, 0.4725762132947374, 0.4886634165594803, 0.5047506198242232, 0.5208378230889661, 0.536925026353709, 0.5530122296184519, 0.5690994328831948, 0.5917941057592337, 0.6144887786352727, 0.6371834515113117, 0.6598781243873507, 0.6825727972633897, 0.7167482507227754, 0.750923704182161, 0.7850991576415467, 0.8192746111009324, 0.853450064560318, 0.8899043865605153, 0.9263587085607126, 0.9628130305609098, 0.9992673525611071, 1.0357216745613043, 1.0949475079560589, 1.1541733413508135, 1.2133991747455681, 1.2726250081403228, 1.3318508415350774, 1.391076674929832, 1.456631284663923, 1.5221858943980142, 1.5877405041321053, 1.6532951138661964, 1.7188497236002875, 1.821990132591995, 1.9251305415837023, 2.0282709505754095, 2.1314113595671165, 2.2345517685588234, 2.3376921775505304, 2.4441212024296566, 2.550550227308783, 2.656979252187909, 2.763408277067035, 2.8698373019461614, 2.9762663268252876, 3.1302310991841664, 3.2841958715430453, 3.438160643901924, 3.592125416260803, 3.746090188619682, 3.9000549609785606, 4.133980978248544, 4.367906995518527, 4.60183301278851, 4.835759030058493, 5.069685047328476, 5.303611064598459, 5.591099429130798, 5.878587793663137, 6.166076158195477, 6.453564522727816, 6.741052887260155, 7.028541251792494, 7.46045037909375, 7.892359506395006, 8.324268633696262, 8.756177760997517, 9.188086888298772, 9.619996015600027, 10.0]</t>
+          <t>[0.0, 1.3326738858711065e-05, 2.665347771742213e-05, 0.00015992086630453275, 0.0002931882548916434, 0.0007403667267013866, 0.0011875451985111298, 0.0016347236703208728, 0.0031083084307092987, 0.0045818931910977245, 0.00605547795148615, 0.011269100155805666, 0.01648272236012518, 0.0216963445644447, 0.026909966768764216, 0.03542771153074821, 0.04394545629273221, 0.052463201054716205, 0.0609809458167002, 0.0694986905786842, 0.07988376800572654, 0.09026884543276888, 0.10065392285981122, 0.11103900028685355, 0.11827363829627963, 0.1255082763057057, 0.1327429143151318, 0.13276552255891125, 0.1327881308026907, 0.13281073904647014, 0.1328333472902496, 0.13285595553402904, 0.1328785637778085, 0.13310464621560297, 0.13333072865339746, 0.13355681109119194, 0.13378289352898642, 0.1340089759667809, 0.13588847003569532, 0.1362643688494782, 0.1366402676632611, 0.13701616647704398, 0.13739206529082687, 0.13741633939665623, 0.13742119421782212, 0.137426049038988, 0.13743090386015389, 0.13743575868131977, 0.13743770060978613, 0.1374396425382525, 0.13743972021539116, 0.13743979789252983, 0.1374398030281024, 0.137439808163675, 0.13743981061810737, 0.13743981148621515, 0.13743981235432293, 0.1374398132224307, 0.13743981467813346, 0.1374398161338362, 0.13743983069086374, 0.13743984524789127, 0.13743999081816655, 0.13744013638844182, 0.1374415920911946, 0.1374430477939474, 0.1374515833571555, 0.13746011892036358, 0.13746865448357168, 0.13751795859199928, 0.13756726270042688, 0.13761656680885448, 0.13810960789313048, 0.13860264897740648, 0.1390956900616825, 0.14026534185086073, 0.14143499364003898, 0.14260464542921722, 0.14377429721839546, 0.14670087066600296, 0.14962744411361045, 0.15255401756121795, 0.15548059100882544, 0.15840716445643294, 0.16361237128502268, 0.16881757811361242, 0.17402278494220216, 0.1792279917707919, 0.18443319859938165, 0.1896384054279714, 0.19608819651948645, 0.2025379876110015, 0.20898777870251656, 0.2154375697940316, 0.22188736088554667, 0.22833715197706173, 0.23436412721651295, 0.24039110245596418, 0.2464180776954154, 0.25244505293486663, 0.25847202817431786, 0.26408034747674897, 0.2696886667791801, 0.2752969860816112, 0.2809053053840423, 0.2865136246864734, 0.2921219439889045, 0.29995817315575407, 0.30779440232260363, 0.3156306314894532, 0.32346686065630276, 0.3313030898231523, 0.3391393189900019, 0.3483330119808192, 0.35752670497163647, 0.36672039796245376, 0.3671818125312527, 0.3672685889954188, 0.3673175141354222, 0.36736643927542556, 0.36741536441542894, 0.3674642895554323, 0.3675132146954357, 0.36756213983543906, 0.36762842109464533, 0.3676947023538516, 0.36776098361305787, 0.36782726487226414, 0.3678935461314704, 0.3679598273906767, 0.368081624778104, 0.36820342216553137, 0.3683252195529587, 0.36844701694038606, 0.3685688143278134, 0.36890881804927905, 0.3692488217707447, 0.36958882549221034, 0.369928829213676, 0.3714050302490951, 0.3728812312845142, 0.37435743231993335, 0.37937295001520155, 0.38438846771046975, 0.38940398540573795, 0.400256048675062, 0.411108111944386, 0.42196017521371004, 0.4328122384830341, 0.44615501100060007, 0.45949778351816606, 0.47284055603573205, 0.48618332855329804, 0.49952610107086404, 0.5260039134368346, 0.5524817258028052, 0.5789595381687758, 0.6054373505347463, 0.6319151629007169, 0.6638068384405363, 0.6956985139803558, 0.7275901895201752, 0.7594818650599946, 0.791373540599814, 0.8300061123202402, 0.8686386840406665, 0.9072712557610927, 0.9459038274815189, 0.9845363992019451, 1.0231689709223715, 1.07435804823052, 1.1255471255386684, 1.176736202846817, 1.2279252801549654, 1.2791143574631139, 1.3481344938075206, 1.4171546301519273, 1.486174766496334, 1.5551949028407408, 1.6242150391851475, 1.6932351755295543, 1.7683527601065883, 1.8434703446836223, 1.9185879292606562, 1.9937055138376902, 2.0688230984147244, 2.143940682991759, 2.2682880263242997, 2.3926353696568405, 2.5169827129893814, 2.641330056321922, 2.765677399654463, 2.890024742987004, 3.038435272149581, 3.186845801312158, 3.335256330474735, 3.483666859637312, 3.632077388799889, 3.780487917962466, 4.004970696606049, 4.229453475249633, 4.453936253893216, 4.6784190325368, 4.902901811180383, 5.127384589823967, 5.419022309172274, 5.71066002852058, 6.002297747868887, 6.293935467217194, 6.585573186565501, 6.877210905913808, 7.212151418589235, 7.547091931264662, 7.882032443940089, 8.216972956615516, 8.551913469290943, 8.88685398196637, 9.426827237789407, 9.966800493612444, 10.0]</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.5437081355180632</v>
+        <v>0.5437082577438921</v>
       </c>
       <c r="D32" t="n">
         <v>9.81</v>
@@ -2577,13 +2577,13 @@
         <v>2</v>
       </c>
       <c r="L32" t="n">
-        <v>5.437081355180632</v>
+        <v>5.437082577438921</v>
       </c>
       <c r="M32" t="n">
-        <v>0.006765475611947775</v>
+        <v>0.006765472570184993</v>
       </c>
       <c r="N32" t="n">
-        <v>0.03382737805973887</v>
+        <v>0.03382736285092496</v>
       </c>
       <c r="O32" t="n">
         <v>19.50486046006736</v>
@@ -2613,11 +2613,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[0.0, 5.964557196075114e-07, 1.1929114392150228e-06, 7.157468635290138e-06, 1.3122025831365253e-05, 3.09763897603625e-05, 4.883075368935974e-05, 6.668511761835698e-05, 0.00011082626014352877, 0.00015496740266870057, 0.00019910854519387237, 0.00041841795487560266, 0.0006377273645573329, 0.0008570367742390632, 0.0019504836267643941, 0.003043930479289725, 0.004137377331815056, 0.005230824184340387, 0.006988891286910877, 0.008746958389481366, 0.010505025492051855, 0.012263092594622344, 0.014021159697192833, 0.021193406293004244, 0.028365652888815655, 0.035537899484627065, 0.04271014608043848, 0.049882392676249894, 0.0586974261495974, 0.06751245962294491, 0.07632749309629243, 0.08514252656963994, 0.09395756004298746, 0.10277259351633497, 0.10995388458860283, 0.1171351756608707, 0.12431646673313856, 0.13149775780540643, 0.1386790488776743, 0.14586033994994216, 0.15240644704477635, 0.15895255413961054, 0.16549866123444473, 0.17204476832927892, 0.17859087542411312, 0.1851369825189473, 0.19051861307208653, 0.19590024362522576, 0.201281874178365, 0.20666350473150422, 0.21204513528464344, 0.21742676583778267, 0.22387400835831256, 0.23032125087884245, 0.23676849339937234, 0.24103500628812297, 0.2453015191768736, 0.24956803206562422, 0.25383454495437485, 0.2581010578431255, 0.26366254799020206, 0.26922403813727863, 0.2747855282843552, 0.2803470184314318, 0.28693540136877205, 0.2935237843061123, 0.3001121672434526, 0.30670055018079284, 0.3132889331181331, 0.32450312829618466, 0.3357173234742362, 0.3469315186522878, 0.35814571383033933, 0.3693599090083909, 0.38057410418644244, 0.38942231579577474, 0.39827052740510704, 0.40711873901443935, 0.41596695062377165, 0.42481516223310395, 0.43366337384243625, 0.4496004470594447, 0.4655375202764531, 0.48147459349346156, 0.49741166671047, 0.5133487399274784, 0.5379532514037988, 0.5625577628801192, 0.5871622743564395, 0.6117667858327599, 0.6363712973090803, 0.6660184859294569, 0.6956656745498335, 0.7253128631702102, 0.7549600517905868, 0.7846072404109634, 0.8292571198149351, 0.8739069992189068, 0.9185568786228785, 0.9632067580268502, 1.0078566374308218, 1.0525065168347933, 1.1060294864254696, 1.1595524560161459, 1.2130754256068221, 1.2665983951974984, 1.3201213647881747, 1.373644334378851, 1.4438379218107433, 1.5140315092426357, 1.5842250966745282, 1.6544186841064206, 1.724612271538313, 1.7948058589702054, 1.8844521151799183, 1.9740983713896312, 2.063744627599344, 2.1533908838090565, 2.243037140018769, 2.332683396228482, 2.4656206665324185, 2.598557936836355, 2.731495207140292, 2.8644324774442285, 2.997369747748165, 3.1303070180521018, 3.2768699660592686, 3.4234329140664355, 3.5699958620736023, 3.716558810080769, 3.863121758087936, 4.009684706095102, 4.220719110430707, 4.431753514766312, 4.642787919101917, 4.853822323437521, 5.064856727773126, 5.275891132108731, 5.565527008638501, 5.855162885168271, 6.144798761698041, 6.4344346382278115, 6.724070514757582, 7.013706391287352, 7.404321188275722, 7.794935985264091, 8.185550782252461, 8.576165579240831, 8.9667803762292, 9.35739517321757, 9.882155888313102, 10.0]</t>
+          <t>[0.0, 1.3238834574645548e-05, 2.6477669149291096e-05, 0.0001588660148957466, 0.0002912543606422021, 0.000721376586918525, 0.0011514988131948478, 0.0015816210394711705, 0.0029648347242496086, 0.004348048409028047, 0.005731262093806485, 0.01085046143115053, 0.015969660768494577, 0.021088860105838624, 0.02620805944318267, 0.03450207308547199, 0.042796086727761314, 0.051090100370050635, 0.05938411401233996, 0.06767812765462927, 0.07802665437378553, 0.08837518109294179, 0.09872370781209805, 0.10907223453125431, 0.11620260738748976, 0.12333298024372522, 0.13046335309996065, 0.1304856355151364, 0.13050791793031213, 0.13053020034548787, 0.1305524827606636, 0.13057476517583935, 0.1305970475910151, 0.1308198717427725, 0.13104269589452988, 0.13126552004628728, 0.13148834419804467, 0.13171116834980207, 0.13356908557928537, 0.13394066902518204, 0.1343122524710787, 0.13468383591697536, 0.1347581526061547, 0.13483246929533405, 0.13483544196290123, 0.13483841463046842, 0.1348413872980356, 0.1348443599656028, 0.13484459777900817, 0.13484464534168925, 0.13484469290437032, 0.1348447404670514, 0.13484475949212382, 0.13484477851719626, 0.13484478612722522, 0.1348447937372542, 0.1348447967812658, 0.1348447998252774, 0.13484480591330059, 0.13484480721813372, 0.13484480852296685, 0.1348448088924741, 0.13484480926198136, 0.1348448100752862, 0.13484481088859104, 0.1348448186183957, 0.13484482634820036, 0.13484490364624693, 0.1348449809442935, 0.13484575392475925, 0.134846526905225, 0.13485375757397947, 0.13486098824273393, 0.1348682189114884, 0.13491964176288268, 0.13497106461427696, 0.13502248746567125, 0.13546984281105798, 0.1359171981564447, 0.13636455350183144, 0.1374794960318032, 0.13859443856177497, 0.13970938109174674, 0.1408243236217185, 0.14368111119335472, 0.14653789876499093, 0.14939468633662714, 0.15225147390826335, 0.15510826147989956, 0.1602829477936718, 0.16545763410744405, 0.1706323204212163, 0.17580700673498853, 0.18098169304876077, 0.18615637936253301, 0.19259058452024433, 0.19902478967795564, 0.20545899483566696, 0.21189319999337827, 0.2183274051510896, 0.2247616103088009, 0.23077539102496808, 0.23678917174113526, 0.24280295245730243, 0.2488167331734696, 0.2548305138896368, 0.2604283963595699, 0.26602627882950297, 0.27162416129943606, 0.27722204376936915, 0.28281992623930224, 0.28841780870923533, 0.296242642671297, 0.3040674766333587, 0.3118923105954204, 0.31971714455748207, 0.32754197851954375, 0.33536681248160544, 0.34453011843315096, 0.3449701853853483, 0.34524454707203617, 0.34532530648730375, 0.34537064068526035, 0.34541597488321696, 0.34546130908117356, 0.34550664327913017, 0.34555197747708677, 0.3455973116750434, 0.34565854618430353, 0.3457197806935637, 0.34578101520282384, 0.345842249712084, 0.34590348422134415, 0.3459647187306043, 0.3460777369451243, 0.34619075515964426, 0.34630377337416424, 0.3464167915886842, 0.3465298098032042, 0.3468447957389423, 0.34715978167468037, 0.34747476761041846, 0.34778975354615654, 0.3491536100813733, 0.35051746661659006, 0.3518813231518068, 0.356116306390125, 0.36035128962844315, 0.3645862728667613, 0.37372837527989067, 0.38287047769302, 0.39201258010614937, 0.4011546825192787, 0.4126892470670613, 0.42422381161484385, 0.4357583761626264, 0.447292940710409, 0.45882750525819155, 0.4788520042764815, 0.49887650329477146, 0.5189010023130614, 0.5389255013313512, 0.558950000349641, 0.5855067474281008, 0.6120634945065606, 0.6386202415850204, 0.6651769886634802, 0.69173373574194, 0.7242085308567163, 0.7566833259714927, 0.789158121086269, 0.8216329162010454, 0.8541077113158217, 0.8996324388745941, 0.9451571664333664, 0.9906818939921388, 1.0362066215509111, 1.0817313491096834, 1.1272560766684556, 1.1794176641669822, 1.2315792516655089, 1.2837408391640355, 1.335902426662562, 1.3880640141610887, 1.4656681582874038, 1.543272302413719, 1.620876446540034, 1.6984805906663492, 1.7760847347926643, 1.8536888789189794, 1.9366819207498691, 2.019674962580759, 2.1026680044116484, 2.185661046242538, 2.2686540880734274, 2.351647129904317, 2.484754899571399, 2.6178626692384808, 2.7509704389055627, 2.8840782085726446, 3.0171859782397266, 3.1502937479068085, 3.3147904765963143, 3.47928720528582, 3.643783933975326, 3.808280662664832, 3.9727773913543376, 4.137274120043843, 4.357071234360866, 4.576868348677889, 4.796665462994913, 5.016462577311936, 5.236259691628959, 5.456056805945982, 5.790418669407534, 6.124780532869085, 6.459142396330637, 6.793504259792188, 7.12786612325374, 7.462227986715291, 7.857471050583942, 8.252714114452592, 8.647957178321242, 9.043200242189892, 9.438443306058542, 9.833686369927191, 10.0]</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.5286314530324919</v>
+        <v>0.5286315219355506</v>
       </c>
       <c r="D33" t="n">
         <v>9.81</v>
@@ -2644,13 +2644,13 @@
         <v>2</v>
       </c>
       <c r="L33" t="n">
-        <v>5.286314530324919</v>
+        <v>5.286315219355506</v>
       </c>
       <c r="M33" t="n">
-        <v>0.007156884300345036</v>
+        <v>0.007156882434655358</v>
       </c>
       <c r="N33" t="n">
-        <v>0.03578442150172518</v>
+        <v>0.03578441217327679</v>
       </c>
       <c r="O33" t="n">
         <v>19.47436515224987</v>
@@ -2680,11 +2680,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[0.0, 5.970471135409412e-07, 1.1940942270818823e-06, 7.164565362491294e-06, 1.3135036497900705e-05, 3.1007142450202685e-05, 4.8879248402504665e-05, 6.675135435480665e-05, 0.00011093778141643541, 0.00015512420847806416, 0.0001993106355396929, 0.00041974214974495165, 0.0006401736639502104, 0.0008606051781554692, 0.0024052261622529094, 0.003624440603532196, 0.004843655044811483, 0.00606286948609077, 0.0072820839273700574, 0.009759909840918611, 0.012237735754467165, 0.01471556166801572, 0.017193387581564273, 0.019671213495112826, 0.026642881156408102, 0.03361454881770338, 0.040586216478998655, 0.04755788414029393, 0.05452955180158921, 0.06220730478723571, 0.06988505777288222, 0.07756281075852872, 0.08524056374417523, 0.09291831672982173, 0.09997591792452895, 0.10703351911923617, 0.11409112031394339, 0.12114872150865061, 0.12820632270335783, 0.13526392389806505, 0.14184091960038528, 0.1484179153027055, 0.15499491100502574, 0.16157190670734597, 0.1681489024096662, 0.17472589811198644, 0.17992283131069203, 0.18511976450939763, 0.19031669770810322, 0.19551363090680882, 0.2007105641055144, 0.20590749730422, 0.2109734703004658, 0.21603944329671157, 0.22110541629295735, 0.22617138928920313, 0.23123736228544892, 0.2363033352816947, 0.24293560402103606, 0.24956787276037742, 0.2562001414997188, 0.26283241023906023, 0.26946467897840165, 0.27609694771774307, 0.2814181581599987, 0.28673936860225435, 0.29206057904451, 0.29738178948676564, 0.3027029999290213, 0.3114877558577526, 0.32027251178648397, 0.3290572677152153, 0.33784202364394667, 0.346626779572678, 0.35571981749514403, 0.36481285541761005, 0.37390589334007607, 0.3829989312625421, 0.3920919691850081, 0.4011850071074741, 0.41367534003880074, 0.42616567297012736, 0.438656005901454, 0.4511463388327806, 0.4636366717641072, 0.47612700469543384, 0.4936174468520955, 0.5111078890087573, 0.528598331165419, 0.5460887733220807, 0.5635792154787425, 0.5810696576354042, 0.6032616051808479, 0.6254535527262917, 0.6476455002717354, 0.6698374478171791, 0.6920293953626229, 0.728265033417769, 0.7645006714729152, 0.8007363095280614, 0.8369719475832076, 0.8732075856383538, 0.9104637335536903, 0.9477198814690267, 0.9849760293843632, 1.0222321772996996, 1.059488325215036, 1.1201091684244209, 1.1807300116338058, 1.2413508548431906, 1.3019716980525755, 1.3625925412619604, 1.4232133844713453, 1.490658095065872, 1.558102805660399, 1.6255475162549258, 1.6929922268494526, 1.7604369374439794, 1.8651155594656699, 1.9697941814873603, 2.0744728035090505, 2.1791514255307405, 2.2838300475524305, 2.3885086695741204, 2.51904063675596, 2.6495726039377994, 2.780104571119639, 2.9106365383014783, 3.0411685054833177, 3.171700472665157, 3.3236157153620165, 3.475530958058876, 3.627446200755735, 3.7793614434525944, 3.9312766861494537, 4.083191928846313, 4.32172173805771, 4.560251547269107, 4.798781356480505, 5.037311165691902, 5.275840974903299, 5.514370784114696, 5.804150215433951, 6.093929646753205, 6.383709078072459, 6.673488509391714, 6.963267940710968, 7.253047372030222, 7.649002629103216, 8.04495788617621, 8.440913143249205, 8.8368684003222, 9.232823657395194, 9.628778914468189, 10.0]</t>
+          <t>[0.0, 1.2452542159865092e-05, 2.4905084319730183e-05, 0.0001494305059183811, 0.000273955927517032, 0.0006768150218492189, 0.0010796741161814057, 0.0014825332105135925, 0.002766849707309371, 0.00405116620410515, 0.005335482700900928, 0.010352124590489042, 0.015368766480077156, 0.02038540836966527, 0.025402050259253385, 0.03345209080792953, 0.04150213135660568, 0.04955217190528183, 0.057602212453957975, 0.06565225300263412, 0.07597330215483294, 0.08629435130703177, 0.09661540045923059, 0.10693644961142941, 0.11395691528888928, 0.12097738096634915, 0.12799784664380903, 0.12804172455429316, 0.1280856024647773, 0.12812948037526142, 0.12817335828574555, 0.12821723619622968, 0.1282611141067138, 0.12869989321155512, 0.12913867231639642, 0.12957745142123772, 0.13001623052607902, 0.13045500963092033, 0.13107369608547467, 0.13169238254002902, 0.13181611983093988, 0.13193985712185075, 0.13196460458003292, 0.13196955407166935, 0.13197450356330578, 0.13197945305494221, 0.1319804429532695, 0.13198143285159677, 0.13198148656039266, 0.13198154026918854, 0.13198156040687778, 0.13198158054456702, 0.1319815860947093, 0.13198158822327322, 0.13198159035183712, 0.13198159206517876, 0.1319815937785204, 0.13198159549186203, 0.13198159720520367, 0.13198160146439925, 0.13198160572359482, 0.1319816099827904, 0.1319816525747462, 0.131981695166702, 0.13198201472629287, 0.13198233428588374, 0.13198552988179246, 0.13198872547770119, 0.13200179287783378, 0.13201486027796638, 0.13202792767809898, 0.13208764562954614, 0.1321473635809933, 0.13220708153244046, 0.13273611247262682, 0.13326514341281318, 0.13379417435299953, 0.13498969830988347, 0.1361852222667674, 0.13738074622365135, 0.13857627018053528, 0.14143625943417712, 0.14429624868781896, 0.1471562379414608, 0.15001622719510263, 0.15287621644874447, 0.1580227278163546, 0.16316923918396473, 0.16831575055157486, 0.17346226191918498, 0.17860877328679511, 0.18375528465440524, 0.19032404716232829, 0.19689280967025133, 0.20346157217817437, 0.21003033468609741, 0.21659909719402046, 0.2231678597019435, 0.22878134650142576, 0.23439483330090802, 0.24000832010039028, 0.24562180689987254, 0.2512352936993548, 0.25692995473230723, 0.26262461576525964, 0.26831927679821205, 0.27401393783116446, 0.27970859886411686, 0.2854032598970693, 0.2923803714019515, 0.2993574829068337, 0.30633459441171595, 0.3133117059165982, 0.3202888174214804, 0.3237403435282676, 0.3252456762731855, 0.3259995925280622, 0.32642336715597253, 0.3265187542931069, 0.326594428454809, 0.32663670147761104, 0.32667897450041306, 0.3267212475232151, 0.3267635205460171, 0.3268057935688191, 0.32684806659162113, 0.3269049790100626, 0.32696189142850407, 0.32701880384694554, 0.327075716265387, 0.3271326286838285, 0.32718954110226994, 0.3272951034208106, 0.3274006657393512, 0.32750622805789187, 0.3276117903764325, 0.32771735269497315, 0.32801102096889173, 0.3283046892428103, 0.3285983575167289, 0.32889202579064747, 0.33015951911922714, 0.3314270124478068, 0.3326945057763865, 0.3363630232657082, 0.34003154075502995, 0.3437000582443517, 0.3512946741000962, 0.3588892899558407, 0.3664839058115852, 0.3740785216673297, 0.38466872717909406, 0.39525893269085843, 0.4058491382026228, 0.4164393437143872, 0.42702954922615155, 0.44228262541542723, 0.4575357016047029, 0.4727887777939786, 0.4880418539832543, 0.50329493017253, 0.5258923173909248, 0.5484897046093196, 0.5710870918277143, 0.5936844790461091, 0.6162818662645039, 0.6480354627600133, 0.6797890592555228, 0.7115426557510323, 0.7432962522465417, 0.7750498487420512, 0.8078011968572273, 0.8405525449724034, 0.8733038930875795, 0.9060552412027556, 0.9388065893179317, 1.0054665784950563, 1.0721265676721807, 1.1387865568493052, 1.2054465460264296, 1.272106535203554, 1.3387665243806786, 1.3949099903965803, 1.451053456412482, 1.5071969224283837, 1.5633403884442854, 1.619483854460187, 1.7087606598847493, 1.7980374653093116, 1.887314270733874, 1.9765910761584362, 2.0658678815829985, 2.1813369057660883, 2.296805929949178, 2.412274954132268, 2.5277439783153577, 2.6432130024984475, 2.7586820266815373, 2.8875067902959386, 3.01633155391034, 3.1451563175247412, 3.2739810811391425, 3.402805844753544, 3.531630608367945, 3.7379690195529034, 3.9443074307378616, 4.15064584192282, 4.356984253107779, 4.563322664292738, 4.769661075477696, 5.018056498753499, 5.266451922029301, 5.514847345305103, 5.763242768580906, 6.011638191856708, 6.26003361513251, 6.599426536540935, 6.938819457949359, 7.278212379357783, 7.617605300766208, 7.956998222174632, 8.296391143583056, 8.817066847935548, 9.33774255228804, 9.858418256640531, 10.0]</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.5120137083934897</v>
+        <v>0.5120136636173407</v>
       </c>
       <c r="D34" t="n">
         <v>9.81</v>
@@ -2711,13 +2711,13 @@
         <v>2</v>
       </c>
       <c r="L34" t="n">
-        <v>5.120137083934897</v>
+        <v>5.120136636173407</v>
       </c>
       <c r="M34" t="n">
-        <v>0.007628986005694798</v>
+        <v>0.007628987340021022</v>
       </c>
       <c r="N34" t="n">
-        <v>0.03814493002847399</v>
+        <v>0.03814493670010511</v>
       </c>
       <c r="O34" t="n">
         <v>19.43579300306733</v>
@@ -2747,11 +2747,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[0.0, 5.977976368016702e-07, 1.1955952736033404e-06, 7.173571641620042e-06, 1.3151548009636744e-05, 3.104616999378204e-05, 4.894079197792733e-05, 6.683541396207263e-05, 0.00011107931322170125, 0.00015532321248132986, 0.00019956711174095847, 0.00042144574141047967, 0.0006433243710800008, 0.000865203000749522, 0.0020681510920384743, 0.0032710991833274266, 0.004474047274616378, 0.00567699536590533, 0.007500944660882868, 0.009324893955860405, 0.011148843250837943, 0.01297279254581548, 0.014796741840793017, 0.020188469830644793, 0.02558019782049657, 0.030971925810348345, 0.036363653800200124, 0.04175538179005191, 0.05087748155947834, 0.059999581328904775, 0.06912168109833121, 0.07650546225397685, 0.08388924340962249, 0.09127302456526813, 0.09865680572091377, 0.10604058687655941, 0.11342436803220506, 0.11979189702952048, 0.12615942602683589, 0.1325269550241513, 0.1388944840214667, 0.1452620130187821, 0.15162954201609752, 0.1579307705455992, 0.1642319990751009, 0.17053322760460257, 0.17513852650512868, 0.17974382540565478, 0.1843491243061809, 0.188954423206707, 0.1935597221072331, 0.20123947253060936, 0.20592107208284488, 0.2106026716350804, 0.2152842711873159, 0.21996587073955143, 0.22464747029178694, 0.22932906984402246, 0.23457210791047, 0.23981514597691755, 0.2450581840433651, 0.25030122210981265, 0.2555442601762602, 0.26078729824270774, 0.26640260941092575, 0.27201792057914376, 0.27763323174736176, 0.28324854291557977, 0.2888638540837978, 0.2944791652520158, 0.30255508281955984, 0.3106310003871039, 0.31870691795464795, 0.326782835522192, 0.33485875308973606, 0.34419517070186995, 0.35353158831400383, 0.3628680059261377, 0.3722044235382716, 0.3815408411504055, 0.39087725876253937, 0.40247284071674816, 0.41406842267095695, 0.42566400462516574, 0.4372595865793745, 0.4488551685335833, 0.4604507504877921, 0.4765919298390439, 0.4927331091902957, 0.5088742885415476, 0.5250154678927994, 0.5411566472440512, 0.5638161478028842, 0.5864756483617173, 0.6091351489205503, 0.6317946494793834, 0.6544541500382164, 0.6871850562695216, 0.7199159625008269, 0.7526468687321322, 0.7853777749634374, 0.8181086811947427, 0.8529126998240104, 0.8877167184532782, 0.9225207370825459, 0.9573247557118136, 0.9921287743410814, 1.0538443456102677, 1.115559916879454, 1.1772754881486405, 1.2389910594178268, 1.3007066306870132, 1.3624222019561996, 1.4266223742665018, 1.4908225465768041, 1.5550227188871064, 1.6192228911974087, 1.683423063507711, 1.7476232358180133, 1.8285638772447383, 1.9095045186714634, 1.9904451600981885, 2.0713858015249134, 2.1523264429516384, 2.2332670843783635, 2.347566844220698, 2.461866604063032, 2.5761663639053665, 2.6904661237477008, 2.804765883590035, 2.9190656434323694, 3.09023118335495, 3.2613967232775307, 3.4325622632001114, 3.603727803122692, 3.7748933430452727, 3.9460588829678533, 4.153941534327906, 4.361824185687959, 4.569706837048011, 4.777589488408064, 4.985472139768117, 5.1933547911281694, 5.507322105403, 5.821289419677831, 6.135256733952662, 6.449224048227493, 6.763191362502324, 7.077158676777155, 7.486211976020116, 7.895265275263077, 8.304318574506038, 8.713371873748997, 9.122425172991957, 9.531478472234916, 10.0]</t>
+          <t>[0.0, 1.1636026210024255e-05, 2.327205242004851e-05, 0.00013963231452029107, 0.0002559925766205336, 0.0006307274987388887, 0.0010054624208572437, 0.0013801973429755988, 0.002563075389751978, 0.0037459534365283566, 0.0049288314833047355, 0.00978424748542656, 0.014639663487548384, 0.01949507948967021, 0.024350495491792034, 0.03212702363801083, 0.03990355178422962, 0.04768007993044841, 0.055456608076667205, 0.063233136222886, 0.07352873138758323, 0.08382432655228046, 0.0941199217169777, 0.10165573851754098, 0.10919155531810426, 0.11672737211866754, 0.12426318891923083, 0.12431028777423435, 0.12435738662923787, 0.12440448548424139, 0.12445158433924491, 0.12449868319424844, 0.12454578204925196, 0.12501677059928717, 0.1254877591493224, 0.1259587476993576, 0.12642973624939283, 0.12690072479942804, 0.12753617487776545, 0.12817162495610285, 0.12880707503444025, 0.12883249303757374, 0.12885791104070723, 0.12886299464133394, 0.12886807824196064, 0.12887316184258735, 0.1288741785627127, 0.12887519528283803, 0.12887621200296337, 0.1288772287230887, 0.12887731006069875, 0.12887739139830878, 0.12887747273591882, 0.12887747663556087, 0.1288774781535034, 0.12887747933373742, 0.12887748051397144, 0.12887748169420546, 0.12887748360942544, 0.12887748552464542, 0.12887750467684525, 0.12887752382904508, 0.12887771535104334, 0.1288779068730416, 0.1288798220930242, 0.1288817373130068, 0.12889207354240534, 0.12890240977180387, 0.1289127460012024, 0.1289688707674617, 0.129024995533721, 0.12908112029998028, 0.12955421740790835, 0.1300273145158364, 0.13050041162376447, 0.1316248600640342, 0.13274930850430394, 0.13387375694457368, 0.13499820538484342, 0.13775623707332185, 0.1405142687618003, 0.14327230045027872, 0.14603033213875716, 0.1487883638272356, 0.15388402839291782, 0.15897969295860004, 0.16407535752428226, 0.16917102208996448, 0.1742666866556467, 0.17936235122132893, 0.18590852843163994, 0.19245470564195094, 0.19900088285226195, 0.20554706006257295, 0.21209323727288396, 0.21863941448319496, 0.2242717425251736, 0.22990407056715223, 0.23553639860913086, 0.2411687266511095, 0.24680105469308813, 0.2525005479566446, 0.2582000412202011, 0.26389953448375764, 0.26959902774731415, 0.27529852101087066, 0.28099801427442717, 0.28798498272506406, 0.29497195117570096, 0.30195891962633786, 0.30894588807697476, 0.3094946556342521, 0.3098159174121147, 0.3099066554312601, 0.3099732180371744, 0.31003978064308874, 0.31010634324900305, 0.31017290585491736, 0.31023946846083167, 0.3103499098312762, 0.3104603512017207, 0.31057079257216524, 0.31068123394260977, 0.3110205053904375, 0.31135977683826527, 0.311699048286093, 0.313065203207024, 0.31443135812795503, 0.31579751304888604, 0.32019566876301214, 0.32459382447713825, 0.32899198019126435, 0.33339013590539046, 0.3423433031785295, 0.35129647045166856, 0.3602496377248076, 0.36920280499794667, 0.3781559722710857, 0.3883074743709903, 0.39845897647089484, 0.4086104785707994, 0.41876198067070397, 0.42891348277060853, 0.44354565847781086, 0.4581778341850132, 0.4728100098922155, 0.4874421855994178, 0.5020743613066201, 0.5231050520619985, 0.544135742817377, 0.5651664335727554, 0.5861971243281339, 0.6072278150835123, 0.6376663087002535, 0.6681048023169948, 0.698543295933736, 0.7289817895504772, 0.7594202831672184, 0.7915363887083108, 0.8236524942494031, 0.8557685997904955, 0.8878847053315878, 0.9200008108726802, 0.9801930145715417, 1.0403852182704032, 1.1005774219692648, 1.1607696256681264, 1.220961829366988, 1.2811540330658495, 1.3464883705867665, 1.4118227081076835, 1.4771570456286005, 1.5424913831495175, 1.6078257206704345, 1.6731600581913515, 1.7511418762761877, 1.8291236943610238, 1.90710551244586, 1.9850873305306962, 2.0630691486155324, 2.1410509667003685, 2.2627936969319222, 2.384536427163476, 2.5062791573950296, 2.6280218876265833, 2.749764617858137, 2.8715073480896907, 3.020256282367806, 3.169005216645921, 3.3177541509240362, 3.4665030852021514, 3.6152520194802666, 3.764000953758382, 3.986809671274794, 4.209618388791206, 4.432427106307618, 4.655235823824031, 4.878044541340443, 5.100853258856855, 5.392054075814184, 5.683254892771513, 5.974455709728843, 6.265656526686172, 6.556857343643501, 6.84805816060083, 7.1828207121348555, 7.517583263668881, 7.852345815202906, 8.18710836673693, 8.521870918270956, 8.856633469804981, 9.396601616355504, 9.936569762906027, 10.0]</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.4939682061568098</v>
+        <v>0.4939682751888413</v>
       </c>
       <c r="D35" t="n">
         <v>9.81</v>
@@ -2778,13 +2778,13 @@
         <v>2</v>
       </c>
       <c r="L35" t="n">
-        <v>4.939682061568098</v>
+        <v>4.939682751888412</v>
       </c>
       <c r="M35" t="n">
-        <v>0.008196567165833021</v>
+        <v>0.008196564874893819</v>
       </c>
       <c r="N35" t="n">
-        <v>0.04098283582916511</v>
+        <v>0.0409828243744691</v>
       </c>
       <c r="O35" t="n">
         <v>19.38700481894847</v>
@@ -2814,11 +2814,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[0.0, 5.987509583809791e-07, 1.1975019167619582e-06, 7.185011500571749e-06, 1.3172521084381541e-05, 3.109574325837268e-05, 4.9018965432363825e-05, 6.694218760635497e-05, 0.00011125909297221616, 0.00015557599833807736, 0.00019989290370393855, 0.0004236482506064, 0.0006474035975088615, 0.0008711589444113229, 0.0018103548825863442, 0.0027495508207613655, 0.0036887467589363865, 0.004627942697111408, 0.006272639667313121, 0.007917336637514835, 0.009562033607716548, 0.011206730577918262, 0.012851427548119975, 0.017563392180811464, 0.022275356813502952, 0.02698732144619444, 0.03169928607888593, 0.03641125071157743, 0.04541147595821801, 0.054411701204858595, 0.06341192645149918, 0.07241215169813976, 0.07959977059050242, 0.08678738948286509, 0.09397500837522775, 0.10116262726759041, 0.10835024615995308, 0.11553786505231574, 0.12191822639165763, 0.1282985877309995, 0.1346789490703414, 0.14105931040968328, 0.14743967174902517, 0.15382003308836706, 0.15967832747925556, 0.16553662187014406, 0.17139491626103256, 0.17725321065192107, 0.18311150504280957, 0.18913751697132833, 0.1951635288998471, 0.20118954082836585, 0.2072155527568846, 0.21324156468540337, 0.21926757661392213, 0.2249317002840964, 0.23059582395427067, 0.23625994762444494, 0.2419240712946192, 0.24758819496479348, 0.2532523186349678, 0.25895748200471175, 0.2646626453744557, 0.2703678087441997, 0.27607297211394366, 0.28177813548368763, 0.2874832988534316, 0.29616797928293465, 0.3048526597124377, 0.31353734014194073, 0.3222220205714438, 0.3309067010009468, 0.34038255246364757, 0.3498584039263483, 0.35933425538904906, 0.3688101068517498, 0.37828595831445055, 0.3877618097771513, 0.39957094395286497, 0.41138007812857863, 0.4231892123042923, 0.43499834648000596, 0.4468074806557196, 0.4586166148314333, 0.4750511995471058, 0.4914857842627783, 0.5079203689784508, 0.5243549536941234, 0.540789538409796, 0.561771900656308, 0.58275426290282, 0.6037366251493319, 0.6247189873958439, 0.6457013496423558, 0.6782739012769959, 0.7108464529116361, 0.7434190045462762, 0.7759915561809163, 0.8085641078155564, 0.8429960441095969, 0.8774279804036375, 0.911859916697678, 0.9462918529917185, 0.980723789285759, 1.0415110303683934, 1.1022982714510279, 1.1630855125336623, 1.2238727536162968, 1.2846599946989312, 1.3454472357815657, 1.4089457327709847, 1.4724442297604037, 1.5359427267498227, 1.5994412237392417, 1.6629397207286607, 1.7264382177180797, 1.8064740565864637, 1.8865098954548476, 1.9665457343232315, 2.0465815731916157, 2.12661741206, 2.206653250928384, 2.3196182514643002, 2.4325832520002164, 2.5455482525361326, 2.6585132530720488, 2.771478253607965, 2.884443254143881, 3.053383991989681, 3.2223247298354805, 3.39126546768128, 3.56020620552708, 3.7291469433728794, 3.898087681218679, 4.103359878500927, 4.3086320757831755, 4.513904273065424, 4.719176470347672, 4.92444866762992, 5.129720864912168, 5.4394452468366135, 5.7491696287610585, 6.058894010685504, 6.368618392609949, 6.678342774534394, 6.988067156458839, 7.3926045469599355, 7.797141937461032, 8.201679327962129, 8.606216718463227, 9.010754108964324, 9.415291499465422, 9.88941401338664, 10.0]</t>
+          <t>[0.0, 1.0805453077242828e-05, 2.1610906154485657e-05, 0.00012966543692691395, 0.00023771996769934224, 0.0005840548406224384, 0.0009303897135455345, 0.0012767245864686305, 0.0023580736374514124, 0.0034394226884341943, 0.004520771739416976, 0.009045346050981035, 0.013569920362545094, 0.018094494674109153, 0.022619068985673212, 0.030061186175225376, 0.03750330336477754, 0.04494542055432971, 0.05238753774388187, 0.059829654933434034, 0.0700380819769881, 0.08024650902054217, 0.09045493606409624, 0.09789431680689012, 0.105333697549684, 0.11277307829247787, 0.12021245903527175, 0.12025895516491422, 0.12030545129455669, 0.12035194742419916, 0.12039844355384163, 0.1204449396834841, 0.12049143581312657, 0.12095639710955128, 0.12142135840597598, 0.12188631970240069, 0.12235128099882539, 0.1228162422952501, 0.12345671646731611, 0.12409719063938213, 0.12473766481144814, 0.12537813898351416, 0.12556409650711386, 0.12557153480805786, 0.12557161130054825, 0.12557168779303865, 0.1255717153216814, 0.12557172810363457, 0.12557173277117392, 0.12557173541922154, 0.12557173753512527, 0.125571739651029, 0.12557174176693273, 0.12557174388283646, 0.12557174911974775, 0.12557175435665904, 0.12557175959357034, 0.12557181196268327, 0.1255718643317962, 0.12557225558478194, 0.12557264683776767, 0.125576559367625, 0.1255804718974823, 0.12559559754523128, 0.12561072319298025, 0.12562584884072922, 0.12569211791783208, 0.12575838699493494, 0.1258246560720378, 0.12632438897124731, 0.12682412187045683, 0.12732385476966634, 0.1284747125353025, 0.12962557030093863, 0.13077642806657477, 0.13192728583221092, 0.13466738234228126, 0.1374074788523516, 0.14014757536242195, 0.1428876718724923, 0.14562776838256264, 0.15070792350593223, 0.15578807862930183, 0.16086823375267142, 0.16594838887604102, 0.17102854399941061, 0.1761086991227802, 0.18274704284323623, 0.18938538656369225, 0.19602373028414827, 0.20089502939841797, 0.20576632851268767, 0.21063762762695737, 0.21550892674122707, 0.22038022585549677, 0.22525152496976647, 0.23146285724419913, 0.23767418951863178, 0.24388552179306444, 0.2500968540674971, 0.25630818634192976, 0.2625195186163624, 0.2681834507849448, 0.27384738295352723, 0.27951131512210964, 0.28517524729069205, 0.29083917945927446, 0.2930541065091168, 0.294066486692412, 0.294372517862954, 0.2945058315206585, 0.29456599700980196, 0.29460820890218364, 0.2946504207945653, 0.294692632686947, 0.2947348445793287, 0.2947770564717104, 0.29481926836409206, 0.2948802141835193, 0.2949411600029465, 0.29500210582237374, 0.29506305164180097, 0.2951239974612282, 0.2951849432806554, 0.29527666930680013, 0.29536839533294484, 0.29546012135908956, 0.29555184738523427, 0.295643573411379, 0.2958844502098383, 0.2961253270082976, 0.2963662038067569, 0.2966070806052162, 0.29793321380490756, 0.29925934700459894, 0.3005854802042903, 0.30389793409724697, 0.3072103879902036, 0.31052284188316026, 0.3138352957761169, 0.31953203530461943, 0.32522877483312196, 0.3309255143616245, 0.336622253890127, 0.34231899341862954, 0.3504198261270802, 0.3585206588355309, 0.3666214915439816, 0.3747223242524323, 0.382823156960883, 0.3937630475480256, 0.4047029381351682, 0.41564282872231084, 0.42658271930945346, 0.4375226098965961, 0.45368844382547024, 0.4698542777543444, 0.48602011168321857, 0.5021859456120927, 0.5183517795409669, 0.5409304077140572, 0.5635090358871475, 0.5860876640602378, 0.6086662922333281, 0.6312449204064184, 0.6631320859561158, 0.6950192515058132, 0.7269064170555106, 0.758793582605208, 0.7906807481549054, 0.8241961611117127, 0.8577115740685199, 0.8912269870253272, 0.9247423999821345, 0.9582578129389417, 1.0254267038814966, 1.0925955948240516, 1.1597644857666065, 1.2269333767091615, 1.2941022676517164, 1.3612711585942714, 1.4241517261455112, 1.487032293696751, 1.5499128612479909, 1.6127934287992307, 1.6756739963504705, 1.7385545639017104, 1.822129604341594, 1.9057046447814776, 1.9892796852213612, 2.072854725661245, 2.1564297661011285, 2.240004806541012, 2.3573370580990862, 2.4746693096571604, 2.5920015612152345, 2.7093338127733086, 2.826666064331383, 2.943998315889457, 3.0996794779392367, 3.2553606399890165, 3.4110418020387963, 3.566722964088576, 3.722404126138356, 3.8780852881881356, 4.109097723079029, 4.340110157969923, 4.571122592860816, 4.80213502775171, 5.033147462642604, 5.264159897533498, 5.546819749886581, 5.829479602239665, 6.112139454592749, 6.394799306945833, 6.677459159298917, 6.960119011652001, 7.38791399253017, 7.81570897340834, 8.24350395428651, 8.67129893516468, 9.09909391604285, 9.52688889692102, 10.0]</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.4746469635961578</v>
+        <v>0.4746469530424428</v>
       </c>
       <c r="D36" t="n">
         <v>9.81</v>
@@ -2845,13 +2845,13 @@
         <v>2</v>
       </c>
       <c r="L36" t="n">
-        <v>4.746469635961578</v>
+        <v>4.746469530424427</v>
       </c>
       <c r="M36" t="n">
-        <v>0.008877457089465258</v>
+        <v>0.008877457484243539</v>
       </c>
       <c r="N36" t="n">
-        <v>0.04438728544732629</v>
+        <v>0.0443872874212177</v>
       </c>
       <c r="O36" t="n">
         <v>19.32529482974482</v>
@@ -2881,11 +2881,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[0.0, 5.99963253593378e-07, 1.199926507186756e-06, 7.1995590431205364e-06, 1.3199191579054317e-05, 3.115878348963488e-05, 4.911837540021544e-05, 6.7077967310796e-05, 0.00011148771826958759, 0.0001558974692283792, 0.0002003072201871708, 0.0004265144060340599, 0.000652721591880949, 0.000878928777727838, 0.0016928264951161522, 0.0025067242125044664, 0.0033206219298927806, 0.004134519647281095, 0.0056821700700981255, 0.006841095381617932, 0.008000020693137738, 0.009158946004657545, 0.010742804025197252, 0.01232666204573696, 0.013910520066276667, 0.015494378086816375, 0.018293867489212433, 0.02109335689160849, 0.023892846294004545, 0.0266923356964006, 0.029491825098796658, 0.037554666048047816, 0.045617506997298975, 0.05368034794655013, 0.06174318889580129, 0.06980602984505245, 0.0778688707943036, 0.08487886234013375, 0.0918888538859639, 0.09889884543179406, 0.10590883697762421, 0.11291882852345436, 0.11992882006928451, 0.12638219730851763, 0.13283557454775075, 0.13928895178698386, 0.14574232902621698, 0.1521957062654501, 0.1586490835046832, 0.16381042131098095, 0.16897175911727869, 0.17413309692357642, 0.17929443472987416, 0.1844557725361719, 0.18961711034246964, 0.19474505395654243, 0.19987299757061522, 0.205000941184688, 0.2101288847987608, 0.21525682841283358, 0.22038477202690637, 0.22658508915212588, 0.2327854062773454, 0.2389857234025649, 0.24518604052778442, 0.25138635765300393, 0.25758667477822345, 0.2628335936990049, 0.2680805126197863, 0.27332743154056777, 0.2785743504613492, 0.28382126938213065, 0.2890681883029121, 0.2972343527777051, 0.3054005172524981, 0.31356668172729113, 0.32173284620208414, 0.32989901067687716, 0.33806517515167017, 0.34759959033439825, 0.3571340055171263, 0.3666684206998544, 0.37620283588258246, 0.38573725106531054, 0.3952716662480386, 0.40739918419802357, 0.4195267021480085, 0.4316542200979935, 0.44378173804797844, 0.4559092559979634, 0.46803677394794835, 0.4866723803361752, 0.5053079867244021, 0.5239435931126291, 0.542579199500856, 0.5612148058890829, 0.5798504122773098, 0.6019263620612305, 0.6240023118451512, 0.6460782616290719, 0.6681542114129926, 0.6902301611969133, 0.7263574805724281, 0.7624847999479429, 0.7986121193234578, 0.8347394386989726, 0.8708667580744874, 0.9156477408895827, 0.9604287237046779, 1.0052097065197731, 1.0499906893348685, 1.0947716721499638, 1.1483664007200078, 1.2019611292900518, 1.2555558578600958, 1.3091505864301398, 1.3627453150001838, 1.4163400435702278, 1.4922825827290378, 1.5682251218878478, 1.6441676610466578, 1.7201102002054678, 1.7960527393642778, 1.8936630092169684, 1.991273279069659, 2.0888835489223494, 2.18649381877504, 2.28410408862773, 2.3817143584804206, 2.5125320187260654, 2.64334967897171, 2.774167339217355, 2.9049849994629997, 3.0358026597086445, 3.1666203199542893, 3.31836002454068, 3.4700997291270705, 3.621839433713461, 3.773579138299852, 3.9253188428862424, 4.0770585474726335, 4.315911342113661, 4.554764136754688, 4.793616931395715, 5.032469726036743, 5.27132252067777, 5.510175315318797, 5.8091741378904445, 6.108172960462092, 6.407171783033739, 6.7061706056053865, 7.005169428177034, 7.304168250748681, 7.75319008519904, 8.202211919649399, 8.651233754099756, 9.100255588550114, 9.549277423000472, 9.99829925745083, 10.0]</t>
+          <t>[0.0, 9.977037987863465e-06, 1.995407597572693e-05, 0.00011972445585436159, 0.00021949483573299624, 0.0005377238091390301, 0.000855952782545064, 0.001174181755951098, 0.0021562101680833467, 0.0031382385802155954, 0.004120266992347844, 0.008119149256188363, 0.012118031520028882, 0.016116913783869403, 0.020115796047709925, 0.02713501790448021, 0.034154239761250496, 0.04117346161802078, 0.04819268347479107, 0.05521190533156135, 0.065195529188043, 0.07517915304452465, 0.08516277690100629, 0.09514640075748794, 0.10198559406908728, 0.10882478738068661, 0.11566398069228595, 0.11570672565048346, 0.11574947060868096, 0.11579221556687846, 0.11583496052507597, 0.11587770548327347, 0.11592045044147098, 0.11634790002344603, 0.11677534960542107, 0.11720279918739612, 0.11763024876937117, 0.11805769835134622, 0.12128247416431091, 0.12192742932690386, 0.12205642035942245, 0.12208221856592617, 0.1221080167724299, 0.12211317641373064, 0.12211420834199078, 0.12211524027025093, 0.12211627219851108, 0.12211647858416311, 0.12211668496981513, 0.12211689135546716, 0.12211691481479295, 0.12211693827411874, 0.12211694104272933, 0.12211694381133992, 0.12211694657995051, 0.1221169493485611, 0.12211695266708152, 0.12211695598560193, 0.12211695930412235, 0.12211696262264277, 0.1221169738847737, 0.12211698514690464, 0.12211699640903557, 0.12211710903034494, 0.1221172216516543, 0.12211834786474791, 0.12211947407784153, 0.12212652348275928, 0.12213357288767702, 0.12215483254873452, 0.12217609220979202, 0.12219735187084951, 0.12227606927352648, 0.12235478667620345, 0.12243350407888041, 0.1229515421133685, 0.1234695801478566, 0.12398761818234469, 0.12515882618114885, 0.126330034179953, 0.12750124217875716, 0.12867245017756132, 0.13139586498060207, 0.13411927978364283, 0.13684269458668358, 0.13956610938972433, 0.14228952419276508, 0.14736905474823944, 0.1524485853037138, 0.15752811585918816, 0.16260764641466252, 0.16768717697013688, 0.17276670752561124, 0.1794195975188053, 0.18607248751199934, 0.1927253775051934, 0.1975695541360169, 0.2024137307668404, 0.20725790739766392, 0.21210208402848743, 0.21694626065931094, 0.22179043729013445, 0.22815620397445283, 0.2345219706587712, 0.24088773734308958, 0.24725350402740795, 0.2536192707117263, 0.2599850373960446, 0.2656979267984475, 0.2714108162008504, 0.2771237056032533, 0.2793251773719903, 0.279836820665834, 0.2799070395442092, 0.2799632538926384, 0.2799950392072797, 0.280026824521921, 0.28005860983656233, 0.28009039515120365, 0.28012218046584497, 0.2801539657804863, 0.2801971105528977, 0.2802402553253091, 0.2802834000977205, 0.2803265448701319, 0.28036968964254333, 0.28041283441495474, 0.28049189361256677, 0.2805709528101788, 0.28065001200779083, 0.28072907120540286, 0.2808081304030149, 0.28102906020957774, 0.2812499900161406, 0.28147091982270345, 0.2816918496292663, 0.28265239792444014, 0.28361294621961397, 0.2845734945147878, 0.28730029364432025, 0.2900270927738527, 0.29275389190338513, 0.2981512588553799, 0.3035486258073747, 0.30894599275936946, 0.31434335971136423, 0.32534093770648714, 0.33220272336269535, 0.33906450901890356, 0.34592629467511177, 0.35278808033132, 0.3596498659875282, 0.3679142397967325, 0.3761786136059368, 0.3844429874151411, 0.3927073612243454, 0.4009717350335497, 0.41490083683370393, 0.42882993863385815, 0.4427590404340124, 0.4566881422341666, 0.4706172440343208, 0.48454634583447503, 0.5154033205555545, 0.5352513284858863, 0.5550993364162181, 0.5749473443465499, 0.5947953522768817, 0.6146433602072136, 0.6344913681375454, 0.6735883177807555, 0.7042512465271205, 0.7349141752734855, 0.7655771040198505, 0.7962400327662155, 0.8269029615125805, 0.8690685289840544, 0.9112340964555283, 0.9533996639270023, 0.9955652313984762, 1.03773079886995, 1.0798963663414238, 1.1433491351436105, 1.2068019039457971, 1.2702546727479838, 1.3337074415501704, 1.397160210352357, 1.4817336557225316, 1.566307101092706, 1.6508805464628806, 1.7354539918330552, 1.8200274372032297, 1.9046008825734042, 1.9893319404641958, 2.0740629983549876, 2.1587940562457795, 2.2435251141365713, 2.328256172027363, 2.412987229918155, 2.550827364729314, 2.6886674995404727, 2.8265076343516315, 2.9643477691627904, 3.1021879039739493, 3.240028038785108, 3.4093019235343354, 3.5785758082835626, 3.74784969303279, 3.917123577782017, 4.086397462531244, 4.2556713472804715, 4.509523445243597, 4.763375543206723, 5.017227641169849, 5.271079739132975, 5.5249318370961005, 5.778783935059226, 6.1113905431099145, 6.443997151160603, 6.776603759211291, 7.109210367261979, 7.441816975312667, 7.7744235833633555, 8.162309674260916, 8.550195765158477, 8.938081856056039, 9.3259679469536, 9.713854037851162, 10.0]</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.4542241292660426</v>
+        <v>0.4542241897197708</v>
       </c>
       <c r="D37" t="n">
         <v>9.81</v>
@@ -2912,13 +2912,13 @@
         <v>2</v>
       </c>
       <c r="L37" t="n">
-        <v>4.542241292660425</v>
+        <v>4.542241897197708</v>
       </c>
       <c r="M37" t="n">
-        <v>0.009693700412141392</v>
+        <v>0.00969369783182839</v>
       </c>
       <c r="N37" t="n">
-        <v>0.04846850206070696</v>
+        <v>0.04846848915914195</v>
       </c>
       <c r="O37" t="n">
         <v>19.24724062796851</v>
@@ -2948,11 +2948,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[0.0, 6.015071089459949e-07, 1.2030142178919898e-06, 7.2180853073519385e-06, 1.3233156396811887e-05, 3.123906539619873e-05, 4.924497439558557e-05, 6.725088339497242e-05, 0.00011177888448070118, 0.00015630688556642994, 0.0002008348866521587, 0.00043027690307861167, 0.0006597189195050646, 0.0008891609359315176, 0.0016207809338878469, 0.002352400931844176, 0.0030840209298005055, 0.003815640927756835, 0.005273140729223344, 0.006730640530689853, 0.008188140332156361, 0.00964564013362287, 0.011103139935089379, 0.015019428852110158, 0.018935717769130937, 0.022852006686151716, 0.026768295603172496, 0.030684584520193275, 0.03884993943626515, 0.04701529435233702, 0.05518064926840889, 0.06334600418448076, 0.07151135910055263, 0.0796767140166245, 0.0866276821266466, 0.09357865023666868, 0.10052961834669077, 0.10748058645671286, 0.11443155456673496, 0.12138252267675705, 0.12785129055355762, 0.1343200584303582, 0.1407888263071588, 0.1472575941839594, 0.15372636206075999, 0.16019512993756058, 0.16546228980931796, 0.17072944968107534, 0.17599660955283272, 0.1812637694245901, 0.1865309292963475, 0.19179808916810487, 0.19752284537411616, 0.20324760158012745, 0.20897235778613873, 0.21469711399215002, 0.2204218701981613, 0.22680967172592073, 0.23319747325368015, 0.23958527478143957, 0.24597307630919898, 0.2523608778369584, 0.2587486793647178, 0.2644559893958015, 0.2701632994268852, 0.27587060945796893, 0.28157791948905264, 0.28728522952013635, 0.29299253955122007, 0.3020443044393331, 0.31109606932744616, 0.3201478342155592, 0.32919959910367225, 0.3382513639917853, 0.34730312887989834, 0.3572686438008643, 0.3672341587218303, 0.3771996736427963, 0.38716518856376225, 0.39713070348472823, 0.4070962184056942, 0.42060258451177435, 0.4341089506178545, 0.4476153167239346, 0.46112168283001476, 0.4746280489360949, 0.48813441504217503, 0.5092086292371352, 0.5302828434320953, 0.5513570576270554, 0.5724312718220156, 0.5935054860169757, 0.6145797002119359, 0.638921643908616, 0.6632635876052962, 0.6876055313019764, 0.7119474749986566, 0.7362894186953368, 0.7754232423944047, 0.8145570660934727, 0.8536908897925406, 0.8928247134916085, 0.9319585371906765, 0.9800842509489388, 1.0282099647072012, 1.0763356784654636, 1.124461392223726, 1.1725871059819886, 1.2292998826615253, 1.2860126593410621, 1.342725436020599, 1.3994382127001357, 1.4561509893796725, 1.5128637660592092, 1.594166202601901, 1.6754686391445928, 1.7567710756872845, 1.8380735122299763, 1.919375948772668, 2.0233512956969206, 2.127326642621173, 2.231301989545426, 2.3352773364696784, 2.439252683393931, 2.5432280303181836, 2.660696932080215, 2.7781658338422464, 2.8956347356042778, 3.013103637366309, 3.1305725391283405, 3.248041440890372, 3.435438273272378, 3.622835105654384, 3.8102319380363903, 3.9976287704183964, 4.185025602800403, 4.3724224351824095, 4.606144176666581, 4.839865918150753, 5.073587659634925, 5.307309401119097, 5.541031142603269, 5.774752884087441, 6.126646864911463, 6.478540845735486, 6.830434826559508, 7.182328807383531, 7.534222788207553, 7.886116769031576, 8.320100913695889, 8.754085058360202, 9.188069203024515, 9.622053347688828, 10.0]</t>
+          <t>[0.0, 9.16577317099757e-06, 1.833154634199514e-05, 0.00010998927805197086, 0.00020164700976194657, 0.0004925741909334038, 0.0007835013721048611, 0.0010744285532763183, 0.001961293672210983, 0.002848158791145647, 0.0037350239100803115, 0.007164032756443938, 0.010593041602807564, 0.01402205044917119, 0.017451059295534817, 0.02398075111137589, 0.03051044292721696, 0.037040134743058034, 0.04356982655889911, 0.05009951837474018, 0.05974319357608643, 0.06938686877743268, 0.07903054397877893, 0.08867421918012518, 0.0955178863090359, 0.10236155343794663, 0.10920522056685736, 0.11604888769576809, 0.11609166061532378, 0.11613443353487947, 0.11617720645443516, 0.11621997937399085, 0.11626275229354655, 0.11630552521310224, 0.11673325440865916, 0.11716098360421608, 0.117588712799773, 0.11801644199532992, 0.11844417119088683, 0.11847476200582957, 0.1185053528207723, 0.11853594363571504, 0.11856653445065778, 0.11857877077663487, 0.11857926022967395, 0.11857974968271304, 0.11858023913575212, 0.11858027829199524, 0.11858028336199511, 0.11858028540458014, 0.11858028700737731, 0.11858028861017449, 0.11858029021297166, 0.11858029283787865, 0.11858029546278563, 0.1185803217118555, 0.11858034796092536, 0.11858061045162398, 0.1185808729423226, 0.11858349784930881, 0.11858612275629503, 0.11859937749360584, 0.11861263223091666, 0.11862588696822747, 0.11869411048782705, 0.11876233400742663, 0.1188305575270262, 0.11927780126597456, 0.11972504500492293, 0.12017228874387129, 0.12124792165116274, 0.1223235545584542, 0.12339918746574566, 0.12447482037303711, 0.12714732455984895, 0.1298198287466608, 0.13249233293347262, 0.13516483712028446, 0.14004454922652756, 0.14492426133277067, 0.14980397343901378, 0.15468368554525688, 0.1595633976515, 0.16514902935940326, 0.17073466106730653, 0.1763202927752098, 0.18190592448311307, 0.18749155619101635, 0.19307718789891962, 0.1989596189238084, 0.20484204994869717, 0.21072448097358595, 0.21660691199847473, 0.2224893430233635, 0.22943500510474302, 0.23638066718612252, 0.24332632926750203, 0.25027199134888156, 0.2572176534302611, 0.26416331551164063, 0.2650306077434397, 0.26547004890676007, 0.2657251806483759, 0.26579583757010006, 0.2658475270302415, 0.26589921649038295, 0.2659509059505244, 0.26600259541066584, 0.2660542848708073, 0.26613989264863586, 0.2662255004264644, 0.266311108204293, 0.26639671598212156, 0.2666594972666584, 0.2669222785511952, 0.26718505983573204, 0.2682421922264104, 0.2692993246170887, 0.27035645700776706, 0.27375099956400867, 0.2771455421202503, 0.2805400846764919, 0.2839346272327335, 0.2900840303674934, 0.29623343350225334, 0.30238283663701326, 0.3085322397717732, 0.3146816429065331, 0.322120046463617, 0.32955845002070094, 0.33699685357778486, 0.3444352571348688, 0.3518736606919527, 0.3599448267918923, 0.36801599289183196, 0.3760871589917716, 0.3841583250917112, 0.39222949119165085, 0.40295601456790037, 0.4136825379441499, 0.4244090613203994, 0.4351355846966489, 0.44586210807289844, 0.4644628554528866, 0.4830636028328748, 0.501664350212863, 0.5202650975928513, 0.5388658449728396, 0.5623378231740155, 0.5858098013751913, 0.6092817795763672, 0.6327537577775431, 0.6562257359787189, 0.684157947609324, 0.7120901592399291, 0.7400223708705342, 0.7679545825011393, 0.7958867941317445, 0.840169778447496, 0.8844527627632475, 0.928735747078999, 0.9730187313947505, 1.017301715710502, 1.0615847000262535, 1.1169639682383246, 1.1723432364503956, 1.2277225046624667, 1.2831017728745377, 1.3384810410866088, 1.3938603092986799, 1.4634829509781524, 1.533105592657625, 1.6027282343370974, 1.67235087601657, 1.7419735176960425, 1.811596159375515, 1.9128557408782765, 2.0141153223810377, 2.115374903883799, 2.2166344853865603, 2.3178940668893215, 2.419153648392083, 2.5555100121538756, 2.6918663759156685, 2.8282227396774613, 2.964579103439254, 3.100935467201047, 3.23729183096284, 3.4235744661401273, 3.6098571013174148, 3.7961397364947023, 3.9824223716719898, 4.168705006849278, 4.354987642026566, 4.6107203589983605, 4.866453075970155, 5.12218579294195, 5.377918509913745, 5.63365122688554, 5.889383943857335, 6.242066646591233, 6.594749349325132, 6.94743205205903, 7.300114754792928, 7.652797457526827, 8.005480160260724, 8.494568944375402, 8.98365772849008, 9.472746512604758, 9.961835296719435, 10.0]</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.432879622606038</v>
+        <v>0.4328794010866924</v>
       </c>
       <c r="D38" t="n">
         <v>9.81</v>
@@ -2979,13 +2979,13 @@
         <v>2</v>
       </c>
       <c r="L38" t="n">
-        <v>4.328796226060379</v>
+        <v>4.328794010866924</v>
       </c>
       <c r="M38" t="n">
-        <v>0.01067322613729393</v>
+        <v>0.01067323706101387</v>
       </c>
       <c r="N38" t="n">
-        <v>0.05336613068646964</v>
+        <v>0.05336618530506937</v>
       </c>
       <c r="O38" t="n">
         <v>19.14851336365426</v>
@@ -3015,11 +3015,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[0.0, 6.034768471339253e-07, 1.2069536942678507e-06, 7.241722165607104e-06, 1.3276490636946357e-05, 3.134149410131338e-05, 4.940649756568041e-05, 6.747150103004744e-05, 0.00011215039093751558, 0.00015682928084498373, 0.00020150817075245187, 0.00043527530953939287, 0.0006690424483263339, 0.0009028095871132748, 0.0015732864719901025, 0.0022437633568669303, 0.002914240241743758, 0.003584717126620586, 0.004956233845862582, 0.006327750565104579, 0.007699267284346575, 0.009070784003588572, 0.01044230072283057, 0.014071125040447802, 0.017699949358065035, 0.02132877367568227, 0.024957597993299503, 0.028586422310916737, 0.036303980047284676, 0.044021537783652614, 0.05173909552002055, 0.05945665325638849, 0.06717421099275643, 0.07489176872912437, 0.08176891548781251, 0.08864606224650065, 0.09552320900518879, 0.10240035576387693, 0.10927750252256507, 0.11615464928125321, 0.12260354941619225, 0.1290524495511313, 0.13550134968607033, 0.14195024982100937, 0.1483991499559484, 0.15484805009088745, 0.16013417220173679, 0.16542029431258612, 0.17070641642343545, 0.1759925385342848, 0.18127866064513412, 0.18656478275598345, 0.19235042183530315, 0.19813606091462285, 0.20392169999394255, 0.20970733907326225, 0.21549297815258195, 0.2220997090300302, 0.22870643990747846, 0.23531317078492672, 0.24191990166237498, 0.24852663253982324, 0.2551333634172715, 0.26087553619779985, 0.2666177089783282, 0.27235988175885656, 0.2781020545393849, 0.28384422731991327, 0.2895864001004416, 0.2990843099972319, 0.3085822198940222, 0.31808012979081246, 0.32757803968760274, 0.337075949584393, 0.3465738594811833, 0.35670450642130974, 0.3668351533614362, 0.3769658003015626, 0.38709644724168907, 0.3972270941818155, 0.40735774112194195, 0.4213717007049371, 0.4353856602879323, 0.44939961987092747, 0.46341357945392264, 0.4774275390369178, 0.4972494556097859, 0.517071372182654, 0.536893288755522, 0.55671520532839, 0.576537121901258, 0.605231857314985, 0.6339265927287119, 0.6626213281424388, 0.6913160635561657, 0.7200107989698926, 0.7506157776327246, 0.7812207562955565, 0.8118257349583885, 0.8424307136212205, 0.8730356922840524, 0.928504458985463, 0.9839732256868735, 1.039441992388284, 1.0949107590896947, 1.1503795257911054, 1.205848292492516, 1.262200118872399, 1.318551945252282, 1.374903771632165, 1.431255598012048, 1.487607424391931, 1.543959250771814, 1.6268346819680848, 1.7097101131643555, 1.7925855443606262, 1.875460975556897, 1.9583364067531677, 2.0412118379494384, 2.146240600059736, 2.2512693621700333, 2.3562981242803307, 2.461326886390628, 2.5663556485009256, 2.671384410611223, 2.810342255102996, 2.949300099594769, 3.088257944086542, 3.227215788578315, 3.3661736330700878, 3.5051314775618607, 3.7118212290199355, 3.9185109804780103, 4.125200731936085, 4.331890483394159, 4.538580234852233, 4.745269986310308, 4.972017535287312, 5.198765084264317, 5.425512633241322, 5.652260182218327, 5.8790077311953315, 6.105755280172336, 6.471882951257965, 6.838010622343593, 7.204138293429222, 7.57026596451485, 7.936393635600479, 8.302521306686106, 8.764683386569274, 9.226845466452442, 9.68900754633561, 10.0]</t>
+          <t>[0.0, 8.384493837153096e-06, 1.676898767430619e-05, 0.00010061392604583715, 0.00018445886441736812, 0.00044930811737648986, 0.0007141573703356116, 0.0009790066232947332, 0.0017763542149566115, 0.0025737018066184897, 0.003371049398280368, 0.006579792576014678, 0.009788535753748988, 0.012997278931483298, 0.017355744846300297, 0.021714210761117295, 0.026072676675934294, 0.030431142590751293, 0.039796932654090574, 0.04916272271742986, 0.05852851278076914, 0.06789430284410843, 0.0772600929074477, 0.08711929073625005, 0.0935559401641607, 0.09999258959207136, 0.10642923901998201, 0.11286588844789266, 0.11288600297735488, 0.11290611750681709, 0.1129262320362793, 0.11294634656574151, 0.11296646109520372, 0.11316760638982584, 0.11336875168444796, 0.11356989697907008, 0.1137710422736922, 0.11417333286293643, 0.11457562345218067, 0.1149779140414249, 0.11500642172565136, 0.1150349294098778, 0.1150406309467231, 0.11504177125409215, 0.11504291156146121, 0.11504291491972225, 0.11504291674331787, 0.1150429185669135, 0.11504292039050912, 0.11504292337167982, 0.11504292635285052, 0.11504295616455751, 0.1150429859762645, 0.11504328409333442, 0.11504358221040434, 0.11504656338110353, 0.11504954455180272, 0.1150642640611878, 0.11507898357057289, 0.11509370307995798, 0.11516821393819374, 0.1152427247964295, 0.11531723565466526, 0.11576054555362265, 0.11620385545258005, 0.11664716535153745, 0.11771428289962292, 0.1187814004477084, 0.11984851799579387, 0.12091563554387934, 0.12365014805699122, 0.1263846605701031, 0.12911917308321502, 0.13185368559632693, 0.13659623623445438, 0.14133878687258183, 0.14608133751070929, 0.15082388814883674, 0.1555664387869642, 0.1612702999678127, 0.1669741611486612, 0.1726780223295097, 0.17838188351035822, 0.18408574469120673, 0.18978960587205523, 0.19612906385846096, 0.2024685218448667, 0.20880797983127242, 0.21308007594585734, 0.21735217206044227, 0.2216242681750272, 0.22589636428961213, 0.23016846040419706, 0.2359023311861942, 0.24163620196819133, 0.24737007275018846, 0.2489582382714253, 0.25054640379266213, 0.25115297560246264, 0.25175954741226314, 0.25184390603376305, 0.25191104180185575, 0.2519652671069897, 0.2520194924121236, 0.25207371771725756, 0.2521279430223915, 0.2522630087178087, 0.2523980744132259, 0.25253314010864314, 0.253042275508241, 0.25355141090783884, 0.25521890833547195, 0.25688640576310506, 0.2585539031907382, 0.2617535500088268, 0.26495319682691537, 0.26815284364500397, 0.2737281225683667, 0.27930340149172944, 0.2848786804150922, 0.2904539593384549, 0.2986983573612674, 0.30694275538407984, 0.3151871534068923, 0.32343155142970476, 0.3316759494525172, 0.3408745343407639, 0.35007311922901063, 0.35927170411725734, 0.36847028900550405, 0.37766887389375076, 0.3897302660081846, 0.40179165812261847, 0.4138530502370523, 0.4259144423514862, 0.43797583446592003, 0.4547775373863326, 0.47157924030674514, 0.4883809432271577, 0.5051826461475702, 0.5219843490679827, 0.5454821860552944, 0.5689800230426061, 0.5924778600299178, 0.6159756970172294, 0.6394735340045411, 0.6690288235384918, 0.6985841130724425, 0.7281394026063932, 0.7576946921403439, 0.7872499816742946, 0.822871659269134, 0.8584933368639733, 0.8941150144588127, 0.9297366920536521, 0.9653583696484914, 1.0009800472433308, 1.0524991980427227, 1.1040183488421147, 1.1555374996415066, 1.2070566504408986, 1.2585758012402906, 1.3272772974055875, 1.3959787935708845, 1.4646802897361815, 1.5333817859014784, 1.6020832820667754, 1.6707847782320724, 1.7454991710175929, 1.8202135638031134, 1.8949279565886339, 1.9696423493741544, 2.0443567421596747, 2.119071134945195, 2.241812682571635, 2.3645542301980753, 2.4872957778245155, 2.6100373254509557, 2.732778873077396, 2.855520420703836, 3.015210824047818, 3.1749012273918003, 3.3345916307357824, 3.4942820340797645, 3.6539724374237466, 3.8136628407677287, 4.033651669040676, 4.253640497313624, 4.473629325586572, 4.69361815385952, 4.9136069821324675, 5.133595810405415, 5.384532944445569, 5.635470078485723, 5.886407212525876, 6.13734434656603, 6.388281480606183, 6.639218614646337, 7.037406875080604, 7.4355951355148715, 7.833783395949139, 8.231971656383406, 8.630159916817673, 9.02834817725194, 9.584969563936578, 10.0]</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.4107841657322466</v>
+        <v>0.4107842029228485</v>
       </c>
       <c r="D39" t="n">
         <v>9.81</v>
@@ -3046,13 +3046,13 @@
         <v>2</v>
       </c>
       <c r="L39" t="n">
-        <v>4.107841657322466</v>
+        <v>4.107842029228485</v>
       </c>
       <c r="M39" t="n">
-        <v>0.01185229919686165</v>
+        <v>0.01185229705075127</v>
       </c>
       <c r="N39" t="n">
-        <v>0.05926149598430826</v>
+        <v>0.05926148525375635</v>
       </c>
       <c r="O39" t="n">
         <v>19.02363766834054</v>
@@ -3082,11 +3082,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[0.0, 6.059959132612402e-07, 1.2119918265224804e-06, 7.271950959134883e-06, 1.3331910091747286e-05, 3.147248931294608e-05, 4.961306853414487e-05, 6.775364775534367e-05, 0.00011262553724049817, 0.00015749742672565268, 0.0002023693162108072, 0.0004420272411152594, 0.0006816851660197116, 0.0009213430909241637, 0.0015435725457180942, 0.0021658020005120245, 0.002788031455305955, 0.0034102609100998857, 0.004691589349699659, 0.005972917789299433, 0.007254246228899206, 0.008535574668498979, 0.009816903108098752, 0.013201957689602618, 0.016587012271106483, 0.019972066852610347, 0.02335712143411421, 0.026742176015618076, 0.033933733306735846, 0.041125290597853616, 0.048316847888971386, 0.055508405180089156, 0.06269996247120693, 0.06989151976232472, 0.07670147426819154, 0.08351142877405837, 0.0903213832799252, 0.09713133778579203, 0.10394129229165885, 0.11075124679752568, 0.1171763731356887, 0.12360149947385171, 0.13002662581201474, 0.13645175215017777, 0.1428768784883408, 0.14930200482650383, 0.15462069964607464, 0.15993939446564545, 0.16525808928521626, 0.17057678410478708, 0.1758954789243579, 0.1812141737439287, 0.1870886625885549, 0.19296315143318107, 0.19883764027780726, 0.20471212912243344, 0.21058661796705963, 0.21742865450535645, 0.22427069104365327, 0.2311127275819501, 0.2379547641202469, 0.24479680065854373, 0.25163883719684055, 0.2574447909532933, 0.2632507447097461, 0.26905669846619884, 0.2748626522226516, 0.28066860597910437, 0.28647455973555713, 0.2963213397275765, 0.3061681197195959, 0.3160148997116153, 0.32586167970363467, 0.33570845969565405, 0.34555523968767343, 0.35591046781533636, 0.3662656959429993, 0.3766209240706622, 0.38697615219832515, 0.3973313803259881, 0.407686608453651, 0.4223580260438096, 0.43702944363396823, 0.45170086122412684, 0.46637227881428545, 0.48104369640444405, 0.5013640468498998, 0.5216843972953555, 0.5420047477408113, 0.5623250981862671, 0.5826454486317229, 0.6118376805336472, 0.6410299124355715, 0.6702221443374958, 0.6994143762394202, 0.7286066081413445, 0.7596651708304939, 0.7907237335196433, 0.8217822962087927, 0.8528408588979421, 0.8838994215870916, 0.9398914965774948, 0.9958835715678981, 1.0518756465583015, 1.107867721548705, 1.1638597965391084, 1.219851871529512, 1.277021266086455, 1.3341906606433982, 1.3913600552003413, 1.4485294497572845, 1.5056988443142276, 1.5628682388711708, 1.6462282682982894, 1.729588297725408, 1.8129483271525266, 1.8963083565796452, 1.9796683860067639, 2.0630284154338825, 2.16619837314478, 2.2693683308556776, 2.372538288566575, 2.4757082462774727, 2.57887820398837, 2.6820481616992677, 2.8384988090296783, 2.994949456360089, 3.1514001036904995, 3.30785075102091, 3.4643013983513207, 3.6207520456817313, 3.825952915788954, 4.031153785896176, 4.236354656003399, 4.441555526110621, 4.646756396217843, 4.851957266325066, 5.0886533530317335, 5.325349439738401, 5.562045526445069, 5.798741613151737, 6.035437699858405, 6.272133786565073, 6.6491393334044, 7.026144880243727, 7.403150427083054, 7.780155973922382, 8.157161520761708, 8.534167067601034, 9.010159838769706, 9.486152609938378, 9.96214538110705, 10.0]</t>
+          <t>[0.0, 7.64337120128889e-06, 1.528674240257778e-05, 9.172045441546669e-05, 0.00016815416642835558, 0.00040846563585316895, 0.0006487771052779823, 0.0008890885747027957, 0.0016035681321179595, 0.0023180476895331235, 0.0030325272469482875, 0.006214826201939911, 0.009397125156931533, 0.012579424111923155, 0.016755753442171388, 0.02093208277241962, 0.02510841210266785, 0.02928474143291608, 0.0372444960140647, 0.045204250595213324, 0.053164005176361946, 0.06112375975751057, 0.0690835143386592, 0.07917871169581642, 0.0858246581512132, 0.09247060460661, 0.09911655106200679, 0.10576249751740358, 0.10578326610007668, 0.10580403468274979, 0.1058248032654229, 0.10584557184809601, 0.10586634043076912, 0.1060740262575002, 0.10628171208423129, 0.10648939791096237, 0.10669708373769346, 0.10877394200500431, 0.11085080027231517, 0.11126617192577734, 0.11134924625646977, 0.11143232058716221, 0.11151539491785464, 0.11154862465013161, 0.11158185438240859, 0.11158850032886398, 0.11159514627531938, 0.11160179222177478, 0.11160232389749121, 0.11160285557320763, 0.11160338724892406, 0.11160342978298138, 0.1116034723170387, 0.11160351485109601, 0.11160353587174773, 0.11160353809544625, 0.11160354031914477, 0.11160354254284328, 0.11160354606259199, 0.11160354958234069, 0.1116035847798277, 0.1116036199773147, 0.11160397195218479, 0.11160432392705487, 0.1116078436757557, 0.11161136342445653, 0.11162813835425747, 0.11164491328405841, 0.11166168821385936, 0.11174473435599049, 0.11182778049812162, 0.11191082664025274, 0.11235451689865829, 0.11279820715706383, 0.11324189741546938, 0.11430840590761306, 0.11537491439975674, 0.11644142289190042, 0.1175079313840441, 0.12034638969879027, 0.12318484801353645, 0.12602330632828262, 0.1288617646430288, 0.13347368937108475, 0.13808561409914072, 0.14269753882719668, 0.14730946355525265, 0.15192138828330862, 0.15761405123220035, 0.16330671418109208, 0.1689993771299838, 0.17469204007887554, 0.18038470302776727, 0.186077365976659, 0.19263616542119302, 0.19919496486572705, 0.20357519827828865, 0.20795543169085026, 0.21233566510341187, 0.21671589851597348, 0.22109613192853508, 0.22649205266446612, 0.23188797340039716, 0.2372838941363282, 0.23771935474173359, 0.23787014977925322, 0.23791343542683946, 0.23793758115150232, 0.23796172687616518, 0.23798587260082804, 0.2380100183254909, 0.23803416405015376, 0.23805830977481662, 0.2380907856051979, 0.23812326143557916, 0.23815573726596043, 0.2381882130963417, 0.23822068892672296, 0.23825316475710423, 0.23831349204817778, 0.23837381933925134, 0.2384341466303249, 0.23849447392139844, 0.238554801212472, 0.23872253692776518, 0.23889027264305837, 0.23905800835835156, 0.23922574407364475, 0.2399491435461259, 0.24067254301860705, 0.2413959424910882, 0.24374332126730291, 0.24609070004351763, 0.24843807881973234, 0.2526120526892758, 0.2567860265588192, 0.26096000042836265, 0.2651339742979061, 0.27110121509312524, 0.2770684558883444, 0.28303569668356354, 0.2890029374787827, 0.29497017827400185, 0.30254004779385585, 0.31010991731370985, 0.31767978683356385, 0.32524965635341785, 0.33281952587327185, 0.3406199461439777, 0.3484203664146836, 0.3562207866853895, 0.36402120695609536, 0.37182162722680123, 0.38197095064601433, 0.3921202740652274, 0.4022695974844405, 0.4124189209036536, 0.4225682443228667, 0.4399072356409643, 0.45724622695906186, 0.47458521827715944, 0.491924209595257, 0.5092632009133546, 0.5313265183636657, 0.5533898358139768, 0.5754531532642879, 0.597516470714599, 0.6195797881649101, 0.6459337344531886, 0.672287680741467, 0.6986416270297455, 0.724995573318024, 0.7513495196063025, 0.7922770738493105, 0.8332046280923184, 0.8741321823353264, 0.9150597365783344, 0.9559872908213424, 0.9969148450643504, 1.0405989677406209, 1.0842830904168914, 1.127967213093162, 1.1716513357694325, 1.215335458445703, 1.2590195811219735, 1.332269936955743, 1.4055202927895123, 1.4787706486232817, 1.552021004457051, 1.6252713602908204, 1.6985217161245898, 1.7823721187422061, 1.8662225213598225, 1.9500729239774388, 2.033923326595055, 2.1177737292126713, 2.2016241318302874, 2.303740879592599, 2.405857627354911, 2.5079743751172225, 2.6100911228795343, 2.712207870641846, 2.8143246184041577, 2.975972683882953, 3.1376207493617483, 3.2992688148405436, 3.460916880319339, 3.622564945798134, 3.7842130112769294, 3.9846154243262126, 4.185017837375495, 4.385420250424778, 4.58582266347406, 4.786225076523342, 4.986627489572625, 5.2795342050508385, 5.572440920529052, 5.865347636007266, 6.15825435148548, 6.451161066963694, 6.744067782441908, 7.136468434903318, 7.528869087364727, 7.921269739826137, 8.313670392287547, 8.706071044748956, 9.098471697210366, 9.60020917785355, 10.0]</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.3880881323867191</v>
+        <v>0.3880881774910435</v>
       </c>
       <c r="D40" t="n">
         <v>9.81</v>
@@ -3113,13 +3113,13 @@
         <v>2</v>
       </c>
       <c r="L40" t="n">
-        <v>3.880881323867191</v>
+        <v>3.880881774910435</v>
       </c>
       <c r="M40" t="n">
-        <v>0.01327911924865743</v>
+        <v>0.01327911616201011</v>
       </c>
       <c r="N40" t="n">
-        <v>0.06639559624328713</v>
+        <v>0.06639558081005052</v>
       </c>
       <c r="O40" t="n">
         <v>18.86568799366454</v>
@@ -3149,11 +3149,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[0.0, 6.092273302409245e-07, 1.218454660481849e-06, 7.310727962891094e-06, 1.3403001265300338e-05, 3.1640529150783536e-05, 4.9878057036266734e-05, 6.811558492174993e-05, 0.00011323510077899071, 0.00015835461663623148, 0.00020347413249347223, 0.0004513703913922762, 0.0006992666502910801, 0.0009471629091898841, 0.0015303014229776737, 0.0021134399367654633, 0.002696578450553253, 0.0032797169643410426, 0.004467599216767598, 0.005655481469194153, 0.0068433637216207075, 0.008031245974047262, 0.009219128226473817, 0.012399733253404531, 0.015580338280335245, 0.018760943307265958, 0.02194154833419667, 0.02512215336112738, 0.03175244320834547, 0.03838273305556356, 0.045013022902781655, 0.05164331274999975, 0.05827360259721784, 0.06490389244443592, 0.0716688006929018, 0.07843370894136767, 0.08519861718983354, 0.09196352543829941, 0.09872843368676529, 0.10549334193523116, 0.11251629245089878, 0.1195392429665664, 0.12656219348223402, 0.13358514399790164, 0.14060809451356926, 0.14763104502923688, 0.1531057657039407, 0.1585804863786445, 0.1640552070533483, 0.16952992772805212, 0.17500464840275592, 0.18047936907745973, 0.1876016280626549, 0.19238716674935363, 0.19717270543605236, 0.2019582441227511, 0.20674378280944983, 0.21152932149614856, 0.2180847006349298, 0.22464007977371103, 0.23119545891249227, 0.2377508380512735, 0.24430621719005474, 0.250861596328836, 0.2573384341454948, 0.2638152719621536, 0.2702921097788124, 0.2767689475954712, 0.28324578541213, 0.29272775295937314, 0.30220972050661626, 0.3116916880538594, 0.3211736556011025, 0.3306556231483456, 0.34013759069558874, 0.35090225492014254, 0.36166691914469634, 0.37243158336925014, 0.38319624759380394, 0.39396091181835774, 0.40472557604291154, 0.41965304155341193, 0.4345805070639123, 0.4495079725744127, 0.4644354380849131, 0.4793629035954135, 0.4942903691059139, 0.514058853996015, 0.5338273388861161, 0.5535958237762172, 0.5733643086663183, 0.5931327935564193, 0.6180301060009757, 0.6429274184455321, 0.6678247308900885, 0.6927220433346449, 0.7176193557792013, 0.7550707471867734, 0.7925221385943454, 0.8299735300019174, 0.8674249214094895, 0.9048763128170615, 0.9524119621549445, 0.9999476114928275, 1.0474832608307105, 1.0950189101685934, 1.1425545595064763, 1.1900902088443592, 1.2464874744484795, 1.3028847400525998, 1.35928200565672, 1.4156792712608404, 1.4720765368649606, 1.5495925449202936, 1.6271085529756266, 1.7046245610309596, 1.7821405690862926, 1.8596565771416256, 1.9371725851969586, 2.024808602057972, 2.1124446189189854, 2.2000806357799987, 2.287716652641012, 2.3753526695020253, 2.4629886863630386, 2.6031957087967497, 2.7434027312304607, 2.883609753664172, 3.023816776097883, 3.164023798531594, 3.304230820965305, 3.495525571479053, 3.6868203219928013, 3.8781150725065494, 4.0694098230202975, 4.260704573534046, 4.451999324047794, 4.708601104239214, 4.965202884430635, 5.221804664622056, 5.478406444813476, 5.735008225004897, 5.991610005196318, 6.280883997991049, 6.5701579907857806, 6.859431983580512, 7.148705976375243, 7.437979969169975, 7.727253961964706, 8.198580287896167, 8.669906613827628, 9.141232939759089, 9.61255926569055, 10.0]</t>
+          <t>[0.0, 6.949812689030429e-06, 1.3899625378060859e-05, 8.339775226836516e-05, 0.00015289587915866945, 0.00037042404385467787, 0.0005879522085506863, 0.0008054803732466946, 0.0014443018921919586, 0.0020831234111372224, 0.0027219449300824863, 0.006044788862828885, 0.009367632795575283, 0.012690476728321682, 0.01674290872065475, 0.020795340712987817, 0.024847772705320886, 0.028900204697653954, 0.03585423738352263, 0.0428082700693913, 0.049762302755259974, 0.05671633544112865, 0.06367036812699732, 0.07238872857359134, 0.08110708902018536, 0.08693509906698944, 0.09276310911379353, 0.09859111916059761, 0.10441912920740169, 0.1044555542701942, 0.10449197933298672, 0.10452840439577923, 0.10456482945857175, 0.10460125452136426, 0.1049655051492894, 0.10532975577721454, 0.10569400640513968, 0.10605825703306482, 0.1067867582889151, 0.10751525954476537, 0.10824376080061565, 0.10838946105178571, 0.1083952890618325, 0.10839645466384186, 0.10839762026585122, 0.10839787054407228, 0.10839812082229335, 0.10839815359915954, 0.10839817063589655, 0.1083981761102801, 0.1083981803768034, 0.1083981846433267, 0.10839818890985001, 0.10839819317637331, 0.10839820357755509, 0.10839821397873686, 0.10839822437991864, 0.10839832839173641, 0.10839843240355418, 0.10839919866515874, 0.10839996492676329, 0.10840762754280886, 0.10841529015885443, 0.10844148147876882, 0.10846767279868322, 0.10849386411859761, 0.10859927637220855, 0.10870468862581949, 0.10881010087943042, 0.10928432101329227, 0.10975854114715412, 0.11023276128101597, 0.11134753855233512, 0.11246231582365426, 0.11357709309497341, 0.11469187036629255, 0.11775348315025154, 0.12081509593421053, 0.12387670871816951, 0.1269383215021285, 0.13143689082450122, 0.13593546014687394, 0.14043402946924666, 0.14493259879161938, 0.1494311681139921, 0.1548515089157671, 0.1602718497175421, 0.1656921905193171, 0.1711125313210921, 0.1765328721228671, 0.18195321292464212, 0.1881431667323908, 0.19433312054013946, 0.20052307434788813, 0.2067130281556368, 0.21290298196338547, 0.21851734539544934, 0.22052482823792383, 0.2225323110803983, 0.2233862878507938, 0.22361745853374917, 0.22368356370522097, 0.22372265024755653, 0.223744270499979, 0.22376589075240147, 0.22378751100482394, 0.2238091312572464, 0.22383075150966888, 0.22385237176209136, 0.22388128852181166, 0.22391020528153197, 0.22393912204125227, 0.22396803880097257, 0.22399695556069288, 0.22402587232041318, 0.22408005897616962, 0.22413424563192605, 0.22418843228768248, 0.22424261894343891, 0.22429680559919535, 0.22444698097049307, 0.22459715634179078, 0.2247473317130885, 0.22489750708438622, 0.2255414897217733, 0.22618547235916037, 0.22682945499654744, 0.22910978792703973, 0.23139012085753202, 0.2336704537880243, 0.2376210018340982, 0.2415715498801721, 0.245522097926246, 0.24947264597231988, 0.25493213529763104, 0.2603916246229422, 0.26585111394825334, 0.2713106032735645, 0.27677009259887564, 0.2844400408087678, 0.2921099890186599, 0.29977993722855206, 0.3074498854384442, 0.31511983364833634, 0.32272892005560055, 0.33033800646286476, 0.337947092870129, 0.3455561792773932, 0.3531652656846574, 0.3607743520919216, 0.3726667353431375, 0.3845591185943534, 0.39645150184556927, 0.40834388509678515, 0.42023626834800104, 0.43212865159921693, 0.450976440444273, 0.46982422928932904, 0.4886720181343851, 0.5075198069794411, 0.5263675958244971, 0.5452153846695531, 0.5676032563255486, 0.5899911279815442, 0.6123789996375397, 0.6347668712935353, 0.6571547429495308, 0.6861607801680604, 0.7151668173865899, 0.7441728546051195, 0.7731788918236491, 0.8021849290421786, 0.8404899543406495, 0.8787949796391205, 0.9171000049375914, 0.9554050302360623, 0.9937100555345332, 1.0413662853370838, 1.0890225151396344, 1.1366787449421851, 1.1843349747447358, 1.2319912045472865, 1.2796474343498372, 1.3475619690338658, 1.4154765037178945, 1.483391038401923, 1.5513055730859517, 1.6192201077699804, 1.7053892904492052, 1.79155847312843, 1.8777276558076548, 1.9638968384868796, 2.0500660211661046, 2.1362352038453296, 2.2341031889968708, 2.331971174148412, 2.429839159299953, 2.5277071444514942, 2.6255751296030354, 2.7234431147545766, 2.881013262301218, 3.0385834098478592, 3.1961535573945006, 3.353723704941142, 3.5112938524877833, 3.6688640000344246, 3.8815825996112974, 4.09430119918817, 4.307019798765042, 4.519738398341914, 4.732456997918787, 4.945175597495659, 5.2321992674245115, 5.519222937353364, 5.806246607282216, 6.093270277211069, 6.380293947139921, 6.667317617068774, 6.991245854862076, 7.315174092655379, 7.639102330448682, 7.963030568241985, 8.286958806035287, 8.610887043828589, 9.140294802521986, 9.669702561215383, 10.0]</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.3649151029617267</v>
+        <v>0.3649151766341683</v>
       </c>
       <c r="D41" t="n">
         <v>9.81</v>
@@ -3180,13 +3180,13 @@
         <v>2</v>
       </c>
       <c r="L41" t="n">
-        <v>3.649151029617267</v>
+        <v>3.649151766341683</v>
       </c>
       <c r="M41" t="n">
-        <v>0.01501918336050952</v>
+        <v>0.01501917729608761</v>
       </c>
       <c r="N41" t="n">
-        <v>0.0750959168025476</v>
+        <v>0.07509588648043802</v>
       </c>
       <c r="O41" t="n">
         <v>18.66590452365001</v>
@@ -3216,11 +3216,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[0.0, 6.133888591916098e-07, 1.2267777183832196e-06, 7.360666310299317e-06, 1.3494554902215414e-05, 3.185693873736091e-05, 5.021932257250641e-05, 6.85817064076519e-05, 0.00011402020583290585, 0.0001594587052581598, 0.00020489720468341377, 0.0004647807511795227, 0.0007246642976756316, 0.0009845478441717404, 0.001536102554446801, 0.0020876572647218618, 0.0026392119749969224, 0.003190766685271983, 0.004285223022126313, 0.005379679358980644, 0.0064741356958349745, 0.007568592032689305, 0.008663048369543635, 0.01168379051119849, 0.014704532652853344, 0.017725274794508198, 0.020746016936163052, 0.023766759077817907, 0.02986999734815197, 0.03597323561848603, 0.04207647388882009, 0.04817971215915415, 0.054282950429488205, 0.06038618869982226, 0.06715774033012636, 0.07392929196043047, 0.08070084359073457, 0.08747239522103867, 0.09424394685134277, 0.10101549848164687, 0.1079397016036003, 0.11486390472555372, 0.12178810784750714, 0.12871231096946056, 0.13563651409141397, 0.14256071721336738, 0.1482031474335196, 0.1538455776536718, 0.159488007873824, 0.1651304380939762, 0.1707728683141284, 0.17641529853428062, 0.18312984105180902, 0.18984438356933742, 0.19427864317061946, 0.1987129027719015, 0.20314716237318356, 0.2075814219744656, 0.21201568157574766, 0.2174214911264904, 0.22282730067723314, 0.22823311022797588, 0.23363891977871862, 0.2393008255372873, 0.24496273129585597, 0.2506246370544246, 0.25628654281299323, 0.26194844857156185, 0.27165621435473325, 0.28136398013790465, 0.29107174592107604, 0.30077951170424744, 0.31048727748741883, 0.32019504327059023, 0.33000004381532905, 0.33980504436006786, 0.3496100449048067, 0.3594150454495455, 0.3692200459942843, 0.37902504653902314, 0.39272643074352614, 0.40642781494802915, 0.42012919915253216, 0.43383058335703517, 0.4475319675615382, 0.4664080590069837, 0.4852841504524292, 0.5041602418978747, 0.5230363333433201, 0.5419124247887656, 0.5691073938768312, 0.5963023629648968, 0.6234973320529624, 0.650692301141028, 0.6778872702290937, 0.7093388659611396, 0.7407904616931855, 0.7722420574252314, 0.8036936531572774, 0.8351452488893233, 0.8851666571744209, 0.9351880654595185, 0.9852094737446161, 1.0352308820297136, 1.085252290314811, 1.1352736985999083, 1.193388956974304, 1.2515042153486995, 1.309619473723095, 1.3677347320974906, 1.4258499904718862, 1.5004825558142665, 1.5751151211566468, 1.649747686499027, 1.7243802518414073, 1.7990128171837876, 1.8736453825261679, 1.9759133607112749, 2.078181338896382, 2.180449317081489, 2.282717295266596, 2.384985273451703, 2.48725325163681, 2.6034989237357755, 2.719744595834741, 2.8359902679337066, 2.952235940032672, 3.0684816121316376, 3.184727284230603, 3.368686279587995, 3.5526452749453865, 3.736604270302778, 3.92056326566017, 4.104522261017562, 4.288481256374953, 4.540915618941829, 4.7933499815087055, 5.045784344075582, 5.298218706642458, 5.550653069209334, 5.80308743177621, 6.1481040852858175, 6.493120738795425, 6.838137392305033, 7.18315404581464, 7.528170699324248, 7.873187352833855, 8.265014049578367, 8.656840746322878, 9.048667443067389, 9.4404941398119, 9.832320836556411, 10.0]</t>
+          <t>[0.0, 6.3086800604277325e-06, 1.2617360120855465e-05, 7.57041607251328e-05, 0.00013879096132941014, 0.0003354147707346723, 0.0005320385801399344, 0.0007286623895451966, 0.0012992329793826492, 0.0018698035692201018, 0.0024403741590575544, 0.0065278270430828116, 0.01061527992710807, 0.013596162751182196, 0.016577045575256324, 0.019557928399330453, 0.023938089637966304, 0.028318250876602155, 0.03269841211523801, 0.037078573353873864, 0.044102586536911154, 0.05112659971994844, 0.05815061290298573, 0.06517462608602302, 0.07219863926906031, 0.07975038089787956, 0.0855680024926525, 0.09138562408742545, 0.09558786917429427, 0.09979011426116308, 0.10399235934803189, 0.10401862337982481, 0.10404488741161774, 0.10407115144341067, 0.1040974154752036, 0.10436005579313287, 0.10462269611106215, 0.10488533642899142, 0.10539677951322458, 0.10549906813007122, 0.10560135674691785, 0.10562181447028718, 0.10562263277922194, 0.10562345108815671, 0.10562426939709148, 0.10562459672066539, 0.1056249240442393, 0.10562498950895409, 0.10562500895839055, 0.10562502840782702, 0.1056250370633317, 0.10562504210799628, 0.10562504487675986, 0.10562504764552344, 0.10562505041428702, 0.1056250549599763, 0.10562505950566559, 0.10562510496255842, 0.10562515041945125, 0.10562560498837958, 0.10562605955730792, 0.10563060524659124, 0.10563515093587456, 0.10565713478844042, 0.10567911864100629, 0.10570110249357216, 0.10581187271609317, 0.10592264293861418, 0.1060334131611352, 0.10648995457410845, 0.10694649598708171, 0.10740303740005497, 0.10849844879120132, 0.10959386018234768, 0.11068927157349404, 0.11178468296464039, 0.11512666930989583, 0.11846865565515127, 0.12181064200040671, 0.12515262834566215, 0.12959788172606002, 0.13404313510645788, 0.13848838848685574, 0.1429336418672536, 0.14737889524765146, 0.15252708790193886, 0.15767528055622626, 0.16282347321051366, 0.16797166586480106, 0.17311985851908845, 0.17826805117337585, 0.1845716790308254, 0.19087530688827492, 0.19717893474572445, 0.203482562603174, 0.20541817501304854, 0.2073537874229231, 0.20810759271603815, 0.2088613980091532, 0.20894284324408227, 0.2089895411469396, 0.20902304096543753, 0.20905654078393546, 0.20909004060243339, 0.20912354042093131, 0.20915704023942924, 0.2092118049479885, 0.20926656965654775, 0.209321334365107, 0.20937609907366625, 0.20954330885113315, 0.20971051862860005, 0.20987772840606694, 0.2105455681340625, 0.21121340786205806, 0.2118812475900536, 0.21435634624156413, 0.21683144489307465, 0.21930654354458518, 0.22325426820648142, 0.22720199286837767, 0.2311497175302739, 0.23509744219217016, 0.2402244181516906, 0.24535139411121104, 0.2504783700707315, 0.2556053460302519, 0.26073232198977236, 0.2699693962021709, 0.2792064704145695, 0.28844354462696803, 0.2976806188393666, 0.30691769305176514, 0.31642399710037866, 0.3259303011489922, 0.3354366051976057, 0.34494290924621923, 0.35444921329483275, 0.3639555173434463, 0.37701415440595965, 0.390072791468473, 0.4031314285309864, 0.41619006559349975, 0.4292487026560131, 0.4423073397185265, 0.4587799587523626, 0.4752525777861987, 0.49172519682003485, 0.5081978158538709, 0.5246704348877069, 0.5411430539215429, 0.565647880133014, 0.5901527063444851, 0.6146575325559562, 0.6391623587674273, 0.6636671849788984, 0.698132912900153, 0.7325986408214076, 0.7670643687426622, 0.8015300966639167, 0.8359958245851713, 0.8723579305006801, 0.9087200364161889, 0.9450821423316977, 0.9814442482472066, 1.0178063541627154, 1.0541684600782242, 1.109629060207451, 1.1650896603366778, 1.2205502604659046, 1.2760108605951315, 1.3314714607243583, 1.4047736557480581, 1.478075850771758, 1.5513780457954578, 1.6246802408191576, 1.6979824358428575, 1.7712846308665573, 1.8584216885426004, 1.9455587462186434, 2.0326958038946863, 2.119832861570729, 2.206969919246772, 2.294106976922815, 2.426034613650529, 2.5579622503782433, 2.6898898871059576, 2.821817523833672, 2.953745160561386, 3.0856727972891003, 3.262642816519426, 3.4396128357497515, 3.616582854980077, 3.7935528742104028, 3.9705228934407284, 4.147492912671054, 4.389128757796679, 4.630764602922304, 4.872400448047929, 5.114036293173554, 5.355672138299179, 5.5973079834248045, 5.868026236669304, 6.138744489913804, 6.409462743158303, 6.680180996402803, 6.9508992496473025, 7.221617502891802, 7.6602770360594565, 8.09893656922711, 8.537596102394764, 8.976255635562417, 9.41491516873007, 9.853574701897724, 10.0]</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.3413620667859624</v>
+        <v>0.3413620975428702</v>
       </c>
       <c r="D42" t="n">
         <v>9.81</v>
@@ -3247,13 +3247,13 @@
         <v>2</v>
       </c>
       <c r="L42" t="n">
-        <v>3.413620667859623</v>
+        <v>3.413620975428702</v>
       </c>
       <c r="M42" t="n">
-        <v>0.01716324796799101</v>
+        <v>0.01716324487515547</v>
       </c>
       <c r="N42" t="n">
-        <v>0.08581623983995502</v>
+        <v>0.08581622437577734</v>
       </c>
       <c r="O42" t="n">
         <v>18.41320735936067</v>
@@ -3283,11 +3283,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>[0.0, 6.187756156509127e-07, 1.2375512313018254e-06, 7.425307387810952e-06, 1.361306354432008e-05, 3.2137066678644804e-05, 5.066106981296953e-05, 6.918507294729425e-05, 0.00011503660653841532, 0.00016088814012953637, 0.00020673967372065744, 0.00048521249666001097, 0.0007636853195993645, 0.001042158142538718, 0.001569500355395304, 0.00209684256825189, 0.0026241847811084755, 0.0031515269939650613, 0.004156273802520952, 0.0051610206110768424, 0.006165767419632733, 0.007170514228188624, 0.008175261036744513, 0.011102433328981767, 0.014029605621219021, 0.016956777913456275, 0.01988395020569353, 0.022811122497930783, 0.028480582272981298, 0.03415004204803181, 0.03981950182308233, 0.04548896159813285, 0.05115842137318337, 0.05682788114823389, 0.06370866162045352, 0.07058944209267315, 0.07747022256489278, 0.0843510030371124, 0.09123178350933203, 0.09811256398155166, 0.10483486059721357, 0.11155715721287549, 0.1182794538285374, 0.1250017504441993, 0.13172404705986124, 0.13844634367552316, 0.14449054133403613, 0.1505347389925491, 0.15657893665106207, 0.16262313430957503, 0.168667331968088, 0.17471152962660097, 0.1805989724144871, 0.18648641520237325, 0.19237385799025938, 0.19826130077814552, 0.20414874356603166, 0.20980830288487123, 0.2154678622037108, 0.22112742152255038, 0.22678698084138996, 0.23244654016022953, 0.2381060994790691, 0.2453927462636744, 0.2526793930482797, 0.25996603983288497, 0.26725268661749024, 0.2745393334020955, 0.2818259801867008, 0.29325562203632655, 0.3046852638859523, 0.31611490573557804, 0.3275445475852038, 0.33897418943482954, 0.3504038312844553, 0.36238021152097855, 0.3743565917575018, 0.38633297199402505, 0.3983093522305483, 0.41028573246707156, 0.4222621127035948, 0.4405683283070926, 0.45887454391059035, 0.4771807595140881, 0.4954869751175859, 0.5137931907210836, 0.5320994063245814, 0.5528317742271148, 0.5735641421296482, 0.5942965100321816, 0.6150288779347151, 0.6357612458372485, 0.6693461676259279, 0.7029310894146074, 0.7365160112032868, 0.7701009329919662, 0.8036858547806457, 0.8384094776253112, 0.8731331004699766, 0.9078567233146421, 0.9425803461593075, 0.977303969003973, 1.037607535982368, 1.0979111029607629, 1.1582146699391578, 1.2185182369175527, 1.2788218038959476, 1.3391253708743425, 1.4092726612892985, 1.4794199517042546, 1.5495672421192106, 1.6197145325341666, 1.6898618229491227, 1.7600091133640787, 1.8493359638936873, 1.9386628144232958, 2.027989664952904, 2.1173165154825124, 2.2066433660121207, 2.295970216541729, 2.4272687230105787, 2.5585672294794284, 2.689865735948278, 2.8211642424171277, 2.9524627488859774, 3.083761255354827, 3.2604349960389674, 3.4371087367231077, 3.613782477407248, 3.7904562180913883, 3.9671299587755287, 4.143803699459669, 4.383621951030065, 4.623440202600461, 4.8632584541708574, 5.103076705741254, 5.34289495731165, 5.582713208882046, 5.881909389407717, 6.181105569933388, 6.480301750459059, 6.77949793098473, 7.078694111510401, 7.3778902920360725, 7.82478895810839, 8.271687624180707, 8.718586290253025, 9.165484956325344, 9.612383622397662, 10.0]</t>
+          <t>[0.0, 5.722714566411929e-06, 1.1445429132823858e-05, 6.867257479694315e-05, 0.00012589972046106245, 0.0003035508252936412, 0.0004812019301262199, 0.0006588530349587987, 0.0011685080926416445, 0.0016781631503244904, 0.0021878182080073364, 0.00588369986990662, 0.009579581531805903, 0.013275463193705187, 0.017159808040335674, 0.021044152886966164, 0.024928497733596653, 0.028812842580227142, 0.0345602688980835, 0.04030769521593986, 0.04605512153379622, 0.05180254785165258, 0.05754997416950894, 0.06503187128943046, 0.07251376840935198, 0.0799956655292735, 0.08747756264919501, 0.09495945976911653, 0.10244135688903805, 0.10251504903601183, 0.10258874118298561, 0.10266243332995939, 0.10273612547693317, 0.10280981762390695, 0.10288350977088073, 0.1030308940648283, 0.10317827835877585, 0.10332566265272342, 0.10347304694667098, 0.10350252380546049, 0.10353200066425, 0.10356147752303951, 0.10359095438182903, 0.10359684975358693, 0.10360274512534484, 0.10360864049710275, 0.10361453586886066, 0.10361581490054522, 0.10361709393222979, 0.10361837296391435, 0.10361965199559892, 0.10361978859399162, 0.10361982106631834, 0.10361983039637068, 0.10361983757779818, 0.10361984267069409, 0.10361984776359, 0.10361985285648591, 0.10361985794938182, 0.10361986304227773, 0.10361987130610813, 0.10361987956993852, 0.10361988783376892, 0.10361989609759932, 0.10361992126695371, 0.1036199464363081, 0.1036199716056625, 0.10362022329920642, 0.10362047499275034, 0.10362299192818958, 0.10362550886362881, 0.10365067821802115, 0.1036758475724135, 0.10370101692680583, 0.10387790649960732, 0.1040547960724088, 0.10423168564521029, 0.10483459137038487, 0.10543749709555944, 0.10604040282073401, 0.10664330854590859, 0.109667242538835, 0.11269117653176142, 0.11571511052468783, 0.11873904451761425, 0.12310564627933489, 0.12747224804105553, 0.13183884980277616, 0.1362054515644968, 0.14057205332621742, 0.1457030748627495, 0.15083409639928158, 0.15596511793581366, 0.16109613947234575, 0.16622716100887783, 0.1713581825454099, 0.17784726239093698, 0.18433634223646406, 0.19082542208199113, 0.19274521267132472, 0.19307395926244106, 0.19317995606385482, 0.19321965223538298, 0.1932478925476897, 0.19327613285999642, 0.19330437317230315, 0.19333261348460987, 0.1933608537969166, 0.1934067643915848, 0.19345267498625301, 0.19349858558092123, 0.19354449617558944, 0.19368436127893204, 0.19382422638227464, 0.19396409148561725, 0.19452086492799545, 0.19507763837037365, 0.19563441181275185, 0.1983486808513613, 0.20106294988997073, 0.20377721892858017, 0.2077297211562532, 0.21168222338392625, 0.2156347256115993, 0.21958722783927234, 0.22559244242203214, 0.23159765700479193, 0.23760287158755172, 0.24360808617031152, 0.25209855967133094, 0.2605890331723504, 0.26907950667336983, 0.2775699801743893, 0.2860604536754087, 0.2959550018007294, 0.3058495499260501, 0.3157440980513708, 0.3256386461766915, 0.3355331943020122, 0.34542774242733293, 0.3571686903302344, 0.3689096382331359, 0.38065058613603736, 0.39239153403893884, 0.4041324819418403, 0.4158734298447418, 0.43257618964042965, 0.4492789494361175, 0.4659817092318054, 0.48268446902749323, 0.4993872288231811, 0.5194704805160336, 0.5395537322088861, 0.5596369839017387, 0.5797202355945912, 0.5998034872874437, 0.6305863310384126, 0.6613691747893814, 0.6921520185403502, 0.7229348622913191, 0.7537177060422879, 0.7861314801893847, 0.8185452543364815, 0.8509590284835783, 0.8833728026306751, 0.9157865767777719, 0.9758589060291406, 1.0359312352805095, 1.0960035645318782, 1.156075893783247, 1.2161482230346157, 1.2762205522859844, 1.3421667274183977, 1.408112902550811, 1.4740590776832243, 1.5400052528156376, 1.605951427948051, 1.6718976030804642, 1.7571348649906942, 1.8423721269009241, 1.927609388811154, 2.012846650721384, 2.0980839126316138, 2.1833211745418435, 2.3077155263360236, 2.4321098781302037, 2.556504229924384, 2.680898581718564, 2.805292933512744, 2.9296872853069242, 3.09696865429145, 3.2642500232759755, 3.431531392260501, 3.5988127612450267, 3.7660941302295523, 3.933375499214078, 4.160301241516875, 4.387226983819673, 4.61415272612247, 4.841078468425268, 5.068004210728065, 5.294929953030863, 5.577929832260808, 5.860929711490753, 6.143929590720698, 6.426929469950643, 6.709929349180588, 6.992929228410533, 7.415204127328014, 7.837479026245495, 8.259753925162975, 8.682028824080456, 9.104303722997937, 9.526578621915418, 10.0]</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.3175069626377336</v>
+        <v>0.3175069747450218</v>
       </c>
       <c r="D43" t="n">
         <v>9.81</v>
@@ -3314,13 +3314,13 @@
         <v>2</v>
       </c>
       <c r="L43" t="n">
-        <v>3.175069626377336</v>
+        <v>3.175069747450217</v>
       </c>
       <c r="M43" t="n">
-        <v>0.01983916954171683</v>
+        <v>0.01983916802868841</v>
       </c>
       <c r="N43" t="n">
-        <v>0.09919584770858413</v>
+        <v>0.09919584014344203</v>
       </c>
       <c r="O43" t="n">
         <v>18.09358203282477</v>
@@ -3350,11 +3350,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[0.0, 6.257949578546094e-07, 1.2515899157092187e-06, 7.509539494255313e-06, 1.3767489072801408e-05, 3.250210003783187e-05, 5.123671100286233e-05, 6.997132196789279e-05, 0.00011636129885445542, 0.00016275127574101806, 0.0002091412526275807, 0.0005199600679686504, 0.0008307788833097202, 0.0011415976986507898, 0.0016542921424863616, 0.0021669865863219334, 0.002679681030157505, 0.003192375473993077, 0.0041450200656975855, 0.005097664657402095, 0.006050309249106604, 0.007002953840811113, 0.009532745608971886, 0.012062537377132658, 0.014592329145293431, 0.017122120913454206, 0.01965191268161498, 0.02390188763241495, 0.02815186258321492, 0.03240183753401489, 0.03665181248481486, 0.04090178743561483, 0.0451517623864148, 0.052164806061107065, 0.05917784973579933, 0.06619089341049159, 0.07320393708518384, 0.0802169807598761, 0.08723002443456836, 0.09415361499644877, 0.10107720555832918, 0.10800079612020959, 0.11492438668209, 0.12184797724397041, 0.1287715678058508, 0.13455174095382977, 0.14033191410180873, 0.1461120872497877, 0.15189226039776665, 0.15767243354574562, 0.16345260669372458, 0.17064028979163362, 0.17782797288954266, 0.18243420611060396, 0.18704043933166525, 0.19164667255272655, 0.19625290577378784, 0.20085913899484914, 0.20633811520764947, 0.2118170914204498, 0.21729606763325013, 0.22277504384605046, 0.22863136203988968, 0.2344876802337289, 0.24034399842756812, 0.24620031662140734, 0.25205663481524654, 0.2637054815484045, 0.2753543282815625, 0.28700317501472045, 0.2986520217478784, 0.3103008684810364, 0.32194971521419435, 0.33136823286785244, 0.34078675052151053, 0.3502052681751686, 0.3596237858288267, 0.3690423034824848, 0.3784608211361429, 0.3955248938569741, 0.4125889665778053, 0.4296530392986365, 0.44671711201946773, 0.46378118474029895, 0.48279333658333173, 0.5018054884263645, 0.5208176402693974, 0.5398297921124302, 0.558841943955463, 0.5875903583003624, 0.6163387726452618, 0.6450871869901612, 0.6738356013350606, 0.70258401567996, 0.7326578060712834, 0.7627315964626068, 0.7928053868539302, 0.8228791772452536, 0.852952967636577, 0.9077328797006511, 0.9625127917647252, 1.017292703828799, 1.072072615892873, 1.126852527956947, 1.181632440021021, 1.232659072878516, 1.2836857057360112, 1.3347123385935062, 1.3857389714510013, 1.4367656043084964, 1.4877922371659915, 1.563598238406292, 1.6394042396465927, 1.7152102408868932, 1.7910162421271938, 1.8668222433674944, 1.942628244607795, 2.0429764965273773, 2.1433247484469597, 2.243673000366542, 2.3440212522861246, 2.444369504205707, 2.5447177561252894, 2.689331903317589, 2.8339460505098883, 2.978560197702188, 3.1231743448944873, 3.267788492086787, 3.4124026392790863, 3.590443894533535, 3.7684851497879834, 3.946526405042432, 4.124567660296881, 4.30260891555133, 4.480650170805779, 4.744804985084039, 5.008959799362298, 5.273114613640558, 5.537269427918817, 5.8014242421970765, 6.065579056475336, 6.365204981636936, 6.664830906798535, 6.964456831960135, 7.264082757121734, 7.563708682283334, 7.8633346074449335, 8.346004893388011, 8.82867517933109, 9.311345465274167, 9.794015751217245, 10.0]</t>
+          <t>[0.0, 5.193074040639605e-06, 1.038614808127921e-05, 6.231688848767526e-05, 0.0001142476288940713, 0.0002748591652986974, 0.00043547070170332346, 0.0005960822381079495, 0.001051910270545044, 0.0015077383029821383, 0.0019635663354192327, 0.004250293049623794, 0.006537019763828356, 0.00882374647803292, 0.0127976514919203, 0.0156643992104172, 0.0185311469289141, 0.021397894647411, 0.025640261932461172, 0.029882629217511343, 0.03412499650256151, 0.03836736378761168, 0.04427698964303853, 0.05018661549846538, 0.056096241353892226, 0.062005867209319075, 0.06791549306474592, 0.07542219523117215, 0.08292889739759837, 0.0904355995640246, 0.09794230173045082, 0.09803613550753115, 0.09812996928461148, 0.09822380306169182, 0.09831763683877215, 0.09841147061585248, 0.09850530439293281, 0.09935322086839096, 0.10020113734384911, 0.10104905381930726, 0.10189697029476541, 0.10274488677022356, 0.1028758078232176, 0.10300672887621165, 0.10303291308681047, 0.10303814992893023, 0.10304338677105, 0.10304862361316977, 0.10304967098159372, 0.10305071835001767, 0.10305176571844162, 0.10305281308686556, 0.10305323203423514, 0.10305325763749522, 0.10305326145096928, 0.10305326526444335, 0.10305326907791741, 0.10305327537375604, 0.10305328166959467, 0.10305334462798095, 0.10305340758636723, 0.10305403717023005, 0.10305466675409287, 0.10306096259272109, 0.1030672584313493, 0.10310248732181297, 0.10313771621227664, 0.10317294510274032, 0.1033885700928516, 0.10360419508296288, 0.10381982007307416, 0.10449794726530108, 0.105176074457528, 0.10585420164975491, 0.10653232884198183, 0.11064785454287507, 0.11476338024376831, 0.11887890594466155, 0.12299443164555479, 0.12742051230909662, 0.13184659297263845, 0.13627267363618029, 0.14069875429972212, 0.14512483496326395, 0.1502943933118433, 0.15546395166042265, 0.160633510009002, 0.16580306835758135, 0.1709726267061607, 0.17272019301687205, 0.1744677593275834, 0.1751501734640902, 0.17546175789826704, 0.1756239004818879, 0.17564236634557986, 0.17565285758669594, 0.175663348827812, 0.17567384006892808, 0.17568433131004416, 0.17569482255116023, 0.1757053137922763, 0.17571960158988023, 0.17573388938748416, 0.1757481771850881, 0.17576246498269202, 0.17577675278029595, 0.17579104057789988, 0.17581709747877733, 0.17584315437965478, 0.17586921128053223, 0.1758952681814097, 0.17592132508228714, 0.1759942675015105, 0.17606720992073388, 0.17614015233995725, 0.17621309475918062, 0.17653119476250353, 0.17684929476582645, 0.17716739476914936, 0.17856877926476442, 0.17997016376037947, 0.18137154825599452, 0.18552854214282258, 0.18968553602965063, 0.19384252991647868, 0.19799952380330674, 0.20339194683556708, 0.20878436986782742, 0.21417679290008776, 0.2195692159323481, 0.22496163896460844, 0.2327561936916415, 0.24055074841867455, 0.2483453031457076, 0.25613985787274063, 0.2639344125997737, 0.2713484653429118, 0.2787625180860499, 0.286176570829188, 0.2935906235723261, 0.30100467631546424, 0.30841872905860235, 0.3206204588447646, 0.33282218863092683, 0.34502391841708907, 0.3572256482032513, 0.36942737798941355, 0.3816291077755758, 0.39667235480164104, 0.4117156018277063, 0.4267588488537715, 0.44180209587983676, 0.456845342905902, 0.47188858993196725, 0.4914461424996805, 0.5110036950673937, 0.5305612476351069, 0.5501188002028201, 0.5696763527705333, 0.594311789398211, 0.6189472260258888, 0.6435826626535666, 0.6682180992812443, 0.6928535359089221, 0.729312614522525, 0.765771693136128, 0.802230771749731, 0.838689850363334, 0.875148928976937, 0.9138501943650924, 0.9525514597532478, 0.9912527251414033, 1.0299539905295587, 1.0686552559177143, 1.1073565213058698, 1.166226423330789, 1.2250963253557083, 1.2839662273806276, 1.3428361294055469, 1.4017060314304661, 1.4667274675344006, 1.5317489036383352, 1.5967703397422697, 1.6617917758462042, 1.7268132119501387, 1.7918346480540732, 1.891649676476987, 1.9914647048999008, 2.0912797333228146, 2.1910947617457284, 2.290909790168642, 2.390724818591556, 2.501439179781467, 2.612153540971378, 2.722867902161289, 2.8335822633512002, 2.9442966245411113, 3.0550109857310224, 3.231844973421113, 3.408678961111204, 3.585512948801295, 3.7623469364913857, 3.9391809241814766, 4.116014911871567, 4.356022890239643, 4.596030868607719, 4.836038846975795, 5.07604682534387, 5.316054803711946, 5.556062782080022, 5.829497879023652, 6.102932975967282, 6.376368072910912, 6.649803169854542, 6.9232382667981724, 7.1966733637418026, 7.635631320488971, 8.07458927723614, 8.513547233983306, 8.952505190730474, 9.39146314747764, 9.830421104224808, 10.0]</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.2934259498071939</v>
+        <v>0.2934259983030558</v>
       </c>
       <c r="D44" t="n">
         <v>9.81</v>
@@ -3381,13 +3381,13 @@
         <v>2</v>
       </c>
       <c r="L44" t="n">
-        <v>2.934259498071939</v>
+        <v>2.934259983030557</v>
       </c>
       <c r="M44" t="n">
-        <v>0.02322913069960428</v>
+        <v>0.02322912302123475</v>
       </c>
       <c r="N44" t="n">
-        <v>0.1161456534980214</v>
+        <v>0.1161456151061738</v>
       </c>
       <c r="O44" t="n">
         <v>17.68930227111675</v>
@@ -3417,11 +3417,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[0.0, 6.350224816450632e-07, 1.2700449632901264e-06, 7.620269779740759e-06, 1.3970494596191392e-05, 3.298197751909547e-05, 5.1993460441999546e-05, 7.100494336490362e-05, 0.00011810314162311481, 0.000165201339881326, 0.0002122995381395372, 0.000596528302389899, 0.0008783681967832332, 0.0011602080911765674, 0.0014420479855699016, 0.0021751878282804653, 0.002908327670991029, 0.0036414675137015923, 0.004374607356412156, 0.005833807216843195, 0.0072930070772742345, 0.008752206937705273, 0.010211406798136312, 0.01167060665856735, 0.014575086966340934, 0.017479567274114517, 0.020384047581888103, 0.023288527889661688, 0.026193008197435273, 0.031237635296345875, 0.036282262395256476, 0.041326889494167074, 0.04637151659307767, 0.05141614369198827, 0.05646077079089887, 0.06376438122915006, 0.07106799166740124, 0.07837160210565243, 0.08567521254390362, 0.0929788229821548, 0.10028243342040599, 0.10639536053812451, 0.11250828765584303, 0.11862121477356155, 0.12473414189128007, 0.1308470690089986, 0.13787143059020296, 0.14489579217140733, 0.14955927224883914, 0.15422275232627095, 0.15888623240370275, 0.16354971248113456, 0.16821319255856637, 0.17287667263599818, 0.17892788319268096, 0.18497909374936375, 0.19103030430604653, 0.19708151486272932, 0.2031327254194121, 0.2091839359760949, 0.21529769482819525, 0.2214114536802956, 0.22752521253239597, 0.23363897138449632, 0.23975273023659668, 0.24586648908869704, 0.25474750225157283, 0.26362851541444865, 0.27250952857732447, 0.2813905417402003, 0.2902715549030761, 0.300557172824728, 0.3108427907463799, 0.3211284086680318, 0.33141402658968366, 0.34169964451133555, 0.35198526243298744, 0.3657727313475908, 0.37956020026219417, 0.39334766917679753, 0.4071351380914009, 0.42092260700600426, 0.4347100759206076, 0.45173100601629695, 0.4687519361119863, 0.4857728662076756, 0.502793796303365, 0.5198147263990542, 0.5415754664421139, 0.5633362064851735, 0.5850969465282331, 0.6068576865712927, 0.6286184266143523, 0.6615504041855049, 0.6944823817566576, 0.7274143593278102, 0.7603463368989628, 0.7932783144701154, 0.8276540226115657, 0.862029730753016, 0.8964054388944663, 0.9307811470359166, 0.9651568551773669, 1.0239595118813785, 1.0827621685853899, 1.1415648252894013, 1.2003674819934127, 1.2591701386974241, 1.3179727954014355, 1.3870417519023166, 1.4561107084031977, 1.5251796649040787, 1.5942486214049598, 1.663317577905841, 1.732386534406722, 1.820846269024376, 1.9093060036420302, 1.9977657382596843, 2.0862254728773384, 2.1746852074949925, 2.2631449421126466, 2.3919450244344898, 2.520745106756333, 2.649545189078176, 2.778345271400019, 2.9071453537218623, 3.0359454360437055, 3.177363109697594, 3.318780783351482, 3.4601984570053705, 3.601616130659259, 3.7430338043131473, 3.8844514779670356, 4.111984660464474, 4.339517842961913, 4.567051025459351, 4.79458420795679, 5.022117390454229, 5.249650572951667, 5.501387944042798, 5.7531253151339286, 6.004862686225059, 6.25660005731619, 6.50833742840732, 6.760074799498451, 7.169328040930774, 7.578581282363096, 7.987834523795419, 8.397087765227742, 8.806341006660064, 9.215594248092387, 9.72916193224914, 10.0]</t>
+          <t>[0.0, 4.719924902324502e-06, 9.439849804649004e-06, 5.663909882789402e-05, 0.00010383834785113904, 0.0002493147778043931, 0.00039479120775764715, 0.0005402676377109012, 0.0009490206624109755, 0.00135777368711105, 0.0017665267118111244, 0.003459027774185438, 0.005151528836559751, 0.006844029898934064, 0.01035298165387335, 0.013861933408812636, 0.017370885163751924, 0.020879836918691212, 0.02688287424943032, 0.03288591158016943, 0.038888948910908536, 0.04489198624164764, 0.05089502357238675, 0.060189274700130926, 0.0694835258278751, 0.07877777695561929, 0.08807202808336347, 0.09424136329322874, 0.10041069850309402, 0.10164456554506707, 0.10287843258704012, 0.10411229962901317, 0.10534616667098622, 0.10559294007938083, 0.10583971348777545, 0.10588906816945437, 0.10589913379126893, 0.1059091994130835, 0.10591926503489806, 0.10592177123826085, 0.10592427744162365, 0.10592505155150865, 0.10592582566139365, 0.10592589002913451, 0.10592589834735693, 0.10592590496191437, 0.10592590866876134, 0.1059259123756083, 0.10592591608245527, 0.10592591978930224, 0.10592592349614921, 0.10592592720299618, 0.10592593220500093, 0.10592593720700569, 0.10592594220901044, 0.1059259472110152, 0.10592595221301995, 0.10592595721502471, 0.10592596646304332, 0.10592597571106194, 0.10592598495908055, 0.10592599420709917, 0.10592600345511778, 0.1059260292308229, 0.105926055006528, 0.10592608078223312, 0.10592610655793823, 0.10592621815775817, 0.10592632975757811, 0.10592644135739805, 0.10592755735559746, 0.10592867335379687, 0.10593983333579095, 0.10595099331778503, 0.10606259313772583, 0.10617419295766663, 0.10628579277760743, 0.10677949892253237, 0.10727320506745731, 0.10776691121238226, 0.1082606173573072, 0.11088094115757828, 0.11350126495784936, 0.11612158875812044, 0.11874191255839152, 0.12326528887486127, 0.12778866519133103, 0.1323120415078008, 0.13683541782427056, 0.14135879414074032, 0.1467817757739645, 0.1522047574071887, 0.15362567674220148, 0.15382918894149414, 0.15393103073128264, 0.1539686177399464, 0.15398444846373027, 0.1539959922866603, 0.15400753610959034, 0.15401907993252037, 0.1540306237554504, 0.15404216757838043, 0.15406124517040096, 0.15408032276242148, 0.154099400354442, 0.15411847794646252, 0.15417698741946867, 0.15423549689247482, 0.15429400636548096, 0.15482186819457391, 0.15534973002366687, 0.1566806698593012, 0.15801160969493555, 0.1593425495305699, 0.1622579455564082, 0.16517334158224653, 0.16808873760808485, 0.17100413363392317, 0.17508017008760524, 0.1791562065412873, 0.18323224299496937, 0.18780588136305318, 0.19237951973113698, 0.1969531580992208, 0.2015267964673046, 0.20994120909033315, 0.2183556217133617, 0.2250121834750205, 0.2316687452366793, 0.2383253069983381, 0.2449818687599969, 0.25523633958352077, 0.26549081040704464, 0.2757452812305685, 0.2859997520540924, 0.29625422287761627, 0.3052636209625921, 0.3142730190475679, 0.3232824171325437, 0.3322918152175195, 0.3413012133024953, 0.3503106113874711, 0.3664267701216454, 0.38254292885581964, 0.3986590875899939, 0.4147752463241682, 0.43089140505834245, 0.4470075637925167, 0.4681481337984742, 0.4892887038044317, 0.5104292738103892, 0.5315698438163466, 0.5527104138223041, 0.5738509838282616, 0.600615269461914, 0.6273795550955664, 0.6541438407292188, 0.6809081263628712, 0.7076724119965236, 0.7395889877546665, 0.7715055635128094, 0.8034221392709523, 0.8353387150290952, 0.8672552907872381, 0.920318746682194, 0.97338220257715, 1.026445658472106, 1.0795091143670619, 1.1325725702620177, 1.1856360261569736, 1.247188304037866, 1.3087405819187583, 1.3702928597996507, 1.431845137680543, 1.4933974155614353, 1.5549496934423277, 1.6346776508490417, 1.7144056082557557, 1.7941335656624697, 1.8738615230691837, 1.9535894804758978, 2.0333174378826118, 2.1477762166045804, 2.262234995326549, 2.3766937740485177, 2.4911525527704863, 2.605611331492455, 2.7200701102144236, 2.846111175306431, 2.972152240398439, 3.0981933054904465, 3.224234370582454, 3.3502754356744617, 3.4763165007664694, 3.6789702258385697, 3.88162395091067, 4.08427767598277, 4.28693140105487, 4.48958512612697, 4.69223885119907, 4.915490583250397, 5.138742315301723, 5.36199404735305, 5.585245779404376, 5.808497511455703, 6.031749243507029, 6.393991379221905, 6.756233514936781, 7.118475650651657, 7.480717786366533, 7.842959922081409, 8.205202057796285, 8.658227231819188, 9.111252405842091, 9.564277579864994, 10.0]</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.2692237827503345</v>
+        <v>0.2692237746716954</v>
       </c>
       <c r="D45" t="n">
         <v>9.81</v>
@@ -3448,13 +3448,13 @@
         <v>2</v>
       </c>
       <c r="L45" t="n">
-        <v>2.692237827503345</v>
+        <v>2.692237746716954</v>
       </c>
       <c r="M45" t="n">
-        <v>0.027593268794869</v>
+        <v>0.02759327045085993</v>
       </c>
       <c r="N45" t="n">
-        <v>0.137966343974345</v>
+        <v>0.1379663522542996</v>
       </c>
       <c r="O45" t="n">
         <v>17.17794690545135</v>
@@ -3484,11 +3484,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[0.0, 6.47296241088557e-07, 1.294592482177114e-06, 7.767554893062685e-06, 1.4240517303948256e-05, 3.362029173428261e-05, 5.300006616461697e-05, 7.237984059495133e-05, 0.00012042074548206309, 0.00016846165036917484, 0.0002165025552562866, 0.0005472666132808359, 0.0008073626719090571, 0.0010674587305372783, 0.0013275547891654995, 0.002154650399529113, 0.002981746009892727, 0.0038088416202563405, 0.004635937230619954, 0.006237397967581177, 0.0078388587045424, 0.009440319441503624, 0.011041780178464848, 0.012643240915426072, 0.01552785769054447, 0.018412474465662867, 0.021297091240781267, 0.024181708015899667, 0.027066324791018066, 0.03182138797763251, 0.03657645116424695, 0.041331514350861395, 0.04608657753747584, 0.05084164072409028, 0.055596703910704724, 0.06237190802693023, 0.06914711214315575, 0.07592231625938126, 0.08269752037560676, 0.08947272449183227, 0.09624792860805778, 0.10197365536781493, 0.10769938212757207, 0.11342510888732922, 0.11915083564708637, 0.12487656240684351, 0.13143231930155652, 0.13798807619626952, 0.1445438330909825, 0.1510995899856955, 0.1576553468804085, 0.1642111037751215, 0.1705933128206984, 0.1769755218662753, 0.1833577309118522, 0.1897399399574291, 0.196122149003006, 0.2025043580485829, 0.20896133267005643, 0.21541830729152994, 0.22187528191300346, 0.22833225653447697, 0.2347892311559505, 0.241246205777424, 0.25094884170268406, 0.2606514776279441, 0.27035411355320416, 0.2800567494784642, 0.28975938540372426, 0.30041276475333567, 0.3110661441029471, 0.3217195234525585, 0.3323729028021699, 0.3430262821517813, 0.35367966150139274, 0.3683968907434556, 0.3831141199855185, 0.39783134922758134, 0.4125485784696442, 0.4272658077117071, 0.44198303695376995, 0.45982265552624085, 0.47766227409871176, 0.49550189267118266, 0.5133415112436536, 0.5311811298161244, 0.5490207483885953, 0.5724676220617502, 0.5959144957349051, 0.61936136940806, 0.6428082430812149, 0.6662551167543698, 0.7016781281865887, 0.7371011396188076, 0.7725241510510266, 0.8079471624832455, 0.8433701739154644, 0.8801737115560395, 0.9169772491966146, 0.9537807868371897, 0.9905843244777648, 1.0273878621183399, 1.064191399758915, 1.1108124351995616, 1.1574334706402083, 1.204054506080855, 1.2506755415215016, 1.2972965769621483, 1.370829669401746, 1.444362761841344, 1.5178958542809418, 1.5914289467205396, 1.6649620391601374, 1.7384951315997352, 1.817220105027365, 1.895945078454995, 1.9746700518826248, 2.0533950253102544, 2.132119998737884, 2.2108449721655132, 2.336858551723055, 2.462872131280597, 2.588885710838139, 2.714899290395681, 2.8409128699532227, 2.9669264495107646, 3.1065496241426294, 3.246172798774494, 3.385795973406359, 3.5254191480382238, 3.6650423226700886, 3.8046654973019534, 4.027097955597434, 4.2495304138929155, 4.471962872188397, 4.694395330483878, 4.916827788779359, 5.13926024707484, 5.384909522518305, 5.630558797961769, 5.876208073405234, 6.121857348848699, 6.367506624292163, 6.613155899735628, 7.013667283844944, 7.41417866795426, 7.814690052063575, 8.21520143617289, 8.615712820282205, 9.01622420439152, 9.516023880605117, 10.0]</t>
+          <t>[0.0, 4.30308379249242e-06, 8.60616758498484e-06, 5.1637005509909044e-05, 9.466784343483325e-05, 0.00022687625303927867, 0.0003590846626437241, 0.0004912930722481695, 0.0008593750126741302, 0.0012274569531000909, 0.0015955388935260514, 0.0029232560210021782, 0.004250973148478305, 0.005578690275954432, 0.010152360085413632, 0.014726029894872832, 0.019299699704332034, 0.023873369513791237, 0.02985669234314481, 0.03584001517249838, 0.04182333800185195, 0.04780666083120552, 0.05378998366055909, 0.06199995398376166, 0.07020992430696422, 0.0784198946301668, 0.08662986495336937, 0.09234933992895647, 0.09806881490454357, 0.10378828988013067, 0.10950776485571777, 0.11522723983130487, 0.12094671480689197, 0.12919148919327242, 0.13448954325926987, 0.13978759732526733, 0.14508565139126478, 0.15038370545726223, 0.1556817595232597, 0.16097981358925714, 0.16722081109554804, 0.17346180860183893, 0.17970280610812983, 0.18594380361442073, 0.19218480112071162, 0.19842579862700252, 0.2047304949658379, 0.21103519130467327, 0.21733988764350864, 0.22364458398234402, 0.2299492803211794, 0.23625397666001477, 0.24739850287432877, 0.2585430290886428, 0.26968755530295685, 0.2808320815172709, 0.29197660773158496, 0.30196542206970417, 0.3119542364078234, 0.3219430507459426, 0.3319318650840618, 0.341920679422181, 0.35190949376030023, 0.3687370072935645, 0.3855645208268288, 0.4023920343600931, 0.41921954789335736, 0.43604706142662164, 0.4528745749598859, 0.4719007235352231, 0.4909268721105603, 0.5099530206858975, 0.5289791692612348, 0.548005317836572, 0.5670314664119093, 0.5934003961201695, 0.6197693258284297, 0.6461382555366899, 0.6725071852449501, 0.6988761149532103, 0.7359985969486338, 0.7731210789440572, 0.8102435609394807, 0.8473660429349041, 0.8844885249303276, 0.9250454120756952, 0.9656022992210629, 1.0061591863664305, 1.0467160735117982, 1.0872729606571658, 1.1278298478025335, 1.1878926012850128, 1.2479553547674922, 1.3080181082499716, 1.368080861732451, 1.4281436152149303, 1.493327338742258, 1.558511062269586, 1.6236947857969137, 1.6888785093242416, 1.7540622328515694, 1.8192459563788972, 1.9189453852517175, 2.0186448141245377, 2.118344242997358, 2.218043671870178, 2.317743100742998, 2.436979933324922, 2.5562167659068455, 2.6754535984887693, 2.794690431070693, 2.913927263652617, 3.0331640962345405, 3.177305315172914, 3.3214465341112875, 3.465587753049661, 3.6097289719880346, 3.753870190926408, 3.8980114098647816, 4.126438709250901, 4.35486600863702, 4.58329330802314, 4.811720607409259, 5.0401479067953785, 5.268575206181498, 5.520890697255057, 5.773206188328616, 6.025521679402175, 6.277837170475734, 6.530152661549293, 6.782468152622852, 7.194168628655329, 7.605869104687806, 8.017569580720284, 8.429270056752763, 8.840970532785242, 9.252671008817721, 9.767269425270886, 10.0]</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.2450823727545197</v>
+        <v>0.2450824161528932</v>
       </c>
       <c r="D46" t="n">
         <v>9.81</v>
@@ -3515,13 +3515,13 @@
         <v>2</v>
       </c>
       <c r="L46" t="n">
-        <v>2.450823727545197</v>
+        <v>2.450824161528932</v>
       </c>
       <c r="M46" t="n">
-        <v>0.03329705650382783</v>
+        <v>0.03329704471156636</v>
       </c>
       <c r="N46" t="n">
-        <v>0.1664852825191391</v>
+        <v>0.1664852235578318</v>
       </c>
       <c r="O46" t="n">
         <v>16.53115640352251</v>
@@ -3551,11 +3551,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[0.0, 6.638846307198666e-07, 1.3277692614397331e-06, 7.966615568638398e-06, 1.4605461875837063e-05, 3.448302478046304e-05, 5.436058768508902e-05, 7.4238150589715e-05, 0.00012355438286464285, 0.0001728706151395707, 0.00022218684741449855, 0.0005764378267353429, 0.0008226437200346997, 0.0010688496133340565, 0.0013150555066334133, 0.0019236946868263602, 0.0025323338670193074, 0.0031409730472122545, 0.0037496122274052017, 0.004927896858840906, 0.00610618149027661, 0.007284466121712314, 0.008462750753148018, 0.009641035384583722, 0.012203992696861616, 0.01476695000913951, 0.017329907321417405, 0.0198928646336953, 0.022455821945973196, 0.02657974934153395, 0.030703676737094704, 0.034827604132655454, 0.038951531528216204, 0.043075458923776955, 0.047199386319337705, 0.05339249867400457, 0.05958561102867144, 0.0657787233833383, 0.07197183573800517, 0.07816494809267203, 0.0843580604473389, 0.09090476950150897, 0.09745147855567904, 0.10399818760984911, 0.11054489666401918, 0.11709160571818925, 0.12365080318240325, 0.13021000064661725, 0.13676919811083127, 0.1433283955750453, 0.1498875930392593, 0.15644679050347332, 0.1631574729540375, 0.1698681554046017, 0.1765788378551659, 0.1832895203057301, 0.19000020275629428, 0.19671088520685848, 0.20338047200256007, 0.21005005879826166, 0.21671964559396326, 0.22338923238966485, 0.23005881918536644, 0.23672840598106804, 0.24720916487650854, 0.25768992377194905, 0.2681706826673895, 0.27865144156283, 0.2891322004582705, 0.3003472885310183, 0.31156237660376607, 0.32277746467651386, 0.33399255274926165, 0.34520764082200944, 0.35642272889475723, 0.37209940924945883, 0.38777608960416043, 0.40345276995886203, 0.41912945031356363, 0.43480613066826523, 0.45048281102296683, 0.4692510692621241, 0.4880193275012814, 0.5067875857404387, 0.525555843979596, 0.5443241022187533, 0.5679164502867704, 0.5915087983547875, 0.6151011464228047, 0.6386934944908218, 0.6622858425588389, 0.6975876471705952, 0.7328894517823514, 0.7681912563941077, 0.8034930610058639, 0.8387948656176202, 0.8754787101340727, 0.9121625546505253, 0.9488463991669779, 0.9855302436834305, 1.022214088199883, 1.086734166472915, 1.1512542447459473, 1.2157743230189795, 1.2802944012920117, 1.3448144795650439, 1.409334557838076, 1.4711879879057699, 1.5330414179734637, 1.5948948480411576, 1.6567482781088514, 1.7186017081765452, 1.780455138244239, 1.8654759577684212, 1.9504967772926034, 2.035517596816786, 2.120538416340968, 2.2055592358651506, 2.290580055389333, 2.4203936822080956, 2.550207309026858, 2.680020935845621, 2.8098345626643835, 2.939648189483146, 3.0694618163019087, 3.211935927554185, 3.3544100388064613, 3.4968841500587375, 3.639358261311014, 3.78183237256329, 3.9243064838155663, 4.154137658219967, 4.383968832624367, 4.613800007028767, 4.843631181433167, 5.0734623558375676, 5.303293530241968, 5.585323942431992, 5.867354354622016, 6.14938476681204, 6.431415179002064, 6.713445591192088, 6.995476003382112, 7.386079873371949, 7.776683743361785, 8.167287613351622, 8.557891483341459, 8.948495353331296, 9.339099223321133, 9.924198751892302, 10.0]</t>
+          <t>[0.0, 3.942775570343534e-06, 7.885551140687069e-06, 4.731330684412241e-05, 8.674106254755775e-05, 0.0002075265381267845, 0.00032831201370601124, 0.00044909748928523795, 0.0007826312091421201, 0.001116164928999002, 0.001449698648855884, 0.0025231812174252243, 0.0035966637859945645, 0.004670146354563904, 0.007624629902029325, 0.010579113449494746, 0.013533596996960167, 0.01648808054442559, 0.02196154571855078, 0.02743501089267597, 0.03290847606680116, 0.03838194124092635, 0.04385540641505154, 0.051482914372295685, 0.05625409029258928, 0.06102526621288287, 0.06579644213317647, 0.07056761805347006, 0.07760999785641357, 0.08465237765935707, 0.09169475746230057, 0.09873713726524408, 0.10427420314909704, 0.10981126903294999, 0.11534833491680295, 0.1208854008006559, 0.12642246668450885, 0.13415685911001496, 0.1398193042357516, 0.14548174936148822, 0.15114419448722485, 0.15680663961296148, 0.16246908473869812, 0.16813152986443475, 0.17551810923539027, 0.1829046886063458, 0.1902912679773013, 0.19767784734825683, 0.20506442671921235, 0.21245100609016787, 0.21952738265468413, 0.2266037592192004, 0.23368013578371666, 0.24075651234823292, 0.24783288891274918, 0.25706785780934915, 0.2663028267059491, 0.2755377956025491, 0.28477276449914907, 0.29400773339574904, 0.3033997708415093, 0.3127918082872696, 0.3221838457330299, 0.33157588317879017, 0.34096792062455045, 0.35035995807031073, 0.367635506195638, 0.3849110543209653, 0.40218660244629256, 0.41946215057161984, 0.4367376986969471, 0.4540132468222744, 0.47709133246699004, 0.5001694181117057, 0.5232475037564213, 0.5463255894011368, 0.5694036750458524, 0.592481760690568, 0.6177687103491262, 0.6430556600076843, 0.6683426096662425, 0.6936295593248006, 0.7189165089833588, 0.7581059531005436, 0.7972953972177285, 0.8364848413349133, 0.8756742854520981, 0.914863729569283, 0.9557634246759631, 0.9966631197826432, 1.0375628148893234, 1.0784625099960037, 1.119362205102684, 1.1602619002093641, 1.212023763358588, 1.2637856265078118, 1.3155474896570356, 1.3673093528062594, 1.4190712159554832, 1.5016761783735206, 1.584281140791558, 1.6668861032095954, 1.7494910656276328, 1.8320960280456702, 1.9147009904637076, 2.0011909023742787, 2.08768081428485, 2.1741707261954213, 2.2606606381059926, 2.347150550016564, 2.4336404619271352, 2.5733647803660733, 2.7130890988050114, 2.8528134172439494, 2.9925377356828875, 3.1322620541218256, 3.2719863725607636, 3.44146097957261, 3.610935586584456, 3.7804101935963024, 3.9498848006081486, 4.119359407619995, 4.288834014631841, 4.54098209287946, 4.793130171127079, 5.045278249374698, 5.2974263276223175, 5.5495744058699366, 5.801722484117556, 6.114334944666652, 6.426947405215748, 6.739559865764845, 7.052172326313941, 7.364784786863037, 7.6773972474121335, 8.11807568523863, 8.558754123065125, 8.99943256089162, 9.440110998718115, 9.88078943654461, 10.0]</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.221321738653843</v>
+        <v>0.2213217405102048</v>
       </c>
       <c r="D47" t="n">
         <v>9.81</v>
@@ -3582,13 +3582,13 @@
         <v>2</v>
       </c>
       <c r="L47" t="n">
-        <v>2.213217386538429</v>
+        <v>2.213217405102048</v>
       </c>
       <c r="M47" t="n">
-        <v>0.04083023214046797</v>
+        <v>0.04083023145553133</v>
       </c>
       <c r="N47" t="n">
-        <v>0.2041511607023399</v>
+        <v>0.2041511572776566</v>
       </c>
       <c r="O47" t="n">
         <v>15.71306006294538</v>
@@ -3618,11 +3618,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[0.0, 6.868075072921821e-07, 1.3736150145843641e-06, 8.241690087506185e-06, 1.5109765160428006e-05, 3.567525909465372e-05, 5.624075302887943e-05, 7.680624696310514e-05, 0.00012788710565362222, 0.0001789679643441393, 0.00023004882303465638, 0.0005080428904928885, 0.0007860369579511207, 0.00100762544891199, 0.0012292139398728595, 0.0014508024308337289, 0.00196935364922555, 0.002487904867617371, 0.003006456086009192, 0.003525007304401013, 0.004507519974115566, 0.005490032643830118, 0.006472545313544671, 0.007455057983259223, 0.008437570652973776, 0.010844636028540224, 0.013251701404106671, 0.01565876677967312, 0.018065832155239568, 0.020472897530806018, 0.02424583820074315, 0.028018778870680282, 0.031791719540617415, 0.035564660210554544, 0.03933760088049167, 0.0431105415504288, 0.04879341010451457, 0.054476278658600344, 0.060159147212686115, 0.06584201576677189, 0.07152488432085766, 0.07720775287494343, 0.08361600340854786, 0.09002425394215229, 0.09643250447575671, 0.10284075500936114, 0.10924900554296557, 0.11562133878160982, 0.12199367202025407, 0.12836600525889832, 0.13473833849754258, 0.14111067173618683, 0.14748300497483108, 0.15442812570441164, 0.1613732464339922, 0.16831836716357276, 0.17526348789315332, 0.1822086086227339, 0.18915372935231445, 0.19605858648015628, 0.20296344360799812, 0.20986830073583995, 0.2167731578636818, 0.22367801499152362, 0.23058287211936546, 0.2431295203559469, 0.25567616859252834, 0.26822281682910976, 0.28076946506569117, 0.2933161133022726, 0.30430591381484534, 0.3152957143274181, 0.32628551483999085, 0.3372753153525636, 0.34826511586513637, 0.3592549163777091, 0.3802569119240299, 0.40125890747035065, 0.4222609030166714, 0.44326289856299217, 0.46426489410931293, 0.4852668896556337, 0.5055580064084639, 0.5258491231612942, 0.5461402399141244, 0.5664313566669547, 0.5867224734197849, 0.6070135901726151, 0.6372850626389209, 0.6675565351052267, 0.6978280075715325, 0.7280994800378383, 0.7583709525041441, 0.7969827938682711, 0.8355946352323981, 0.8742064765965251, 0.912818317960652, 0.951430159324779, 0.990042000688906, 1.037619850630241, 1.0851977005715758, 1.1327755505129107, 1.1803534004542455, 1.2279312503955804, 1.2755091003369152, 1.335688959017265, 1.3958688176976146, 1.4560486763779643, 1.516228535058314, 1.5764083937386637, 1.6365882524190134, 1.7265849722975122, 1.816581692176011, 1.9065784120545097, 1.9965751319330085, 2.0865718518115073, 2.176568571690006, 2.275139600795321, 2.3737106299006356, 2.4722816590059504, 2.570852688111265, 2.66942371721658, 2.767994746321895, 2.8988765017814795, 3.029758257241064, 3.160640012700649, 3.2915217681602336, 3.4224035236198183, 3.553285279079403, 3.75969317710971, 3.966101075140017, 4.1725089731703235, 4.37891687120063, 4.585324769230937, 4.791732667261243, 5.0456178454672695, 5.299503023673296, 5.553388201879322, 5.807273380085348, 6.061158558291375, 6.315043736497401, 6.657760476144355, 7.000477215791308, 7.343193955438262, 7.685910695085216, 8.028627434732169, 8.371344174379121, 8.90022928998354, 9.42911440558796, 9.957999521192379, 10.0]</t>
+          <t>[0.0, 3.6407044927800724e-06, 7.281408985560145e-06, 4.368845391336087e-05, 8.00954988411616e-05, 0.00019132939298369177, 0.00030256328712622194, 0.0004137971812687521, 0.0007187909621769848, 0.0010237847430852173, 0.0013287785239934498, 0.002214692432951083, 0.003100606341908716, 0.003986520250866349, 0.0061157416389730455, 0.008244963027079742, 0.010374184415186439, 0.012503405803293136, 0.018814563468806396, 0.023591981384925024, 0.028369399301043652, 0.03314681721716228, 0.037924235133280915, 0.042701653049399546, 0.05033390484358154, 0.05796615663776353, 0.06559840843194552, 0.07323066022612751, 0.0808629120203095, 0.08849516381449149, 0.09447135437096651, 0.10044754492744154, 0.10642373548391657, 0.11239992604039159, 0.11837611659686662, 0.12435230715334164, 0.131242259450084, 0.13813221174682636, 0.1450221640435687, 0.15191211634031107, 0.15880206863705343, 0.1656032313836036, 0.1724043941301538, 0.17920555687670398, 0.18600671962325416, 0.19280788236980434, 0.19960904511635452, 0.20741425715953338, 0.21521946920271223, 0.2230246812458911, 0.23082989328906994, 0.2386351053322488, 0.24644031737542765, 0.25689120459750564, 0.2673420918195836, 0.2777929790416616, 0.2882438662637396, 0.2986947534858176, 0.3091456407078956, 0.32067329597359456, 0.33220095123929355, 0.34372860650499254, 0.35525626177069153, 0.3667839170363905, 0.3783115723020895, 0.39723703916110625, 0.416162506020123, 0.43508797287913975, 0.4540134397381565, 0.47293890659717325, 0.49186437345619, 0.5137693500315444, 0.5356743266068988, 0.5575793031822532, 0.5794842797576076, 0.601389256332962, 0.6232942329083164, 0.6531975098726753, 0.6831007868370342, 0.7130040638013931, 0.742907340765752, 0.772810617730111, 0.8141828209819243, 0.8555550242337376, 0.896927227485551, 0.9382994307373643, 0.9796716339891777, 1.024997557091322, 1.070323480193466, 1.1156494032956101, 1.1609753263977542, 1.2063012494998984, 1.2516271726020425, 1.307711566628091, 1.3637959606541394, 1.419880354680188, 1.4759647487062364, 1.5320491427322849, 1.6232436460517732, 1.7144381493712615, 1.8056326526907498, 1.896827156010238, 1.9880216593297264, 2.0792161626492147, 2.1733680483692077, 2.2675199340892007, 2.3616718198091937, 2.4558237055291867, 2.5499755912491797, 2.6441274769691727, 2.770525161060531, 2.896922845151889, 3.023320529243247, 3.149718213334605, 3.276115897425963, 3.4025135815173213, 3.599666357590099, 3.7968191336628765, 3.993971909735654, 4.191124685808432, 4.388277461881209, 4.585430237953987, 4.827543384290622, 5.069656530627257, 5.311769676963892, 5.553882823300527, 5.795995969637162, 6.038109115973797, 6.363946472734823, 6.689783829495849, 7.015621186256875, 7.341458543017901, 7.667295899778927, 7.993133256539953, 8.489603249591228, 8.986073242642505, 9.48254323569378, 9.979013228745057, 10.0]</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.1984354002627979</v>
+        <v>0.1984354092139284</v>
       </c>
       <c r="D48" t="n">
         <v>9.81</v>
@@ -3649,13 +3649,13 @@
         <v>2</v>
       </c>
       <c r="L48" t="n">
-        <v>1.984354002627979</v>
+        <v>1.984354092139284</v>
       </c>
       <c r="M48" t="n">
-        <v>0.05079157646249891</v>
+        <v>0.05079157188023187</v>
       </c>
       <c r="N48" t="n">
-        <v>0.2539578823124946</v>
+        <v>0.2539578594011593</v>
       </c>
       <c r="O48" t="n">
         <v>14.67828663867616</v>
@@ -3685,11 +3685,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[0.0, 7.195087894027813e-07, 1.4390175788055626e-06, 8.634105472833376e-06, 1.582919336686119e-05, 3.737618303619494e-05, 5.892317270552869e-05, 8.047016237486244e-05, 0.00013407296714960433, 0.00018767577192434622, 0.0002412785766990881, 0.0004817770496744477, 0.0007222755226498072, 0.0009627739956251667, 0.0013400026022211927, 0.0017172312088172188, 0.0020944598154132446, 0.0024716884220092705, 0.0032283820796659983, 0.0039850757373227266, 0.004741769394979455, 0.005498463052636184, 0.007181097021466018, 0.008863730990295852, 0.010546364959125688, 0.012228998927955523, 0.013911632896785358, 0.01676762187027691, 0.01962361084376846, 0.022479599817260013, 0.025335588790751564, 0.028191577764243116, 0.031047566737734667, 0.03580583975454306, 0.040564112771351454, 0.04532238578815985, 0.050080658804968245, 0.05483893182177664, 0.059597204838585036, 0.0673070652753267, 0.07501692571206837, 0.08062338178932042, 0.08622983786657247, 0.09183629394382452, 0.09744275002107657, 0.10304920609832861, 0.11235601551423484, 0.11816825463118563, 0.12398049374813642, 0.12979273286508722, 0.13560497198203803, 0.14141721109898883, 0.14722945021593964, 0.15464043307861663, 0.16205141594129363, 0.16946239880397063, 0.17687338166664762, 0.18428436452932462, 0.1916953473920016, 0.19898064383287375, 0.2062659402737459, 0.21355123671461804, 0.22083653315549018, 0.22812182959636232, 0.23540712603723446, 0.24655259446381161, 0.25769806289038877, 0.2688435313169659, 0.2799889997435431, 0.29113446817012023, 0.30395127601179417, 0.3167680838534681, 0.32958489169514205, 0.342401699536816, 0.3552185073784899, 0.36803531522016386, 0.3863901521642261, 0.4047449891082884, 0.42309982605235064, 0.4414546629964129, 0.45980949994047515, 0.4781643368845374, 0.499669679816573, 0.5211750227486086, 0.5426803656806443, 0.5641857086126799, 0.5856910515447156, 0.6071963944767512, 0.6366689386471107, 0.6661414828174702, 0.6956140269878297, 0.7250865711581892, 0.7545591153285487, 0.795300895184519, 0.8360426750404892, 0.8767844548964595, 0.9175262347524298, 0.9582680146084, 1.0019600561275144, 1.0456520976466286, 1.0893441391657428, 1.133036180684857, 1.1767282222039712, 1.2204202637230854, 1.2748218974766816, 1.3292235312302778, 1.383625164983874, 1.4380267987374702, 1.4924284324910664, 1.5784985474557705, 1.6645686624204745, 1.7506387773851786, 1.8367088923498827, 1.9227790073145867, 2.008849122279291, 2.109096965042299, 2.2093448078053073, 2.3095926505683155, 2.4098404933313238, 2.510088336094332, 2.6103361788573403, 2.7337800912986916, 2.857224003740043, 2.9806679161813943, 3.1041118286227456, 3.227555741064097, 3.3509996535054483, 3.5451378192030405, 3.7392759849006327, 3.933414150598225, 4.127552316295818, 4.321690481993411, 4.515828647691004, 4.755868405378014, 4.995908163065025, 5.235947920752035, 5.475987678439045, 5.716027436126056, 5.956067193813066, 6.28539531690239, 6.614723439991714, 6.944051563081038, 7.273379686170362, 7.602707809259686, 7.9320359323490095, 8.385022532220734, 8.83800913209246, 9.290995731964184, 9.743982331835909, 10.0]</t>
+          <t>[0.0, 3.4019496567938326e-06, 6.803899313587665e-06, 4.082339588152599e-05, 7.484289244946432e-05, 0.0001785284793311112, 0.0002822140662127581, 0.00038589965309440493, 0.0006685823613548998, 0.0009512650696153947, 0.0012339477778758896, 0.0019779695078208683, 0.002721991237765847, 0.0034660129677108256, 0.005163441935200089, 0.006860870902689352, 0.008558299870178615, 0.010255728837667878, 0.013893313999346896, 0.017530899161025914, 0.021168484322704934, 0.024806069484383953, 0.028443654646062973, 0.033046853727714987, 0.037650052809367, 0.042253251891019014, 0.04685645097267103, 0.05212413107275523, 0.05739181117283943, 0.06265949127292364, 0.06792717137300786, 0.07442056308528792, 0.080913954797568, 0.08740734650984806, 0.09390073822212813, 0.1003941299344082, 0.10676794572789017, 0.11314176152137213, 0.1195155773148541, 0.12588939310833608, 0.13226320890181806, 0.13863702469530004, 0.1467127969813395, 0.15478856926737894, 0.1628643415534184, 0.17094011383945784, 0.1790158861254973, 0.18709165841153674, 0.19366150022278023, 0.2002313420340237, 0.2068011838452672, 0.21337102565651067, 0.21994086746775415, 0.22651070927899764, 0.23920580145749654, 0.25190089363599544, 0.26459598581449434, 0.27729107799299324, 0.28998617017149214, 0.3033047029393152, 0.3166232357071383, 0.32994176847496137, 0.34326030124278445, 0.3565788340106075, 0.3698973667784306, 0.387618246290228, 0.4053391258020254, 0.4230600053138228, 0.4407808848256202, 0.4585017643374176, 0.47622264384921503, 0.49787956559066254, 0.51953648733211, 0.5411934090735575, 0.562850330815005, 0.5845072525564525, 0.6162135539667826, 0.6479198553771126, 0.6796261567874426, 0.7113324581977727, 0.7430387596081027, 0.7790434166968944, 0.815048073785686, 0.8510527308744776, 0.8870573879632693, 0.9230620450520609, 0.9694064907188973, 1.0157509363857335, 1.0620953820525698, 1.108439827719406, 1.1547842733862423, 1.2011287190530786, 1.264845103568985, 1.3285614880848913, 1.3922778726007976, 1.455994257116704, 1.5197106416326103, 1.5973401766370687, 1.6749697116415272, 1.7525992466459857, 1.8302287816504441, 1.9078583166549026, 1.985487851659361, 2.074436527395844, 2.163385203132327, 2.25233387886881, 2.341282554605293, 2.430231230341776, 2.5743372312409205, 2.718443232140065, 2.8625492330392097, 3.0066552339383543, 3.150761234837499, 3.2948672357366435, 3.4644974104475037, 3.634127585158364, 3.803757759869224, 3.973387934580084, 4.143018109290944, 4.312648284001804, 4.543603719515282, 4.7745591550287605, 5.005514590542239, 5.236470026055717, 5.467425461569196, 5.698380897082674, 6.018680580158804, 6.338980263234935, 6.659279946311065, 6.979579629387195, 7.299879312463325, 7.620178995539455, 8.097704913787823, 8.57523083203619, 9.052756750284559, 9.530282668532926, 10.0]</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.1770146826388335</v>
+        <v>0.1770146607841643</v>
       </c>
       <c r="D49" t="n">
         <v>9.81</v>
@@ -3716,13 +3716,13 @@
         <v>2</v>
       </c>
       <c r="L49" t="n">
-        <v>1.770146826388335</v>
+        <v>1.770146607841643</v>
       </c>
       <c r="M49" t="n">
-        <v>0.06382802611750495</v>
+        <v>0.06382804187823889</v>
       </c>
       <c r="N49" t="n">
-        <v>0.3191401305875247</v>
+        <v>0.3191402093911944</v>
       </c>
       <c r="O49" t="n">
         <v>13.36944807472602</v>
@@ -3752,11 +3752,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[0.0, 7.684472056127673e-07, 1.5368944112255346e-06, 9.221366467353208e-06, 1.6905838523480884e-05, 3.992189452834577e-05, 6.293795053321065e-05, 8.595400653807554e-05, 0.0001433409185124701, 0.00020072783048686465, 0.0002581147424612592, 0.0004766651885086167, 0.0006952156345559742, 0.0009137660806033316, 0.0012754388115050583, 0.001637111542406785, 0.0019987842733085117, 0.0023604570042102383, 0.0030825925336414738, 0.0038047280630727092, 0.004526863592503944, 0.00524899912193518, 0.006851894888869916, 0.008454790655804652, 0.010057686422739388, 0.011660582189674125, 0.01326347795660886, 0.015919128306646445, 0.01857477865668403, 0.021230429006721615, 0.0238860793567592, 0.026541729706796784, 0.02919738005683437, 0.033642750179895264, 0.03808812030295616, 0.04253349042601706, 0.04697886054907796, 0.05142423067213886, 0.05586960079519976, 0.06655260702127923, 0.07363939466637802, 0.08072618231147681, 0.0878129699565756, 0.09489975760167439, 0.10198654524677318, 0.1093370527563521, 0.11668756026593101, 0.12403806777550992, 0.13138857528508885, 0.1387390827946678, 0.14839063247521547, 0.15804218215576316, 0.16769373183631084, 0.17734528151685852, 0.1869968311974062, 0.1966483808779539, 0.20410989456442455, 0.2115714082508952, 0.21903292193736587, 0.22649443562383653, 0.2339559493103072, 0.24141746299677785, 0.2538103543012884, 0.26620324560579894, 0.2785961369103095, 0.29098902821482003, 0.3033819195193306, 0.3157748108238411, 0.328445574718965, 0.3411163386140889, 0.3537871025092128, 0.3664578664043367, 0.3791286302994606, 0.3917993941945845, 0.4108255725666482, 0.4298517509387119, 0.44887792931077564, 0.46790410768283935, 0.48693028605490307, 0.5135007788038283, 0.5400712715527535, 0.5666417643016787, 0.5932122570506039, 0.6197827497995291, 0.6505180667200824, 0.6812533836406357, 0.711988700561189, 0.7427240174817423, 0.7734593344022956, 0.8111896520461266, 0.8489199696899575, 0.8866502873337885, 0.9243806049776194, 0.9621109226214504, 0.9998412402652813, 1.0445527161458887, 1.089264192026496, 1.1339756679071034, 1.1786871437877107, 1.223398619668318, 1.2681100955489253, 1.3426782166710354, 1.4172463377931455, 1.4918144589152555, 1.5663825800373656, 1.6409507011594757, 1.7155188222815858, 1.801100806155716, 1.8866827900298464, 1.9722647739039767, 2.057846757778107, 2.1434287416522375, 2.229010725526368, 2.341207372636825, 2.4534040197472824, 2.5656006668577396, 2.6777973139681968, 2.789993961078654, 2.902190608189111, 3.068911623979194, 3.235632639769277, 3.40235365555936, 3.569074671349443, 3.7357956871395257, 3.9025167029296086, 4.136505744575877, 4.370494786222146, 4.604483827868415, 4.838472869514684, 5.072461911160953, 5.3064509528072215, 5.5981287837496305, 5.88980661469204, 6.181484445634449, 6.473162276576858, 6.764840107519267, 7.056517938461676, 7.492240923414765, 7.927963908367854, 8.363686893320942, 8.79940987827403, 9.235132863227118, 9.670855848180206, 10.0]</t>
+          <t>[0.0, 3.239150097619405e-06, 6.47830019523881e-06, 3.886980117143286e-05, 7.126130214762691e-05, 0.0001697658827812369, 0.0002682704634148469, 0.0003667750440484569, 0.0006343053628540352, 0.0009018356816596134, 0.0011693660004651917, 0.0018496508916848713, 0.0025299357829045507, 0.00321022067412423, 0.0038905055653439095, 0.005717809044734833, 0.007545112524125756, 0.00937241600351668, 0.011199719482907603, 0.014697337728640457, 0.01819495597437331, 0.02169257422010616, 0.025190192465839013, 0.028687810711571865, 0.03311090719247546, 0.03753400367337906, 0.04195710015428265, 0.04638019663518625, 0.050803293116089845, 0.05808107241358036, 0.06535885171107088, 0.0726366310085614, 0.07991441030605191, 0.08719218960354243, 0.09759176731427031, 0.1038420660003342, 0.11009236468639809, 0.11634266337246198, 0.12259296205852586, 0.12884326074458974, 0.1350935594306536, 0.1428232483351755, 0.15055293723969743, 0.15828262614421934, 0.16601231504874125, 0.17374200395326317, 0.18147169285778508, 0.18903301546322568, 0.19659433806866627, 0.20415566067410687, 0.21171698327954747, 0.21927830588498806, 0.22683962849042866, 0.2423813589880412, 0.25792308948565373, 0.27346481998326627, 0.2890065504808788, 0.30454828097849135, 0.31780323069883226, 0.3310581804191732, 0.3443131301395141, 0.357568079859855, 0.3708230295801959, 0.38407797930053683, 0.42144257715007516, 0.43357724496541405, 0.44571191278075295, 0.45784658059609185, 0.46998124841143074, 0.48211591622676964, 0.49425058404210853, 0.5167857609471846, 0.5393209378522608, 0.5618561147573369, 0.584391291662413, 0.6069264685674891, 0.6437917377510755, 0.6806570069346618, 0.7175222761182481, 0.7543875453018345, 0.7912528144854208, 0.8313090440984242, 0.8713652737114276, 0.911421503324431, 0.9514777329374343, 0.9915339625504377, 1.0315901921634412, 1.0773654211609311, 1.1231406501584211, 1.168915879155911, 1.214691108153401, 1.260466337150891, 1.331916227381893, 1.4033661176128949, 1.4748160078438968, 1.5462658980748987, 1.6177157883059006, 1.6891656785369025, 1.7732760846134954, 1.8573864906900883, 1.9414968967666812, 2.025607302843274, 2.1097177089198667, 2.1938281149964594, 2.3070377779811113, 2.4202474409657633, 2.5334571039504152, 2.646666766935067, 2.759876429919719, 2.873086092904371, 3.0380005605936082, 3.2029150282828454, 3.3678294959720825, 3.5327439636613196, 3.6976584313505567, 3.862572899039794, 4.0944965978157635, 4.326420296591733, 4.558343995367703, 4.790267694143672, 5.022191392919642, 5.254115091695612, 5.542939563238388, 5.831764034781164, 6.120588506323941, 6.409412977866717, 6.698237449409493, 6.98706192095227, 7.384510714269234, 7.781959507586198, 8.179408300903162, 8.576857094220127, 8.974305887537092, 9.371754680854057, 9.925548046208839, 10.0]</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.1575171711353884</v>
+        <v>0.1575171710489333</v>
       </c>
       <c r="D50" t="n">
         <v>9.81</v>
@@ -3783,13 +3783,13 @@
         <v>2</v>
       </c>
       <c r="L50" t="n">
-        <v>1.575171711353884</v>
+        <v>1.575171710489333</v>
       </c>
       <c r="M50" t="n">
-        <v>0.0806072654665056</v>
+        <v>0.08060726555499004</v>
       </c>
       <c r="N50" t="n">
-        <v>0.4030363273325279</v>
+        <v>0.4030363277749502</v>
       </c>
       <c r="O50" t="n">
         <v>11.7139567890923</v>
@@ -3819,11 +3819,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[0.0, 8.475713663360658e-07, 1.6951427326721315e-06, 1.017085639603279e-05, 1.8646570059393445e-05, 4.403839359699854e-05, 6.943021713460364e-05, 9.482204067220873e-05, 0.00015835223838193721, 0.0002218824360916657, 0.00028541263380139415, 0.0004922848764268234, 0.0006991571190522527, 0.000906029361677682, 0.0012641926632400646, 0.0016223559648024472, 0.0019805192663648295, 0.002338682567927212, 0.003035389932622859, 0.003732097297318506, 0.004428804662014153, 0.005125512026709801, 0.006667603159510426, 0.00820969429231105, 0.009751785425111674, 0.011293876557912298, 0.012835967690712921, 0.01531283565315338, 0.01778970361559384, 0.020266571578034298, 0.022743439540474756, 0.025220307502915214, 0.02769717546535567, 0.0318779104682798, 0.03605864547120392, 0.04023938047412805, 0.04442011547705217, 0.048600850479976296, 0.05278158548290042, 0.05900285797225384, 0.06522413046160726, 0.07144540295096068, 0.0776666754403141, 0.08388794792966751, 0.09010922041902093, 0.09813478672646633, 0.10616035303391173, 0.11418591934135713, 0.12221148564880253, 0.13023705195624793, 0.13826261826369335, 0.14672278560015206, 0.15518295293661077, 0.1636431202730695, 0.1721032876095282, 0.1805634549459869, 0.18902362228244562, 0.19784831065093672, 0.20667299901942782, 0.2154976873879189, 0.22432237575641, 0.2331470641249011, 0.24911022656850193, 0.26507338901210276, 0.2810365514557036, 0.29699971389930446, 0.3129628763429053, 0.32970456682497884, 0.34644625730705236, 0.3631879477891259, 0.3799296382711994, 0.39667132875327293, 0.41341301923534646, 0.4388413148648016, 0.46426961049425675, 0.4896979061237119, 0.515126201753167, 0.5405544973826222, 0.5659827930120773, 0.5938351558514448, 0.6216875186908122, 0.6495398815301796, 0.677392244369547, 0.7052446072089145, 0.7330969700482819, 0.7729001916800771, 0.8127034133118722, 0.8525066349436674, 0.8923098565754626, 0.9321130782072578, 0.9719162998390529, 1.0270988964645344, 1.082281493090016, 1.1374640897154975, 1.192646686340979, 1.2478292829664606, 1.303011879591942, 1.3686279451317964, 1.4342440106716507, 1.499860076211505, 1.5654761417513594, 1.6310922072912137, 1.696708272831068, 1.7835656315519943, 1.8704229902729206, 1.9572803489938468, 2.044137707714773, 2.130995066435699, 2.217852425156625, 2.329588240888406, 2.4413240566201866, 2.5530598723519673, 2.664795688083748, 2.7765315038155287, 2.8882673195473094, 3.0567540273875, 3.2252407352276906, 3.393727443067881, 3.562214150908072, 3.7307008587482624, 3.899187566588453, 4.131110365484365, 4.363033164380277, 4.594955963276189, 4.826878762172101, 5.058801561068013, 5.290724359963925, 5.616016670112232, 5.941308980260538, 6.266601290408844, 6.5918936005571505, 6.917185910705457, 7.242478220853763, 7.709075973104904, 8.175673725356045, 8.642271477607187, 9.108869229858328, 9.57546698210947, 10.0]</t>
+          <t>[0.0, 3.1840770342421448e-06, 6.3681540684842895e-06, 3.8208924410905744e-05, 7.00496947533272e-05, 0.00016668690286665713, 0.00026332411097998703, 0.00035996131909331693, 0.000622195003190466, 0.0008844286872876151, 0.0011466623713847642, 0.001788478237066714, 0.0024302941027486637, 0.0030721099684306134, 0.003713925834112563, 0.005350897365170403, 0.006987868896228242, 0.008624840427286081, 0.01026181195834392, 0.013454277555618545, 0.01664674315289317, 0.019839208750167793, 0.023031674347442417, 0.02622413994471704, 0.030238776473517744, 0.03425341300231845, 0.03826804953111915, 0.04228268605991985, 0.046297322588720546, 0.05200664120677706, 0.057715959824833574, 0.06342527844289009, 0.0691345970609466, 0.07484391567900311, 0.08289819797574755, 0.09095248027249198, 0.0990067625692364, 0.10706104486598084, 0.11511532716272527, 0.12624775579013078, 0.1373801844175363, 0.14442001578991126, 0.15145984716228622, 0.15849967853466118, 0.16553950990703614, 0.1725793412794111, 0.17961917265178606, 0.18996067750839385, 0.20030218236500164, 0.21064368722160942, 0.2209851920782172, 0.231326696934825, 0.24489596094095048, 0.25846522494707597, 0.2720344889532015, 0.285603752959327, 0.2991730169654525, 0.3144465867154453, 0.32972015646543806, 0.34499372621543084, 0.3602672959654236, 0.3755408657154164, 0.39081443546540917, 0.4096510819884752, 0.42848772851154127, 0.4473243750346073, 0.46616102155767336, 0.4849976680807394, 0.5038343146038055, 0.5321635737574697, 0.5604928329111339, 0.5888220920647982, 0.6171513512184624, 0.6454806103721267, 0.678559906689157, 0.7116392030061873, 0.7447184993232177, 0.777797795640248, 0.8108770919572783, 0.8534396069457652, 0.896002121934252, 0.9385646369227388, 0.9811271519112257, 1.0236896668997124, 1.0662521818881991, 1.1151384346357618, 1.1640246873833244, 1.212910940130887, 1.2617971928784497, 1.3106834456260124, 1.359569698373575, 1.4421248860020461, 1.5246800736305173, 1.6072352612589884, 1.6897904488874596, 1.7723456365159307, 1.8549008241444018, 1.9481635802253086, 2.0414263363062153, 2.134689092387122, 2.2279518484680283, 2.321214604548935, 2.4144773606298413, 2.5404837290865787, 2.666490097543316, 2.7924964660000535, 2.918502834456791, 3.0445092029135283, 3.1705155713702657, 3.339426131682601, 3.508336691994936, 3.677247252307271, 3.846157812619606, 4.015068372931941, 4.183978933244275, 4.414113939343987, 4.644248945443699, 4.87438395154341, 5.104518957643122, 5.334653963742833, 5.564788969842545, 5.873762562595783, 6.182736155349022, 6.49170974810226, 6.800683340855499, 7.109656933608737, 7.418630526361976, 7.901204637410911, 8.383778748459846, 8.866352859508783, 9.34892697055772, 9.831501081606657, 10.0]</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.1400708294490355</v>
+        <v>0.1400708293964681</v>
       </c>
       <c r="D51" t="n">
         <v>9.81</v>
@@ -3850,13 +3850,13 @@
         <v>2</v>
       </c>
       <c r="L51" t="n">
-        <v>1.400708294490355</v>
+        <v>1.400708293964681</v>
       </c>
       <c r="M51" t="n">
-        <v>0.1019376447030222</v>
+        <v>0.101937644779535</v>
       </c>
       <c r="N51" t="n">
-        <v>0.5096882235151112</v>
+        <v>0.5096882238976749</v>
       </c>
       <c r="O51" t="n">
         <v>9.620000000000001</v>
